--- a/E/MKTN.xlsx
+++ b/E/MKTN.xlsx
@@ -4093,7 +4093,7 @@
     <t>20128139</t>
   </si>
   <si>
-    <t>XL/D XT.CMB6.5GB 37K</t>
+    <t>XL/D XT.CMB 7GB 28HR</t>
   </si>
   <si>
     <t>566</t>
@@ -4102,7 +4102,7 @@
     <t>20128140</t>
   </si>
   <si>
-    <t>XL/D XT.CMB FLX 50K</t>
+    <t>XL/D XT.CMB FLX 13GB</t>
   </si>
   <si>
     <t>567</t>
@@ -4111,7 +4111,7 @@
     <t>20128141</t>
   </si>
   <si>
-    <t>XL/D XT.CMB FLX 70K</t>
+    <t>XL/D XT.CMB FLX 34GB</t>
   </si>
   <si>
     <t>568</t>
@@ -4120,7 +4120,7 @@
     <t>20128142</t>
   </si>
   <si>
-    <t>XL/D XT.CMB FLX 100K</t>
+    <t>XL/D XT.CMB FLX 43GB</t>
   </si>
   <si>
     <t>569</t>

--- a/E/MKTN.xlsx
+++ b/E/MKTN.xlsx
@@ -4093,7 +4093,7 @@
     <t>20128139</t>
   </si>
   <si>
-    <t>XL/D XT.CMB 7GB 28HR</t>
+    <t>XL/D FLEX 7GB 28HR</t>
   </si>
   <si>
     <t>566</t>
@@ -4102,7 +4102,7 @@
     <t>20128140</t>
   </si>
   <si>
-    <t>XL/D XT.CMB FLX 13GB</t>
+    <t>XL/D FLEX 13GB</t>
   </si>
   <si>
     <t>567</t>
@@ -4111,7 +4111,7 @@
     <t>20128141</t>
   </si>
   <si>
-    <t>XL/D XT.CMB FLX 34GB</t>
+    <t>XL/D FLEX 34GB</t>
   </si>
   <si>
     <t>568</t>
@@ -4120,7 +4120,7 @@
     <t>20128142</t>
   </si>
   <si>
-    <t>XL/D XT.CMB FLX 43GB</t>
+    <t>XL/D FLEX 43GB</t>
   </si>
   <si>
     <t>569</t>

--- a/E/MKTN.xlsx
+++ b/E/MKTN.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5101" uniqueCount="2385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5101" uniqueCount="2384">
   <si>
     <t/>
   </si>
@@ -2098,7 +2098,7 @@
     <t>20108811</t>
   </si>
   <si>
-    <t>INDOSAT OBR PUAS10.5</t>
+    <t>INDOSAT INET 9GB 3HR</t>
   </si>
   <si>
     <t>217</t>
@@ -3094,7 +3094,7 @@
     <t>20122474</t>
   </si>
   <si>
-    <t>INDST FRDM HT/P 50GB</t>
+    <t>INDST FRDM 30GB 5HR</t>
   </si>
   <si>
     <t>337</t>
@@ -4144,7 +4144,7 @@
     <t>20128143</t>
   </si>
   <si>
-    <t>XL/D FLEX 52GB</t>
+    <t>XL/D FLEXMAX 52GB</t>
   </si>
   <si>
     <t>569</t>
@@ -4315,7 +4315,7 @@
     <t>20129636</t>
   </si>
   <si>
-    <t>INDST FDM 100GB 125K</t>
+    <t>INDST FDM SATSPAM300</t>
   </si>
   <si>
     <t>590</t>
@@ -4324,6 +4324,9 @@
     <t>20129637</t>
   </si>
   <si>
+    <t>INDST SATSPAM 300GB</t>
+  </si>
+  <si>
     <t>591</t>
   </si>
   <si>
@@ -4399,7 +4402,7 @@
     <t>20130172</t>
   </si>
   <si>
-    <t>INDST FDM 200GB 165K</t>
+    <t>INDST FDM 20GB 3HARI</t>
   </si>
   <si>
     <t>600</t>
@@ -4570,7 +4573,7 @@
     <t>20131136</t>
   </si>
   <si>
-    <t>INDST FRDM 70GB 30HR</t>
+    <t>INDST FRDM 75GB 7HR</t>
   </si>
   <si>
     <t>623</t>
@@ -4579,7 +4582,7 @@
     <t>20131137</t>
   </si>
   <si>
-    <t>INDST FDM 100GB 90HR</t>
+    <t>INDST FDM 150GB 28HR</t>
   </si>
   <si>
     <t>624</t>
@@ -4804,7 +4807,7 @@
     <t>20131452</t>
   </si>
   <si>
-    <t>INDST FRDM 75GB 28HR</t>
+    <t>INDST FRDM 12GB 5HR</t>
   </si>
   <si>
     <t>658</t>
@@ -4822,9 +4825,6 @@
     <t>20131454</t>
   </si>
   <si>
-    <t>INDST FRDM 55GB 28HR</t>
-  </si>
-  <si>
     <t>660</t>
   </si>
   <si>
@@ -4987,7 +4987,7 @@
     <t>20133825</t>
   </si>
   <si>
-    <t>INDST RAMA 20GB 3HR</t>
+    <t>INDST INET 5GB 3HARI</t>
   </si>
   <si>
     <t>680</t>
@@ -4996,7 +4996,7 @@
     <t>20133826</t>
   </si>
   <si>
-    <t>INDST FRDM APPS 12GB</t>
+    <t>INDST FRDM INET 5GB</t>
   </si>
   <si>
     <t>681</t>
@@ -5005,7 +5005,7 @@
     <t>20133827</t>
   </si>
   <si>
-    <t>INDST FRDM PLAY 20GB</t>
+    <t>INDST FRDM 9GB 1HARI</t>
   </si>
   <si>
     <t>682</t>
@@ -5020,7 +5020,7 @@
     <t>20133829</t>
   </si>
   <si>
-    <t>INDST FRDM PLAY 8GB</t>
+    <t>INDST FRDM 6GB 2HR</t>
   </si>
   <si>
     <t>684</t>
@@ -5986,7 +5986,7 @@
     <t>20137277</t>
   </si>
   <si>
-    <t>INDST  FRDM INET12GB</t>
+    <t>INDST  FRDM INET21GB</t>
   </si>
   <si>
     <t>813</t>
@@ -5995,7 +5995,7 @@
     <t>20137276</t>
   </si>
   <si>
-    <t>INDST INET 8GB 33K</t>
+    <t>INDST INET 25GB 14HR</t>
   </si>
   <si>
     <t>814</t>
@@ -6100,7 +6100,7 @@
     <t>20137261</t>
   </si>
   <si>
-    <t>INDST  FRDM INET 8GB</t>
+    <t>INDST  FRDM INET25GB</t>
   </si>
   <si>
     <t>829</t>
@@ -6163,7 +6163,7 @@
     <t>20137893</t>
   </si>
   <si>
-    <t>INDST FR RMDN150GB</t>
+    <t>INDST FRD INET 6GB</t>
   </si>
   <si>
     <t>836</t>
@@ -6217,7 +6217,7 @@
     <t>20137897</t>
   </si>
   <si>
-    <t>INDST FRD 150GB 150K</t>
+    <t>INDST FRD 6GB 5HARI</t>
   </si>
   <si>
     <t>842</t>
@@ -6608,9 +6608,6 @@
   </si>
   <si>
     <t>20137154</t>
-  </si>
-  <si>
-    <t>INDST  FRDM INET11GB</t>
   </si>
   <si>
     <t>891</t>
@@ -17614,7 +17611,7 @@
         <v>1436</v>
       </c>
       <c r="B524" s="1" t="s">
-        <v>1434</v>
+        <v>1437</v>
       </c>
       <c r="C524" s="1" t="s">
         <v>3</v>
@@ -17623,7 +17620,7 @@
         <v>4</v>
       </c>
       <c r="E524" s="1" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="F524" s="1" t="s">
         <v>5</v>
@@ -17631,10 +17628,10 @@
     </row>
     <row r="525" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A525" s="1" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="B525" s="1" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="C525" s="1" t="s">
         <v>3</v>
@@ -17643,7 +17640,7 @@
         <v>4</v>
       </c>
       <c r="E525" s="1" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="F525" s="1" t="s">
         <v>5</v>
@@ -17651,10 +17648,10 @@
     </row>
     <row r="526" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A526" s="1" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="B526" s="1" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="C526" s="1" t="s">
         <v>3</v>
@@ -17663,7 +17660,7 @@
         <v>4</v>
       </c>
       <c r="E526" s="1" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="F526" s="1" t="s">
         <v>5</v>
@@ -17671,10 +17668,10 @@
     </row>
     <row r="527" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A527" s="1" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="B527" s="1" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="C527" s="1" t="s">
         <v>3</v>
@@ -17683,7 +17680,7 @@
         <v>4</v>
       </c>
       <c r="E527" s="1" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="F527" s="1" t="s">
         <v>5</v>
@@ -17691,10 +17688,10 @@
     </row>
     <row r="528" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A528" s="1" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="B528" s="1" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="C528" s="1" t="s">
         <v>3</v>
@@ -17703,7 +17700,7 @@
         <v>4</v>
       </c>
       <c r="E528" s="1" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="F528" s="1" t="s">
         <v>5</v>
@@ -17711,10 +17708,10 @@
     </row>
     <row r="529" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A529" s="1" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="B529" s="1" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="C529" s="1" t="s">
         <v>3</v>
@@ -17723,7 +17720,7 @@
         <v>4</v>
       </c>
       <c r="E529" s="1" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="F529" s="1" t="s">
         <v>5</v>
@@ -17731,10 +17728,10 @@
     </row>
     <row r="530" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A530" s="1" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="B530" s="1" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="C530" s="1" t="s">
         <v>3</v>
@@ -17743,7 +17740,7 @@
         <v>4</v>
       </c>
       <c r="E530" s="1" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="F530" s="1" t="s">
         <v>5</v>
@@ -17751,10 +17748,10 @@
     </row>
     <row r="531" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A531" s="1" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="B531" s="1" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="C531" s="1" t="s">
         <v>3</v>
@@ -17763,7 +17760,7 @@
         <v>4</v>
       </c>
       <c r="E531" s="1" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="F531" s="1" t="s">
         <v>5</v>
@@ -17771,10 +17768,10 @@
     </row>
     <row r="532" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A532" s="1" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="B532" s="1" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="C532" s="1" t="s">
         <v>3</v>
@@ -17783,7 +17780,7 @@
         <v>4</v>
       </c>
       <c r="E532" s="1" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="F532" s="1" t="s">
         <v>5</v>
@@ -17791,10 +17788,10 @@
     </row>
     <row r="533" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A533" s="1" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="B533" s="1" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="C533" s="1" t="s">
         <v>3</v>
@@ -17803,7 +17800,7 @@
         <v>4</v>
       </c>
       <c r="E533" s="1" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="F533" s="1" t="s">
         <v>5</v>
@@ -17811,10 +17808,10 @@
     </row>
     <row r="534" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A534" s="1" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="B534" s="1" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="C534" s="1" t="s">
         <v>3</v>
@@ -17823,7 +17820,7 @@
         <v>4</v>
       </c>
       <c r="E534" s="1" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="F534" s="1" t="s">
         <v>83</v>
@@ -17831,10 +17828,10 @@
     </row>
     <row r="535" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A535" s="1" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="B535" s="1" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="C535" s="1" t="s">
         <v>3</v>
@@ -17843,7 +17840,7 @@
         <v>4</v>
       </c>
       <c r="E535" s="1" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="F535" s="1" t="s">
         <v>5</v>
@@ -17851,10 +17848,10 @@
     </row>
     <row r="536" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A536" s="1" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="B536" s="1" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="C536" s="1" t="s">
         <v>3</v>
@@ -17863,7 +17860,7 @@
         <v>4</v>
       </c>
       <c r="E536" s="1" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="F536" s="1" t="s">
         <v>5</v>
@@ -17871,10 +17868,10 @@
     </row>
     <row r="537" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A537" s="1" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="B537" s="1" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="C537" s="1" t="s">
         <v>3</v>
@@ -17883,7 +17880,7 @@
         <v>4</v>
       </c>
       <c r="E537" s="1" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="F537" s="1" t="s">
         <v>5</v>
@@ -17891,10 +17888,10 @@
     </row>
     <row r="538" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A538" s="1" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="B538" s="1" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="C538" s="1" t="s">
         <v>3</v>
@@ -17903,15 +17900,15 @@
         <v>4</v>
       </c>
       <c r="E538" s="1" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="539" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A539" s="1" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="B539" s="1" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="C539" s="1" t="s">
         <v>3</v>
@@ -17920,15 +17917,15 @@
         <v>4</v>
       </c>
       <c r="E539" s="1" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="540" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A540" s="1" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="B540" s="1" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="C540" s="1" t="s">
         <v>3</v>
@@ -17937,15 +17934,15 @@
         <v>4</v>
       </c>
       <c r="E540" s="1" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="541" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A541" s="1" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="B541" s="1" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="C541" s="1" t="s">
         <v>3</v>
@@ -17954,15 +17951,15 @@
         <v>4</v>
       </c>
       <c r="E541" s="1" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="542" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A542" s="1" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="B542" s="1" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="C542" s="1" t="s">
         <v>3</v>
@@ -17971,15 +17968,15 @@
         <v>4</v>
       </c>
       <c r="E542" s="1" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="543" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A543" s="1" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="B543" s="1" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="C543" s="1" t="s">
         <v>3</v>
@@ -17988,15 +17985,15 @@
         <v>4</v>
       </c>
       <c r="E543" s="1" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="544" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A544" s="1" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="B544" s="1" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="C544" s="1" t="s">
         <v>3</v>
@@ -18005,15 +18002,15 @@
         <v>4</v>
       </c>
       <c r="E544" s="1" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="545" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A545" s="1" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="B545" s="1" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="C545" s="1" t="s">
         <v>3</v>
@@ -18022,15 +18019,15 @@
         <v>4</v>
       </c>
       <c r="E545" s="1" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="546" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A546" s="1" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="B546" s="1" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="C546" s="1" t="s">
         <v>3</v>
@@ -18039,7 +18036,7 @@
         <v>4</v>
       </c>
       <c r="E546" s="1" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="F546" s="1" t="s">
         <v>5</v>
@@ -18047,10 +18044,10 @@
     </row>
     <row r="547" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A547" s="1" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="B547" s="1" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="C547" s="1" t="s">
         <v>3</v>
@@ -18059,15 +18056,15 @@
         <v>4</v>
       </c>
       <c r="E547" s="1" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="548" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A548" s="1" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="B548" s="1" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="C548" s="1" t="s">
         <v>3</v>
@@ -18076,15 +18073,15 @@
         <v>4</v>
       </c>
       <c r="E548" s="1" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="549" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A549" s="1" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="B549" s="1" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="C549" s="1" t="s">
         <v>3</v>
@@ -18093,15 +18090,15 @@
         <v>4</v>
       </c>
       <c r="E549" s="1" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="550" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A550" s="1" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="B550" s="1" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="C550" s="1" t="s">
         <v>3</v>
@@ -18110,7 +18107,7 @@
         <v>4</v>
       </c>
       <c r="E550" s="1" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="F550" s="1" t="s">
         <v>5</v>
@@ -18118,10 +18115,10 @@
     </row>
     <row r="551" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A551" s="1" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="B551" s="1" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="C551" s="1" t="s">
         <v>3</v>
@@ -18130,7 +18127,7 @@
         <v>4</v>
       </c>
       <c r="E551" s="1" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="F551" s="1" t="s">
         <v>5</v>
@@ -18138,10 +18135,10 @@
     </row>
     <row r="552" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A552" s="1" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="B552" s="1" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="C552" s="1" t="s">
         <v>3</v>
@@ -18150,7 +18147,7 @@
         <v>4</v>
       </c>
       <c r="E552" s="1" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="F552" s="1" t="s">
         <v>5</v>
@@ -18158,10 +18155,10 @@
     </row>
     <row r="553" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A553" s="1" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="B553" s="1" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="C553" s="1" t="s">
         <v>3</v>
@@ -18170,7 +18167,7 @@
         <v>4</v>
       </c>
       <c r="E553" s="1" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="F553" s="1" t="s">
         <v>5</v>
@@ -18178,10 +18175,10 @@
     </row>
     <row r="554" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A554" s="1" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="B554" s="1" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="C554" s="1" t="s">
         <v>3</v>
@@ -18190,7 +18187,7 @@
         <v>4</v>
       </c>
       <c r="E554" s="1" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="F554" s="1" t="s">
         <v>5</v>
@@ -18198,10 +18195,10 @@
     </row>
     <row r="555" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A555" s="1" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="B555" s="1" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="C555" s="1" t="s">
         <v>3</v>
@@ -18210,7 +18207,7 @@
         <v>4</v>
       </c>
       <c r="E555" s="1" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="F555" s="1" t="s">
         <v>5</v>
@@ -18218,10 +18215,10 @@
     </row>
     <row r="556" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A556" s="1" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="B556" s="1" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="C556" s="1" t="s">
         <v>3</v>
@@ -18230,7 +18227,7 @@
         <v>4</v>
       </c>
       <c r="E556" s="1" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="F556" s="1" t="s">
         <v>5</v>
@@ -18238,10 +18235,10 @@
     </row>
     <row r="557" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A557" s="1" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="B557" s="1" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="C557" s="1" t="s">
         <v>3</v>
@@ -18250,7 +18247,7 @@
         <v>4</v>
       </c>
       <c r="E557" s="1" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="F557" s="1" t="s">
         <v>5</v>
@@ -18258,10 +18255,10 @@
     </row>
     <row r="558" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A558" s="1" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="B558" s="1" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="C558" s="1" t="s">
         <v>3</v>
@@ -18270,7 +18267,7 @@
         <v>4</v>
       </c>
       <c r="E558" s="1" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="F558" s="1" t="s">
         <v>5</v>
@@ -18278,10 +18275,10 @@
     </row>
     <row r="559" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A559" s="1" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="B559" s="1" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="C559" s="1" t="s">
         <v>3</v>
@@ -18290,7 +18287,7 @@
         <v>4</v>
       </c>
       <c r="E559" s="1" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="F559" s="1" t="s">
         <v>5</v>
@@ -18298,10 +18295,10 @@
     </row>
     <row r="560" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A560" s="1" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="B560" s="1" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="C560" s="1" t="s">
         <v>3</v>
@@ -18310,7 +18307,7 @@
         <v>4</v>
       </c>
       <c r="E560" s="1" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="F560" s="1" t="s">
         <v>5</v>
@@ -18318,10 +18315,10 @@
     </row>
     <row r="561" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A561" s="1" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="B561" s="1" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="C561" s="1" t="s">
         <v>3</v>
@@ -18330,7 +18327,7 @@
         <v>4</v>
       </c>
       <c r="E561" s="1" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="F561" s="1" t="s">
         <v>5</v>
@@ -18338,10 +18335,10 @@
     </row>
     <row r="562" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A562" s="1" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="B562" s="1" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="C562" s="1" t="s">
         <v>3</v>
@@ -18350,7 +18347,7 @@
         <v>4</v>
       </c>
       <c r="E562" s="1" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="F562" s="1" t="s">
         <v>5</v>
@@ -18358,10 +18355,10 @@
     </row>
     <row r="563" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A563" s="1" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="B563" s="1" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="C563" s="1" t="s">
         <v>3</v>
@@ -18370,7 +18367,7 @@
         <v>4</v>
       </c>
       <c r="E563" s="1" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="F563" s="1" t="s">
         <v>5</v>
@@ -18378,10 +18375,10 @@
     </row>
     <row r="564" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A564" s="1" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="B564" s="1" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="C564" s="1" t="s">
         <v>3</v>
@@ -18390,7 +18387,7 @@
         <v>4</v>
       </c>
       <c r="E564" s="1" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="F564" s="1" t="s">
         <v>5</v>
@@ -18398,10 +18395,10 @@
     </row>
     <row r="565" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A565" s="1" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="B565" s="1" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="C565" s="1" t="s">
         <v>3</v>
@@ -18410,7 +18407,7 @@
         <v>4</v>
       </c>
       <c r="E565" s="1" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="F565" s="1" t="s">
         <v>5</v>
@@ -18418,10 +18415,10 @@
     </row>
     <row r="566" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A566" s="1" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="B566" s="1" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="C566" s="1" t="s">
         <v>3</v>
@@ -18430,7 +18427,7 @@
         <v>4</v>
       </c>
       <c r="E566" s="1" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="F566" s="1" t="s">
         <v>83</v>
@@ -18438,10 +18435,10 @@
     </row>
     <row r="567" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A567" s="1" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="B567" s="1" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="C567" s="1" t="s">
         <v>3</v>
@@ -18450,7 +18447,7 @@
         <v>4</v>
       </c>
       <c r="E567" s="1" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="F567" s="1" t="s">
         <v>83</v>
@@ -18458,10 +18455,10 @@
     </row>
     <row r="568" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A568" s="1" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="B568" s="1" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="C568" s="1" t="s">
         <v>3</v>
@@ -18470,7 +18467,7 @@
         <v>4</v>
       </c>
       <c r="E568" s="1" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="F568" s="1" t="s">
         <v>5</v>
@@ -18478,10 +18475,10 @@
     </row>
     <row r="569" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A569" s="1" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="B569" s="1" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="C569" s="1" t="s">
         <v>3</v>
@@ -18490,7 +18487,7 @@
         <v>4</v>
       </c>
       <c r="E569" s="1" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="F569" s="1" t="s">
         <v>5</v>
@@ -18498,10 +18495,10 @@
     </row>
     <row r="570" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A570" s="1" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="B570" s="1" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="C570" s="1" t="s">
         <v>3</v>
@@ -18510,7 +18507,7 @@
         <v>4</v>
       </c>
       <c r="E570" s="1" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="F570" s="1" t="s">
         <v>5</v>
@@ -18518,10 +18515,10 @@
     </row>
     <row r="571" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A571" s="1" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="B571" s="1" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="C571" s="1" t="s">
         <v>3</v>
@@ -18530,7 +18527,7 @@
         <v>4</v>
       </c>
       <c r="E571" s="1" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="F571" s="1" t="s">
         <v>5</v>
@@ -18538,10 +18535,10 @@
     </row>
     <row r="572" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A572" s="1" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="B572" s="1" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="C572" s="1" t="s">
         <v>3</v>
@@ -18550,7 +18547,7 @@
         <v>4</v>
       </c>
       <c r="E572" s="1" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="F572" s="1" t="s">
         <v>5</v>
@@ -18558,10 +18555,10 @@
     </row>
     <row r="573" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A573" s="1" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="B573" s="1" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="C573" s="1" t="s">
         <v>3</v>
@@ -18570,7 +18567,7 @@
         <v>4</v>
       </c>
       <c r="E573" s="1" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="F573" s="1" t="s">
         <v>5</v>
@@ -18578,10 +18575,10 @@
     </row>
     <row r="574" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A574" s="1" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="B574" s="1" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="C574" s="1" t="s">
         <v>3</v>
@@ -18590,7 +18587,7 @@
         <v>4</v>
       </c>
       <c r="E574" s="1" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="F574" s="1" t="s">
         <v>5</v>
@@ -18598,10 +18595,10 @@
     </row>
     <row r="575" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A575" s="1" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="B575" s="1" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="C575" s="1" t="s">
         <v>3</v>
@@ -18610,7 +18607,7 @@
         <v>4</v>
       </c>
       <c r="E575" s="1" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="F575" s="1" t="s">
         <v>5</v>
@@ -18630,7 +18627,7 @@
         <v>4</v>
       </c>
       <c r="E576" s="1" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="F576" s="1" t="s">
         <v>5</v>
@@ -18650,7 +18647,7 @@
         <v>4</v>
       </c>
       <c r="E577" s="1" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="F577" s="1" t="s">
         <v>5</v>
@@ -18670,7 +18667,7 @@
         <v>4</v>
       </c>
       <c r="E578" s="1" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="F578" s="1" t="s">
         <v>5</v>
@@ -18690,7 +18687,7 @@
         <v>4</v>
       </c>
       <c r="E579" s="1" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="F579" s="1" t="s">
         <v>5</v>
@@ -18698,10 +18695,10 @@
     </row>
     <row r="580" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A580" s="1" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="B580" s="1" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="C580" s="1" t="s">
         <v>3</v>
@@ -18710,7 +18707,7 @@
         <v>4</v>
       </c>
       <c r="E580" s="1" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="F580" s="1" t="s">
         <v>83</v>
@@ -18718,10 +18715,10 @@
     </row>
     <row r="581" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A581" s="1" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="B581" s="1" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="C581" s="1" t="s">
         <v>3</v>
@@ -18730,7 +18727,7 @@
         <v>4</v>
       </c>
       <c r="E581" s="1" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="F581" s="1" t="s">
         <v>83</v>
@@ -18738,10 +18735,10 @@
     </row>
     <row r="582" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A582" s="1" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="B582" s="1" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="C582" s="1" t="s">
         <v>3</v>
@@ -18750,7 +18747,7 @@
         <v>4</v>
       </c>
       <c r="E582" s="1" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="F582" s="1" t="s">
         <v>83</v>
@@ -18758,10 +18755,10 @@
     </row>
     <row r="583" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A583" s="1" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="B583" s="1" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="C583" s="1" t="s">
         <v>3</v>
@@ -18770,7 +18767,7 @@
         <v>4</v>
       </c>
       <c r="E583" s="1" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="F583" s="1" t="s">
         <v>83</v>
@@ -18778,10 +18775,10 @@
     </row>
     <row r="584" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A584" s="1" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="B584" s="1" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="C584" s="1" t="s">
         <v>3</v>
@@ -18790,7 +18787,7 @@
         <v>4</v>
       </c>
       <c r="E584" s="1" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="F584" s="1" t="s">
         <v>5</v>
@@ -18798,10 +18795,10 @@
     </row>
     <row r="585" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A585" s="1" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="B585" s="1" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="C585" s="1" t="s">
         <v>3</v>
@@ -18810,7 +18807,7 @@
         <v>4</v>
       </c>
       <c r="E585" s="1" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="F585" s="1" t="s">
         <v>5</v>
@@ -18818,10 +18815,10 @@
     </row>
     <row r="586" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A586" s="1" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="B586" s="1" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="C586" s="1" t="s">
         <v>3</v>
@@ -18830,7 +18827,7 @@
         <v>4</v>
       </c>
       <c r="E586" s="1" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="F586" s="1" t="s">
         <v>5</v>
@@ -18838,10 +18835,10 @@
     </row>
     <row r="587" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A587" s="1" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="B587" s="1" t="s">
-        <v>1603</v>
+        <v>1598</v>
       </c>
       <c r="C587" s="1" t="s">
         <v>3</v>
@@ -22661,7 +22658,7 @@
         <v>2108</v>
       </c>
       <c r="B778" s="1" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="C778" s="1" t="s">
         <v>3</v>
@@ -23315,16 +23312,16 @@
         <v>2198</v>
       </c>
       <c r="B811" s="1" t="s">
+        <v>1991</v>
+      </c>
+      <c r="C811" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D811" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E811" s="1" t="s">
         <v>2199</v>
-      </c>
-      <c r="C811" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D811" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E811" s="1" t="s">
-        <v>2200</v>
       </c>
       <c r="F811" s="1" t="s">
         <v>5</v>
@@ -23332,7 +23329,7 @@
     </row>
     <row r="812" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A812" s="1" t="s">
-        <v>2201</v>
+        <v>2200</v>
       </c>
       <c r="B812" s="1" t="s">
         <v>2047</v>
@@ -23344,7 +23341,7 @@
         <v>4</v>
       </c>
       <c r="E812" s="1" t="s">
-        <v>2202</v>
+        <v>2201</v>
       </c>
       <c r="F812" s="1" t="s">
         <v>5</v>
@@ -23352,19 +23349,19 @@
     </row>
     <row r="813" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A813" s="1" t="s">
+        <v>2202</v>
+      </c>
+      <c r="B813" s="1" t="s">
         <v>2203</v>
       </c>
-      <c r="B813" s="1" t="s">
+      <c r="C813" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D813" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E813" s="1" t="s">
         <v>2204</v>
-      </c>
-      <c r="C813" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D813" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E813" s="1" t="s">
-        <v>2205</v>
       </c>
       <c r="F813" s="1" t="s">
         <v>5</v>
@@ -23372,19 +23369,19 @@
     </row>
     <row r="814" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A814" s="1" t="s">
+        <v>2205</v>
+      </c>
+      <c r="B814" s="1" t="s">
         <v>2206</v>
       </c>
-      <c r="B814" s="1" t="s">
+      <c r="C814" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D814" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E814" s="1" t="s">
         <v>2207</v>
-      </c>
-      <c r="C814" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D814" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E814" s="1" t="s">
-        <v>2208</v>
       </c>
       <c r="F814" s="1" t="s">
         <v>5</v>
@@ -23392,19 +23389,19 @@
     </row>
     <row r="815" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A815" s="1" t="s">
+        <v>2208</v>
+      </c>
+      <c r="B815" s="1" t="s">
         <v>2209</v>
       </c>
-      <c r="B815" s="1" t="s">
+      <c r="C815" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D815" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E815" s="1" t="s">
         <v>2210</v>
-      </c>
-      <c r="C815" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D815" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E815" s="1" t="s">
-        <v>2211</v>
       </c>
       <c r="F815" s="1" t="s">
         <v>5</v>
@@ -23412,19 +23409,19 @@
     </row>
     <row r="816" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A816" s="1" t="s">
+        <v>2211</v>
+      </c>
+      <c r="B816" s="1" t="s">
         <v>2212</v>
       </c>
-      <c r="B816" s="1" t="s">
+      <c r="C816" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D816" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E816" s="1" t="s">
         <v>2213</v>
-      </c>
-      <c r="C816" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D816" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E816" s="1" t="s">
-        <v>2214</v>
       </c>
       <c r="F816" s="1" t="s">
         <v>5</v>
@@ -23432,19 +23429,19 @@
     </row>
     <row r="817" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A817" s="1" t="s">
+        <v>2214</v>
+      </c>
+      <c r="B817" s="1" t="s">
         <v>2215</v>
       </c>
-      <c r="B817" s="1" t="s">
+      <c r="C817" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D817" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E817" s="1" t="s">
         <v>2216</v>
-      </c>
-      <c r="C817" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D817" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E817" s="1" t="s">
-        <v>2217</v>
       </c>
       <c r="F817" s="1" t="s">
         <v>5</v>
@@ -23452,189 +23449,189 @@
     </row>
     <row r="818" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A818" s="1" t="s">
+        <v>2217</v>
+      </c>
+      <c r="B818" s="1" t="s">
         <v>2218</v>
       </c>
-      <c r="B818" s="1" t="s">
+      <c r="C818" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D818" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E818" s="1" t="s">
         <v>2219</v>
-      </c>
-      <c r="C818" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D818" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E818" s="1" t="s">
-        <v>2220</v>
       </c>
     </row>
     <row r="819" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A819" s="1" t="s">
+        <v>2220</v>
+      </c>
+      <c r="B819" s="1" t="s">
         <v>2221</v>
       </c>
-      <c r="B819" s="1" t="s">
+      <c r="C819" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D819" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E819" s="1" t="s">
         <v>2222</v>
-      </c>
-      <c r="C819" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D819" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E819" s="1" t="s">
-        <v>2223</v>
       </c>
     </row>
     <row r="820" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A820" s="1" t="s">
+        <v>2223</v>
+      </c>
+      <c r="B820" s="1" t="s">
         <v>2224</v>
       </c>
-      <c r="B820" s="1" t="s">
+      <c r="C820" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D820" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E820" s="1" t="s">
         <v>2225</v>
-      </c>
-      <c r="C820" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D820" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E820" s="1" t="s">
-        <v>2226</v>
       </c>
     </row>
     <row r="821" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A821" s="1" t="s">
+        <v>2226</v>
+      </c>
+      <c r="B821" s="1" t="s">
         <v>2227</v>
       </c>
-      <c r="B821" s="1" t="s">
+      <c r="C821" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D821" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E821" s="1" t="s">
         <v>2228</v>
-      </c>
-      <c r="C821" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D821" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E821" s="1" t="s">
-        <v>2229</v>
       </c>
     </row>
     <row r="822" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A822" s="1" t="s">
+        <v>2229</v>
+      </c>
+      <c r="B822" s="1" t="s">
+        <v>2218</v>
+      </c>
+      <c r="C822" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D822" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E822" s="1" t="s">
         <v>2230</v>
-      </c>
-      <c r="B822" s="1" t="s">
-        <v>2219</v>
-      </c>
-      <c r="C822" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D822" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E822" s="1" t="s">
-        <v>2231</v>
       </c>
     </row>
     <row r="823" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A823" s="1" t="s">
+        <v>2231</v>
+      </c>
+      <c r="B823" s="1" t="s">
+        <v>2221</v>
+      </c>
+      <c r="C823" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D823" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E823" s="1" t="s">
         <v>2232</v>
-      </c>
-      <c r="B823" s="1" t="s">
-        <v>2222</v>
-      </c>
-      <c r="C823" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D823" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E823" s="1" t="s">
-        <v>2233</v>
       </c>
     </row>
     <row r="824" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A824" s="1" t="s">
+        <v>2233</v>
+      </c>
+      <c r="B824" s="1" t="s">
+        <v>2224</v>
+      </c>
+      <c r="C824" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D824" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E824" s="1" t="s">
         <v>2234</v>
-      </c>
-      <c r="B824" s="1" t="s">
-        <v>2225</v>
-      </c>
-      <c r="C824" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D824" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E824" s="1" t="s">
-        <v>2235</v>
       </c>
     </row>
     <row r="825" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A825" s="1" t="s">
+        <v>2235</v>
+      </c>
+      <c r="B825" s="1" t="s">
+        <v>2227</v>
+      </c>
+      <c r="C825" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D825" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E825" s="1" t="s">
         <v>2236</v>
-      </c>
-      <c r="B825" s="1" t="s">
-        <v>2228</v>
-      </c>
-      <c r="C825" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D825" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E825" s="1" t="s">
-        <v>2237</v>
       </c>
     </row>
     <row r="826" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A826" s="1" t="s">
+        <v>2237</v>
+      </c>
+      <c r="B826" s="1" t="s">
         <v>2238</v>
       </c>
-      <c r="B826" s="1" t="s">
+      <c r="C826" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D826" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E826" s="1" t="s">
         <v>2239</v>
-      </c>
-      <c r="C826" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D826" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E826" s="1" t="s">
-        <v>2240</v>
       </c>
     </row>
     <row r="827" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A827" s="1" t="s">
+        <v>2240</v>
+      </c>
+      <c r="B827" s="1" t="s">
         <v>2241</v>
       </c>
-      <c r="B827" s="1" t="s">
+      <c r="C827" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D827" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E827" s="1" t="s">
         <v>2242</v>
-      </c>
-      <c r="C827" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D827" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E827" s="1" t="s">
-        <v>2243</v>
       </c>
     </row>
     <row r="828" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A828" s="1" t="s">
+        <v>2243</v>
+      </c>
+      <c r="B828" s="1" t="s">
         <v>2244</v>
       </c>
-      <c r="B828" s="1" t="s">
+      <c r="C828" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D828" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E828" s="1" t="s">
         <v>2245</v>
-      </c>
-      <c r="C828" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D828" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E828" s="1" t="s">
-        <v>2246</v>
       </c>
       <c r="F828" s="1" t="s">
         <v>5</v>
@@ -23642,70 +23639,70 @@
     </row>
     <row r="829" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A829" s="1" t="s">
+        <v>2246</v>
+      </c>
+      <c r="B829" s="1" t="s">
+        <v>2238</v>
+      </c>
+      <c r="C829" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D829" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E829" s="1" t="s">
         <v>2247</v>
-      </c>
-      <c r="B829" s="1" t="s">
-        <v>2239</v>
-      </c>
-      <c r="C829" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D829" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E829" s="1" t="s">
-        <v>2248</v>
       </c>
     </row>
     <row r="830" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A830" s="1" t="s">
+        <v>2248</v>
+      </c>
+      <c r="B830" s="1" t="s">
+        <v>2241</v>
+      </c>
+      <c r="C830" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D830" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E830" s="1" t="s">
         <v>2249</v>
-      </c>
-      <c r="B830" s="1" t="s">
-        <v>2242</v>
-      </c>
-      <c r="C830" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D830" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E830" s="1" t="s">
-        <v>2250</v>
       </c>
     </row>
     <row r="831" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A831" s="1" t="s">
+        <v>2250</v>
+      </c>
+      <c r="B831" s="1" t="s">
+        <v>2244</v>
+      </c>
+      <c r="C831" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D831" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E831" s="1" t="s">
         <v>2251</v>
-      </c>
-      <c r="B831" s="1" t="s">
-        <v>2245</v>
-      </c>
-      <c r="C831" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D831" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E831" s="1" t="s">
-        <v>2252</v>
       </c>
     </row>
     <row r="832" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A832" s="1" t="s">
+        <v>2252</v>
+      </c>
+      <c r="B832" s="1" t="s">
         <v>2253</v>
       </c>
-      <c r="B832" s="1" t="s">
+      <c r="C832" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D832" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E832" s="1" t="s">
         <v>2254</v>
-      </c>
-      <c r="C832" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D832" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E832" s="1" t="s">
-        <v>2255</v>
       </c>
       <c r="F832" s="1" t="s">
         <v>5</v>
@@ -23713,19 +23710,19 @@
     </row>
     <row r="833" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A833" s="1" t="s">
+        <v>2255</v>
+      </c>
+      <c r="B833" s="1" t="s">
         <v>2256</v>
       </c>
-      <c r="B833" s="1" t="s">
+      <c r="C833" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D833" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E833" s="1" t="s">
         <v>2257</v>
-      </c>
-      <c r="C833" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D833" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E833" s="1" t="s">
-        <v>2258</v>
       </c>
       <c r="F833" s="1" t="s">
         <v>5</v>
@@ -23733,19 +23730,19 @@
     </row>
     <row r="834" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A834" s="1" t="s">
+        <v>2258</v>
+      </c>
+      <c r="B834" s="1" t="s">
         <v>2259</v>
       </c>
-      <c r="B834" s="1" t="s">
+      <c r="C834" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D834" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E834" s="1" t="s">
         <v>2260</v>
-      </c>
-      <c r="C834" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D834" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E834" s="1" t="s">
-        <v>2261</v>
       </c>
       <c r="F834" s="1" t="s">
         <v>5</v>
@@ -23753,19 +23750,19 @@
     </row>
     <row r="835" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A835" s="1" t="s">
+        <v>2261</v>
+      </c>
+      <c r="B835" s="1" t="s">
         <v>2262</v>
       </c>
-      <c r="B835" s="1" t="s">
+      <c r="C835" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D835" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E835" s="1" t="s">
         <v>2263</v>
-      </c>
-      <c r="C835" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D835" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E835" s="1" t="s">
-        <v>2264</v>
       </c>
       <c r="F835" s="1" t="s">
         <v>5</v>
@@ -23773,19 +23770,19 @@
     </row>
     <row r="836" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A836" s="1" t="s">
+        <v>2264</v>
+      </c>
+      <c r="B836" s="1" t="s">
         <v>2265</v>
       </c>
-      <c r="B836" s="1" t="s">
+      <c r="C836" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D836" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E836" s="1" t="s">
         <v>2266</v>
-      </c>
-      <c r="C836" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D836" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E836" s="1" t="s">
-        <v>2267</v>
       </c>
       <c r="F836" s="1" t="s">
         <v>5</v>
@@ -23793,19 +23790,19 @@
     </row>
     <row r="837" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A837" s="1" t="s">
+        <v>2267</v>
+      </c>
+      <c r="B837" s="1" t="s">
         <v>2268</v>
       </c>
-      <c r="B837" s="1" t="s">
+      <c r="C837" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D837" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E837" s="1" t="s">
         <v>2269</v>
-      </c>
-      <c r="C837" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D837" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E837" s="1" t="s">
-        <v>2270</v>
       </c>
       <c r="F837" s="1" t="s">
         <v>5</v>
@@ -23813,19 +23810,19 @@
     </row>
     <row r="838" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A838" s="1" t="s">
+        <v>2270</v>
+      </c>
+      <c r="B838" s="1" t="s">
         <v>2271</v>
       </c>
-      <c r="B838" s="1" t="s">
+      <c r="C838" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D838" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E838" s="1" t="s">
         <v>2272</v>
-      </c>
-      <c r="C838" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D838" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E838" s="1" t="s">
-        <v>2273</v>
       </c>
       <c r="F838" s="1" t="s">
         <v>5</v>
@@ -23833,19 +23830,19 @@
     </row>
     <row r="839" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A839" s="1" t="s">
+        <v>2273</v>
+      </c>
+      <c r="B839" s="1" t="s">
         <v>2274</v>
       </c>
-      <c r="B839" s="1" t="s">
+      <c r="C839" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D839" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E839" s="1" t="s">
         <v>2275</v>
-      </c>
-      <c r="C839" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D839" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E839" s="1" t="s">
-        <v>2276</v>
       </c>
       <c r="F839" s="1" t="s">
         <v>5</v>
@@ -23853,19 +23850,19 @@
     </row>
     <row r="840" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A840" s="1" t="s">
+        <v>2276</v>
+      </c>
+      <c r="B840" s="1" t="s">
         <v>2277</v>
       </c>
-      <c r="B840" s="1" t="s">
+      <c r="C840" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D840" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E840" s="1" t="s">
         <v>2278</v>
-      </c>
-      <c r="C840" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D840" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E840" s="1" t="s">
-        <v>2279</v>
       </c>
       <c r="F840" s="1" t="s">
         <v>5</v>
@@ -23873,19 +23870,19 @@
     </row>
     <row r="841" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A841" s="1" t="s">
+        <v>2279</v>
+      </c>
+      <c r="B841" s="1" t="s">
         <v>2280</v>
       </c>
-      <c r="B841" s="1" t="s">
+      <c r="C841" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D841" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E841" s="1" t="s">
         <v>2281</v>
-      </c>
-      <c r="C841" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D841" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E841" s="1" t="s">
-        <v>2282</v>
       </c>
       <c r="F841" s="1" t="s">
         <v>5</v>
@@ -23893,19 +23890,19 @@
     </row>
     <row r="842" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A842" s="1" t="s">
+        <v>2282</v>
+      </c>
+      <c r="B842" s="1" t="s">
+        <v>2268</v>
+      </c>
+      <c r="C842" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D842" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E842" s="1" t="s">
         <v>2283</v>
-      </c>
-      <c r="B842" s="1" t="s">
-        <v>2269</v>
-      </c>
-      <c r="C842" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D842" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E842" s="1" t="s">
-        <v>2284</v>
       </c>
       <c r="F842" s="1" t="s">
         <v>5</v>
@@ -23913,19 +23910,19 @@
     </row>
     <row r="843" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A843" s="1" t="s">
+        <v>2284</v>
+      </c>
+      <c r="B843" s="1" t="s">
+        <v>2271</v>
+      </c>
+      <c r="C843" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D843" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E843" s="1" t="s">
         <v>2285</v>
-      </c>
-      <c r="B843" s="1" t="s">
-        <v>2272</v>
-      </c>
-      <c r="C843" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D843" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E843" s="1" t="s">
-        <v>2286</v>
       </c>
       <c r="F843" s="1" t="s">
         <v>5</v>
@@ -23933,19 +23930,19 @@
     </row>
     <row r="844" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A844" s="1" t="s">
+        <v>2286</v>
+      </c>
+      <c r="B844" s="1" t="s">
         <v>2287</v>
       </c>
-      <c r="B844" s="1" t="s">
+      <c r="C844" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D844" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E844" s="1" t="s">
         <v>2288</v>
-      </c>
-      <c r="C844" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D844" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E844" s="1" t="s">
-        <v>2289</v>
       </c>
       <c r="F844" s="1" t="s">
         <v>5</v>
@@ -23953,19 +23950,19 @@
     </row>
     <row r="845" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A845" s="1" t="s">
+        <v>2289</v>
+      </c>
+      <c r="B845" s="1" t="s">
         <v>2290</v>
       </c>
-      <c r="B845" s="1" t="s">
+      <c r="C845" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D845" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E845" s="1" t="s">
         <v>2291</v>
-      </c>
-      <c r="C845" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D845" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E845" s="1" t="s">
-        <v>2292</v>
       </c>
       <c r="F845" s="1" t="s">
         <v>5</v>
@@ -23973,19 +23970,19 @@
     </row>
     <row r="846" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A846" s="1" t="s">
+        <v>2292</v>
+      </c>
+      <c r="B846" s="1" t="s">
+        <v>2280</v>
+      </c>
+      <c r="C846" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D846" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E846" s="1" t="s">
         <v>2293</v>
-      </c>
-      <c r="B846" s="1" t="s">
-        <v>2281</v>
-      </c>
-      <c r="C846" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D846" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E846" s="1" t="s">
-        <v>2294</v>
       </c>
       <c r="F846" s="1" t="s">
         <v>5</v>
@@ -23993,19 +23990,19 @@
     </row>
     <row r="847" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A847" s="1" t="s">
+        <v>2294</v>
+      </c>
+      <c r="B847" s="1" t="s">
         <v>2295</v>
       </c>
-      <c r="B847" s="1" t="s">
+      <c r="C847" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D847" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E847" s="1" t="s">
         <v>2296</v>
-      </c>
-      <c r="C847" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D847" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E847" s="1" t="s">
-        <v>2297</v>
       </c>
       <c r="F847" s="1" t="s">
         <v>5</v>
@@ -24013,19 +24010,19 @@
     </row>
     <row r="848" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A848" s="1" t="s">
+        <v>2297</v>
+      </c>
+      <c r="B848" s="1" t="s">
         <v>2298</v>
       </c>
-      <c r="B848" s="1" t="s">
+      <c r="C848" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D848" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E848" s="1" t="s">
         <v>2299</v>
-      </c>
-      <c r="C848" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D848" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E848" s="1" t="s">
-        <v>2300</v>
       </c>
       <c r="F848" s="1" t="s">
         <v>5</v>
@@ -24033,19 +24030,19 @@
     </row>
     <row r="849" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A849" s="1" t="s">
+        <v>2300</v>
+      </c>
+      <c r="B849" s="1" t="s">
         <v>2301</v>
       </c>
-      <c r="B849" s="1" t="s">
+      <c r="C849" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D849" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E849" s="1" t="s">
         <v>2302</v>
-      </c>
-      <c r="C849" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D849" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E849" s="1" t="s">
-        <v>2303</v>
       </c>
       <c r="F849" s="1" t="s">
         <v>5</v>
@@ -24053,70 +24050,70 @@
     </row>
     <row r="850" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A850" s="1" t="s">
+        <v>2303</v>
+      </c>
+      <c r="B850" s="1" t="s">
         <v>2304</v>
       </c>
-      <c r="B850" s="1" t="s">
+      <c r="C850" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D850" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E850" s="1" t="s">
         <v>2305</v>
-      </c>
-      <c r="C850" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D850" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E850" s="1" t="s">
-        <v>2306</v>
       </c>
     </row>
     <row r="851" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A851" s="1" t="s">
+        <v>2306</v>
+      </c>
+      <c r="B851" s="1" t="s">
         <v>2307</v>
       </c>
-      <c r="B851" s="1" t="s">
+      <c r="C851" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D851" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E851" s="1" t="s">
         <v>2308</v>
-      </c>
-      <c r="C851" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D851" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E851" s="1" t="s">
-        <v>2309</v>
       </c>
     </row>
     <row r="852" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A852" s="1" t="s">
+        <v>2309</v>
+      </c>
+      <c r="B852" s="1" t="s">
         <v>2310</v>
       </c>
-      <c r="B852" s="1" t="s">
+      <c r="C852" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D852" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E852" s="1" t="s">
         <v>2311</v>
-      </c>
-      <c r="C852" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D852" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E852" s="1" t="s">
-        <v>2312</v>
       </c>
     </row>
     <row r="853" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A853" s="1" t="s">
+        <v>2312</v>
+      </c>
+      <c r="B853" s="1" t="s">
         <v>2313</v>
       </c>
-      <c r="B853" s="1" t="s">
+      <c r="C853" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D853" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E853" s="1" t="s">
         <v>2314</v>
-      </c>
-      <c r="C853" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D853" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E853" s="1" t="s">
-        <v>2315</v>
       </c>
       <c r="F853" s="1" t="s">
         <v>5</v>
@@ -24124,19 +24121,19 @@
     </row>
     <row r="854" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A854" s="1" t="s">
+        <v>2315</v>
+      </c>
+      <c r="B854" s="1" t="s">
         <v>2316</v>
       </c>
-      <c r="B854" s="1" t="s">
+      <c r="C854" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D854" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E854" s="1" t="s">
         <v>2317</v>
-      </c>
-      <c r="C854" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D854" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E854" s="1" t="s">
-        <v>2318</v>
       </c>
       <c r="F854" s="1" t="s">
         <v>5</v>
@@ -24144,19 +24141,19 @@
     </row>
     <row r="855" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A855" s="1" t="s">
+        <v>2318</v>
+      </c>
+      <c r="B855" s="1" t="s">
         <v>2319</v>
       </c>
-      <c r="B855" s="1" t="s">
+      <c r="C855" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D855" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E855" s="1" t="s">
         <v>2320</v>
-      </c>
-      <c r="C855" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D855" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E855" s="1" t="s">
-        <v>2321</v>
       </c>
       <c r="F855" s="1" t="s">
         <v>5</v>
@@ -24164,19 +24161,19 @@
     </row>
     <row r="856" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A856" s="1" t="s">
+        <v>2321</v>
+      </c>
+      <c r="B856" s="1" t="s">
         <v>2322</v>
       </c>
-      <c r="B856" s="1" t="s">
+      <c r="C856" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D856" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E856" s="1" t="s">
         <v>2323</v>
-      </c>
-      <c r="C856" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D856" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E856" s="1" t="s">
-        <v>2324</v>
       </c>
       <c r="F856" s="1" t="s">
         <v>5</v>
@@ -24184,19 +24181,19 @@
     </row>
     <row r="857" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A857" s="1" t="s">
+        <v>2324</v>
+      </c>
+      <c r="B857" s="1" t="s">
         <v>2325</v>
       </c>
-      <c r="B857" s="1" t="s">
+      <c r="C857" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D857" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E857" s="1" t="s">
         <v>2326</v>
-      </c>
-      <c r="C857" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D857" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E857" s="1" t="s">
-        <v>2327</v>
       </c>
       <c r="F857" s="1" t="s">
         <v>5</v>
@@ -24204,19 +24201,19 @@
     </row>
     <row r="858" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A858" s="1" t="s">
+        <v>2327</v>
+      </c>
+      <c r="B858" s="1" t="s">
         <v>2328</v>
       </c>
-      <c r="B858" s="1" t="s">
+      <c r="C858" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D858" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E858" s="1" t="s">
         <v>2329</v>
-      </c>
-      <c r="C858" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D858" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E858" s="1" t="s">
-        <v>2330</v>
       </c>
       <c r="F858" s="1" t="s">
         <v>5</v>
@@ -24224,19 +24221,19 @@
     </row>
     <row r="859" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A859" s="1" t="s">
+        <v>2330</v>
+      </c>
+      <c r="B859" s="1" t="s">
         <v>2331</v>
       </c>
-      <c r="B859" s="1" t="s">
+      <c r="C859" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D859" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E859" s="1" t="s">
         <v>2332</v>
-      </c>
-      <c r="C859" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D859" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E859" s="1" t="s">
-        <v>2333</v>
       </c>
       <c r="F859" s="1" t="s">
         <v>5</v>
@@ -24244,19 +24241,19 @@
     </row>
     <row r="860" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A860" s="1" t="s">
+        <v>2333</v>
+      </c>
+      <c r="B860" s="1" t="s">
         <v>2334</v>
       </c>
-      <c r="B860" s="1" t="s">
+      <c r="C860" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D860" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E860" s="1" t="s">
         <v>2335</v>
-      </c>
-      <c r="C860" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D860" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E860" s="1" t="s">
-        <v>2336</v>
       </c>
       <c r="F860" s="1" t="s">
         <v>5</v>
@@ -24264,19 +24261,19 @@
     </row>
     <row r="861" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A861" s="1" t="s">
+        <v>2336</v>
+      </c>
+      <c r="B861" s="1" t="s">
+        <v>2313</v>
+      </c>
+      <c r="C861" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D861" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E861" s="1" t="s">
         <v>2337</v>
-      </c>
-      <c r="B861" s="1" t="s">
-        <v>2314</v>
-      </c>
-      <c r="C861" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D861" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E861" s="1" t="s">
-        <v>2338</v>
       </c>
       <c r="F861" s="1" t="s">
         <v>5</v>
@@ -24284,19 +24281,19 @@
     </row>
     <row r="862" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A862" s="1" t="s">
+        <v>2338</v>
+      </c>
+      <c r="B862" s="1" t="s">
+        <v>2316</v>
+      </c>
+      <c r="C862" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D862" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E862" s="1" t="s">
         <v>2339</v>
-      </c>
-      <c r="B862" s="1" t="s">
-        <v>2317</v>
-      </c>
-      <c r="C862" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D862" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E862" s="1" t="s">
-        <v>2340</v>
       </c>
       <c r="F862" s="1" t="s">
         <v>5</v>
@@ -24304,19 +24301,19 @@
     </row>
     <row r="863" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A863" s="1" t="s">
+        <v>2340</v>
+      </c>
+      <c r="B863" s="1" t="s">
+        <v>2319</v>
+      </c>
+      <c r="C863" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D863" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E863" s="1" t="s">
         <v>2341</v>
-      </c>
-      <c r="B863" s="1" t="s">
-        <v>2320</v>
-      </c>
-      <c r="C863" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D863" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E863" s="1" t="s">
-        <v>2342</v>
       </c>
       <c r="F863" s="1" t="s">
         <v>5</v>
@@ -24324,19 +24321,19 @@
     </row>
     <row r="864" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A864" s="1" t="s">
+        <v>2342</v>
+      </c>
+      <c r="B864" s="1" t="s">
+        <v>2322</v>
+      </c>
+      <c r="C864" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D864" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E864" s="1" t="s">
         <v>2343</v>
-      </c>
-      <c r="B864" s="1" t="s">
-        <v>2323</v>
-      </c>
-      <c r="C864" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D864" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E864" s="1" t="s">
-        <v>2344</v>
       </c>
       <c r="F864" s="1" t="s">
         <v>5</v>
@@ -24344,19 +24341,19 @@
     </row>
     <row r="865" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A865" s="1" t="s">
+        <v>2344</v>
+      </c>
+      <c r="B865" s="1" t="s">
+        <v>2325</v>
+      </c>
+      <c r="C865" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D865" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E865" s="1" t="s">
         <v>2345</v>
-      </c>
-      <c r="B865" s="1" t="s">
-        <v>2326</v>
-      </c>
-      <c r="C865" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D865" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E865" s="1" t="s">
-        <v>2346</v>
       </c>
       <c r="F865" s="1" t="s">
         <v>5</v>
@@ -24364,19 +24361,19 @@
     </row>
     <row r="866" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A866" s="1" t="s">
+        <v>2346</v>
+      </c>
+      <c r="B866" s="1" t="s">
+        <v>2328</v>
+      </c>
+      <c r="C866" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D866" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E866" s="1" t="s">
         <v>2347</v>
-      </c>
-      <c r="B866" s="1" t="s">
-        <v>2329</v>
-      </c>
-      <c r="C866" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D866" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E866" s="1" t="s">
-        <v>2348</v>
       </c>
       <c r="F866" s="1" t="s">
         <v>5</v>
@@ -24384,19 +24381,19 @@
     </row>
     <row r="867" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A867" s="1" t="s">
+        <v>2348</v>
+      </c>
+      <c r="B867" s="1" t="s">
         <v>2349</v>
       </c>
-      <c r="B867" s="1" t="s">
+      <c r="C867" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D867" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E867" s="1" t="s">
         <v>2350</v>
-      </c>
-      <c r="C867" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D867" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E867" s="1" t="s">
-        <v>2351</v>
       </c>
       <c r="F867" s="1" t="s">
         <v>5</v>
@@ -24404,19 +24401,19 @@
     </row>
     <row r="868" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A868" s="1" t="s">
+        <v>2351</v>
+      </c>
+      <c r="B868" s="1" t="s">
+        <v>2334</v>
+      </c>
+      <c r="C868" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D868" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E868" s="1" t="s">
         <v>2352</v>
-      </c>
-      <c r="B868" s="1" t="s">
-        <v>2335</v>
-      </c>
-      <c r="C868" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D868" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E868" s="1" t="s">
-        <v>2353</v>
       </c>
       <c r="F868" s="1" t="s">
         <v>5</v>
@@ -24424,70 +24421,70 @@
     </row>
     <row r="869" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A869" s="1" t="s">
+        <v>2353</v>
+      </c>
+      <c r="B869" s="1" t="s">
         <v>2354</v>
       </c>
-      <c r="B869" s="1" t="s">
+      <c r="C869" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D869" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E869" s="1" t="s">
         <v>2355</v>
-      </c>
-      <c r="C869" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D869" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E869" s="1" t="s">
-        <v>2356</v>
       </c>
     </row>
     <row r="870" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A870" s="1" t="s">
+        <v>2356</v>
+      </c>
+      <c r="B870" s="1" t="s">
         <v>2357</v>
       </c>
-      <c r="B870" s="1" t="s">
+      <c r="C870" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D870" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E870" s="1" t="s">
         <v>2358</v>
-      </c>
-      <c r="C870" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D870" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E870" s="1" t="s">
-        <v>2359</v>
       </c>
     </row>
     <row r="871" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A871" s="1" t="s">
+        <v>2359</v>
+      </c>
+      <c r="B871" s="1" t="s">
         <v>2360</v>
       </c>
-      <c r="B871" s="1" t="s">
+      <c r="C871" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D871" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E871" s="1" t="s">
         <v>2361</v>
-      </c>
-      <c r="C871" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D871" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E871" s="1" t="s">
-        <v>2362</v>
       </c>
     </row>
     <row r="872" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A872" s="1" t="s">
+        <v>2362</v>
+      </c>
+      <c r="B872" s="1" t="s">
         <v>2363</v>
       </c>
-      <c r="B872" s="1" t="s">
+      <c r="C872" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D872" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E872" s="1" t="s">
         <v>2364</v>
-      </c>
-      <c r="C872" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D872" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E872" s="1" t="s">
-        <v>2365</v>
       </c>
     </row>
     <row r="873" spans="1:6" x14ac:dyDescent="0.25">
@@ -24504,7 +24501,7 @@
         <v>4</v>
       </c>
       <c r="E873" s="1" t="s">
-        <v>2366</v>
+        <v>2365</v>
       </c>
       <c r="F873" s="1" t="s">
         <v>5</v>
@@ -24512,19 +24509,19 @@
     </row>
     <row r="874" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A874" s="1" t="s">
+        <v>2366</v>
+      </c>
+      <c r="B874" s="1" t="s">
         <v>2367</v>
       </c>
-      <c r="B874" s="1" t="s">
+      <c r="C874" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D874" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E874" s="1" t="s">
         <v>2368</v>
-      </c>
-      <c r="C874" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D874" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E874" s="1" t="s">
-        <v>2369</v>
       </c>
       <c r="F874" s="1" t="s">
         <v>5</v>
@@ -24532,19 +24529,19 @@
     </row>
     <row r="875" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A875" s="1" t="s">
+        <v>2369</v>
+      </c>
+      <c r="B875" s="1" t="s">
         <v>2370</v>
       </c>
-      <c r="B875" s="1" t="s">
+      <c r="C875" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D875" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E875" s="1" t="s">
         <v>2371</v>
-      </c>
-      <c r="C875" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D875" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E875" s="1" t="s">
-        <v>2372</v>
       </c>
       <c r="F875" s="1" t="s">
         <v>5</v>
@@ -24552,19 +24549,19 @@
     </row>
     <row r="876" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A876" s="1" t="s">
+        <v>2372</v>
+      </c>
+      <c r="B876" s="1" t="s">
         <v>2373</v>
       </c>
-      <c r="B876" s="1" t="s">
+      <c r="C876" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D876" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E876" s="1" t="s">
         <v>2374</v>
-      </c>
-      <c r="C876" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D876" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E876" s="1" t="s">
-        <v>2375</v>
       </c>
       <c r="F876" s="1" t="s">
         <v>5</v>
@@ -24572,19 +24569,19 @@
     </row>
     <row r="877" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A877" s="1" t="s">
+        <v>2375</v>
+      </c>
+      <c r="B877" s="1" t="s">
         <v>2376</v>
       </c>
-      <c r="B877" s="1" t="s">
+      <c r="C877" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D877" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E877" s="1" t="s">
         <v>2377</v>
-      </c>
-      <c r="C877" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D877" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E877" s="1" t="s">
-        <v>2378</v>
       </c>
       <c r="F877" s="1" t="s">
         <v>5</v>
@@ -24592,19 +24589,19 @@
     </row>
     <row r="878" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A878" s="1" t="s">
+        <v>2378</v>
+      </c>
+      <c r="B878" s="1" t="s">
         <v>2379</v>
       </c>
-      <c r="B878" s="1" t="s">
+      <c r="C878" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D878" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E878" s="1" t="s">
         <v>2380</v>
-      </c>
-      <c r="C878" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D878" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E878" s="1" t="s">
-        <v>2381</v>
       </c>
       <c r="F878" s="1" t="s">
         <v>5</v>
@@ -24612,19 +24609,19 @@
     </row>
     <row r="879" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A879" s="1" t="s">
+        <v>2381</v>
+      </c>
+      <c r="B879" s="1" t="s">
         <v>2382</v>
       </c>
-      <c r="B879" s="1" t="s">
+      <c r="C879" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D879" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E879" s="1" t="s">
         <v>2383</v>
-      </c>
-      <c r="C879" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D879" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E879" s="1" t="s">
-        <v>2384</v>
       </c>
       <c r="F879" s="1" t="s">
         <v>5</v>

--- a/E/MKTN.xlsx
+++ b/E/MKTN.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5101" uniqueCount="2384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5089" uniqueCount="2378">
   <si>
     <t/>
   </si>
@@ -1078,15 +1078,6 @@
     <t>101</t>
   </si>
   <si>
-    <t>20092904</t>
-  </si>
-  <si>
-    <t>IDM VCHR NEW.YR FSK</t>
-  </si>
-  <si>
-    <t>102</t>
-  </si>
-  <si>
     <t>20092903</t>
   </si>
   <si>
@@ -1112,15 +1103,6 @@
   </si>
   <si>
     <t>105</t>
-  </si>
-  <si>
-    <t>20092899</t>
-  </si>
-  <si>
-    <t>IDM VCHR HUT-RI FSK</t>
-  </si>
-  <si>
-    <t>106</t>
   </si>
   <si>
     <t>20078414</t>
@@ -7555,7 +7537,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F879"/>
+  <dimension ref="A1:F877"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -10009,7 +9991,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>355</v>
       </c>
@@ -10024,9 +10006,6 @@
       </c>
       <c r="E129" s="1" t="s">
         <v>357</v>
-      </c>
-      <c r="F129" s="1" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
@@ -10063,7 +10042,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>364</v>
       </c>
@@ -10078,6 +10057,9 @@
       </c>
       <c r="E132" s="1" t="s">
         <v>366</v>
+      </c>
+      <c r="F132" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -10277,7 +10259,7 @@
         <v>396</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -10377,7 +10359,7 @@
         <v>411</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>5</v>
+        <v>67</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -10397,7 +10379,7 @@
         <v>414</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -10417,7 +10399,7 @@
         <v>417</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>67</v>
+        <v>5</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -10497,7 +10479,7 @@
         <v>429</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -10537,7 +10519,7 @@
         <v>435</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -10557,7 +10539,7 @@
         <v>438</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -10597,7 +10579,7 @@
         <v>444</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -10717,7 +10699,7 @@
         <v>462</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -10757,7 +10739,7 @@
         <v>468</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -10797,7 +10779,7 @@
         <v>474</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -10837,7 +10819,7 @@
         <v>480</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -10845,16 +10827,16 @@
         <v>481</v>
       </c>
       <c r="B171" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D171" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E171" s="1" t="s">
         <v>482</v>
-      </c>
-      <c r="C171" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D171" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E171" s="1" t="s">
-        <v>483</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>5</v>
@@ -10862,19 +10844,19 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="B172" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="B172" s="1" t="s">
+      <c r="C172" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D172" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E172" s="1" t="s">
         <v>485</v>
-      </c>
-      <c r="C172" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D172" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E172" s="1" t="s">
-        <v>486</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>5</v>
@@ -10882,10 +10864,10 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="B173" s="1" t="s">
         <v>487</v>
-      </c>
-      <c r="B173" s="1" t="s">
-        <v>103</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
@@ -11197,7 +11179,7 @@
         <v>533</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -11237,7 +11219,7 @@
         <v>539</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -11460,7 +11442,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
         <v>573</v>
       </c>
@@ -11475,9 +11457,6 @@
       </c>
       <c r="E202" s="1" t="s">
         <v>575</v>
-      </c>
-      <c r="F202" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
@@ -11500,7 +11479,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
         <v>579</v>
       </c>
@@ -11515,6 +11494,9 @@
       </c>
       <c r="E204" s="1" t="s">
         <v>581</v>
+      </c>
+      <c r="F204" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -11562,16 +11544,16 @@
         <v>588</v>
       </c>
       <c r="B207" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D207" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E207" s="1" t="s">
         <v>589</v>
-      </c>
-      <c r="C207" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D207" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E207" s="1" t="s">
-        <v>590</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>5</v>
@@ -11579,30 +11561,30 @@
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="B208" s="1" t="s">
         <v>591</v>
       </c>
-      <c r="B208" s="1" t="s">
+      <c r="C208" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D208" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E208" s="1" t="s">
         <v>592</v>
       </c>
-      <c r="C208" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D208" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E208" s="1" t="s">
+      <c r="F208" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A209" s="1" t="s">
         <v>593</v>
       </c>
-      <c r="F208" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A209" s="1" t="s">
+      <c r="B209" s="1" t="s">
         <v>594</v>
-      </c>
-      <c r="B209" s="1" t="s">
-        <v>535</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>3</v>
@@ -11612,9 +11594,6 @@
       </c>
       <c r="E209" s="1" t="s">
         <v>595</v>
-      </c>
-      <c r="F209" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
@@ -11654,7 +11633,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
         <v>602</v>
       </c>
@@ -11669,9 +11648,6 @@
       </c>
       <c r="E212" s="1" t="s">
         <v>604</v>
-      </c>
-      <c r="F212" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
@@ -11708,7 +11684,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
         <v>611</v>
       </c>
@@ -11724,8 +11700,11 @@
       <c r="E215" s="1" t="s">
         <v>613</v>
       </c>
-    </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F215" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
         <v>614</v>
       </c>
@@ -11741,8 +11720,11 @@
       <c r="E216" s="1" t="s">
         <v>616</v>
       </c>
-    </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F216" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
         <v>617</v>
       </c>
@@ -11757,9 +11739,6 @@
       </c>
       <c r="E217" s="1" t="s">
         <v>619</v>
-      </c>
-      <c r="F217" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
@@ -11782,38 +11761,41 @@
         <v>5</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
         <v>623</v>
       </c>
       <c r="B219" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="C219" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D219" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E219" s="1" t="s">
         <v>624</v>
       </c>
-      <c r="C219" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D219" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E219" s="1" t="s">
-        <v>625</v>
+      <c r="F219" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="B220" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="C220" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D220" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E220" s="1" t="s">
         <v>626</v>
-      </c>
-      <c r="B220" s="1" t="s">
-        <v>627</v>
-      </c>
-      <c r="C220" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D220" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E220" s="1" t="s">
-        <v>628</v>
       </c>
       <c r="F220" s="1" t="s">
         <v>5</v>
@@ -11821,10 +11803,10 @@
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>407</v>
+        <v>437</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>3</v>
@@ -11833,7 +11815,7 @@
         <v>4</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="F221" s="1" t="s">
         <v>5</v>
@@ -11841,19 +11823,19 @@
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="B222" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="C222" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D222" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E222" s="1" t="s">
         <v>631</v>
-      </c>
-      <c r="B222" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="C222" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D222" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E222" s="1" t="s">
-        <v>632</v>
       </c>
       <c r="F222" s="1" t="s">
         <v>5</v>
@@ -11861,10 +11843,10 @@
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="B223" s="1" t="s">
         <v>633</v>
-      </c>
-      <c r="B223" s="1" t="s">
-        <v>443</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>3</v>
@@ -12104,16 +12086,16 @@
         <v>668</v>
       </c>
       <c r="B235" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C235" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D235" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E235" s="1" t="s">
         <v>669</v>
-      </c>
-      <c r="C235" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D235" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E235" s="1" t="s">
-        <v>670</v>
       </c>
       <c r="F235" s="1" t="s">
         <v>5</v>
@@ -12121,19 +12103,19 @@
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="B236" s="1" t="s">
         <v>671</v>
       </c>
-      <c r="B236" s="1" t="s">
+      <c r="C236" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D236" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E236" s="1" t="s">
         <v>672</v>
-      </c>
-      <c r="C236" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D236" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E236" s="1" t="s">
-        <v>673</v>
       </c>
       <c r="F236" s="1" t="s">
         <v>5</v>
@@ -12141,10 +12123,10 @@
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="B237" s="1" t="s">
         <v>674</v>
-      </c>
-      <c r="B237" s="1" t="s">
-        <v>79</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>3</v>
@@ -12316,15 +12298,15 @@
         <v>699</v>
       </c>
       <c r="F245" s="1" t="s">
-        <v>5</v>
+        <v>700</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>3</v>
@@ -12333,7 +12315,7 @@
         <v>4</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="F246" s="1" t="s">
         <v>5</v>
@@ -12341,10 +12323,10 @@
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>3</v>
@@ -12353,10 +12335,10 @@
         <v>4</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>706</v>
+        <v>5</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
@@ -12804,16 +12786,16 @@
         <v>773</v>
       </c>
       <c r="B270" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="C270" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D270" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E270" s="1" t="s">
         <v>774</v>
-      </c>
-      <c r="C270" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D270" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E270" s="1" t="s">
-        <v>775</v>
       </c>
       <c r="F270" s="1" t="s">
         <v>5</v>
@@ -12821,19 +12803,19 @@
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
+        <v>775</v>
+      </c>
+      <c r="B271" s="1" t="s">
         <v>776</v>
       </c>
-      <c r="B271" s="1" t="s">
+      <c r="C271" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D271" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E271" s="1" t="s">
         <v>777</v>
-      </c>
-      <c r="C271" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D271" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E271" s="1" t="s">
-        <v>778</v>
       </c>
       <c r="F271" s="1" t="s">
         <v>5</v>
@@ -12841,10 +12823,10 @@
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
+        <v>778</v>
+      </c>
+      <c r="B272" s="1" t="s">
         <v>779</v>
-      </c>
-      <c r="B272" s="1" t="s">
-        <v>589</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>3</v>
@@ -12861,19 +12843,19 @@
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B273" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C273" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D273" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E273" s="1" t="s">
         <v>781</v>
-      </c>
-      <c r="B273" s="1" t="s">
-        <v>782</v>
-      </c>
-      <c r="C273" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D273" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E273" s="1" t="s">
-        <v>783</v>
       </c>
       <c r="F273" s="1" t="s">
         <v>5</v>
@@ -12881,10 +12863,10 @@
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
-        <v>784</v>
+        <v>35</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>785</v>
+        <v>36</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>3</v>
@@ -12893,7 +12875,7 @@
         <v>4</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="F274" s="1" t="s">
         <v>5</v>
@@ -12901,10 +12883,10 @@
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>3</v>
@@ -12913,38 +12895,35 @@
         <v>4</v>
       </c>
       <c r="E275" s="1" t="s">
+        <v>783</v>
+      </c>
+      <c r="F275" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A276" s="1" t="s">
+        <v>784</v>
+      </c>
+      <c r="B276" s="1" t="s">
+        <v>785</v>
+      </c>
+      <c r="C276" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D276" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E276" s="1" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A277" s="1" t="s">
         <v>787</v>
       </c>
-      <c r="F275" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A276" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B276" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C276" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D276" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E276" s="1" t="s">
+      <c r="B277" s="1" t="s">
         <v>788</v>
-      </c>
-      <c r="F276" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A277" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B277" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>3</v>
@@ -12954,9 +12933,6 @@
       </c>
       <c r="E277" s="1" t="s">
         <v>789</v>
-      </c>
-      <c r="F277" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.25">
@@ -12976,7 +12952,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
         <v>793</v>
       </c>
@@ -12992,30 +12968,36 @@
       <c r="E279" s="1" t="s">
         <v>795</v>
       </c>
-    </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F279" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B280" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C280" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D280" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E280" s="1" t="s">
         <v>796</v>
       </c>
-      <c r="B280" s="1" t="s">
-        <v>797</v>
-      </c>
-      <c r="C280" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D280" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E280" s="1" t="s">
-        <v>798</v>
+      <c r="F280" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
-        <v>799</v>
+        <v>26</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>800</v>
+        <v>27</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>3</v>
@@ -13024,7 +13006,7 @@
         <v>4</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="F281" s="1" t="s">
         <v>5</v>
@@ -13032,10 +13014,10 @@
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
-        <v>24</v>
+        <v>798</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>25</v>
+        <v>799</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>3</v>
@@ -13044,7 +13026,7 @@
         <v>4</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="F282" s="1" t="s">
         <v>5</v>
@@ -13052,10 +13034,10 @@
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
-        <v>26</v>
+        <v>801</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>27</v>
+        <v>802</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>3</v>
@@ -13090,7 +13072,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
         <v>807</v>
       </c>
@@ -13106,11 +13088,8 @@
       <c r="E285" s="1" t="s">
         <v>809</v>
       </c>
-      <c r="F285" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="286" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
         <v>810</v>
       </c>
@@ -13125,9 +13104,6 @@
       </c>
       <c r="E286" s="1" t="s">
         <v>812</v>
-      </c>
-      <c r="F286" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.25">
@@ -13254,41 +13230,41 @@
         <v>834</v>
       </c>
       <c r="B294" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="C294" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D294" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E294" s="1" t="s">
         <v>835</v>
-      </c>
-      <c r="C294" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D294" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E294" s="1" t="s">
-        <v>836</v>
       </c>
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
+        <v>836</v>
+      </c>
+      <c r="B295" s="1" t="s">
         <v>837</v>
       </c>
-      <c r="B295" s="1" t="s">
+      <c r="C295" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D295" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E295" s="1" t="s">
         <v>838</v>
-      </c>
-      <c r="C295" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D295" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E295" s="1" t="s">
-        <v>839</v>
       </c>
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
+        <v>839</v>
+      </c>
+      <c r="B296" s="1" t="s">
         <v>840</v>
-      </c>
-      <c r="B296" s="1" t="s">
-        <v>829</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>3</v>
@@ -13509,41 +13485,41 @@
         <v>878</v>
       </c>
       <c r="B309" s="1" t="s">
+        <v>837</v>
+      </c>
+      <c r="C309" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D309" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E309" s="1" t="s">
         <v>879</v>
-      </c>
-      <c r="C309" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D309" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E309" s="1" t="s">
-        <v>880</v>
       </c>
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="s">
+        <v>880</v>
+      </c>
+      <c r="B310" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="C310" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D310" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E310" s="1" t="s">
         <v>881</v>
-      </c>
-      <c r="B310" s="1" t="s">
-        <v>882</v>
-      </c>
-      <c r="C310" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D310" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E310" s="1" t="s">
-        <v>883</v>
       </c>
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>843</v>
+        <v>837</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>3</v>
@@ -13552,15 +13528,15 @@
         <v>4</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>829</v>
+        <v>840</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>3</v>
@@ -13569,32 +13545,32 @@
         <v>4</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="B313" s="1" t="s">
+        <v>887</v>
+      </c>
+      <c r="C313" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D313" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E313" s="1" t="s">
         <v>888</v>
-      </c>
-      <c r="B313" s="1" t="s">
-        <v>843</v>
-      </c>
-      <c r="C313" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D313" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E313" s="1" t="s">
-        <v>889</v>
       </c>
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="s">
+        <v>889</v>
+      </c>
+      <c r="B314" s="1" t="s">
         <v>890</v>
-      </c>
-      <c r="B314" s="1" t="s">
-        <v>846</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>3</v>
@@ -13611,41 +13587,41 @@
         <v>892</v>
       </c>
       <c r="B315" s="1" t="s">
+        <v>855</v>
+      </c>
+      <c r="C315" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D315" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E315" s="1" t="s">
         <v>893</v>
-      </c>
-      <c r="C315" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D315" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E315" s="1" t="s">
-        <v>894</v>
       </c>
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
+        <v>894</v>
+      </c>
+      <c r="B316" s="1" t="s">
+        <v>858</v>
+      </c>
+      <c r="C316" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D316" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E316" s="1" t="s">
         <v>895</v>
-      </c>
-      <c r="B316" s="1" t="s">
-        <v>896</v>
-      </c>
-      <c r="C316" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D316" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E316" s="1" t="s">
-        <v>897</v>
       </c>
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>861</v>
+        <v>823</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>3</v>
@@ -13654,83 +13630,83 @@
         <v>4</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
+        <v>898</v>
+      </c>
+      <c r="B318" s="1" t="s">
+        <v>899</v>
+      </c>
+      <c r="C318" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D318" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E318" s="1" t="s">
         <v>900</v>
-      </c>
-      <c r="B318" s="1" t="s">
-        <v>864</v>
-      </c>
-      <c r="C318" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D318" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E318" s="1" t="s">
-        <v>901</v>
       </c>
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
+        <v>901</v>
+      </c>
+      <c r="B319" s="1" t="s">
+        <v>837</v>
+      </c>
+      <c r="C319" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D319" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E319" s="1" t="s">
         <v>902</v>
-      </c>
-      <c r="B319" s="1" t="s">
-        <v>829</v>
-      </c>
-      <c r="C319" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D319" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E319" s="1" t="s">
-        <v>903</v>
       </c>
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
+        <v>903</v>
+      </c>
+      <c r="B320" s="1" t="s">
+        <v>840</v>
+      </c>
+      <c r="C320" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D320" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E320" s="1" t="s">
         <v>904</v>
-      </c>
-      <c r="B320" s="1" t="s">
-        <v>905</v>
-      </c>
-      <c r="C320" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D320" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E320" s="1" t="s">
-        <v>906</v>
       </c>
     </row>
     <row r="321" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
+        <v>905</v>
+      </c>
+      <c r="B321" s="1" t="s">
+        <v>906</v>
+      </c>
+      <c r="C321" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D321" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E321" s="1" t="s">
         <v>907</v>
-      </c>
-      <c r="B321" s="1" t="s">
-        <v>843</v>
-      </c>
-      <c r="C321" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D321" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E321" s="1" t="s">
-        <v>908</v>
       </c>
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="B322" s="1" t="s">
         <v>909</v>
-      </c>
-      <c r="B322" s="1" t="s">
-        <v>846</v>
       </c>
       <c r="C322" s="1" t="s">
         <v>3</v>
@@ -14274,41 +14250,41 @@
         <v>1004</v>
       </c>
       <c r="B354" s="1" t="s">
+        <v>837</v>
+      </c>
+      <c r="C354" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D354" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E354" s="1" t="s">
         <v>1005</v>
-      </c>
-      <c r="C354" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D354" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E354" s="1" t="s">
-        <v>1006</v>
       </c>
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B355" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="B355" s="1" t="s">
+      <c r="C355" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D355" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E355" s="1" t="s">
         <v>1008</v>
-      </c>
-      <c r="C355" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D355" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E355" s="1" t="s">
-        <v>1009</v>
       </c>
     </row>
     <row r="356" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A356" s="1" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B356" s="1" t="s">
         <v>1010</v>
-      </c>
-      <c r="B356" s="1" t="s">
-        <v>843</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>3</v>
@@ -14359,41 +14335,44 @@
         <v>1018</v>
       </c>
       <c r="B359" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="C359" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D359" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E359" s="1" t="s">
         <v>1019</v>
       </c>
-      <c r="C359" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D359" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E359" s="1" t="s">
+    </row>
+    <row r="360" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A360" s="1" t="s">
         <v>1020</v>
       </c>
-    </row>
-    <row r="360" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A360" s="1" t="s">
+      <c r="B360" s="1" t="s">
         <v>1021</v>
       </c>
-      <c r="B360" s="1" t="s">
+      <c r="C360" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D360" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E360" s="1" t="s">
         <v>1022</v>
       </c>
-      <c r="C360" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D360" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E360" s="1" t="s">
+      <c r="F360" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="361" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A361" s="1" t="s">
         <v>1023</v>
       </c>
-    </row>
-    <row r="361" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A361" s="1" t="s">
+      <c r="B361" s="1" t="s">
         <v>1024</v>
-      </c>
-      <c r="B361" s="1" t="s">
-        <v>829</v>
       </c>
       <c r="C361" s="1" t="s">
         <v>3</v>
@@ -14403,6 +14382,9 @@
       </c>
       <c r="E361" s="1" t="s">
         <v>1025</v>
+      </c>
+      <c r="F361" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.25">
@@ -14425,7 +14407,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="363" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A363" s="1" t="s">
         <v>1029</v>
       </c>
@@ -14440,9 +14422,6 @@
       </c>
       <c r="E363" s="1" t="s">
         <v>1031</v>
-      </c>
-      <c r="F363" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.25">
@@ -14465,7 +14444,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="365" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A365" s="1" t="s">
         <v>1035</v>
       </c>
@@ -14480,6 +14459,9 @@
       </c>
       <c r="E365" s="1" t="s">
         <v>1037</v>
+      </c>
+      <c r="F365" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.25">
@@ -14487,47 +14469,47 @@
         <v>1038</v>
       </c>
       <c r="B366" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="C366" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D366" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E366" s="1" t="s">
         <v>1039</v>
       </c>
-      <c r="C366" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D366" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E366" s="1" t="s">
-        <v>1040</v>
-      </c>
       <c r="F366" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A367" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B367" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="C367" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D367" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E367" s="1" t="s">
         <v>1041</v>
       </c>
-      <c r="B367" s="1" t="s">
-        <v>1042</v>
-      </c>
-      <c r="C367" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D367" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E367" s="1" t="s">
-        <v>1043</v>
-      </c>
       <c r="F367" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A368" s="1" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="B368" s="1" t="s">
-        <v>419</v>
+        <v>281</v>
       </c>
       <c r="C368" s="1" t="s">
         <v>3</v>
@@ -14536,7 +14518,7 @@
         <v>4</v>
       </c>
       <c r="E368" s="1" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="F368" s="1" t="s">
         <v>83</v>
@@ -14544,10 +14526,10 @@
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A369" s="1" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="B369" s="1" t="s">
-        <v>284</v>
+        <v>347</v>
       </c>
       <c r="C369" s="1" t="s">
         <v>3</v>
@@ -14556,7 +14538,7 @@
         <v>4</v>
       </c>
       <c r="E369" s="1" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="F369" s="1" t="s">
         <v>83</v>
@@ -14564,10 +14546,10 @@
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A370" s="1" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>281</v>
+        <v>347</v>
       </c>
       <c r="C370" s="1" t="s">
         <v>3</v>
@@ -14576,7 +14558,7 @@
         <v>4</v>
       </c>
       <c r="E370" s="1" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="F370" s="1" t="s">
         <v>83</v>
@@ -14584,10 +14566,10 @@
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A371" s="1" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="B371" s="1" t="s">
-        <v>347</v>
+        <v>212</v>
       </c>
       <c r="C371" s="1" t="s">
         <v>3</v>
@@ -14596,7 +14578,7 @@
         <v>4</v>
       </c>
       <c r="E371" s="1" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="F371" s="1" t="s">
         <v>83</v>
@@ -14604,10 +14586,10 @@
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A372" s="1" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="B372" s="1" t="s">
-        <v>347</v>
+        <v>200</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>3</v>
@@ -14616,7 +14598,7 @@
         <v>4</v>
       </c>
       <c r="E372" s="1" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="F372" s="1" t="s">
         <v>83</v>
@@ -14624,10 +14606,10 @@
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A373" s="1" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="B373" s="1" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>3</v>
@@ -14636,7 +14618,7 @@
         <v>4</v>
       </c>
       <c r="E373" s="1" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="F373" s="1" t="s">
         <v>83</v>
@@ -14644,10 +14626,10 @@
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A374" s="1" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="B374" s="1" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>3</v>
@@ -14656,7 +14638,7 @@
         <v>4</v>
       </c>
       <c r="E374" s="1" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="F374" s="1" t="s">
         <v>83</v>
@@ -14664,10 +14646,10 @@
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A375" s="1" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="B375" s="1" t="s">
-        <v>203</v>
+        <v>320</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>3</v>
@@ -14676,7 +14658,7 @@
         <v>4</v>
       </c>
       <c r="E375" s="1" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="F375" s="1" t="s">
         <v>83</v>
@@ -14684,10 +14666,10 @@
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A376" s="1" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="B376" s="1" t="s">
-        <v>206</v>
+        <v>317</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>3</v>
@@ -14696,7 +14678,7 @@
         <v>4</v>
       </c>
       <c r="E376" s="1" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="F376" s="1" t="s">
         <v>83</v>
@@ -14704,10 +14686,10 @@
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A377" s="1" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="B377" s="1" t="s">
-        <v>320</v>
+        <v>209</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>3</v>
@@ -14716,7 +14698,7 @@
         <v>4</v>
       </c>
       <c r="E377" s="1" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="F377" s="1" t="s">
         <v>83</v>
@@ -14724,19 +14706,19 @@
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A378" s="1" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B378" s="1" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C378" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D378" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E378" s="1" t="s">
         <v>1064</v>
-      </c>
-      <c r="B378" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="C378" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D378" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E378" s="1" t="s">
-        <v>1065</v>
       </c>
       <c r="F378" s="1" t="s">
         <v>83</v>
@@ -14744,10 +14726,10 @@
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A379" s="1" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B379" s="1" t="s">
         <v>1066</v>
-      </c>
-      <c r="B379" s="1" t="s">
-        <v>209</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>3</v>
@@ -14807,16 +14789,16 @@
         <v>1074</v>
       </c>
       <c r="B382" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C382" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D382" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E382" s="1" t="s">
         <v>1075</v>
-      </c>
-      <c r="C382" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D382" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E382" s="1" t="s">
-        <v>1076</v>
       </c>
       <c r="F382" s="1" t="s">
         <v>83</v>
@@ -14824,19 +14806,19 @@
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A383" s="1" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B383" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C383" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D383" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E383" s="1" t="s">
         <v>1077</v>
-      </c>
-      <c r="B383" s="1" t="s">
-        <v>1078</v>
-      </c>
-      <c r="C383" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D383" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E383" s="1" t="s">
-        <v>1079</v>
       </c>
       <c r="F383" s="1" t="s">
         <v>83</v>
@@ -14844,19 +14826,19 @@
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A384" s="1" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B384" s="1" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C384" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D384" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E384" s="1" t="s">
         <v>1080</v>
-      </c>
-      <c r="B384" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="C384" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D384" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E384" s="1" t="s">
-        <v>1081</v>
       </c>
       <c r="F384" s="1" t="s">
         <v>83</v>
@@ -14864,19 +14846,19 @@
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A385" s="1" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B385" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C385" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D385" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E385" s="1" t="s">
         <v>1082</v>
-      </c>
-      <c r="B385" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="C385" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D385" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E385" s="1" t="s">
-        <v>1083</v>
       </c>
       <c r="F385" s="1" t="s">
         <v>83</v>
@@ -14884,19 +14866,19 @@
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A386" s="1" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B386" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C386" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D386" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E386" s="1" t="s">
         <v>1084</v>
-      </c>
-      <c r="B386" s="1" t="s">
-        <v>1085</v>
-      </c>
-      <c r="C386" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D386" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E386" s="1" t="s">
-        <v>1086</v>
       </c>
       <c r="F386" s="1" t="s">
         <v>83</v>
@@ -14904,19 +14886,19 @@
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A387" s="1" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B387" s="1" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C387" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D387" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E387" s="1" t="s">
         <v>1087</v>
-      </c>
-      <c r="B387" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="C387" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D387" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E387" s="1" t="s">
-        <v>1088</v>
       </c>
       <c r="F387" s="1" t="s">
         <v>83</v>
@@ -14924,19 +14906,19 @@
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A388" s="1" t="s">
+        <v>1088</v>
+      </c>
+      <c r="B388" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="C388" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D388" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E388" s="1" t="s">
         <v>1089</v>
-      </c>
-      <c r="B388" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="C388" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D388" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E388" s="1" t="s">
-        <v>1090</v>
       </c>
       <c r="F388" s="1" t="s">
         <v>83</v>
@@ -14944,30 +14926,30 @@
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A389" s="1" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B389" s="1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C389" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D389" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E389" s="1" t="s">
         <v>1091</v>
       </c>
-      <c r="B389" s="1" t="s">
-        <v>1092</v>
-      </c>
-      <c r="C389" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D389" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E389" s="1" t="s">
-        <v>1093</v>
-      </c>
       <c r="F389" s="1" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A390" s="1" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="B390" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="C390" s="1" t="s">
         <v>3</v>
@@ -14976,7 +14958,7 @@
         <v>4</v>
       </c>
       <c r="E390" s="1" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="F390" s="1" t="s">
         <v>83</v>
@@ -14984,10 +14966,10 @@
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A391" s="1" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="B391" s="1" t="s">
-        <v>1027</v>
+        <v>338</v>
       </c>
       <c r="C391" s="1" t="s">
         <v>3</v>
@@ -14996,18 +14978,18 @@
         <v>4</v>
       </c>
       <c r="E391" s="1" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="F391" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A392" s="1" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="B392" s="1" t="s">
-        <v>698</v>
+        <v>106</v>
       </c>
       <c r="C392" s="1" t="s">
         <v>3</v>
@@ -15016,7 +14998,7 @@
         <v>4</v>
       </c>
       <c r="E392" s="1" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="F392" s="1" t="s">
         <v>83</v>
@@ -15024,10 +15006,10 @@
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A393" s="1" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="B393" s="1" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C393" s="1" t="s">
         <v>3</v>
@@ -15036,7 +15018,7 @@
         <v>4</v>
       </c>
       <c r="E393" s="1" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="F393" s="1" t="s">
         <v>83</v>
@@ -15044,10 +15026,10 @@
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A394" s="1" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="B394" s="1" t="s">
-        <v>106</v>
+        <v>341</v>
       </c>
       <c r="C394" s="1" t="s">
         <v>3</v>
@@ -15056,7 +15038,7 @@
         <v>4</v>
       </c>
       <c r="E394" s="1" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="F394" s="1" t="s">
         <v>83</v>
@@ -15064,10 +15046,10 @@
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A395" s="1" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="B395" s="1" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>3</v>
@@ -15076,7 +15058,7 @@
         <v>4</v>
       </c>
       <c r="E395" s="1" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="F395" s="1" t="s">
         <v>83</v>
@@ -15084,10 +15066,10 @@
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A396" s="1" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="B396" s="1" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="C396" s="1" t="s">
         <v>3</v>
@@ -15096,7 +15078,7 @@
         <v>4</v>
       </c>
       <c r="E396" s="1" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="F396" s="1" t="s">
         <v>83</v>
@@ -15104,10 +15086,10 @@
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A397" s="1" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="B397" s="1" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="C397" s="1" t="s">
         <v>3</v>
@@ -15116,7 +15098,7 @@
         <v>4</v>
       </c>
       <c r="E397" s="1" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="F397" s="1" t="s">
         <v>83</v>
@@ -15124,10 +15106,10 @@
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A398" s="1" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="B398" s="1" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C398" s="1" t="s">
         <v>3</v>
@@ -15136,7 +15118,7 @@
         <v>4</v>
       </c>
       <c r="E398" s="1" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="F398" s="1" t="s">
         <v>83</v>
@@ -15144,10 +15126,10 @@
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A399" s="1" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="B399" s="1" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="C399" s="1" t="s">
         <v>3</v>
@@ -15156,7 +15138,7 @@
         <v>4</v>
       </c>
       <c r="E399" s="1" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="F399" s="1" t="s">
         <v>83</v>
@@ -15164,10 +15146,10 @@
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A400" s="1" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="B400" s="1" t="s">
-        <v>323</v>
+        <v>523</v>
       </c>
       <c r="C400" s="1" t="s">
         <v>3</v>
@@ -15176,18 +15158,18 @@
         <v>4</v>
       </c>
       <c r="E400" s="1" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="F400" s="1" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A401" s="1" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="B401" s="1" t="s">
-        <v>326</v>
+        <v>499</v>
       </c>
       <c r="C401" s="1" t="s">
         <v>3</v>
@@ -15196,18 +15178,18 @@
         <v>4</v>
       </c>
       <c r="E401" s="1" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="F401" s="1" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A402" s="1" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="B402" s="1" t="s">
-        <v>529</v>
+        <v>502</v>
       </c>
       <c r="C402" s="1" t="s">
         <v>3</v>
@@ -15216,7 +15198,7 @@
         <v>4</v>
       </c>
       <c r="E402" s="1" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="F402" s="1" t="s">
         <v>5</v>
@@ -15224,10 +15206,10 @@
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A403" s="1" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="B403" s="1" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="C403" s="1" t="s">
         <v>3</v>
@@ -15236,7 +15218,7 @@
         <v>4</v>
       </c>
       <c r="E403" s="1" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="F403" s="1" t="s">
         <v>5</v>
@@ -15244,19 +15226,19 @@
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A404" s="1" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B404" s="1" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C404" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D404" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E404" s="1" t="s">
         <v>1122</v>
-      </c>
-      <c r="B404" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="C404" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D404" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E404" s="1" t="s">
-        <v>1123</v>
       </c>
       <c r="F404" s="1" t="s">
         <v>5</v>
@@ -15264,10 +15246,10 @@
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A405" s="1" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B405" s="1" t="s">
         <v>1124</v>
-      </c>
-      <c r="B405" s="1" t="s">
-        <v>517</v>
       </c>
       <c r="C405" s="1" t="s">
         <v>3</v>
@@ -15307,16 +15289,16 @@
         <v>1129</v>
       </c>
       <c r="B407" s="1" t="s">
+        <v>805</v>
+      </c>
+      <c r="C407" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D407" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E407" s="1" t="s">
         <v>1130</v>
-      </c>
-      <c r="C407" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D407" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E407" s="1" t="s">
-        <v>1131</v>
       </c>
       <c r="F407" s="1" t="s">
         <v>5</v>
@@ -15324,19 +15306,19 @@
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A408" s="1" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B408" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="C408" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D408" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E408" s="1" t="s">
         <v>1132</v>
-      </c>
-      <c r="B408" s="1" t="s">
-        <v>1133</v>
-      </c>
-      <c r="C408" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D408" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E408" s="1" t="s">
-        <v>1134</v>
       </c>
       <c r="F408" s="1" t="s">
         <v>5</v>
@@ -15344,10 +15326,10 @@
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A409" s="1" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="B409" s="1" t="s">
-        <v>811</v>
+        <v>434</v>
       </c>
       <c r="C409" s="1" t="s">
         <v>3</v>
@@ -15356,7 +15338,7 @@
         <v>4</v>
       </c>
       <c r="E409" s="1" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="F409" s="1" t="s">
         <v>5</v>
@@ -15364,10 +15346,10 @@
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A410" s="1" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="B410" s="1" t="s">
-        <v>458</v>
+        <v>479</v>
       </c>
       <c r="C410" s="1" t="s">
         <v>3</v>
@@ -15376,7 +15358,7 @@
         <v>4</v>
       </c>
       <c r="E410" s="1" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
       <c r="F410" s="1" t="s">
         <v>5</v>
@@ -15384,10 +15366,10 @@
     </row>
     <row r="411" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A411" s="1" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="B411" s="1" t="s">
-        <v>440</v>
+        <v>419</v>
       </c>
       <c r="C411" s="1" t="s">
         <v>3</v>
@@ -15396,7 +15378,7 @@
         <v>4</v>
       </c>
       <c r="E411" s="1" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="F411" s="1" t="s">
         <v>5</v>
@@ -15404,10 +15386,10 @@
     </row>
     <row r="412" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A412" s="1" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="B412" s="1" t="s">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="C412" s="1" t="s">
         <v>3</v>
@@ -15416,7 +15398,7 @@
         <v>4</v>
       </c>
       <c r="E412" s="1" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="F412" s="1" t="s">
         <v>5</v>
@@ -15424,10 +15406,10 @@
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A413" s="1" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="B413" s="1" t="s">
-        <v>425</v>
+        <v>458</v>
       </c>
       <c r="C413" s="1" t="s">
         <v>3</v>
@@ -15436,7 +15418,7 @@
         <v>4</v>
       </c>
       <c r="E413" s="1" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="F413" s="1" t="s">
         <v>5</v>
@@ -15444,10 +15426,10 @@
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A414" s="1" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>482</v>
+        <v>404</v>
       </c>
       <c r="C414" s="1" t="s">
         <v>3</v>
@@ -15456,7 +15438,7 @@
         <v>4</v>
       </c>
       <c r="E414" s="1" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="F414" s="1" t="s">
         <v>5</v>
@@ -15464,10 +15446,10 @@
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A415" s="1" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="B415" s="1" t="s">
-        <v>464</v>
+        <v>425</v>
       </c>
       <c r="C415" s="1" t="s">
         <v>3</v>
@@ -15476,7 +15458,7 @@
         <v>4</v>
       </c>
       <c r="E415" s="1" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="F415" s="1" t="s">
         <v>5</v>
@@ -15484,10 +15466,10 @@
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A416" s="1" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>410</v>
+        <v>194</v>
       </c>
       <c r="C416" s="1" t="s">
         <v>3</v>
@@ -15496,7 +15478,7 @@
         <v>4</v>
       </c>
       <c r="E416" s="1" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="F416" s="1" t="s">
         <v>5</v>
@@ -15504,19 +15486,19 @@
     </row>
     <row r="417" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A417" s="1" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B417" s="1" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C417" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D417" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E417" s="1" t="s">
         <v>1151</v>
-      </c>
-      <c r="B417" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="C417" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D417" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E417" s="1" t="s">
-        <v>1152</v>
       </c>
       <c r="F417" s="1" t="s">
         <v>5</v>
@@ -15524,19 +15506,19 @@
     </row>
     <row r="418" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A418" s="1" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B418" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C418" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D418" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E418" s="1" t="s">
         <v>1153</v>
-      </c>
-      <c r="B418" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="C418" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D418" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E418" s="1" t="s">
-        <v>1154</v>
       </c>
       <c r="F418" s="1" t="s">
         <v>5</v>
@@ -15544,19 +15526,19 @@
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A419" s="1" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B419" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="C419" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D419" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E419" s="1" t="s">
         <v>1155</v>
-      </c>
-      <c r="B419" s="1" t="s">
-        <v>1156</v>
-      </c>
-      <c r="C419" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D419" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E419" s="1" t="s">
-        <v>1157</v>
       </c>
       <c r="F419" s="1" t="s">
         <v>5</v>
@@ -15564,10 +15546,10 @@
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A420" s="1" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="B420" s="1" t="s">
-        <v>191</v>
+        <v>374</v>
       </c>
       <c r="C420" s="1" t="s">
         <v>3</v>
@@ -15576,7 +15558,7 @@
         <v>4</v>
       </c>
       <c r="E420" s="1" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="F420" s="1" t="s">
         <v>5</v>
@@ -15584,10 +15566,10 @@
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A421" s="1" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="B421" s="1" t="s">
-        <v>398</v>
+        <v>702</v>
       </c>
       <c r="C421" s="1" t="s">
         <v>3</v>
@@ -15596,7 +15578,7 @@
         <v>4</v>
       </c>
       <c r="E421" s="1" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="F421" s="1" t="s">
         <v>5</v>
@@ -15604,10 +15586,10 @@
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A422" s="1" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
       <c r="B422" s="1" t="s">
-        <v>380</v>
+        <v>705</v>
       </c>
       <c r="C422" s="1" t="s">
         <v>3</v>
@@ -15616,7 +15598,7 @@
         <v>4</v>
       </c>
       <c r="E422" s="1" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="F422" s="1" t="s">
         <v>5</v>
@@ -15624,10 +15606,10 @@
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A423" s="1" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="B423" s="1" t="s">
-        <v>708</v>
+        <v>383</v>
       </c>
       <c r="C423" s="1" t="s">
         <v>3</v>
@@ -15636,7 +15618,7 @@
         <v>4</v>
       </c>
       <c r="E423" s="1" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="F423" s="1" t="s">
         <v>5</v>
@@ -15644,10 +15626,10 @@
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A424" s="1" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
       <c r="B424" s="1" t="s">
-        <v>711</v>
+        <v>389</v>
       </c>
       <c r="C424" s="1" t="s">
         <v>3</v>
@@ -15656,7 +15638,7 @@
         <v>4</v>
       </c>
       <c r="E424" s="1" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="F424" s="1" t="s">
         <v>5</v>
@@ -15664,10 +15646,10 @@
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A425" s="1" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="B425" s="1" t="s">
-        <v>389</v>
+        <v>371</v>
       </c>
       <c r="C425" s="1" t="s">
         <v>3</v>
@@ -15676,7 +15658,7 @@
         <v>4</v>
       </c>
       <c r="E425" s="1" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="F425" s="1" t="s">
         <v>5</v>
@@ -15684,10 +15666,10 @@
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A426" s="1" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="B426" s="1" t="s">
-        <v>395</v>
+        <v>365</v>
       </c>
       <c r="C426" s="1" t="s">
         <v>3</v>
@@ -15696,7 +15678,7 @@
         <v>4</v>
       </c>
       <c r="E426" s="1" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="F426" s="1" t="s">
         <v>5</v>
@@ -15704,10 +15686,10 @@
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A427" s="1" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
       <c r="B427" s="1" t="s">
-        <v>377</v>
+        <v>708</v>
       </c>
       <c r="C427" s="1" t="s">
         <v>3</v>
@@ -15716,7 +15698,7 @@
         <v>4</v>
       </c>
       <c r="E427" s="1" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="F427" s="1" t="s">
         <v>5</v>
@@ -15724,10 +15706,10 @@
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A428" s="1" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
       <c r="B428" s="1" t="s">
-        <v>371</v>
+        <v>711</v>
       </c>
       <c r="C428" s="1" t="s">
         <v>3</v>
@@ -15736,7 +15718,7 @@
         <v>4</v>
       </c>
       <c r="E428" s="1" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="F428" s="1" t="s">
         <v>5</v>
@@ -15744,7 +15726,7 @@
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A429" s="1" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="B429" s="1" t="s">
         <v>714</v>
@@ -15756,38 +15738,35 @@
         <v>4</v>
       </c>
       <c r="E429" s="1" t="s">
+        <v>1175</v>
+      </c>
+      <c r="F429" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="430" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A430" s="1" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B430" s="1" t="s">
         <v>1177</v>
       </c>
-      <c r="F429" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="430" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A430" s="1" t="s">
+      <c r="C430" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D430" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E430" s="1" t="s">
         <v>1178</v>
       </c>
-      <c r="B430" s="1" t="s">
-        <v>717</v>
-      </c>
-      <c r="C430" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D430" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E430" s="1" t="s">
+    </row>
+    <row r="431" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A431" s="1" t="s">
         <v>1179</v>
       </c>
-      <c r="F430" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="431" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A431" s="1" t="s">
+      <c r="B431" s="1" t="s">
         <v>1180</v>
-      </c>
-      <c r="B431" s="1" t="s">
-        <v>720</v>
       </c>
       <c r="C431" s="1" t="s">
         <v>3</v>
@@ -15797,9 +15776,6 @@
       </c>
       <c r="E431" s="1" t="s">
         <v>1181</v>
-      </c>
-      <c r="F431" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="432" spans="1:5" x14ac:dyDescent="0.25">
@@ -15853,7 +15829,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="435" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A435" s="1" t="s">
         <v>1191</v>
       </c>
@@ -15869,8 +15845,11 @@
       <c r="E435" s="1" t="s">
         <v>1193</v>
       </c>
-    </row>
-    <row r="436" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F435" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="436" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A436" s="1" t="s">
         <v>1194</v>
       </c>
@@ -15885,6 +15864,9 @@
       </c>
       <c r="E436" s="1" t="s">
         <v>1196</v>
+      </c>
+      <c r="F436" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.25">
@@ -15907,7 +15889,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="438" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A438" s="1" t="s">
         <v>1200</v>
       </c>
@@ -15923,25 +15905,22 @@
       <c r="E438" s="1" t="s">
         <v>1202</v>
       </c>
-      <c r="F438" s="1" t="s">
-        <v>5</v>
-      </c>
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A439" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B439" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C439" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D439" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E439" s="1" t="s">
         <v>1203</v>
-      </c>
-      <c r="B439" s="1" t="s">
-        <v>1204</v>
-      </c>
-      <c r="C439" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D439" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E439" s="1" t="s">
-        <v>1205</v>
       </c>
       <c r="F439" s="1" t="s">
         <v>5</v>
@@ -15949,27 +15928,27 @@
     </row>
     <row r="440" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A440" s="1" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B440" s="1" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C440" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D440" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E440" s="1" t="s">
         <v>1206</v>
       </c>
-      <c r="B440" s="1" t="s">
+    </row>
+    <row r="441" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A441" s="1" t="s">
         <v>1207</v>
       </c>
-      <c r="C440" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D440" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E440" s="1" t="s">
+      <c r="B441" s="1" t="s">
         <v>1208</v>
-      </c>
-    </row>
-    <row r="441" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A441" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B441" s="1" t="s">
-        <v>2</v>
       </c>
       <c r="C441" s="1" t="s">
         <v>3</v>
@@ -15979,9 +15958,6 @@
       </c>
       <c r="E441" s="1" t="s">
         <v>1209</v>
-      </c>
-      <c r="F441" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="442" spans="1:5" x14ac:dyDescent="0.25">
@@ -16001,46 +15977,52 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="443" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A443" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B443" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C443" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D443" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E443" s="1" t="s">
         <v>1213</v>
       </c>
-      <c r="B443" s="1" t="s">
+      <c r="F443" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="444" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A444" s="1" t="s">
         <v>1214</v>
       </c>
-      <c r="C443" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D443" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E443" s="1" t="s">
+      <c r="B444" s="1" t="s">
         <v>1215</v>
       </c>
-    </row>
-    <row r="444" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A444" s="1" t="s">
+      <c r="C444" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D444" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E444" s="1" t="s">
         <v>1216</v>
       </c>
-      <c r="B444" s="1" t="s">
-        <v>1217</v>
-      </c>
-      <c r="C444" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D444" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E444" s="1" t="s">
-        <v>1218</v>
+      <c r="F444" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A445" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B445" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C445" s="1" t="s">
         <v>3</v>
@@ -16049,7 +16031,7 @@
         <v>4</v>
       </c>
       <c r="E445" s="1" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="F445" s="1" t="s">
         <v>5</v>
@@ -16057,10 +16039,10 @@
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A446" s="1" t="s">
-        <v>1220</v>
+        <v>47</v>
       </c>
       <c r="B446" s="1" t="s">
-        <v>1221</v>
+        <v>48</v>
       </c>
       <c r="C446" s="1" t="s">
         <v>3</v>
@@ -16069,7 +16051,7 @@
         <v>4</v>
       </c>
       <c r="E446" s="1" t="s">
-        <v>1222</v>
+        <v>1218</v>
       </c>
       <c r="F446" s="1" t="s">
         <v>5</v>
@@ -16077,10 +16059,10 @@
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A447" s="1" t="s">
-        <v>45</v>
+        <v>1219</v>
       </c>
       <c r="B447" s="1" t="s">
-        <v>46</v>
+        <v>1220</v>
       </c>
       <c r="C447" s="1" t="s">
         <v>3</v>
@@ -16089,18 +16071,18 @@
         <v>4</v>
       </c>
       <c r="E447" s="1" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="F447" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A448" s="1" t="s">
-        <v>47</v>
+        <v>1222</v>
       </c>
       <c r="B448" s="1" t="s">
-        <v>48</v>
+        <v>1223</v>
       </c>
       <c r="C448" s="1" t="s">
         <v>3</v>
@@ -16112,7 +16094,7 @@
         <v>1224</v>
       </c>
       <c r="F448" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.25">
@@ -16132,7 +16114,7 @@
         <v>1227</v>
       </c>
       <c r="F449" s="1" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="450" spans="1:6" x14ac:dyDescent="0.25">
@@ -16152,7 +16134,7 @@
         <v>1230</v>
       </c>
       <c r="F450" s="1" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="451" spans="1:6" x14ac:dyDescent="0.25">
@@ -16212,7 +16194,7 @@
         <v>1239</v>
       </c>
       <c r="F453" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="454" spans="1:6" x14ac:dyDescent="0.25">
@@ -16232,7 +16214,7 @@
         <v>1242</v>
       </c>
       <c r="F454" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="455" spans="1:6" x14ac:dyDescent="0.25">
@@ -16492,7 +16474,7 @@
         <v>1281</v>
       </c>
       <c r="F467" s="1" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="468" spans="1:6" x14ac:dyDescent="0.25">
@@ -16512,7 +16494,7 @@
         <v>1284</v>
       </c>
       <c r="F468" s="1" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.25">
@@ -16720,47 +16702,44 @@
         <v>1315</v>
       </c>
       <c r="B479" s="1" t="s">
+        <v>1298</v>
+      </c>
+      <c r="C479" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D479" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E479" s="1" t="s">
         <v>1316</v>
       </c>
-      <c r="C479" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D479" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E479" s="1" t="s">
+      <c r="F479" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="480" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A480" s="1" t="s">
         <v>1317</v>
       </c>
-      <c r="F479" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="480" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A480" s="1" t="s">
+      <c r="B480" s="1" t="s">
         <v>1318</v>
       </c>
-      <c r="B480" s="1" t="s">
+      <c r="C480" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D480" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E480" s="1" t="s">
         <v>1319</v>
       </c>
-      <c r="C480" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D480" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E480" s="1" t="s">
+    </row>
+    <row r="481" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A481" s="1" t="s">
         <v>1320</v>
       </c>
-      <c r="F480" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="481" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A481" s="1" t="s">
+      <c r="B481" s="1" t="s">
         <v>1321</v>
-      </c>
-      <c r="B481" s="1" t="s">
-        <v>1304</v>
       </c>
       <c r="C481" s="1" t="s">
         <v>3</v>
@@ -16771,50 +16750,53 @@
       <c r="E481" s="1" t="s">
         <v>1322</v>
       </c>
-      <c r="F481" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="482" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="482" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A482" s="1" t="s">
         <v>1323</v>
       </c>
       <c r="B482" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C482" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D482" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E482" s="1" t="s">
         <v>1324</v>
       </c>
-      <c r="C482" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D482" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E482" s="1" t="s">
+      <c r="F482" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="483" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A483" s="1" t="s">
         <v>1325</v>
       </c>
-    </row>
-    <row r="483" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A483" s="1" t="s">
+      <c r="B483" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C483" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D483" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E483" s="1" t="s">
         <v>1326</v>
       </c>
-      <c r="B483" s="1" t="s">
-        <v>1327</v>
-      </c>
-      <c r="C483" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D483" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E483" s="1" t="s">
-        <v>1328</v>
+      <c r="F483" s="1" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="484" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A484" s="1" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="B484" s="1" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="C484" s="1" t="s">
         <v>3</v>
@@ -16823,7 +16805,7 @@
         <v>4</v>
       </c>
       <c r="E484" s="1" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="F484" s="1" t="s">
         <v>83</v>
@@ -16831,10 +16813,10 @@
     </row>
     <row r="485" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A485" s="1" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="B485" s="1" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="C485" s="1" t="s">
         <v>3</v>
@@ -16843,7 +16825,7 @@
         <v>4</v>
       </c>
       <c r="E485" s="1" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
       <c r="F485" s="1" t="s">
         <v>83</v>
@@ -16851,10 +16833,10 @@
     </row>
     <row r="486" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A486" s="1" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="B486" s="1" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="C486" s="1" t="s">
         <v>3</v>
@@ -16863,7 +16845,7 @@
         <v>4</v>
       </c>
       <c r="E486" s="1" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
       <c r="F486" s="1" t="s">
         <v>83</v>
@@ -16871,10 +16853,10 @@
     </row>
     <row r="487" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A487" s="1" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
       <c r="B487" s="1" t="s">
-        <v>257</v>
+        <v>221</v>
       </c>
       <c r="C487" s="1" t="s">
         <v>3</v>
@@ -16883,38 +16865,35 @@
         <v>4</v>
       </c>
       <c r="E487" s="1" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
       <c r="F487" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="488" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A488" s="1" t="s">
+        <v>1335</v>
+      </c>
+      <c r="B488" s="1" t="s">
+        <v>1336</v>
+      </c>
+      <c r="C488" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D488" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E488" s="1" t="s">
         <v>1337</v>
-      </c>
-      <c r="B488" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="C488" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D488" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E488" s="1" t="s">
-        <v>1338</v>
-      </c>
-      <c r="F488" s="1" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="489" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A489" s="1" t="s">
+        <v>1338</v>
+      </c>
+      <c r="B489" s="1" t="s">
         <v>1339</v>
-      </c>
-      <c r="B489" s="1" t="s">
-        <v>221</v>
       </c>
       <c r="C489" s="1" t="s">
         <v>3</v>
@@ -16926,52 +16905,55 @@
         <v>1340</v>
       </c>
       <c r="F489" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="490" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="490" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A490" s="1" t="s">
         <v>1341</v>
       </c>
       <c r="B490" s="1" t="s">
+        <v>1339</v>
+      </c>
+      <c r="C490" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D490" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E490" s="1" t="s">
         <v>1342</v>
       </c>
-      <c r="C490" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D490" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E490" s="1" t="s">
-        <v>1343</v>
+      <c r="F490" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="491" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A491" s="1" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B491" s="1" t="s">
         <v>1344</v>
       </c>
-      <c r="B491" s="1" t="s">
+      <c r="C491" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D491" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E491" s="1" t="s">
         <v>1345</v>
       </c>
-      <c r="C491" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D491" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E491" s="1" t="s">
-        <v>1346</v>
-      </c>
       <c r="F491" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="492" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A492" s="1" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B492" s="1" t="s">
         <v>1347</v>
-      </c>
-      <c r="B492" s="1" t="s">
-        <v>1345</v>
       </c>
       <c r="C492" s="1" t="s">
         <v>3</v>
@@ -16983,7 +16965,7 @@
         <v>1348</v>
       </c>
       <c r="F492" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="493" spans="1:6" x14ac:dyDescent="0.25">
@@ -17003,7 +16985,7 @@
         <v>1351</v>
       </c>
       <c r="F493" s="1" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="494" spans="1:6" x14ac:dyDescent="0.25">
@@ -17023,7 +17005,7 @@
         <v>1354</v>
       </c>
       <c r="F494" s="1" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="495" spans="1:6" x14ac:dyDescent="0.25">
@@ -17163,7 +17145,7 @@
         <v>1375</v>
       </c>
       <c r="F501" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="502" spans="1:6" x14ac:dyDescent="0.25">
@@ -17183,7 +17165,7 @@
         <v>1378</v>
       </c>
       <c r="F502" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="503" spans="1:6" x14ac:dyDescent="0.25">
@@ -17211,16 +17193,16 @@
         <v>1382</v>
       </c>
       <c r="B504" s="1" t="s">
+        <v>1359</v>
+      </c>
+      <c r="C504" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D504" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E504" s="1" t="s">
         <v>1383</v>
-      </c>
-      <c r="C504" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D504" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E504" s="1" t="s">
-        <v>1384</v>
       </c>
       <c r="F504" s="1" t="s">
         <v>83</v>
@@ -17228,19 +17210,19 @@
     </row>
     <row r="505" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A505" s="1" t="s">
+        <v>1384</v>
+      </c>
+      <c r="B505" s="1" t="s">
+        <v>1362</v>
+      </c>
+      <c r="C505" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D505" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E505" s="1" t="s">
         <v>1385</v>
-      </c>
-      <c r="B505" s="1" t="s">
-        <v>1386</v>
-      </c>
-      <c r="C505" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D505" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E505" s="1" t="s">
-        <v>1387</v>
       </c>
       <c r="F505" s="1" t="s">
         <v>83</v>
@@ -17248,7 +17230,7 @@
     </row>
     <row r="506" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A506" s="1" t="s">
-        <v>1388</v>
+        <v>1386</v>
       </c>
       <c r="B506" s="1" t="s">
         <v>1365</v>
@@ -17260,7 +17242,7 @@
         <v>4</v>
       </c>
       <c r="E506" s="1" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="F506" s="1" t="s">
         <v>83</v>
@@ -17268,7 +17250,7 @@
     </row>
     <row r="507" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A507" s="1" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
       <c r="B507" s="1" t="s">
         <v>1368</v>
@@ -17280,7 +17262,7 @@
         <v>4</v>
       </c>
       <c r="E507" s="1" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
       <c r="F507" s="1" t="s">
         <v>83</v>
@@ -17288,19 +17270,19 @@
     </row>
     <row r="508" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A508" s="1" t="s">
+        <v>1390</v>
+      </c>
+      <c r="B508" s="1" t="s">
+        <v>1391</v>
+      </c>
+      <c r="C508" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D508" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E508" s="1" t="s">
         <v>1392</v>
-      </c>
-      <c r="B508" s="1" t="s">
-        <v>1371</v>
-      </c>
-      <c r="C508" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D508" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E508" s="1" t="s">
-        <v>1393</v>
       </c>
       <c r="F508" s="1" t="s">
         <v>83</v>
@@ -17308,10 +17290,10 @@
     </row>
     <row r="509" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A509" s="1" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B509" s="1" t="s">
         <v>1394</v>
-      </c>
-      <c r="B509" s="1" t="s">
-        <v>1374</v>
       </c>
       <c r="C509" s="1" t="s">
         <v>3</v>
@@ -17323,7 +17305,7 @@
         <v>1395</v>
       </c>
       <c r="F509" s="1" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="510" spans="1:6" x14ac:dyDescent="0.25">
@@ -17331,36 +17313,36 @@
         <v>1396</v>
       </c>
       <c r="B510" s="1" t="s">
+        <v>1394</v>
+      </c>
+      <c r="C510" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D510" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E510" s="1" t="s">
         <v>1397</v>
       </c>
-      <c r="C510" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D510" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E510" s="1" t="s">
-        <v>1398</v>
-      </c>
       <c r="F510" s="1" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="511" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A511" s="1" t="s">
+        <v>1398</v>
+      </c>
+      <c r="B511" s="1" t="s">
         <v>1399</v>
       </c>
-      <c r="B511" s="1" t="s">
+      <c r="C511" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D511" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E511" s="1" t="s">
         <v>1400</v>
-      </c>
-      <c r="C511" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D511" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E511" s="1" t="s">
-        <v>1401</v>
       </c>
       <c r="F511" s="1" t="s">
         <v>5</v>
@@ -17368,10 +17350,10 @@
     </row>
     <row r="512" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A512" s="1" t="s">
+        <v>1401</v>
+      </c>
+      <c r="B512" s="1" t="s">
         <v>1402</v>
-      </c>
-      <c r="B512" s="1" t="s">
-        <v>1400</v>
       </c>
       <c r="C512" s="1" t="s">
         <v>3</v>
@@ -17391,16 +17373,16 @@
         <v>1404</v>
       </c>
       <c r="B513" s="1" t="s">
+        <v>1402</v>
+      </c>
+      <c r="C513" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D513" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E513" s="1" t="s">
         <v>1405</v>
-      </c>
-      <c r="C513" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D513" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E513" s="1" t="s">
-        <v>1406</v>
       </c>
       <c r="F513" s="1" t="s">
         <v>5</v>
@@ -17408,19 +17390,19 @@
     </row>
     <row r="514" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A514" s="1" t="s">
+        <v>1406</v>
+      </c>
+      <c r="B514" s="1" t="s">
         <v>1407</v>
       </c>
-      <c r="B514" s="1" t="s">
+      <c r="C514" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D514" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E514" s="1" t="s">
         <v>1408</v>
-      </c>
-      <c r="C514" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D514" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E514" s="1" t="s">
-        <v>1409</v>
       </c>
       <c r="F514" s="1" t="s">
         <v>5</v>
@@ -17428,10 +17410,10 @@
     </row>
     <row r="515" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A515" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="B515" s="1" t="s">
         <v>1410</v>
-      </c>
-      <c r="B515" s="1" t="s">
-        <v>1408</v>
       </c>
       <c r="C515" s="1" t="s">
         <v>3</v>
@@ -17691,16 +17673,16 @@
         <v>1448</v>
       </c>
       <c r="B528" s="1" t="s">
+        <v>1440</v>
+      </c>
+      <c r="C528" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D528" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E528" s="1" t="s">
         <v>1449</v>
-      </c>
-      <c r="C528" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D528" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E528" s="1" t="s">
-        <v>1450</v>
       </c>
       <c r="F528" s="1" t="s">
         <v>5</v>
@@ -17708,19 +17690,19 @@
     </row>
     <row r="529" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A529" s="1" t="s">
+        <v>1450</v>
+      </c>
+      <c r="B529" s="1" t="s">
         <v>1451</v>
       </c>
-      <c r="B529" s="1" t="s">
+      <c r="C529" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D529" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E529" s="1" t="s">
         <v>1452</v>
-      </c>
-      <c r="C529" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D529" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E529" s="1" t="s">
-        <v>1453</v>
       </c>
       <c r="F529" s="1" t="s">
         <v>5</v>
@@ -17728,10 +17710,10 @@
     </row>
     <row r="530" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A530" s="1" t="s">
+        <v>1453</v>
+      </c>
+      <c r="B530" s="1" t="s">
         <v>1454</v>
-      </c>
-      <c r="B530" s="1" t="s">
-        <v>1446</v>
       </c>
       <c r="C530" s="1" t="s">
         <v>3</v>
@@ -17771,36 +17753,36 @@
         <v>1459</v>
       </c>
       <c r="B532" s="1" t="s">
+        <v>1457</v>
+      </c>
+      <c r="C532" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D532" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E532" s="1" t="s">
         <v>1460</v>
       </c>
-      <c r="C532" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D532" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E532" s="1" t="s">
-        <v>1461</v>
-      </c>
       <c r="F532" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="533" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A533" s="1" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B533" s="1" t="s">
         <v>1462</v>
       </c>
-      <c r="B533" s="1" t="s">
+      <c r="C533" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D533" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E533" s="1" t="s">
         <v>1463</v>
-      </c>
-      <c r="C533" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D533" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E533" s="1" t="s">
-        <v>1464</v>
       </c>
       <c r="F533" s="1" t="s">
         <v>5</v>
@@ -17808,10 +17790,10 @@
     </row>
     <row r="534" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A534" s="1" t="s">
+        <v>1464</v>
+      </c>
+      <c r="B534" s="1" t="s">
         <v>1465</v>
-      </c>
-      <c r="B534" s="1" t="s">
-        <v>1463</v>
       </c>
       <c r="C534" s="1" t="s">
         <v>3</v>
@@ -17823,7 +17805,7 @@
         <v>1466</v>
       </c>
       <c r="F534" s="1" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="535" spans="1:6" x14ac:dyDescent="0.25">
@@ -17846,7 +17828,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="536" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A536" s="1" t="s">
         <v>1470</v>
       </c>
@@ -17862,11 +17844,8 @@
       <c r="E536" s="1" t="s">
         <v>1472</v>
       </c>
-      <c r="F536" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="537" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="537" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A537" s="1" t="s">
         <v>1473</v>
       </c>
@@ -17881,9 +17860,6 @@
       </c>
       <c r="E537" s="1" t="s">
         <v>1475</v>
-      </c>
-      <c r="F537" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="538" spans="1:5" x14ac:dyDescent="0.25">
@@ -17925,38 +17901,38 @@
         <v>1482</v>
       </c>
       <c r="B540" s="1" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C540" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D540" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E540" s="1" t="s">
         <v>1483</v>
-      </c>
-      <c r="C540" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D540" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E540" s="1" t="s">
-        <v>1484</v>
       </c>
     </row>
     <row r="541" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A541" s="1" t="s">
+        <v>1484</v>
+      </c>
+      <c r="B541" s="1" t="s">
+        <v>1474</v>
+      </c>
+      <c r="C541" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D541" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E541" s="1" t="s">
         <v>1485</v>
-      </c>
-      <c r="B541" s="1" t="s">
-        <v>1486</v>
-      </c>
-      <c r="C541" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D541" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E541" s="1" t="s">
-        <v>1487</v>
       </c>
     </row>
     <row r="542" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A542" s="1" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
       <c r="B542" s="1" t="s">
         <v>1477</v>
@@ -17968,12 +17944,12 @@
         <v>4</v>
       </c>
       <c r="E542" s="1" t="s">
-        <v>1489</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="543" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A543" s="1" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
       <c r="B543" s="1" t="s">
         <v>1480</v>
@@ -17985,32 +17961,35 @@
         <v>4</v>
       </c>
       <c r="E543" s="1" t="s">
+        <v>1489</v>
+      </c>
+    </row>
+    <row r="544" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A544" s="1" t="s">
+        <v>1490</v>
+      </c>
+      <c r="B544" s="1" t="s">
         <v>1491</v>
       </c>
-    </row>
-    <row r="544" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A544" s="1" t="s">
+      <c r="C544" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D544" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E544" s="1" t="s">
         <v>1492</v>
       </c>
-      <c r="B544" s="1" t="s">
-        <v>1483</v>
-      </c>
-      <c r="C544" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D544" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E544" s="1" t="s">
-        <v>1493</v>
+      <c r="F544" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="545" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A545" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="B545" s="1" t="s">
         <v>1494</v>
-      </c>
-      <c r="B545" s="1" t="s">
-        <v>1486</v>
       </c>
       <c r="C545" s="1" t="s">
         <v>3</v>
@@ -18022,7 +18001,7 @@
         <v>1495</v>
       </c>
     </row>
-    <row r="546" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A546" s="1" t="s">
         <v>1496</v>
       </c>
@@ -18037,9 +18016,6 @@
       </c>
       <c r="E546" s="1" t="s">
         <v>1498</v>
-      </c>
-      <c r="F546" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="547" spans="1:5" x14ac:dyDescent="0.25">
@@ -18047,41 +18023,44 @@
         <v>1499</v>
       </c>
       <c r="B547" s="1" t="s">
+        <v>1497</v>
+      </c>
+      <c r="C547" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D547" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E547" s="1" t="s">
         <v>1500</v>
       </c>
-      <c r="C547" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D547" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E547" s="1" t="s">
+    </row>
+    <row r="548" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A548" s="1" t="s">
         <v>1501</v>
       </c>
-    </row>
-    <row r="548" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A548" s="1" t="s">
+      <c r="B548" s="1" t="s">
         <v>1502</v>
       </c>
-      <c r="B548" s="1" t="s">
+      <c r="C548" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D548" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E548" s="1" t="s">
         <v>1503</v>
       </c>
-      <c r="C548" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D548" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E548" s="1" t="s">
+      <c r="F548" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="549" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A549" s="1" t="s">
         <v>1504</v>
       </c>
-    </row>
-    <row r="549" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A549" s="1" t="s">
+      <c r="B549" s="1" t="s">
         <v>1505</v>
-      </c>
-      <c r="B549" s="1" t="s">
-        <v>1503</v>
       </c>
       <c r="C549" s="1" t="s">
         <v>3</v>
@@ -18091,6 +18070,9 @@
       </c>
       <c r="E549" s="1" t="s">
         <v>1506</v>
+      </c>
+      <c r="F549" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="550" spans="1:6" x14ac:dyDescent="0.25">
@@ -18178,16 +18160,16 @@
         <v>1519</v>
       </c>
       <c r="B554" s="1" t="s">
+        <v>1502</v>
+      </c>
+      <c r="C554" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D554" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E554" s="1" t="s">
         <v>1520</v>
-      </c>
-      <c r="C554" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D554" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E554" s="1" t="s">
-        <v>1521</v>
       </c>
       <c r="F554" s="1" t="s">
         <v>5</v>
@@ -18195,19 +18177,19 @@
     </row>
     <row r="555" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A555" s="1" t="s">
+        <v>1521</v>
+      </c>
+      <c r="B555" s="1" t="s">
         <v>1522</v>
       </c>
-      <c r="B555" s="1" t="s">
+      <c r="C555" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D555" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E555" s="1" t="s">
         <v>1523</v>
-      </c>
-      <c r="C555" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D555" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E555" s="1" t="s">
-        <v>1524</v>
       </c>
       <c r="F555" s="1" t="s">
         <v>5</v>
@@ -18215,10 +18197,10 @@
     </row>
     <row r="556" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A556" s="1" t="s">
+        <v>1524</v>
+      </c>
+      <c r="B556" s="1" t="s">
         <v>1525</v>
-      </c>
-      <c r="B556" s="1" t="s">
-        <v>1508</v>
       </c>
       <c r="C556" s="1" t="s">
         <v>3</v>
@@ -18258,16 +18240,16 @@
         <v>1530</v>
       </c>
       <c r="B558" s="1" t="s">
+        <v>1514</v>
+      </c>
+      <c r="C558" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D558" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E558" s="1" t="s">
         <v>1531</v>
-      </c>
-      <c r="C558" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D558" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E558" s="1" t="s">
-        <v>1532</v>
       </c>
       <c r="F558" s="1" t="s">
         <v>5</v>
@@ -18275,19 +18257,19 @@
     </row>
     <row r="559" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A559" s="1" t="s">
+        <v>1532</v>
+      </c>
+      <c r="B559" s="1" t="s">
+        <v>1517</v>
+      </c>
+      <c r="C559" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D559" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E559" s="1" t="s">
         <v>1533</v>
-      </c>
-      <c r="B559" s="1" t="s">
-        <v>1534</v>
-      </c>
-      <c r="C559" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D559" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E559" s="1" t="s">
-        <v>1535</v>
       </c>
       <c r="F559" s="1" t="s">
         <v>5</v>
@@ -18295,19 +18277,19 @@
     </row>
     <row r="560" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A560" s="1" t="s">
+        <v>1534</v>
+      </c>
+      <c r="B560" s="1" t="s">
+        <v>1535</v>
+      </c>
+      <c r="C560" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D560" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E560" s="1" t="s">
         <v>1536</v>
-      </c>
-      <c r="B560" s="1" t="s">
-        <v>1520</v>
-      </c>
-      <c r="C560" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D560" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E560" s="1" t="s">
-        <v>1537</v>
       </c>
       <c r="F560" s="1" t="s">
         <v>5</v>
@@ -18315,10 +18297,10 @@
     </row>
     <row r="561" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A561" s="1" t="s">
+        <v>1537</v>
+      </c>
+      <c r="B561" s="1" t="s">
         <v>1538</v>
-      </c>
-      <c r="B561" s="1" t="s">
-        <v>1523</v>
       </c>
       <c r="C561" s="1" t="s">
         <v>3</v>
@@ -18338,16 +18320,16 @@
         <v>1540</v>
       </c>
       <c r="B562" s="1" t="s">
+        <v>1538</v>
+      </c>
+      <c r="C562" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D562" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E562" s="1" t="s">
         <v>1541</v>
-      </c>
-      <c r="C562" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D562" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E562" s="1" t="s">
-        <v>1542</v>
       </c>
       <c r="F562" s="1" t="s">
         <v>5</v>
@@ -18355,19 +18337,19 @@
     </row>
     <row r="563" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A563" s="1" t="s">
+        <v>1542</v>
+      </c>
+      <c r="B563" s="1" t="s">
         <v>1543</v>
       </c>
-      <c r="B563" s="1" t="s">
+      <c r="C563" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D563" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E563" s="1" t="s">
         <v>1544</v>
-      </c>
-      <c r="C563" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D563" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E563" s="1" t="s">
-        <v>1545</v>
       </c>
       <c r="F563" s="1" t="s">
         <v>5</v>
@@ -18375,10 +18357,10 @@
     </row>
     <row r="564" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A564" s="1" t="s">
+        <v>1545</v>
+      </c>
+      <c r="B564" s="1" t="s">
         <v>1546</v>
-      </c>
-      <c r="B564" s="1" t="s">
-        <v>1544</v>
       </c>
       <c r="C564" s="1" t="s">
         <v>3</v>
@@ -18390,7 +18372,7 @@
         <v>1547</v>
       </c>
       <c r="F564" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="565" spans="1:6" x14ac:dyDescent="0.25">
@@ -18410,7 +18392,7 @@
         <v>1550</v>
       </c>
       <c r="F565" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="566" spans="1:6" x14ac:dyDescent="0.25">
@@ -18430,7 +18412,7 @@
         <v>1553</v>
       </c>
       <c r="F566" s="1" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="567" spans="1:6" x14ac:dyDescent="0.25">
@@ -18450,7 +18432,7 @@
         <v>1556</v>
       </c>
       <c r="F567" s="1" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="568" spans="1:6" x14ac:dyDescent="0.25">
@@ -18518,16 +18500,16 @@
         <v>1566</v>
       </c>
       <c r="B571" s="1" t="s">
+        <v>1555</v>
+      </c>
+      <c r="C571" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D571" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E571" s="1" t="s">
         <v>1567</v>
-      </c>
-      <c r="C571" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D571" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E571" s="1" t="s">
-        <v>1568</v>
       </c>
       <c r="F571" s="1" t="s">
         <v>5</v>
@@ -18535,19 +18517,19 @@
     </row>
     <row r="572" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A572" s="1" t="s">
+        <v>1568</v>
+      </c>
+      <c r="B572" s="1" t="s">
+        <v>1558</v>
+      </c>
+      <c r="C572" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D572" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E572" s="1" t="s">
         <v>1569</v>
-      </c>
-      <c r="B572" s="1" t="s">
-        <v>1570</v>
-      </c>
-      <c r="C572" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D572" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E572" s="1" t="s">
-        <v>1571</v>
       </c>
       <c r="F572" s="1" t="s">
         <v>5</v>
@@ -18555,7 +18537,7 @@
     </row>
     <row r="573" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A573" s="1" t="s">
-        <v>1572</v>
+        <v>1570</v>
       </c>
       <c r="B573" s="1" t="s">
         <v>1561</v>
@@ -18567,7 +18549,7 @@
         <v>4</v>
       </c>
       <c r="E573" s="1" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="F573" s="1" t="s">
         <v>5</v>
@@ -18575,10 +18557,10 @@
     </row>
     <row r="574" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A574" s="1" t="s">
-        <v>1574</v>
+        <v>55</v>
       </c>
       <c r="B574" s="1" t="s">
-        <v>1564</v>
+        <v>56</v>
       </c>
       <c r="C574" s="1" t="s">
         <v>3</v>
@@ -18587,7 +18569,7 @@
         <v>4</v>
       </c>
       <c r="E574" s="1" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="F574" s="1" t="s">
         <v>5</v>
@@ -18595,10 +18577,10 @@
     </row>
     <row r="575" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A575" s="1" t="s">
-        <v>1576</v>
+        <v>51</v>
       </c>
       <c r="B575" s="1" t="s">
-        <v>1567</v>
+        <v>52</v>
       </c>
       <c r="C575" s="1" t="s">
         <v>3</v>
@@ -18607,7 +18589,7 @@
         <v>4</v>
       </c>
       <c r="E575" s="1" t="s">
-        <v>1577</v>
+        <v>1573</v>
       </c>
       <c r="F575" s="1" t="s">
         <v>5</v>
@@ -18615,10 +18597,10 @@
     </row>
     <row r="576" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A576" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B576" s="1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="C576" s="1" t="s">
         <v>3</v>
@@ -18627,7 +18609,7 @@
         <v>4</v>
       </c>
       <c r="E576" s="1" t="s">
-        <v>1578</v>
+        <v>1574</v>
       </c>
       <c r="F576" s="1" t="s">
         <v>5</v>
@@ -18635,10 +18617,10 @@
     </row>
     <row r="577" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A577" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B577" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C577" s="1" t="s">
         <v>3</v>
@@ -18647,7 +18629,7 @@
         <v>4</v>
       </c>
       <c r="E577" s="1" t="s">
-        <v>1579</v>
+        <v>1575</v>
       </c>
       <c r="F577" s="1" t="s">
         <v>5</v>
@@ -18655,10 +18637,10 @@
     </row>
     <row r="578" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A578" s="1" t="s">
-        <v>49</v>
+        <v>1576</v>
       </c>
       <c r="B578" s="1" t="s">
-        <v>50</v>
+        <v>1577</v>
       </c>
       <c r="C578" s="1" t="s">
         <v>3</v>
@@ -18667,18 +18649,18 @@
         <v>4</v>
       </c>
       <c r="E578" s="1" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="F578" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="579" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A579" s="1" t="s">
-        <v>53</v>
+        <v>1579</v>
       </c>
       <c r="B579" s="1" t="s">
-        <v>54</v>
+        <v>1580</v>
       </c>
       <c r="C579" s="1" t="s">
         <v>3</v>
@@ -18690,7 +18672,7 @@
         <v>1581</v>
       </c>
       <c r="F579" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="580" spans="1:6" x14ac:dyDescent="0.25">
@@ -18750,7 +18732,7 @@
         <v>1590</v>
       </c>
       <c r="F582" s="1" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="583" spans="1:6" x14ac:dyDescent="0.25">
@@ -18770,7 +18752,7 @@
         <v>1593</v>
       </c>
       <c r="F583" s="1" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="584" spans="1:6" x14ac:dyDescent="0.25">
@@ -18798,16 +18780,16 @@
         <v>1597</v>
       </c>
       <c r="B585" s="1" t="s">
+        <v>1592</v>
+      </c>
+      <c r="C585" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D585" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E585" s="1" t="s">
         <v>1598</v>
-      </c>
-      <c r="C585" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D585" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E585" s="1" t="s">
-        <v>1599</v>
       </c>
       <c r="F585" s="1" t="s">
         <v>5</v>
@@ -18815,19 +18797,19 @@
     </row>
     <row r="586" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A586" s="1" t="s">
+        <v>1599</v>
+      </c>
+      <c r="B586" s="1" t="s">
         <v>1600</v>
       </c>
-      <c r="B586" s="1" t="s">
+      <c r="C586" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D586" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E586" s="1" t="s">
         <v>1601</v>
-      </c>
-      <c r="C586" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D586" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E586" s="1" t="s">
-        <v>1602</v>
       </c>
       <c r="F586" s="1" t="s">
         <v>5</v>
@@ -18835,19 +18817,19 @@
     </row>
     <row r="587" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A587" s="1" t="s">
+        <v>1602</v>
+      </c>
+      <c r="B587" s="1" t="s">
+        <v>1600</v>
+      </c>
+      <c r="C587" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D587" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E587" s="1" t="s">
         <v>1603</v>
-      </c>
-      <c r="B587" s="1" t="s">
-        <v>1598</v>
-      </c>
-      <c r="C587" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D587" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E587" s="1" t="s">
-        <v>1604</v>
       </c>
       <c r="F587" s="1" t="s">
         <v>5</v>
@@ -18855,19 +18837,19 @@
     </row>
     <row r="588" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A588" s="1" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B588" s="1" t="s">
         <v>1605</v>
       </c>
-      <c r="B588" s="1" t="s">
+      <c r="C588" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D588" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E588" s="1" t="s">
         <v>1606</v>
-      </c>
-      <c r="C588" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D588" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E588" s="1" t="s">
-        <v>1607</v>
       </c>
       <c r="F588" s="1" t="s">
         <v>5</v>
@@ -18875,19 +18857,19 @@
     </row>
     <row r="589" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A589" s="1" t="s">
+        <v>1607</v>
+      </c>
+      <c r="B589" s="1" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C589" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D589" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E589" s="1" t="s">
         <v>1608</v>
-      </c>
-      <c r="B589" s="1" t="s">
-        <v>1606</v>
-      </c>
-      <c r="C589" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D589" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E589" s="1" t="s">
-        <v>1609</v>
       </c>
       <c r="F589" s="1" t="s">
         <v>5</v>
@@ -18895,19 +18877,19 @@
     </row>
     <row r="590" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A590" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B590" s="1" t="s">
         <v>1610</v>
       </c>
-      <c r="B590" s="1" t="s">
+      <c r="C590" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D590" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E590" s="1" t="s">
         <v>1611</v>
-      </c>
-      <c r="C590" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D590" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E590" s="1" t="s">
-        <v>1612</v>
       </c>
       <c r="F590" s="1" t="s">
         <v>5</v>
@@ -18915,19 +18897,19 @@
     </row>
     <row r="591" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A591" s="1" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B591" s="1" t="s">
+        <v>1610</v>
+      </c>
+      <c r="C591" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D591" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E591" s="1" t="s">
         <v>1613</v>
-      </c>
-      <c r="B591" s="1" t="s">
-        <v>1611</v>
-      </c>
-      <c r="C591" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D591" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E591" s="1" t="s">
-        <v>1614</v>
       </c>
       <c r="F591" s="1" t="s">
         <v>5</v>
@@ -18935,19 +18917,19 @@
     </row>
     <row r="592" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A592" s="1" t="s">
+        <v>1614</v>
+      </c>
+      <c r="B592" s="1" t="s">
         <v>1615</v>
       </c>
-      <c r="B592" s="1" t="s">
+      <c r="C592" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D592" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E592" s="1" t="s">
         <v>1616</v>
-      </c>
-      <c r="C592" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D592" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E592" s="1" t="s">
-        <v>1617</v>
       </c>
       <c r="F592" s="1" t="s">
         <v>5</v>
@@ -18955,10 +18937,10 @@
     </row>
     <row r="593" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A593" s="1" t="s">
+        <v>1617</v>
+      </c>
+      <c r="B593" s="1" t="s">
         <v>1618</v>
-      </c>
-      <c r="B593" s="1" t="s">
-        <v>1616</v>
       </c>
       <c r="C593" s="1" t="s">
         <v>3</v>
@@ -18998,16 +18980,16 @@
         <v>1623</v>
       </c>
       <c r="B595" s="1" t="s">
+        <v>1618</v>
+      </c>
+      <c r="C595" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D595" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E595" s="1" t="s">
         <v>1624</v>
-      </c>
-      <c r="C595" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D595" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E595" s="1" t="s">
-        <v>1625</v>
       </c>
       <c r="F595" s="1" t="s">
         <v>5</v>
@@ -19015,19 +18997,19 @@
     </row>
     <row r="596" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A596" s="1" t="s">
+        <v>1625</v>
+      </c>
+      <c r="B596" s="1" t="s">
         <v>1626</v>
       </c>
-      <c r="B596" s="1" t="s">
+      <c r="C596" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D596" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E596" s="1" t="s">
         <v>1627</v>
-      </c>
-      <c r="C596" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D596" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E596" s="1" t="s">
-        <v>1628</v>
       </c>
       <c r="F596" s="1" t="s">
         <v>5</v>
@@ -19035,10 +19017,10 @@
     </row>
     <row r="597" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A597" s="1" t="s">
+        <v>1628</v>
+      </c>
+      <c r="B597" s="1" t="s">
         <v>1629</v>
-      </c>
-      <c r="B597" s="1" t="s">
-        <v>1624</v>
       </c>
       <c r="C597" s="1" t="s">
         <v>3</v>
@@ -19138,16 +19120,16 @@
         <v>1643</v>
       </c>
       <c r="B602" s="1" t="s">
+        <v>1641</v>
+      </c>
+      <c r="C602" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D602" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E602" s="1" t="s">
         <v>1644</v>
-      </c>
-      <c r="C602" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D602" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E602" s="1" t="s">
-        <v>1645</v>
       </c>
       <c r="F602" s="1" t="s">
         <v>5</v>
@@ -19155,19 +19137,19 @@
     </row>
     <row r="603" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A603" s="1" t="s">
+        <v>1645</v>
+      </c>
+      <c r="B603" s="1" t="s">
         <v>1646</v>
       </c>
-      <c r="B603" s="1" t="s">
+      <c r="C603" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D603" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E603" s="1" t="s">
         <v>1647</v>
-      </c>
-      <c r="C603" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D603" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E603" s="1" t="s">
-        <v>1648</v>
       </c>
       <c r="F603" s="1" t="s">
         <v>5</v>
@@ -19175,10 +19157,10 @@
     </row>
     <row r="604" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A604" s="1" t="s">
+        <v>1648</v>
+      </c>
+      <c r="B604" s="1" t="s">
         <v>1649</v>
-      </c>
-      <c r="B604" s="1" t="s">
-        <v>1647</v>
       </c>
       <c r="C604" s="1" t="s">
         <v>3</v>
@@ -19258,16 +19240,16 @@
         <v>1660</v>
       </c>
       <c r="B608" s="1" t="s">
+        <v>1658</v>
+      </c>
+      <c r="C608" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D608" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E608" s="1" t="s">
         <v>1661</v>
-      </c>
-      <c r="C608" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D608" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E608" s="1" t="s">
-        <v>1662</v>
       </c>
       <c r="F608" s="1" t="s">
         <v>5</v>
@@ -19275,19 +19257,19 @@
     </row>
     <row r="609" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A609" s="1" t="s">
+        <v>1662</v>
+      </c>
+      <c r="B609" s="1" t="s">
         <v>1663</v>
       </c>
-      <c r="B609" s="1" t="s">
+      <c r="C609" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D609" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E609" s="1" t="s">
         <v>1664</v>
-      </c>
-      <c r="C609" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D609" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E609" s="1" t="s">
-        <v>1665</v>
       </c>
       <c r="F609" s="1" t="s">
         <v>5</v>
@@ -19295,19 +19277,19 @@
     </row>
     <row r="610" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A610" s="1" t="s">
+        <v>1665</v>
+      </c>
+      <c r="B610" s="1" t="s">
+        <v>1663</v>
+      </c>
+      <c r="C610" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D610" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E610" s="1" t="s">
         <v>1666</v>
-      </c>
-      <c r="B610" s="1" t="s">
-        <v>1664</v>
-      </c>
-      <c r="C610" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D610" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E610" s="1" t="s">
-        <v>1667</v>
       </c>
       <c r="F610" s="1" t="s">
         <v>5</v>
@@ -19315,19 +19297,19 @@
     </row>
     <row r="611" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A611" s="1" t="s">
+        <v>1667</v>
+      </c>
+      <c r="B611" s="1" t="s">
         <v>1668</v>
       </c>
-      <c r="B611" s="1" t="s">
+      <c r="C611" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D611" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E611" s="1" t="s">
         <v>1669</v>
-      </c>
-      <c r="C611" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D611" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E611" s="1" t="s">
-        <v>1670</v>
       </c>
       <c r="F611" s="1" t="s">
         <v>5</v>
@@ -19335,19 +19317,19 @@
     </row>
     <row r="612" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A612" s="1" t="s">
+        <v>1670</v>
+      </c>
+      <c r="B612" s="1" t="s">
+        <v>1668</v>
+      </c>
+      <c r="C612" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D612" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E612" s="1" t="s">
         <v>1671</v>
-      </c>
-      <c r="B612" s="1" t="s">
-        <v>1669</v>
-      </c>
-      <c r="C612" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D612" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E612" s="1" t="s">
-        <v>1672</v>
       </c>
       <c r="F612" s="1" t="s">
         <v>5</v>
@@ -19355,19 +19337,19 @@
     </row>
     <row r="613" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A613" s="1" t="s">
+        <v>1672</v>
+      </c>
+      <c r="B613" s="1" t="s">
         <v>1673</v>
       </c>
-      <c r="B613" s="1" t="s">
+      <c r="C613" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D613" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E613" s="1" t="s">
         <v>1674</v>
-      </c>
-      <c r="C613" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D613" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E613" s="1" t="s">
-        <v>1675</v>
       </c>
       <c r="F613" s="1" t="s">
         <v>5</v>
@@ -19375,10 +19357,10 @@
     </row>
     <row r="614" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A614" s="1" t="s">
+        <v>1675</v>
+      </c>
+      <c r="B614" s="1" t="s">
         <v>1676</v>
-      </c>
-      <c r="B614" s="1" t="s">
-        <v>1674</v>
       </c>
       <c r="C614" s="1" t="s">
         <v>3</v>
@@ -19418,16 +19400,16 @@
         <v>1681</v>
       </c>
       <c r="B616" s="1" t="s">
+        <v>1679</v>
+      </c>
+      <c r="C616" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D616" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E616" s="1" t="s">
         <v>1682</v>
-      </c>
-      <c r="C616" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D616" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E616" s="1" t="s">
-        <v>1683</v>
       </c>
       <c r="F616" s="1" t="s">
         <v>5</v>
@@ -19435,19 +19417,19 @@
     </row>
     <row r="617" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A617" s="1" t="s">
+        <v>1683</v>
+      </c>
+      <c r="B617" s="1" t="s">
         <v>1684</v>
       </c>
-      <c r="B617" s="1" t="s">
+      <c r="C617" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D617" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E617" s="1" t="s">
         <v>1685</v>
-      </c>
-      <c r="C617" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D617" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E617" s="1" t="s">
-        <v>1686</v>
       </c>
       <c r="F617" s="1" t="s">
         <v>5</v>
@@ -19455,10 +19437,10 @@
     </row>
     <row r="618" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A618" s="1" t="s">
+        <v>1686</v>
+      </c>
+      <c r="B618" s="1" t="s">
         <v>1687</v>
-      </c>
-      <c r="B618" s="1" t="s">
-        <v>1685</v>
       </c>
       <c r="C618" s="1" t="s">
         <v>3</v>
@@ -19498,16 +19480,16 @@
         <v>1692</v>
       </c>
       <c r="B620" s="1" t="s">
+        <v>1690</v>
+      </c>
+      <c r="C620" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D620" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E620" s="1" t="s">
         <v>1693</v>
-      </c>
-      <c r="C620" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D620" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E620" s="1" t="s">
-        <v>1694</v>
       </c>
       <c r="F620" s="1" t="s">
         <v>5</v>
@@ -19515,19 +19497,19 @@
     </row>
     <row r="621" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A621" s="1" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B621" s="1" t="s">
         <v>1695</v>
       </c>
-      <c r="B621" s="1" t="s">
+      <c r="C621" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D621" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E621" s="1" t="s">
         <v>1696</v>
-      </c>
-      <c r="C621" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D621" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E621" s="1" t="s">
-        <v>1697</v>
       </c>
       <c r="F621" s="1" t="s">
         <v>5</v>
@@ -19535,19 +19517,19 @@
     </row>
     <row r="622" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A622" s="1" t="s">
+        <v>1697</v>
+      </c>
+      <c r="B622" s="1" t="s">
+        <v>1695</v>
+      </c>
+      <c r="C622" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D622" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E622" s="1" t="s">
         <v>1698</v>
-      </c>
-      <c r="B622" s="1" t="s">
-        <v>1696</v>
-      </c>
-      <c r="C622" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D622" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E622" s="1" t="s">
-        <v>1699</v>
       </c>
       <c r="F622" s="1" t="s">
         <v>5</v>
@@ -19555,19 +19537,19 @@
     </row>
     <row r="623" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A623" s="1" t="s">
+        <v>1699</v>
+      </c>
+      <c r="B623" s="1" t="s">
         <v>1700</v>
       </c>
-      <c r="B623" s="1" t="s">
+      <c r="C623" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D623" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E623" s="1" t="s">
         <v>1701</v>
-      </c>
-      <c r="C623" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D623" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E623" s="1" t="s">
-        <v>1702</v>
       </c>
       <c r="F623" s="1" t="s">
         <v>5</v>
@@ -19575,19 +19557,19 @@
     </row>
     <row r="624" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A624" s="1" t="s">
+        <v>1702</v>
+      </c>
+      <c r="B624" s="1" t="s">
+        <v>1700</v>
+      </c>
+      <c r="C624" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D624" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E624" s="1" t="s">
         <v>1703</v>
-      </c>
-      <c r="B624" s="1" t="s">
-        <v>1701</v>
-      </c>
-      <c r="C624" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D624" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E624" s="1" t="s">
-        <v>1704</v>
       </c>
       <c r="F624" s="1" t="s">
         <v>5</v>
@@ -19595,19 +19577,19 @@
     </row>
     <row r="625" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A625" s="1" t="s">
+        <v>1704</v>
+      </c>
+      <c r="B625" s="1" t="s">
         <v>1705</v>
       </c>
-      <c r="B625" s="1" t="s">
+      <c r="C625" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D625" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E625" s="1" t="s">
         <v>1706</v>
-      </c>
-      <c r="C625" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D625" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E625" s="1" t="s">
-        <v>1707</v>
       </c>
       <c r="F625" s="1" t="s">
         <v>5</v>
@@ -19615,19 +19597,19 @@
     </row>
     <row r="626" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A626" s="1" t="s">
+        <v>1707</v>
+      </c>
+      <c r="B626" s="1" t="s">
+        <v>1705</v>
+      </c>
+      <c r="C626" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D626" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E626" s="1" t="s">
         <v>1708</v>
-      </c>
-      <c r="B626" s="1" t="s">
-        <v>1706</v>
-      </c>
-      <c r="C626" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D626" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E626" s="1" t="s">
-        <v>1709</v>
       </c>
       <c r="F626" s="1" t="s">
         <v>5</v>
@@ -19635,19 +19617,19 @@
     </row>
     <row r="627" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A627" s="1" t="s">
+        <v>1709</v>
+      </c>
+      <c r="B627" s="1" t="s">
         <v>1710</v>
       </c>
-      <c r="B627" s="1" t="s">
+      <c r="C627" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D627" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E627" s="1" t="s">
         <v>1711</v>
-      </c>
-      <c r="C627" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D627" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E627" s="1" t="s">
-        <v>1712</v>
       </c>
       <c r="F627" s="1" t="s">
         <v>5</v>
@@ -19655,10 +19637,10 @@
     </row>
     <row r="628" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A628" s="1" t="s">
+        <v>1712</v>
+      </c>
+      <c r="B628" s="1" t="s">
         <v>1713</v>
-      </c>
-      <c r="B628" s="1" t="s">
-        <v>1711</v>
       </c>
       <c r="C628" s="1" t="s">
         <v>3</v>
@@ -19858,16 +19840,16 @@
         <v>1742</v>
       </c>
       <c r="B638" s="1" t="s">
+        <v>1740</v>
+      </c>
+      <c r="C638" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D638" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E638" s="1" t="s">
         <v>1743</v>
-      </c>
-      <c r="C638" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D638" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E638" s="1" t="s">
-        <v>1744</v>
       </c>
       <c r="F638" s="1" t="s">
         <v>5</v>
@@ -19875,19 +19857,19 @@
     </row>
     <row r="639" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A639" s="1" t="s">
+        <v>1744</v>
+      </c>
+      <c r="B639" s="1" t="s">
         <v>1745</v>
       </c>
-      <c r="B639" s="1" t="s">
+      <c r="C639" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D639" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E639" s="1" t="s">
         <v>1746</v>
-      </c>
-      <c r="C639" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D639" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E639" s="1" t="s">
-        <v>1747</v>
       </c>
       <c r="F639" s="1" t="s">
         <v>5</v>
@@ -19895,10 +19877,10 @@
     </row>
     <row r="640" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A640" s="1" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B640" s="1" t="s">
         <v>1748</v>
-      </c>
-      <c r="B640" s="1" t="s">
-        <v>1746</v>
       </c>
       <c r="C640" s="1" t="s">
         <v>3</v>
@@ -19978,16 +19960,16 @@
         <v>1759</v>
       </c>
       <c r="B644" s="1" t="s">
+        <v>1716</v>
+      </c>
+      <c r="C644" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D644" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E644" s="1" t="s">
         <v>1760</v>
-      </c>
-      <c r="C644" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D644" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E644" s="1" t="s">
-        <v>1761</v>
       </c>
       <c r="F644" s="1" t="s">
         <v>5</v>
@@ -19995,19 +19977,19 @@
     </row>
     <row r="645" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A645" s="1" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B645" s="1" t="s">
+        <v>1719</v>
+      </c>
+      <c r="C645" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D645" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E645" s="1" t="s">
         <v>1762</v>
-      </c>
-      <c r="B645" s="1" t="s">
-        <v>1763</v>
-      </c>
-      <c r="C645" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D645" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E645" s="1" t="s">
-        <v>1764</v>
       </c>
       <c r="F645" s="1" t="s">
         <v>5</v>
@@ -20015,7 +19997,7 @@
     </row>
     <row r="646" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A646" s="1" t="s">
-        <v>1765</v>
+        <v>1763</v>
       </c>
       <c r="B646" s="1" t="s">
         <v>1722</v>
@@ -20027,7 +20009,7 @@
         <v>4</v>
       </c>
       <c r="E646" s="1" t="s">
-        <v>1766</v>
+        <v>1764</v>
       </c>
       <c r="F646" s="1" t="s">
         <v>5</v>
@@ -20035,7 +20017,7 @@
     </row>
     <row r="647" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A647" s="1" t="s">
-        <v>1767</v>
+        <v>1765</v>
       </c>
       <c r="B647" s="1" t="s">
         <v>1725</v>
@@ -20047,7 +20029,7 @@
         <v>4</v>
       </c>
       <c r="E647" s="1" t="s">
-        <v>1768</v>
+        <v>1766</v>
       </c>
       <c r="F647" s="1" t="s">
         <v>5</v>
@@ -20055,7 +20037,7 @@
     </row>
     <row r="648" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A648" s="1" t="s">
-        <v>1769</v>
+        <v>1767</v>
       </c>
       <c r="B648" s="1" t="s">
         <v>1728</v>
@@ -20067,7 +20049,7 @@
         <v>4</v>
       </c>
       <c r="E648" s="1" t="s">
-        <v>1770</v>
+        <v>1768</v>
       </c>
       <c r="F648" s="1" t="s">
         <v>5</v>
@@ -20075,7 +20057,7 @@
     </row>
     <row r="649" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A649" s="1" t="s">
-        <v>1771</v>
+        <v>1769</v>
       </c>
       <c r="B649" s="1" t="s">
         <v>1731</v>
@@ -20087,7 +20069,7 @@
         <v>4</v>
       </c>
       <c r="E649" s="1" t="s">
-        <v>1772</v>
+        <v>1770</v>
       </c>
       <c r="F649" s="1" t="s">
         <v>5</v>
@@ -20095,19 +20077,19 @@
     </row>
     <row r="650" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A650" s="1" t="s">
+        <v>1771</v>
+      </c>
+      <c r="B650" s="1" t="s">
+        <v>1772</v>
+      </c>
+      <c r="C650" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D650" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E650" s="1" t="s">
         <v>1773</v>
-      </c>
-      <c r="B650" s="1" t="s">
-        <v>1734</v>
-      </c>
-      <c r="C650" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D650" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E650" s="1" t="s">
-        <v>1774</v>
       </c>
       <c r="F650" s="1" t="s">
         <v>5</v>
@@ -20115,7 +20097,7 @@
     </row>
     <row r="651" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A651" s="1" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="B651" s="1" t="s">
         <v>1737</v>
@@ -20127,7 +20109,7 @@
         <v>4</v>
       </c>
       <c r="E651" s="1" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
       <c r="F651" s="1" t="s">
         <v>5</v>
@@ -20135,19 +20117,19 @@
     </row>
     <row r="652" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A652" s="1" t="s">
+        <v>1776</v>
+      </c>
+      <c r="B652" s="1" t="s">
         <v>1777</v>
       </c>
-      <c r="B652" s="1" t="s">
+      <c r="C652" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D652" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E652" s="1" t="s">
         <v>1778</v>
-      </c>
-      <c r="C652" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D652" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E652" s="1" t="s">
-        <v>1779</v>
       </c>
       <c r="F652" s="1" t="s">
         <v>5</v>
@@ -20155,19 +20137,19 @@
     </row>
     <row r="653" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A653" s="1" t="s">
+        <v>1779</v>
+      </c>
+      <c r="B653" s="1" t="s">
+        <v>1777</v>
+      </c>
+      <c r="C653" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D653" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E653" s="1" t="s">
         <v>1780</v>
-      </c>
-      <c r="B653" s="1" t="s">
-        <v>1743</v>
-      </c>
-      <c r="C653" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D653" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E653" s="1" t="s">
-        <v>1781</v>
       </c>
       <c r="F653" s="1" t="s">
         <v>5</v>
@@ -20175,19 +20157,19 @@
     </row>
     <row r="654" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A654" s="1" t="s">
+        <v>1781</v>
+      </c>
+      <c r="B654" s="1" t="s">
+        <v>1710</v>
+      </c>
+      <c r="C654" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D654" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E654" s="1" t="s">
         <v>1782</v>
-      </c>
-      <c r="B654" s="1" t="s">
-        <v>1783</v>
-      </c>
-      <c r="C654" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D654" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E654" s="1" t="s">
-        <v>1784</v>
       </c>
       <c r="F654" s="1" t="s">
         <v>5</v>
@@ -20195,19 +20177,19 @@
     </row>
     <row r="655" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A655" s="1" t="s">
+        <v>1783</v>
+      </c>
+      <c r="B655" s="1" t="s">
+        <v>1784</v>
+      </c>
+      <c r="C655" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D655" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E655" s="1" t="s">
         <v>1785</v>
-      </c>
-      <c r="B655" s="1" t="s">
-        <v>1783</v>
-      </c>
-      <c r="C655" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D655" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E655" s="1" t="s">
-        <v>1786</v>
       </c>
       <c r="F655" s="1" t="s">
         <v>5</v>
@@ -20215,10 +20197,10 @@
     </row>
     <row r="656" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A656" s="1" t="s">
+        <v>1786</v>
+      </c>
+      <c r="B656" s="1" t="s">
         <v>1787</v>
-      </c>
-      <c r="B656" s="1" t="s">
-        <v>1716</v>
       </c>
       <c r="C656" s="1" t="s">
         <v>3</v>
@@ -20258,16 +20240,16 @@
         <v>1792</v>
       </c>
       <c r="B658" s="1" t="s">
+        <v>1784</v>
+      </c>
+      <c r="C658" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D658" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E658" s="1" t="s">
         <v>1793</v>
-      </c>
-      <c r="C658" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D658" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E658" s="1" t="s">
-        <v>1794</v>
       </c>
       <c r="F658" s="1" t="s">
         <v>5</v>
@@ -20275,19 +20257,19 @@
     </row>
     <row r="659" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A659" s="1" t="s">
+        <v>1794</v>
+      </c>
+      <c r="B659" s="1" t="s">
+        <v>1787</v>
+      </c>
+      <c r="C659" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D659" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E659" s="1" t="s">
         <v>1795</v>
-      </c>
-      <c r="B659" s="1" t="s">
-        <v>1796</v>
-      </c>
-      <c r="C659" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D659" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E659" s="1" t="s">
-        <v>1797</v>
       </c>
       <c r="F659" s="1" t="s">
         <v>5</v>
@@ -20295,7 +20277,7 @@
     </row>
     <row r="660" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A660" s="1" t="s">
-        <v>1798</v>
+        <v>1796</v>
       </c>
       <c r="B660" s="1" t="s">
         <v>1790</v>
@@ -20307,7 +20289,7 @@
         <v>4</v>
       </c>
       <c r="E660" s="1" t="s">
-        <v>1799</v>
+        <v>1797</v>
       </c>
       <c r="F660" s="1" t="s">
         <v>5</v>
@@ -20315,19 +20297,19 @@
     </row>
     <row r="661" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A661" s="1" t="s">
+        <v>1798</v>
+      </c>
+      <c r="B661" s="1" t="s">
+        <v>1799</v>
+      </c>
+      <c r="C661" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D661" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E661" s="1" t="s">
         <v>1800</v>
-      </c>
-      <c r="B661" s="1" t="s">
-        <v>1793</v>
-      </c>
-      <c r="C661" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D661" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E661" s="1" t="s">
-        <v>1801</v>
       </c>
       <c r="F661" s="1" t="s">
         <v>5</v>
@@ -20335,19 +20317,19 @@
     </row>
     <row r="662" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A662" s="1" t="s">
+        <v>1801</v>
+      </c>
+      <c r="B662" s="1" t="s">
+        <v>1799</v>
+      </c>
+      <c r="C662" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D662" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E662" s="1" t="s">
         <v>1802</v>
-      </c>
-      <c r="B662" s="1" t="s">
-        <v>1796</v>
-      </c>
-      <c r="C662" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D662" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E662" s="1" t="s">
-        <v>1803</v>
       </c>
       <c r="F662" s="1" t="s">
         <v>5</v>
@@ -20355,19 +20337,19 @@
     </row>
     <row r="663" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A663" s="1" t="s">
+        <v>1803</v>
+      </c>
+      <c r="B663" s="1" t="s">
         <v>1804</v>
       </c>
-      <c r="B663" s="1" t="s">
+      <c r="C663" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D663" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E663" s="1" t="s">
         <v>1805</v>
-      </c>
-      <c r="C663" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D663" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E663" s="1" t="s">
-        <v>1806</v>
       </c>
       <c r="F663" s="1" t="s">
         <v>5</v>
@@ -20375,19 +20357,19 @@
     </row>
     <row r="664" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A664" s="1" t="s">
+        <v>1806</v>
+      </c>
+      <c r="B664" s="1" t="s">
+        <v>1804</v>
+      </c>
+      <c r="C664" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D664" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E664" s="1" t="s">
         <v>1807</v>
-      </c>
-      <c r="B664" s="1" t="s">
-        <v>1805</v>
-      </c>
-      <c r="C664" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D664" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E664" s="1" t="s">
-        <v>1808</v>
       </c>
       <c r="F664" s="1" t="s">
         <v>5</v>
@@ -20395,19 +20377,19 @@
     </row>
     <row r="665" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A665" s="1" t="s">
+        <v>1808</v>
+      </c>
+      <c r="B665" s="1" t="s">
         <v>1809</v>
       </c>
-      <c r="B665" s="1" t="s">
+      <c r="C665" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D665" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E665" s="1" t="s">
         <v>1810</v>
-      </c>
-      <c r="C665" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D665" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E665" s="1" t="s">
-        <v>1811</v>
       </c>
       <c r="F665" s="1" t="s">
         <v>5</v>
@@ -20415,19 +20397,19 @@
     </row>
     <row r="666" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A666" s="1" t="s">
+        <v>1811</v>
+      </c>
+      <c r="B666" s="1" t="s">
+        <v>1809</v>
+      </c>
+      <c r="C666" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D666" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E666" s="1" t="s">
         <v>1812</v>
-      </c>
-      <c r="B666" s="1" t="s">
-        <v>1810</v>
-      </c>
-      <c r="C666" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D666" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E666" s="1" t="s">
-        <v>1813</v>
       </c>
       <c r="F666" s="1" t="s">
         <v>5</v>
@@ -20435,19 +20417,19 @@
     </row>
     <row r="667" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A667" s="1" t="s">
+        <v>1813</v>
+      </c>
+      <c r="B667" s="1" t="s">
         <v>1814</v>
       </c>
-      <c r="B667" s="1" t="s">
+      <c r="C667" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D667" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E667" s="1" t="s">
         <v>1815</v>
-      </c>
-      <c r="C667" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D667" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E667" s="1" t="s">
-        <v>1816</v>
       </c>
       <c r="F667" s="1" t="s">
         <v>5</v>
@@ -20455,19 +20437,19 @@
     </row>
     <row r="668" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A668" s="1" t="s">
+        <v>1816</v>
+      </c>
+      <c r="B668" s="1" t="s">
+        <v>1814</v>
+      </c>
+      <c r="C668" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D668" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E668" s="1" t="s">
         <v>1817</v>
-      </c>
-      <c r="B668" s="1" t="s">
-        <v>1815</v>
-      </c>
-      <c r="C668" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D668" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E668" s="1" t="s">
-        <v>1818</v>
       </c>
       <c r="F668" s="1" t="s">
         <v>5</v>
@@ -20475,39 +20457,39 @@
     </row>
     <row r="669" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A669" s="1" t="s">
+        <v>1818</v>
+      </c>
+      <c r="B669" s="1" t="s">
         <v>1819</v>
       </c>
-      <c r="B669" s="1" t="s">
+      <c r="C669" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D669" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E669" s="1" t="s">
         <v>1820</v>
       </c>
-      <c r="C669" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D669" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E669" s="1" t="s">
-        <v>1821</v>
-      </c>
       <c r="F669" s="1" t="s">
-        <v>5</v>
+        <v>67</v>
       </c>
     </row>
     <row r="670" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A670" s="1" t="s">
+        <v>1821</v>
+      </c>
+      <c r="B670" s="1" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C670" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D670" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E670" s="1" t="s">
         <v>1822</v>
-      </c>
-      <c r="B670" s="1" t="s">
-        <v>1820</v>
-      </c>
-      <c r="C670" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D670" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E670" s="1" t="s">
-        <v>1823</v>
       </c>
       <c r="F670" s="1" t="s">
         <v>5</v>
@@ -20515,30 +20497,30 @@
     </row>
     <row r="671" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A671" s="1" t="s">
+        <v>1823</v>
+      </c>
+      <c r="B671" s="1" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C671" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D671" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E671" s="1" t="s">
         <v>1824</v>
       </c>
-      <c r="B671" s="1" t="s">
-        <v>1825</v>
-      </c>
-      <c r="C671" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D671" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E671" s="1" t="s">
-        <v>1826</v>
-      </c>
       <c r="F671" s="1" t="s">
-        <v>67</v>
+        <v>5</v>
       </c>
     </row>
     <row r="672" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A672" s="1" t="s">
-        <v>1827</v>
+        <v>1825</v>
       </c>
       <c r="B672" s="1" t="s">
-        <v>1092</v>
+        <v>1072</v>
       </c>
       <c r="C672" s="1" t="s">
         <v>3</v>
@@ -20547,7 +20529,7 @@
         <v>4</v>
       </c>
       <c r="E672" s="1" t="s">
-        <v>1828</v>
+        <v>1826</v>
       </c>
       <c r="F672" s="1" t="s">
         <v>5</v>
@@ -20555,10 +20537,10 @@
     </row>
     <row r="673" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A673" s="1" t="s">
-        <v>1829</v>
+        <v>1827</v>
       </c>
       <c r="B673" s="1" t="s">
-        <v>1085</v>
+        <v>1066</v>
       </c>
       <c r="C673" s="1" t="s">
         <v>3</v>
@@ -20567,7 +20549,7 @@
         <v>4</v>
       </c>
       <c r="E673" s="1" t="s">
-        <v>1830</v>
+        <v>1828</v>
       </c>
       <c r="F673" s="1" t="s">
         <v>5</v>
@@ -20575,10 +20557,10 @@
     </row>
     <row r="674" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A674" s="1" t="s">
-        <v>1831</v>
+        <v>1829</v>
       </c>
       <c r="B674" s="1" t="s">
-        <v>1078</v>
+        <v>1069</v>
       </c>
       <c r="C674" s="1" t="s">
         <v>3</v>
@@ -20587,7 +20569,7 @@
         <v>4</v>
       </c>
       <c r="E674" s="1" t="s">
-        <v>1832</v>
+        <v>1830</v>
       </c>
       <c r="F674" s="1" t="s">
         <v>5</v>
@@ -20595,10 +20577,10 @@
     </row>
     <row r="675" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A675" s="1" t="s">
-        <v>1833</v>
+        <v>18</v>
       </c>
       <c r="B675" s="1" t="s">
-        <v>1072</v>
+        <v>19</v>
       </c>
       <c r="C675" s="1" t="s">
         <v>3</v>
@@ -20607,7 +20589,7 @@
         <v>4</v>
       </c>
       <c r="E675" s="1" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="F675" s="1" t="s">
         <v>5</v>
@@ -20615,10 +20597,10 @@
     </row>
     <row r="676" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A676" s="1" t="s">
-        <v>1835</v>
+        <v>15</v>
       </c>
       <c r="B676" s="1" t="s">
-        <v>1075</v>
+        <v>16</v>
       </c>
       <c r="C676" s="1" t="s">
         <v>3</v>
@@ -20627,7 +20609,7 @@
         <v>4</v>
       </c>
       <c r="E676" s="1" t="s">
-        <v>1836</v>
+        <v>1832</v>
       </c>
       <c r="F676" s="1" t="s">
         <v>5</v>
@@ -20635,10 +20617,10 @@
     </row>
     <row r="677" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A677" s="1" t="s">
-        <v>18</v>
+        <v>1833</v>
       </c>
       <c r="B677" s="1" t="s">
-        <v>19</v>
+        <v>1834</v>
       </c>
       <c r="C677" s="1" t="s">
         <v>3</v>
@@ -20647,7 +20629,7 @@
         <v>4</v>
       </c>
       <c r="E677" s="1" t="s">
-        <v>1837</v>
+        <v>1835</v>
       </c>
       <c r="F677" s="1" t="s">
         <v>5</v>
@@ -20655,10 +20637,10 @@
     </row>
     <row r="678" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A678" s="1" t="s">
-        <v>15</v>
+        <v>1836</v>
       </c>
       <c r="B678" s="1" t="s">
-        <v>16</v>
+        <v>1837</v>
       </c>
       <c r="C678" s="1" t="s">
         <v>3</v>
@@ -21018,16 +21000,16 @@
         <v>1890</v>
       </c>
       <c r="B696" s="1" t="s">
+        <v>1864</v>
+      </c>
+      <c r="C696" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D696" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E696" s="1" t="s">
         <v>1891</v>
-      </c>
-      <c r="C696" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D696" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E696" s="1" t="s">
-        <v>1892</v>
       </c>
       <c r="F696" s="1" t="s">
         <v>5</v>
@@ -21035,19 +21017,19 @@
     </row>
     <row r="697" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A697" s="1" t="s">
+        <v>1892</v>
+      </c>
+      <c r="B697" s="1" t="s">
+        <v>1867</v>
+      </c>
+      <c r="C697" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D697" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E697" s="1" t="s">
         <v>1893</v>
-      </c>
-      <c r="B697" s="1" t="s">
-        <v>1894</v>
-      </c>
-      <c r="C697" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D697" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E697" s="1" t="s">
-        <v>1895</v>
       </c>
       <c r="F697" s="1" t="s">
         <v>5</v>
@@ -21055,7 +21037,7 @@
     </row>
     <row r="698" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A698" s="1" t="s">
-        <v>1896</v>
+        <v>1894</v>
       </c>
       <c r="B698" s="1" t="s">
         <v>1870</v>
@@ -21067,7 +21049,7 @@
         <v>4</v>
       </c>
       <c r="E698" s="1" t="s">
-        <v>1897</v>
+        <v>1895</v>
       </c>
       <c r="F698" s="1" t="s">
         <v>5</v>
@@ -21075,7 +21057,7 @@
     </row>
     <row r="699" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A699" s="1" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="B699" s="1" t="s">
         <v>1873</v>
@@ -21087,7 +21069,7 @@
         <v>4</v>
       </c>
       <c r="E699" s="1" t="s">
-        <v>1899</v>
+        <v>1897</v>
       </c>
       <c r="F699" s="1" t="s">
         <v>5</v>
@@ -21095,7 +21077,7 @@
     </row>
     <row r="700" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A700" s="1" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
       <c r="B700" s="1" t="s">
         <v>1876</v>
@@ -21107,7 +21089,7 @@
         <v>4</v>
       </c>
       <c r="E700" s="1" t="s">
-        <v>1901</v>
+        <v>1899</v>
       </c>
       <c r="F700" s="1" t="s">
         <v>5</v>
@@ -21115,7 +21097,7 @@
     </row>
     <row r="701" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A701" s="1" t="s">
-        <v>1902</v>
+        <v>1900</v>
       </c>
       <c r="B701" s="1" t="s">
         <v>1879</v>
@@ -21127,7 +21109,7 @@
         <v>4</v>
       </c>
       <c r="E701" s="1" t="s">
-        <v>1903</v>
+        <v>1901</v>
       </c>
       <c r="F701" s="1" t="s">
         <v>5</v>
@@ -21135,7 +21117,7 @@
     </row>
     <row r="702" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A702" s="1" t="s">
-        <v>1904</v>
+        <v>1902</v>
       </c>
       <c r="B702" s="1" t="s">
         <v>1882</v>
@@ -21147,7 +21129,7 @@
         <v>4</v>
       </c>
       <c r="E702" s="1" t="s">
-        <v>1905</v>
+        <v>1903</v>
       </c>
       <c r="F702" s="1" t="s">
         <v>5</v>
@@ -21155,7 +21137,7 @@
     </row>
     <row r="703" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A703" s="1" t="s">
-        <v>1906</v>
+        <v>1904</v>
       </c>
       <c r="B703" s="1" t="s">
         <v>1885</v>
@@ -21167,7 +21149,7 @@
         <v>4</v>
       </c>
       <c r="E703" s="1" t="s">
-        <v>1907</v>
+        <v>1905</v>
       </c>
       <c r="F703" s="1" t="s">
         <v>5</v>
@@ -21175,7 +21157,7 @@
     </row>
     <row r="704" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A704" s="1" t="s">
-        <v>1908</v>
+        <v>1906</v>
       </c>
       <c r="B704" s="1" t="s">
         <v>1888</v>
@@ -21187,7 +21169,7 @@
         <v>4</v>
       </c>
       <c r="E704" s="1" t="s">
-        <v>1909</v>
+        <v>1907</v>
       </c>
       <c r="F704" s="1" t="s">
         <v>5</v>
@@ -21195,19 +21177,19 @@
     </row>
     <row r="705" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A705" s="1" t="s">
+        <v>1908</v>
+      </c>
+      <c r="B705" s="1" t="s">
+        <v>1909</v>
+      </c>
+      <c r="C705" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D705" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E705" s="1" t="s">
         <v>1910</v>
-      </c>
-      <c r="B705" s="1" t="s">
-        <v>1891</v>
-      </c>
-      <c r="C705" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D705" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E705" s="1" t="s">
-        <v>1911</v>
       </c>
       <c r="F705" s="1" t="s">
         <v>5</v>
@@ -21215,10 +21197,10 @@
     </row>
     <row r="706" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A706" s="1" t="s">
+        <v>1911</v>
+      </c>
+      <c r="B706" s="1" t="s">
         <v>1912</v>
-      </c>
-      <c r="B706" s="1" t="s">
-        <v>1894</v>
       </c>
       <c r="C706" s="1" t="s">
         <v>3</v>
@@ -21258,16 +21240,16 @@
         <v>1917</v>
       </c>
       <c r="B708" s="1" t="s">
+        <v>1915</v>
+      </c>
+      <c r="C708" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D708" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E708" s="1" t="s">
         <v>1918</v>
-      </c>
-      <c r="C708" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D708" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E708" s="1" t="s">
-        <v>1919</v>
       </c>
       <c r="F708" s="1" t="s">
         <v>5</v>
@@ -21275,19 +21257,19 @@
     </row>
     <row r="709" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A709" s="1" t="s">
+        <v>1919</v>
+      </c>
+      <c r="B709" s="1" t="s">
         <v>1920</v>
       </c>
-      <c r="B709" s="1" t="s">
+      <c r="C709" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D709" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E709" s="1" t="s">
         <v>1921</v>
-      </c>
-      <c r="C709" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D709" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E709" s="1" t="s">
-        <v>1922</v>
       </c>
       <c r="F709" s="1" t="s">
         <v>5</v>
@@ -21295,10 +21277,10 @@
     </row>
     <row r="710" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A710" s="1" t="s">
+        <v>1922</v>
+      </c>
+      <c r="B710" s="1" t="s">
         <v>1923</v>
-      </c>
-      <c r="B710" s="1" t="s">
-        <v>1921</v>
       </c>
       <c r="C710" s="1" t="s">
         <v>3</v>
@@ -21338,16 +21320,16 @@
         <v>1928</v>
       </c>
       <c r="B712" s="1" t="s">
+        <v>1909</v>
+      </c>
+      <c r="C712" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D712" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E712" s="1" t="s">
         <v>1929</v>
-      </c>
-      <c r="C712" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D712" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E712" s="1" t="s">
-        <v>1930</v>
       </c>
       <c r="F712" s="1" t="s">
         <v>5</v>
@@ -21355,19 +21337,19 @@
     </row>
     <row r="713" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A713" s="1" t="s">
+        <v>1930</v>
+      </c>
+      <c r="B713" s="1" t="s">
+        <v>1912</v>
+      </c>
+      <c r="C713" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D713" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E713" s="1" t="s">
         <v>1931</v>
-      </c>
-      <c r="B713" s="1" t="s">
-        <v>1932</v>
-      </c>
-      <c r="C713" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D713" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E713" s="1" t="s">
-        <v>1933</v>
       </c>
       <c r="F713" s="1" t="s">
         <v>5</v>
@@ -21375,19 +21357,19 @@
     </row>
     <row r="714" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A714" s="1" t="s">
+        <v>1932</v>
+      </c>
+      <c r="B714" s="1" t="s">
+        <v>1933</v>
+      </c>
+      <c r="C714" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D714" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E714" s="1" t="s">
         <v>1934</v>
-      </c>
-      <c r="B714" s="1" t="s">
-        <v>1915</v>
-      </c>
-      <c r="C714" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D714" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E714" s="1" t="s">
-        <v>1935</v>
       </c>
       <c r="F714" s="1" t="s">
         <v>5</v>
@@ -21395,19 +21377,19 @@
     </row>
     <row r="715" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A715" s="1" t="s">
+        <v>1935</v>
+      </c>
+      <c r="B715" s="1" t="s">
+        <v>1915</v>
+      </c>
+      <c r="C715" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D715" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E715" s="1" t="s">
         <v>1936</v>
-      </c>
-      <c r="B715" s="1" t="s">
-        <v>1918</v>
-      </c>
-      <c r="C715" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D715" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E715" s="1" t="s">
-        <v>1937</v>
       </c>
       <c r="F715" s="1" t="s">
         <v>5</v>
@@ -21415,19 +21397,19 @@
     </row>
     <row r="716" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A716" s="1" t="s">
+        <v>1937</v>
+      </c>
+      <c r="B716" s="1" t="s">
         <v>1938</v>
       </c>
-      <c r="B716" s="1" t="s">
+      <c r="C716" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D716" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E716" s="1" t="s">
         <v>1939</v>
-      </c>
-      <c r="C716" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D716" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E716" s="1" t="s">
-        <v>1940</v>
       </c>
       <c r="F716" s="1" t="s">
         <v>5</v>
@@ -21435,19 +21417,19 @@
     </row>
     <row r="717" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A717" s="1" t="s">
+        <v>1940</v>
+      </c>
+      <c r="B717" s="1" t="s">
+        <v>1926</v>
+      </c>
+      <c r="C717" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D717" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E717" s="1" t="s">
         <v>1941</v>
-      </c>
-      <c r="B717" s="1" t="s">
-        <v>1921</v>
-      </c>
-      <c r="C717" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D717" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E717" s="1" t="s">
-        <v>1942</v>
       </c>
       <c r="F717" s="1" t="s">
         <v>5</v>
@@ -21455,19 +21437,19 @@
     </row>
     <row r="718" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A718" s="1" t="s">
+        <v>1942</v>
+      </c>
+      <c r="B718" s="1" t="s">
         <v>1943</v>
       </c>
-      <c r="B718" s="1" t="s">
+      <c r="C718" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D718" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E718" s="1" t="s">
         <v>1944</v>
-      </c>
-      <c r="C718" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D718" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E718" s="1" t="s">
-        <v>1945</v>
       </c>
       <c r="F718" s="1" t="s">
         <v>5</v>
@@ -21475,10 +21457,10 @@
     </row>
     <row r="719" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A719" s="1" t="s">
+        <v>1945</v>
+      </c>
+      <c r="B719" s="1" t="s">
         <v>1946</v>
-      </c>
-      <c r="B719" s="1" t="s">
-        <v>1932</v>
       </c>
       <c r="C719" s="1" t="s">
         <v>3</v>
@@ -21798,16 +21780,16 @@
         <v>1993</v>
       </c>
       <c r="B735" s="1" t="s">
+        <v>1946</v>
+      </c>
+      <c r="C735" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D735" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E735" s="1" t="s">
         <v>1994</v>
-      </c>
-      <c r="C735" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D735" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E735" s="1" t="s">
-        <v>1995</v>
       </c>
       <c r="F735" s="1" t="s">
         <v>5</v>
@@ -21815,19 +21797,19 @@
     </row>
     <row r="736" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A736" s="1" t="s">
+        <v>1995</v>
+      </c>
+      <c r="B736" s="1" t="s">
+        <v>1949</v>
+      </c>
+      <c r="C736" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D736" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E736" s="1" t="s">
         <v>1996</v>
-      </c>
-      <c r="B736" s="1" t="s">
-        <v>1997</v>
-      </c>
-      <c r="C736" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D736" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E736" s="1" t="s">
-        <v>1998</v>
       </c>
       <c r="F736" s="1" t="s">
         <v>5</v>
@@ -21835,10 +21817,10 @@
     </row>
     <row r="737" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A737" s="1" t="s">
-        <v>1999</v>
+        <v>1997</v>
       </c>
       <c r="B737" s="1" t="s">
-        <v>1952</v>
+        <v>1955</v>
       </c>
       <c r="C737" s="1" t="s">
         <v>3</v>
@@ -21847,7 +21829,7 @@
         <v>4</v>
       </c>
       <c r="E737" s="1" t="s">
-        <v>2000</v>
+        <v>1998</v>
       </c>
       <c r="F737" s="1" t="s">
         <v>5</v>
@@ -21855,19 +21837,19 @@
     </row>
     <row r="738" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A738" s="1" t="s">
+        <v>1999</v>
+      </c>
+      <c r="B738" s="1" t="s">
+        <v>2000</v>
+      </c>
+      <c r="C738" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D738" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E738" s="1" t="s">
         <v>2001</v>
-      </c>
-      <c r="B738" s="1" t="s">
-        <v>1955</v>
-      </c>
-      <c r="C738" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D738" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E738" s="1" t="s">
-        <v>2002</v>
       </c>
       <c r="F738" s="1" t="s">
         <v>5</v>
@@ -21875,10 +21857,10 @@
     </row>
     <row r="739" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A739" s="1" t="s">
+        <v>2002</v>
+      </c>
+      <c r="B739" s="1" t="s">
         <v>2003</v>
-      </c>
-      <c r="B739" s="1" t="s">
-        <v>1961</v>
       </c>
       <c r="C739" s="1" t="s">
         <v>3</v>
@@ -21938,16 +21920,16 @@
         <v>2011</v>
       </c>
       <c r="B742" s="1" t="s">
+        <v>1970</v>
+      </c>
+      <c r="C742" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D742" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E742" s="1" t="s">
         <v>2012</v>
-      </c>
-      <c r="C742" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D742" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E742" s="1" t="s">
-        <v>2013</v>
       </c>
       <c r="F742" s="1" t="s">
         <v>5</v>
@@ -21955,19 +21937,19 @@
     </row>
     <row r="743" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A743" s="1" t="s">
+        <v>2013</v>
+      </c>
+      <c r="B743" s="1" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C743" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D743" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E743" s="1" t="s">
         <v>2014</v>
-      </c>
-      <c r="B743" s="1" t="s">
-        <v>2015</v>
-      </c>
-      <c r="C743" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D743" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E743" s="1" t="s">
-        <v>2016</v>
       </c>
       <c r="F743" s="1" t="s">
         <v>5</v>
@@ -21975,7 +21957,7 @@
     </row>
     <row r="744" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A744" s="1" t="s">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="B744" s="1" t="s">
         <v>1976</v>
@@ -21987,7 +21969,7 @@
         <v>4</v>
       </c>
       <c r="E744" s="1" t="s">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="F744" s="1" t="s">
         <v>5</v>
@@ -21995,7 +21977,7 @@
     </row>
     <row r="745" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A745" s="1" t="s">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="B745" s="1" t="s">
         <v>1979</v>
@@ -22007,7 +21989,7 @@
         <v>4</v>
       </c>
       <c r="E745" s="1" t="s">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="F745" s="1" t="s">
         <v>5</v>
@@ -22015,19 +21997,19 @@
     </row>
     <row r="746" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A746" s="1" t="s">
+        <v>2019</v>
+      </c>
+      <c r="B746" s="1" t="s">
+        <v>2020</v>
+      </c>
+      <c r="C746" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D746" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E746" s="1" t="s">
         <v>2021</v>
-      </c>
-      <c r="B746" s="1" t="s">
-        <v>1982</v>
-      </c>
-      <c r="C746" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D746" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E746" s="1" t="s">
-        <v>2022</v>
       </c>
       <c r="F746" s="1" t="s">
         <v>5</v>
@@ -22035,10 +22017,10 @@
     </row>
     <row r="747" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A747" s="1" t="s">
+        <v>2022</v>
+      </c>
+      <c r="B747" s="1" t="s">
         <v>2023</v>
-      </c>
-      <c r="B747" s="1" t="s">
-        <v>1985</v>
       </c>
       <c r="C747" s="1" t="s">
         <v>3</v>
@@ -22378,16 +22360,16 @@
         <v>2073</v>
       </c>
       <c r="B764" s="1" t="s">
+        <v>2056</v>
+      </c>
+      <c r="C764" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D764" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E764" s="1" t="s">
         <v>2074</v>
-      </c>
-      <c r="C764" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D764" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E764" s="1" t="s">
-        <v>2075</v>
       </c>
       <c r="F764" s="1" t="s">
         <v>5</v>
@@ -22395,19 +22377,19 @@
     </row>
     <row r="765" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A765" s="1" t="s">
+        <v>2075</v>
+      </c>
+      <c r="B765" s="1" t="s">
         <v>2076</v>
       </c>
-      <c r="B765" s="1" t="s">
+      <c r="C765" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D765" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E765" s="1" t="s">
         <v>2077</v>
-      </c>
-      <c r="C765" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D765" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E765" s="1" t="s">
-        <v>2078</v>
       </c>
       <c r="F765" s="1" t="s">
         <v>5</v>
@@ -22415,10 +22397,10 @@
     </row>
     <row r="766" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A766" s="1" t="s">
+        <v>2078</v>
+      </c>
+      <c r="B766" s="1" t="s">
         <v>2079</v>
-      </c>
-      <c r="B766" s="1" t="s">
-        <v>2062</v>
       </c>
       <c r="C766" s="1" t="s">
         <v>3</v>
@@ -22458,16 +22440,16 @@
         <v>2084</v>
       </c>
       <c r="B768" s="1" t="s">
+        <v>1600</v>
+      </c>
+      <c r="C768" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D768" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E768" s="1" t="s">
         <v>2085</v>
-      </c>
-      <c r="C768" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D768" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E768" s="1" t="s">
-        <v>2086</v>
       </c>
       <c r="F768" s="1" t="s">
         <v>5</v>
@@ -22475,19 +22457,19 @@
     </row>
     <row r="769" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A769" s="1" t="s">
+        <v>2086</v>
+      </c>
+      <c r="B769" s="1" t="s">
         <v>2087</v>
       </c>
-      <c r="B769" s="1" t="s">
+      <c r="C769" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D769" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E769" s="1" t="s">
         <v>2088</v>
-      </c>
-      <c r="C769" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D769" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E769" s="1" t="s">
-        <v>2089</v>
       </c>
       <c r="F769" s="1" t="s">
         <v>5</v>
@@ -22495,10 +22477,10 @@
     </row>
     <row r="770" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A770" s="1" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B770" s="1" t="s">
         <v>2090</v>
-      </c>
-      <c r="B770" s="1" t="s">
-        <v>1606</v>
       </c>
       <c r="C770" s="1" t="s">
         <v>3</v>
@@ -22518,16 +22500,16 @@
         <v>2092</v>
       </c>
       <c r="B771" s="1" t="s">
+        <v>2079</v>
+      </c>
+      <c r="C771" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D771" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E771" s="1" t="s">
         <v>2093</v>
-      </c>
-      <c r="C771" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D771" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E771" s="1" t="s">
-        <v>2094</v>
       </c>
       <c r="F771" s="1" t="s">
         <v>5</v>
@@ -22535,19 +22517,19 @@
     </row>
     <row r="772" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A772" s="1" t="s">
+        <v>2094</v>
+      </c>
+      <c r="B772" s="1" t="s">
+        <v>2082</v>
+      </c>
+      <c r="C772" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D772" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E772" s="1" t="s">
         <v>2095</v>
-      </c>
-      <c r="B772" s="1" t="s">
-        <v>2096</v>
-      </c>
-      <c r="C772" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D772" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E772" s="1" t="s">
-        <v>2097</v>
       </c>
       <c r="F772" s="1" t="s">
         <v>5</v>
@@ -22555,10 +22537,10 @@
     </row>
     <row r="773" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A773" s="1" t="s">
-        <v>2098</v>
+        <v>2096</v>
       </c>
       <c r="B773" s="1" t="s">
-        <v>2085</v>
+        <v>1600</v>
       </c>
       <c r="C773" s="1" t="s">
         <v>3</v>
@@ -22567,7 +22549,7 @@
         <v>4</v>
       </c>
       <c r="E773" s="1" t="s">
-        <v>2099</v>
+        <v>2097</v>
       </c>
       <c r="F773" s="1" t="s">
         <v>5</v>
@@ -22575,10 +22557,10 @@
     </row>
     <row r="774" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A774" s="1" t="s">
-        <v>2100</v>
+        <v>2098</v>
       </c>
       <c r="B774" s="1" t="s">
-        <v>2088</v>
+        <v>2090</v>
       </c>
       <c r="C774" s="1" t="s">
         <v>3</v>
@@ -22587,7 +22569,7 @@
         <v>4</v>
       </c>
       <c r="E774" s="1" t="s">
-        <v>2101</v>
+        <v>2099</v>
       </c>
       <c r="F774" s="1" t="s">
         <v>5</v>
@@ -22595,10 +22577,10 @@
     </row>
     <row r="775" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A775" s="1" t="s">
-        <v>2102</v>
+        <v>2100</v>
       </c>
       <c r="B775" s="1" t="s">
-        <v>1606</v>
+        <v>2087</v>
       </c>
       <c r="C775" s="1" t="s">
         <v>3</v>
@@ -22607,7 +22589,7 @@
         <v>4</v>
       </c>
       <c r="E775" s="1" t="s">
-        <v>2103</v>
+        <v>2101</v>
       </c>
       <c r="F775" s="1" t="s">
         <v>5</v>
@@ -22615,10 +22597,10 @@
     </row>
     <row r="776" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A776" s="1" t="s">
-        <v>2104</v>
+        <v>2102</v>
       </c>
       <c r="B776" s="1" t="s">
-        <v>2096</v>
+        <v>1491</v>
       </c>
       <c r="C776" s="1" t="s">
         <v>3</v>
@@ -22627,7 +22609,7 @@
         <v>4</v>
       </c>
       <c r="E776" s="1" t="s">
-        <v>2105</v>
+        <v>2103</v>
       </c>
       <c r="F776" s="1" t="s">
         <v>5</v>
@@ -22635,19 +22617,19 @@
     </row>
     <row r="777" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A777" s="1" t="s">
+        <v>2104</v>
+      </c>
+      <c r="B777" s="1" t="s">
+        <v>2105</v>
+      </c>
+      <c r="C777" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D777" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E777" s="1" t="s">
         <v>2106</v>
-      </c>
-      <c r="B777" s="1" t="s">
-        <v>2093</v>
-      </c>
-      <c r="C777" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D777" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E777" s="1" t="s">
-        <v>2107</v>
       </c>
       <c r="F777" s="1" t="s">
         <v>5</v>
@@ -22655,19 +22637,19 @@
     </row>
     <row r="778" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A778" s="1" t="s">
+        <v>2107</v>
+      </c>
+      <c r="B778" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C778" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D778" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E778" s="1" t="s">
         <v>2108</v>
-      </c>
-      <c r="B778" s="1" t="s">
-        <v>1497</v>
-      </c>
-      <c r="C778" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D778" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E778" s="1" t="s">
-        <v>2109</v>
       </c>
       <c r="F778" s="1" t="s">
         <v>5</v>
@@ -22675,19 +22657,19 @@
     </row>
     <row r="779" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A779" s="1" t="s">
+        <v>2109</v>
+      </c>
+      <c r="B779" s="1" t="s">
+        <v>2105</v>
+      </c>
+      <c r="C779" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D779" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E779" s="1" t="s">
         <v>2110</v>
-      </c>
-      <c r="B779" s="1" t="s">
-        <v>2111</v>
-      </c>
-      <c r="C779" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D779" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E779" s="1" t="s">
-        <v>2112</v>
       </c>
       <c r="F779" s="1" t="s">
         <v>5</v>
@@ -22695,7 +22677,7 @@
     </row>
     <row r="780" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A780" s="1" t="s">
-        <v>2113</v>
+        <v>2111</v>
       </c>
       <c r="B780" s="1" t="s">
         <v>139</v>
@@ -22707,7 +22689,7 @@
         <v>4</v>
       </c>
       <c r="E780" s="1" t="s">
-        <v>2114</v>
+        <v>2112</v>
       </c>
       <c r="F780" s="1" t="s">
         <v>5</v>
@@ -22715,19 +22697,19 @@
     </row>
     <row r="781" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A781" s="1" t="s">
+        <v>2113</v>
+      </c>
+      <c r="B781" s="1" t="s">
+        <v>2114</v>
+      </c>
+      <c r="C781" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D781" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E781" s="1" t="s">
         <v>2115</v>
-      </c>
-      <c r="B781" s="1" t="s">
-        <v>2111</v>
-      </c>
-      <c r="C781" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D781" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E781" s="1" t="s">
-        <v>2116</v>
       </c>
       <c r="F781" s="1" t="s">
         <v>5</v>
@@ -22735,19 +22717,19 @@
     </row>
     <row r="782" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A782" s="1" t="s">
+        <v>2116</v>
+      </c>
+      <c r="B782" s="1" t="s">
+        <v>2114</v>
+      </c>
+      <c r="C782" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D782" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E782" s="1" t="s">
         <v>2117</v>
-      </c>
-      <c r="B782" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C782" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D782" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E782" s="1" t="s">
-        <v>2118</v>
       </c>
       <c r="F782" s="1" t="s">
         <v>5</v>
@@ -22755,30 +22737,30 @@
     </row>
     <row r="783" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A783" s="1" t="s">
+        <v>2118</v>
+      </c>
+      <c r="B783" s="1" t="s">
         <v>2119</v>
       </c>
-      <c r="B783" s="1" t="s">
+      <c r="C783" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D783" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E783" s="1" t="s">
         <v>2120</v>
       </c>
-      <c r="C783" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D783" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E783" s="1" t="s">
+      <c r="F783" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="784" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A784" s="1" t="s">
         <v>2121</v>
       </c>
-      <c r="F783" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="784" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A784" s="1" t="s">
+      <c r="B784" s="1" t="s">
         <v>2122</v>
-      </c>
-      <c r="B784" s="1" t="s">
-        <v>2120</v>
       </c>
       <c r="C784" s="1" t="s">
         <v>3</v>
@@ -22788,9 +22770,6 @@
       </c>
       <c r="E784" s="1" t="s">
         <v>2123</v>
-      </c>
-      <c r="F784" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="785" spans="1:6" x14ac:dyDescent="0.25">
@@ -22850,7 +22829,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="788" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A788" s="1" t="s">
         <v>2133</v>
       </c>
@@ -22865,6 +22844,9 @@
       </c>
       <c r="E788" s="1" t="s">
         <v>2135</v>
+      </c>
+      <c r="F788" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="789" spans="1:6" x14ac:dyDescent="0.25">
@@ -22892,16 +22874,16 @@
         <v>2139</v>
       </c>
       <c r="B790" s="1" t="s">
+        <v>2131</v>
+      </c>
+      <c r="C790" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D790" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E790" s="1" t="s">
         <v>2140</v>
-      </c>
-      <c r="C790" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D790" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E790" s="1" t="s">
-        <v>2141</v>
       </c>
       <c r="F790" s="1" t="s">
         <v>5</v>
@@ -22909,19 +22891,19 @@
     </row>
     <row r="791" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A791" s="1" t="s">
+        <v>2141</v>
+      </c>
+      <c r="B791" s="1" t="s">
+        <v>2134</v>
+      </c>
+      <c r="C791" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D791" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E791" s="1" t="s">
         <v>2142</v>
-      </c>
-      <c r="B791" s="1" t="s">
-        <v>2143</v>
-      </c>
-      <c r="C791" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D791" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E791" s="1" t="s">
-        <v>2144</v>
       </c>
       <c r="F791" s="1" t="s">
         <v>5</v>
@@ -22929,7 +22911,7 @@
     </row>
     <row r="792" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A792" s="1" t="s">
-        <v>2145</v>
+        <v>2143</v>
       </c>
       <c r="B792" s="1" t="s">
         <v>2137</v>
@@ -22941,7 +22923,7 @@
         <v>4</v>
       </c>
       <c r="E792" s="1" t="s">
-        <v>2146</v>
+        <v>2144</v>
       </c>
       <c r="F792" s="1" t="s">
         <v>5</v>
@@ -22949,30 +22931,30 @@
     </row>
     <row r="793" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A793" s="1" t="s">
+        <v>2145</v>
+      </c>
+      <c r="B793" s="1" t="s">
+        <v>2146</v>
+      </c>
+      <c r="C793" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D793" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E793" s="1" t="s">
         <v>2147</v>
       </c>
-      <c r="B793" s="1" t="s">
-        <v>2140</v>
-      </c>
-      <c r="C793" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D793" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E793" s="1" t="s">
-        <v>2148</v>
-      </c>
       <c r="F793" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="794" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A794" s="1" t="s">
+        <v>2148</v>
+      </c>
+      <c r="B794" s="1" t="s">
         <v>2149</v>
-      </c>
-      <c r="B794" s="1" t="s">
-        <v>2143</v>
       </c>
       <c r="C794" s="1" t="s">
         <v>3</v>
@@ -22984,7 +22966,7 @@
         <v>2150</v>
       </c>
       <c r="F794" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="795" spans="1:6" x14ac:dyDescent="0.25">
@@ -23104,7 +23086,7 @@
         <v>2168</v>
       </c>
       <c r="F800" s="1" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="801" spans="1:6" x14ac:dyDescent="0.25">
@@ -23124,7 +23106,7 @@
         <v>2171</v>
       </c>
       <c r="F801" s="1" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="802" spans="1:6" x14ac:dyDescent="0.25">
@@ -23192,16 +23174,16 @@
         <v>2181</v>
       </c>
       <c r="B805" s="1" t="s">
+        <v>2161</v>
+      </c>
+      <c r="C805" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D805" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E805" s="1" t="s">
         <v>2182</v>
-      </c>
-      <c r="C805" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D805" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E805" s="1" t="s">
-        <v>2183</v>
       </c>
       <c r="F805" s="1" t="s">
         <v>5</v>
@@ -23209,19 +23191,19 @@
     </row>
     <row r="806" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A806" s="1" t="s">
+        <v>2183</v>
+      </c>
+      <c r="B806" s="1" t="s">
+        <v>2164</v>
+      </c>
+      <c r="C806" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D806" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E806" s="1" t="s">
         <v>2184</v>
-      </c>
-      <c r="B806" s="1" t="s">
-        <v>2185</v>
-      </c>
-      <c r="C806" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D806" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E806" s="1" t="s">
-        <v>2186</v>
       </c>
       <c r="F806" s="1" t="s">
         <v>5</v>
@@ -23229,22 +23211,22 @@
     </row>
     <row r="807" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A807" s="1" t="s">
+        <v>2185</v>
+      </c>
+      <c r="B807" s="1" t="s">
+        <v>2186</v>
+      </c>
+      <c r="C807" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D807" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E807" s="1" t="s">
         <v>2187</v>
       </c>
-      <c r="B807" s="1" t="s">
-        <v>2167</v>
-      </c>
-      <c r="C807" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D807" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E807" s="1" t="s">
+      <c r="F807" s="1" t="s">
         <v>2188</v>
-      </c>
-      <c r="F807" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="808" spans="1:6" x14ac:dyDescent="0.25">
@@ -23252,7 +23234,7 @@
         <v>2189</v>
       </c>
       <c r="B808" s="1" t="s">
-        <v>2170</v>
+        <v>2190</v>
       </c>
       <c r="C808" s="1" t="s">
         <v>3</v>
@@ -23261,7 +23243,7 @@
         <v>4</v>
       </c>
       <c r="E808" s="1" t="s">
-        <v>2190</v>
+        <v>2191</v>
       </c>
       <c r="F808" s="1" t="s">
         <v>5</v>
@@ -23269,10 +23251,10 @@
     </row>
     <row r="809" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A809" s="1" t="s">
-        <v>2191</v>
+        <v>2192</v>
       </c>
       <c r="B809" s="1" t="s">
-        <v>2192</v>
+        <v>1985</v>
       </c>
       <c r="C809" s="1" t="s">
         <v>3</v>
@@ -23284,24 +23266,24 @@
         <v>2193</v>
       </c>
       <c r="F809" s="1" t="s">
-        <v>2194</v>
+        <v>5</v>
       </c>
     </row>
     <row r="810" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A810" s="1" t="s">
+        <v>2194</v>
+      </c>
+      <c r="B810" s="1" t="s">
+        <v>2041</v>
+      </c>
+      <c r="C810" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D810" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E810" s="1" t="s">
         <v>2195</v>
-      </c>
-      <c r="B810" s="1" t="s">
-        <v>2196</v>
-      </c>
-      <c r="C810" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D810" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E810" s="1" t="s">
-        <v>2197</v>
       </c>
       <c r="F810" s="1" t="s">
         <v>5</v>
@@ -23309,19 +23291,19 @@
     </row>
     <row r="811" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A811" s="1" t="s">
+        <v>2196</v>
+      </c>
+      <c r="B811" s="1" t="s">
+        <v>2197</v>
+      </c>
+      <c r="C811" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D811" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E811" s="1" t="s">
         <v>2198</v>
-      </c>
-      <c r="B811" s="1" t="s">
-        <v>1991</v>
-      </c>
-      <c r="C811" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D811" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E811" s="1" t="s">
-        <v>2199</v>
       </c>
       <c r="F811" s="1" t="s">
         <v>5</v>
@@ -23329,10 +23311,10 @@
     </row>
     <row r="812" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A812" s="1" t="s">
+        <v>2199</v>
+      </c>
+      <c r="B812" s="1" t="s">
         <v>2200</v>
-      </c>
-      <c r="B812" s="1" t="s">
-        <v>2047</v>
       </c>
       <c r="C812" s="1" t="s">
         <v>3</v>
@@ -23407,7 +23389,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="816" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A816" s="1" t="s">
         <v>2211</v>
       </c>
@@ -23423,11 +23405,8 @@
       <c r="E816" s="1" t="s">
         <v>2213</v>
       </c>
-      <c r="F816" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="817" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="817" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A817" s="1" t="s">
         <v>2214</v>
       </c>
@@ -23442,9 +23421,6 @@
       </c>
       <c r="E817" s="1" t="s">
         <v>2216</v>
-      </c>
-      <c r="F817" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="818" spans="1:5" x14ac:dyDescent="0.25">
@@ -23486,38 +23462,38 @@
         <v>2223</v>
       </c>
       <c r="B820" s="1" t="s">
+        <v>2212</v>
+      </c>
+      <c r="C820" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D820" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E820" s="1" t="s">
         <v>2224</v>
-      </c>
-      <c r="C820" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D820" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E820" s="1" t="s">
-        <v>2225</v>
       </c>
     </row>
     <row r="821" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A821" s="1" t="s">
+        <v>2225</v>
+      </c>
+      <c r="B821" s="1" t="s">
+        <v>2215</v>
+      </c>
+      <c r="C821" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D821" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E821" s="1" t="s">
         <v>2226</v>
-      </c>
-      <c r="B821" s="1" t="s">
-        <v>2227</v>
-      </c>
-      <c r="C821" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D821" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E821" s="1" t="s">
-        <v>2228</v>
       </c>
     </row>
     <row r="822" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A822" s="1" t="s">
-        <v>2229</v>
+        <v>2227</v>
       </c>
       <c r="B822" s="1" t="s">
         <v>2218</v>
@@ -23529,12 +23505,12 @@
         <v>4</v>
       </c>
       <c r="E822" s="1" t="s">
-        <v>2230</v>
+        <v>2228</v>
       </c>
     </row>
     <row r="823" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A823" s="1" t="s">
-        <v>2231</v>
+        <v>2229</v>
       </c>
       <c r="B823" s="1" t="s">
         <v>2221</v>
@@ -23546,32 +23522,32 @@
         <v>4</v>
       </c>
       <c r="E823" s="1" t="s">
-        <v>2232</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="824" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A824" s="1" t="s">
+        <v>2231</v>
+      </c>
+      <c r="B824" s="1" t="s">
+        <v>2232</v>
+      </c>
+      <c r="C824" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D824" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E824" s="1" t="s">
         <v>2233</v>
-      </c>
-      <c r="B824" s="1" t="s">
-        <v>2224</v>
-      </c>
-      <c r="C824" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D824" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E824" s="1" t="s">
-        <v>2234</v>
       </c>
     </row>
     <row r="825" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A825" s="1" t="s">
+        <v>2234</v>
+      </c>
+      <c r="B825" s="1" t="s">
         <v>2235</v>
-      </c>
-      <c r="B825" s="1" t="s">
-        <v>2227</v>
       </c>
       <c r="C825" s="1" t="s">
         <v>3</v>
@@ -23583,7 +23559,7 @@
         <v>2236</v>
       </c>
     </row>
-    <row r="826" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A826" s="1" t="s">
         <v>2237</v>
       </c>
@@ -23598,6 +23574,9 @@
       </c>
       <c r="E826" s="1" t="s">
         <v>2239</v>
+      </c>
+      <c r="F826" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="827" spans="1:5" x14ac:dyDescent="0.25">
@@ -23605,41 +23584,38 @@
         <v>2240</v>
       </c>
       <c r="B827" s="1" t="s">
+        <v>2232</v>
+      </c>
+      <c r="C827" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D827" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E827" s="1" t="s">
         <v>2241</v>
       </c>
-      <c r="C827" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D827" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E827" s="1" t="s">
+    </row>
+    <row r="828" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A828" s="1" t="s">
         <v>2242</v>
       </c>
-    </row>
-    <row r="828" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A828" s="1" t="s">
+      <c r="B828" s="1" t="s">
+        <v>2235</v>
+      </c>
+      <c r="C828" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D828" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E828" s="1" t="s">
         <v>2243</v>
-      </c>
-      <c r="B828" s="1" t="s">
-        <v>2244</v>
-      </c>
-      <c r="C828" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D828" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E828" s="1" t="s">
-        <v>2245</v>
-      </c>
-      <c r="F828" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="829" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A829" s="1" t="s">
-        <v>2246</v>
+        <v>2244</v>
       </c>
       <c r="B829" s="1" t="s">
         <v>2238</v>
@@ -23651,32 +23627,35 @@
         <v>4</v>
       </c>
       <c r="E829" s="1" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="830" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A830" s="1" t="s">
+        <v>2246</v>
+      </c>
+      <c r="B830" s="1" t="s">
         <v>2247</v>
       </c>
-    </row>
-    <row r="830" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A830" s="1" t="s">
+      <c r="C830" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D830" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E830" s="1" t="s">
         <v>2248</v>
       </c>
-      <c r="B830" s="1" t="s">
-        <v>2241</v>
-      </c>
-      <c r="C830" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D830" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E830" s="1" t="s">
+      <c r="F830" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="831" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A831" s="1" t="s">
         <v>2249</v>
       </c>
-    </row>
-    <row r="831" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A831" s="1" t="s">
+      <c r="B831" s="1" t="s">
         <v>2250</v>
-      </c>
-      <c r="B831" s="1" t="s">
-        <v>2244</v>
       </c>
       <c r="C831" s="1" t="s">
         <v>3</v>
@@ -23686,6 +23665,9 @@
       </c>
       <c r="E831" s="1" t="s">
         <v>2251</v>
+      </c>
+      <c r="F831" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="832" spans="1:6" x14ac:dyDescent="0.25">
@@ -23853,16 +23835,16 @@
         <v>2276</v>
       </c>
       <c r="B840" s="1" t="s">
+        <v>2262</v>
+      </c>
+      <c r="C840" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D840" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E840" s="1" t="s">
         <v>2277</v>
-      </c>
-      <c r="C840" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D840" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E840" s="1" t="s">
-        <v>2278</v>
       </c>
       <c r="F840" s="1" t="s">
         <v>5</v>
@@ -23870,19 +23852,19 @@
     </row>
     <row r="841" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A841" s="1" t="s">
+        <v>2278</v>
+      </c>
+      <c r="B841" s="1" t="s">
+        <v>2265</v>
+      </c>
+      <c r="C841" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D841" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E841" s="1" t="s">
         <v>2279</v>
-      </c>
-      <c r="B841" s="1" t="s">
-        <v>2280</v>
-      </c>
-      <c r="C841" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D841" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E841" s="1" t="s">
-        <v>2281</v>
       </c>
       <c r="F841" s="1" t="s">
         <v>5</v>
@@ -23890,19 +23872,19 @@
     </row>
     <row r="842" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A842" s="1" t="s">
+        <v>2280</v>
+      </c>
+      <c r="B842" s="1" t="s">
+        <v>2281</v>
+      </c>
+      <c r="C842" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D842" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E842" s="1" t="s">
         <v>2282</v>
-      </c>
-      <c r="B842" s="1" t="s">
-        <v>2268</v>
-      </c>
-      <c r="C842" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D842" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E842" s="1" t="s">
-        <v>2283</v>
       </c>
       <c r="F842" s="1" t="s">
         <v>5</v>
@@ -23910,10 +23892,10 @@
     </row>
     <row r="843" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A843" s="1" t="s">
+        <v>2283</v>
+      </c>
+      <c r="B843" s="1" t="s">
         <v>2284</v>
-      </c>
-      <c r="B843" s="1" t="s">
-        <v>2271</v>
       </c>
       <c r="C843" s="1" t="s">
         <v>3</v>
@@ -23933,16 +23915,16 @@
         <v>2286</v>
       </c>
       <c r="B844" s="1" t="s">
+        <v>2274</v>
+      </c>
+      <c r="C844" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D844" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E844" s="1" t="s">
         <v>2287</v>
-      </c>
-      <c r="C844" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D844" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E844" s="1" t="s">
-        <v>2288</v>
       </c>
       <c r="F844" s="1" t="s">
         <v>5</v>
@@ -23950,19 +23932,19 @@
     </row>
     <row r="845" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A845" s="1" t="s">
+        <v>2288</v>
+      </c>
+      <c r="B845" s="1" t="s">
         <v>2289</v>
       </c>
-      <c r="B845" s="1" t="s">
+      <c r="C845" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D845" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E845" s="1" t="s">
         <v>2290</v>
-      </c>
-      <c r="C845" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D845" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E845" s="1" t="s">
-        <v>2291</v>
       </c>
       <c r="F845" s="1" t="s">
         <v>5</v>
@@ -23970,10 +23952,10 @@
     </row>
     <row r="846" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A846" s="1" t="s">
+        <v>2291</v>
+      </c>
+      <c r="B846" s="1" t="s">
         <v>2292</v>
-      </c>
-      <c r="B846" s="1" t="s">
-        <v>2280</v>
       </c>
       <c r="C846" s="1" t="s">
         <v>3</v>
@@ -24008,7 +23990,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="848" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A848" s="1" t="s">
         <v>2297</v>
       </c>
@@ -24024,11 +24006,8 @@
       <c r="E848" s="1" t="s">
         <v>2299</v>
       </c>
-      <c r="F848" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="849" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="849" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A849" s="1" t="s">
         <v>2300</v>
       </c>
@@ -24043,9 +24022,6 @@
       </c>
       <c r="E849" s="1" t="s">
         <v>2302</v>
-      </c>
-      <c r="F849" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="850" spans="1:5" x14ac:dyDescent="0.25">
@@ -24065,7 +24041,7 @@
         <v>2305</v>
       </c>
     </row>
-    <row r="851" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A851" s="1" t="s">
         <v>2306</v>
       </c>
@@ -24081,8 +24057,11 @@
       <c r="E851" s="1" t="s">
         <v>2308</v>
       </c>
-    </row>
-    <row r="852" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F851" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="852" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A852" s="1" t="s">
         <v>2309</v>
       </c>
@@ -24097,6 +24076,9 @@
       </c>
       <c r="E852" s="1" t="s">
         <v>2311</v>
+      </c>
+      <c r="F852" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="853" spans="1:6" x14ac:dyDescent="0.25">
@@ -24224,16 +24206,16 @@
         <v>2330</v>
       </c>
       <c r="B859" s="1" t="s">
+        <v>2307</v>
+      </c>
+      <c r="C859" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D859" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E859" s="1" t="s">
         <v>2331</v>
-      </c>
-      <c r="C859" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D859" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E859" s="1" t="s">
-        <v>2332</v>
       </c>
       <c r="F859" s="1" t="s">
         <v>5</v>
@@ -24241,19 +24223,19 @@
     </row>
     <row r="860" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A860" s="1" t="s">
+        <v>2332</v>
+      </c>
+      <c r="B860" s="1" t="s">
+        <v>2310</v>
+      </c>
+      <c r="C860" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D860" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E860" s="1" t="s">
         <v>2333</v>
-      </c>
-      <c r="B860" s="1" t="s">
-        <v>2334</v>
-      </c>
-      <c r="C860" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D860" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E860" s="1" t="s">
-        <v>2335</v>
       </c>
       <c r="F860" s="1" t="s">
         <v>5</v>
@@ -24261,7 +24243,7 @@
     </row>
     <row r="861" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A861" s="1" t="s">
-        <v>2336</v>
+        <v>2334</v>
       </c>
       <c r="B861" s="1" t="s">
         <v>2313</v>
@@ -24273,7 +24255,7 @@
         <v>4</v>
       </c>
       <c r="E861" s="1" t="s">
-        <v>2337</v>
+        <v>2335</v>
       </c>
       <c r="F861" s="1" t="s">
         <v>5</v>
@@ -24281,7 +24263,7 @@
     </row>
     <row r="862" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A862" s="1" t="s">
-        <v>2338</v>
+        <v>2336</v>
       </c>
       <c r="B862" s="1" t="s">
         <v>2316</v>
@@ -24293,7 +24275,7 @@
         <v>4</v>
       </c>
       <c r="E862" s="1" t="s">
-        <v>2339</v>
+        <v>2337</v>
       </c>
       <c r="F862" s="1" t="s">
         <v>5</v>
@@ -24301,7 +24283,7 @@
     </row>
     <row r="863" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A863" s="1" t="s">
-        <v>2340</v>
+        <v>2338</v>
       </c>
       <c r="B863" s="1" t="s">
         <v>2319</v>
@@ -24313,7 +24295,7 @@
         <v>4</v>
       </c>
       <c r="E863" s="1" t="s">
-        <v>2341</v>
+        <v>2339</v>
       </c>
       <c r="F863" s="1" t="s">
         <v>5</v>
@@ -24321,7 +24303,7 @@
     </row>
     <row r="864" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A864" s="1" t="s">
-        <v>2342</v>
+        <v>2340</v>
       </c>
       <c r="B864" s="1" t="s">
         <v>2322</v>
@@ -24333,7 +24315,7 @@
         <v>4</v>
       </c>
       <c r="E864" s="1" t="s">
-        <v>2343</v>
+        <v>2341</v>
       </c>
       <c r="F864" s="1" t="s">
         <v>5</v>
@@ -24341,19 +24323,19 @@
     </row>
     <row r="865" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A865" s="1" t="s">
+        <v>2342</v>
+      </c>
+      <c r="B865" s="1" t="s">
+        <v>2343</v>
+      </c>
+      <c r="C865" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D865" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E865" s="1" t="s">
         <v>2344</v>
-      </c>
-      <c r="B865" s="1" t="s">
-        <v>2325</v>
-      </c>
-      <c r="C865" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D865" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E865" s="1" t="s">
-        <v>2345</v>
       </c>
       <c r="F865" s="1" t="s">
         <v>5</v>
@@ -24361,7 +24343,7 @@
     </row>
     <row r="866" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A866" s="1" t="s">
-        <v>2346</v>
+        <v>2345</v>
       </c>
       <c r="B866" s="1" t="s">
         <v>2328</v>
@@ -24373,38 +24355,35 @@
         <v>4</v>
       </c>
       <c r="E866" s="1" t="s">
+        <v>2346</v>
+      </c>
+      <c r="F866" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="867" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A867" s="1" t="s">
         <v>2347</v>
       </c>
-      <c r="F866" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="867" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A867" s="1" t="s">
+      <c r="B867" s="1" t="s">
         <v>2348</v>
       </c>
-      <c r="B867" s="1" t="s">
+      <c r="C867" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D867" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E867" s="1" t="s">
         <v>2349</v>
       </c>
-      <c r="C867" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D867" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E867" s="1" t="s">
+    </row>
+    <row r="868" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A868" s="1" t="s">
         <v>2350</v>
       </c>
-      <c r="F867" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="868" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A868" s="1" t="s">
+      <c r="B868" s="1" t="s">
         <v>2351</v>
-      </c>
-      <c r="B868" s="1" t="s">
-        <v>2334</v>
       </c>
       <c r="C868" s="1" t="s">
         <v>3</v>
@@ -24414,9 +24393,6 @@
       </c>
       <c r="E868" s="1" t="s">
         <v>2352</v>
-      </c>
-      <c r="F868" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="869" spans="1:5" x14ac:dyDescent="0.25">
@@ -24453,46 +24429,52 @@
         <v>2358</v>
       </c>
     </row>
-    <row r="871" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A871" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B871" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C871" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D871" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E871" s="1" t="s">
         <v>2359</v>
       </c>
-      <c r="B871" s="1" t="s">
+      <c r="F871" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="872" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A872" s="1" t="s">
         <v>2360</v>
       </c>
-      <c r="C871" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D871" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E871" s="1" t="s">
+      <c r="B872" s="1" t="s">
         <v>2361</v>
       </c>
-    </row>
-    <row r="872" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A872" s="1" t="s">
+      <c r="C872" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D872" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E872" s="1" t="s">
         <v>2362</v>
       </c>
-      <c r="B872" s="1" t="s">
-        <v>2363</v>
-      </c>
-      <c r="C872" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D872" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E872" s="1" t="s">
-        <v>2364</v>
+      <c r="F872" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="873" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A873" s="1" t="s">
-        <v>21</v>
+        <v>2363</v>
       </c>
       <c r="B873" s="1" t="s">
-        <v>22</v>
+        <v>2364</v>
       </c>
       <c r="C873" s="1" t="s">
         <v>3</v>
@@ -24584,46 +24566,6 @@
         <v>2377</v>
       </c>
       <c r="F877" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="878" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A878" s="1" t="s">
-        <v>2378</v>
-      </c>
-      <c r="B878" s="1" t="s">
-        <v>2379</v>
-      </c>
-      <c r="C878" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D878" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E878" s="1" t="s">
-        <v>2380</v>
-      </c>
-      <c r="F878" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="879" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A879" s="1" t="s">
-        <v>2381</v>
-      </c>
-      <c r="B879" s="1" t="s">
-        <v>2382</v>
-      </c>
-      <c r="C879" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D879" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E879" s="1" t="s">
-        <v>2383</v>
-      </c>
-      <c r="F879" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/E/MKTN.xlsx
+++ b/E/MKTN.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5089" uniqueCount="2378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5089" uniqueCount="2377">
   <si>
     <t/>
   </si>
@@ -3880,7 +3880,7 @@
     <t>20126045</t>
   </si>
   <si>
-    <t>THREE HAPPY 60GB 28H</t>
+    <t>THREE HAPPY 65GB 28H</t>
   </si>
   <si>
     <t>458</t>
@@ -3943,9 +3943,6 @@
     <t>20126075</t>
   </si>
   <si>
-    <t>THREE HAPPY 35GB 28H</t>
-  </si>
-  <si>
     <t>465</t>
   </si>
   <si>
@@ -4519,60 +4516,63 @@
     <t>20131131</t>
   </si>
   <si>
+    <t>INDST FDM 73GB 28HR</t>
+  </si>
+  <si>
+    <t>618</t>
+  </si>
+  <si>
+    <t>20131132</t>
+  </si>
+  <si>
+    <t>INDST FRDM 7GB 28HR</t>
+  </si>
+  <si>
+    <t>619</t>
+  </si>
+  <si>
+    <t>20131133</t>
+  </si>
+  <si>
+    <t>INDST FRDM INET 18GB</t>
+  </si>
+  <si>
+    <t>620</t>
+  </si>
+  <si>
+    <t>20131134</t>
+  </si>
+  <si>
+    <t>INDST FRDM 35GB 28HR</t>
+  </si>
+  <si>
+    <t>621</t>
+  </si>
+  <si>
+    <t>20131136</t>
+  </si>
+  <si>
+    <t>INDST FRDM 75GB 7HR</t>
+  </si>
+  <si>
+    <t>623</t>
+  </si>
+  <si>
+    <t>20131137</t>
+  </si>
+  <si>
+    <t>INDST FDM 150GB 28HR</t>
+  </si>
+  <si>
+    <t>624</t>
+  </si>
+  <si>
+    <t>20131139</t>
+  </si>
+  <si>
     <t>INDST FDM 18GB 34K</t>
   </si>
   <si>
-    <t>618</t>
-  </si>
-  <si>
-    <t>20131132</t>
-  </si>
-  <si>
-    <t>INDST FRDM 7GB 28HR</t>
-  </si>
-  <si>
-    <t>619</t>
-  </si>
-  <si>
-    <t>20131133</t>
-  </si>
-  <si>
-    <t>INDST FRDM INET 18GB</t>
-  </si>
-  <si>
-    <t>620</t>
-  </si>
-  <si>
-    <t>20131134</t>
-  </si>
-  <si>
-    <t>INDST FRDM 35GB 28HR</t>
-  </si>
-  <si>
-    <t>621</t>
-  </si>
-  <si>
-    <t>20131136</t>
-  </si>
-  <si>
-    <t>INDST FRDM 75GB 7HR</t>
-  </si>
-  <si>
-    <t>623</t>
-  </si>
-  <si>
-    <t>20131137</t>
-  </si>
-  <si>
-    <t>INDST FDM 150GB 28HR</t>
-  </si>
-  <si>
-    <t>624</t>
-  </si>
-  <si>
-    <t>20131139</t>
-  </si>
-  <si>
     <t>626</t>
   </si>
   <si>
@@ -5344,7 +5344,7 @@
     <t>20134775</t>
   </si>
   <si>
-    <t>THREE PKT KHUSUS 3GB</t>
+    <t>THREE HAPY 3GB 30HR</t>
   </si>
   <si>
     <t>727</t>
@@ -5923,7 +5923,7 @@
     <t>20137282</t>
   </si>
   <si>
-    <t>THREE HPY 13GB 28HR</t>
+    <t>THREE HPY 11GB 28HR</t>
   </si>
   <si>
     <t>808</t>
@@ -5950,7 +5950,7 @@
     <t>20137279</t>
   </si>
   <si>
-    <t>THREE HPY 150GB 28HR</t>
+    <t>THREE HPY 156GB 28HR</t>
   </si>
   <si>
     <t>811</t>
@@ -5959,7 +5959,7 @@
     <t>20137278</t>
   </si>
   <si>
-    <t>THREE HPY 80GB 28HR</t>
+    <t>THREE HPY 100GB 28HR</t>
   </si>
   <si>
     <t>812</t>
@@ -6071,9 +6071,6 @@
   </si>
   <si>
     <t>20137262</t>
-  </si>
-  <si>
-    <t>THREE HPY 50GB 28HR</t>
   </si>
   <si>
     <t>828</t>
@@ -16662,16 +16659,16 @@
         <v>1309</v>
       </c>
       <c r="B477" s="1" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C477" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D477" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E477" s="1" t="s">
         <v>1310</v>
-      </c>
-      <c r="C477" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D477" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E477" s="1" t="s">
-        <v>1311</v>
       </c>
       <c r="F477" s="1" t="s">
         <v>5</v>
@@ -16679,19 +16676,19 @@
     </row>
     <row r="478" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A478" s="1" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B478" s="1" t="s">
         <v>1312</v>
       </c>
-      <c r="B478" s="1" t="s">
+      <c r="C478" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D478" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E478" s="1" t="s">
         <v>1313</v>
-      </c>
-      <c r="C478" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D478" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E478" s="1" t="s">
-        <v>1314</v>
       </c>
       <c r="F478" s="1" t="s">
         <v>5</v>
@@ -16699,7 +16696,7 @@
     </row>
     <row r="479" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A479" s="1" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="B479" s="1" t="s">
         <v>1298</v>
@@ -16711,7 +16708,7 @@
         <v>4</v>
       </c>
       <c r="E479" s="1" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="F479" s="1" t="s">
         <v>5</v>
@@ -16719,41 +16716,41 @@
     </row>
     <row r="480" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A480" s="1" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B480" s="1" t="s">
         <v>1317</v>
       </c>
-      <c r="B480" s="1" t="s">
+      <c r="C480" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D480" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E480" s="1" t="s">
         <v>1318</v>
-      </c>
-      <c r="C480" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D480" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E480" s="1" t="s">
-        <v>1319</v>
       </c>
     </row>
     <row r="481" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A481" s="1" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B481" s="1" t="s">
         <v>1320</v>
       </c>
-      <c r="B481" s="1" t="s">
+      <c r="C481" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D481" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E481" s="1" t="s">
         <v>1321</v>
-      </c>
-      <c r="C481" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D481" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E481" s="1" t="s">
-        <v>1322</v>
       </c>
     </row>
     <row r="482" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A482" s="1" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="B482" s="1" t="s">
         <v>239</v>
@@ -16765,7 +16762,7 @@
         <v>4</v>
       </c>
       <c r="E482" s="1" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="F482" s="1" t="s">
         <v>83</v>
@@ -16773,7 +16770,7 @@
     </row>
     <row r="483" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A483" s="1" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="B483" s="1" t="s">
         <v>248</v>
@@ -16785,7 +16782,7 @@
         <v>4</v>
       </c>
       <c r="E483" s="1" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="F483" s="1" t="s">
         <v>83</v>
@@ -16793,7 +16790,7 @@
     </row>
     <row r="484" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A484" s="1" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="B484" s="1" t="s">
         <v>251</v>
@@ -16805,7 +16802,7 @@
         <v>4</v>
       </c>
       <c r="E484" s="1" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="F484" s="1" t="s">
         <v>83</v>
@@ -16813,7 +16810,7 @@
     </row>
     <row r="485" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A485" s="1" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="B485" s="1" t="s">
         <v>257</v>
@@ -16825,7 +16822,7 @@
         <v>4</v>
       </c>
       <c r="E485" s="1" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="F485" s="1" t="s">
         <v>83</v>
@@ -16833,7 +16830,7 @@
     </row>
     <row r="486" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A486" s="1" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="B486" s="1" t="s">
         <v>260</v>
@@ -16845,7 +16842,7 @@
         <v>4</v>
       </c>
       <c r="E486" s="1" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="F486" s="1" t="s">
         <v>83</v>
@@ -16853,7 +16850,7 @@
     </row>
     <row r="487" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A487" s="1" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="B487" s="1" t="s">
         <v>221</v>
@@ -16865,7 +16862,7 @@
         <v>4</v>
       </c>
       <c r="E487" s="1" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="F487" s="1" t="s">
         <v>83</v>
@@ -16873,36 +16870,36 @@
     </row>
     <row r="488" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A488" s="1" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B488" s="1" t="s">
         <v>1335</v>
       </c>
-      <c r="B488" s="1" t="s">
+      <c r="C488" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D488" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E488" s="1" t="s">
         <v>1336</v>
-      </c>
-      <c r="C488" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D488" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E488" s="1" t="s">
-        <v>1337</v>
       </c>
     </row>
     <row r="489" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A489" s="1" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B489" s="1" t="s">
         <v>1338</v>
       </c>
-      <c r="B489" s="1" t="s">
+      <c r="C489" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D489" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E489" s="1" t="s">
         <v>1339</v>
-      </c>
-      <c r="C489" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D489" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E489" s="1" t="s">
-        <v>1340</v>
       </c>
       <c r="F489" s="1" t="s">
         <v>5</v>
@@ -16910,19 +16907,19 @@
     </row>
     <row r="490" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A490" s="1" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B490" s="1" t="s">
+        <v>1338</v>
+      </c>
+      <c r="C490" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D490" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E490" s="1" t="s">
         <v>1341</v>
-      </c>
-      <c r="B490" s="1" t="s">
-        <v>1339</v>
-      </c>
-      <c r="C490" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D490" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E490" s="1" t="s">
-        <v>1342</v>
       </c>
       <c r="F490" s="1" t="s">
         <v>5</v>
@@ -16930,19 +16927,19 @@
     </row>
     <row r="491" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A491" s="1" t="s">
+        <v>1342</v>
+      </c>
+      <c r="B491" s="1" t="s">
         <v>1343</v>
       </c>
-      <c r="B491" s="1" t="s">
+      <c r="C491" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D491" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E491" s="1" t="s">
         <v>1344</v>
-      </c>
-      <c r="C491" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D491" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E491" s="1" t="s">
-        <v>1345</v>
       </c>
       <c r="F491" s="1" t="s">
         <v>83</v>
@@ -16950,19 +16947,19 @@
     </row>
     <row r="492" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A492" s="1" t="s">
+        <v>1345</v>
+      </c>
+      <c r="B492" s="1" t="s">
         <v>1346</v>
       </c>
-      <c r="B492" s="1" t="s">
+      <c r="C492" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D492" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E492" s="1" t="s">
         <v>1347</v>
-      </c>
-      <c r="C492" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D492" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E492" s="1" t="s">
-        <v>1348</v>
       </c>
       <c r="F492" s="1" t="s">
         <v>83</v>
@@ -16970,19 +16967,19 @@
     </row>
     <row r="493" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A493" s="1" t="s">
+        <v>1348</v>
+      </c>
+      <c r="B493" s="1" t="s">
         <v>1349</v>
       </c>
-      <c r="B493" s="1" t="s">
+      <c r="C493" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D493" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E493" s="1" t="s">
         <v>1350</v>
-      </c>
-      <c r="C493" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D493" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E493" s="1" t="s">
-        <v>1351</v>
       </c>
       <c r="F493" s="1" t="s">
         <v>5</v>
@@ -16990,19 +16987,19 @@
     </row>
     <row r="494" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A494" s="1" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B494" s="1" t="s">
         <v>1352</v>
       </c>
-      <c r="B494" s="1" t="s">
+      <c r="C494" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D494" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E494" s="1" t="s">
         <v>1353</v>
-      </c>
-      <c r="C494" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D494" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E494" s="1" t="s">
-        <v>1354</v>
       </c>
       <c r="F494" s="1" t="s">
         <v>5</v>
@@ -17010,19 +17007,19 @@
     </row>
     <row r="495" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A495" s="1" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B495" s="1" t="s">
         <v>1355</v>
       </c>
-      <c r="B495" s="1" t="s">
+      <c r="C495" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D495" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E495" s="1" t="s">
         <v>1356</v>
-      </c>
-      <c r="C495" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D495" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E495" s="1" t="s">
-        <v>1357</v>
       </c>
       <c r="F495" s="1" t="s">
         <v>5</v>
@@ -17030,19 +17027,19 @@
     </row>
     <row r="496" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A496" s="1" t="s">
+        <v>1357</v>
+      </c>
+      <c r="B496" s="1" t="s">
         <v>1358</v>
       </c>
-      <c r="B496" s="1" t="s">
+      <c r="C496" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D496" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E496" s="1" t="s">
         <v>1359</v>
-      </c>
-      <c r="C496" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D496" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E496" s="1" t="s">
-        <v>1360</v>
       </c>
       <c r="F496" s="1" t="s">
         <v>5</v>
@@ -17050,19 +17047,19 @@
     </row>
     <row r="497" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A497" s="1" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B497" s="1" t="s">
         <v>1361</v>
       </c>
-      <c r="B497" s="1" t="s">
+      <c r="C497" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D497" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E497" s="1" t="s">
         <v>1362</v>
-      </c>
-      <c r="C497" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D497" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E497" s="1" t="s">
-        <v>1363</v>
       </c>
       <c r="F497" s="1" t="s">
         <v>5</v>
@@ -17070,19 +17067,19 @@
     </row>
     <row r="498" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A498" s="1" t="s">
+        <v>1363</v>
+      </c>
+      <c r="B498" s="1" t="s">
         <v>1364</v>
       </c>
-      <c r="B498" s="1" t="s">
+      <c r="C498" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D498" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E498" s="1" t="s">
         <v>1365</v>
-      </c>
-      <c r="C498" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D498" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E498" s="1" t="s">
-        <v>1366</v>
       </c>
       <c r="F498" s="1" t="s">
         <v>5</v>
@@ -17090,19 +17087,19 @@
     </row>
     <row r="499" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A499" s="1" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B499" s="1" t="s">
         <v>1367</v>
       </c>
-      <c r="B499" s="1" t="s">
+      <c r="C499" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D499" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E499" s="1" t="s">
         <v>1368</v>
-      </c>
-      <c r="C499" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D499" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E499" s="1" t="s">
-        <v>1369</v>
       </c>
       <c r="F499" s="1" t="s">
         <v>5</v>
@@ -17110,19 +17107,19 @@
     </row>
     <row r="500" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A500" s="1" t="s">
+        <v>1369</v>
+      </c>
+      <c r="B500" s="1" t="s">
         <v>1370</v>
       </c>
-      <c r="B500" s="1" t="s">
+      <c r="C500" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D500" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E500" s="1" t="s">
         <v>1371</v>
-      </c>
-      <c r="C500" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D500" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E500" s="1" t="s">
-        <v>1372</v>
       </c>
       <c r="F500" s="1" t="s">
         <v>5</v>
@@ -17130,19 +17127,19 @@
     </row>
     <row r="501" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A501" s="1" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B501" s="1" t="s">
         <v>1373</v>
       </c>
-      <c r="B501" s="1" t="s">
+      <c r="C501" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D501" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E501" s="1" t="s">
         <v>1374</v>
-      </c>
-      <c r="C501" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D501" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E501" s="1" t="s">
-        <v>1375</v>
       </c>
       <c r="F501" s="1" t="s">
         <v>83</v>
@@ -17150,19 +17147,19 @@
     </row>
     <row r="502" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A502" s="1" t="s">
+        <v>1375</v>
+      </c>
+      <c r="B502" s="1" t="s">
         <v>1376</v>
       </c>
-      <c r="B502" s="1" t="s">
+      <c r="C502" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D502" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E502" s="1" t="s">
         <v>1377</v>
-      </c>
-      <c r="C502" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D502" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E502" s="1" t="s">
-        <v>1378</v>
       </c>
       <c r="F502" s="1" t="s">
         <v>83</v>
@@ -17170,19 +17167,19 @@
     </row>
     <row r="503" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A503" s="1" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B503" s="1" t="s">
         <v>1379</v>
       </c>
-      <c r="B503" s="1" t="s">
+      <c r="C503" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D503" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E503" s="1" t="s">
         <v>1380</v>
-      </c>
-      <c r="C503" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D503" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E503" s="1" t="s">
-        <v>1381</v>
       </c>
       <c r="F503" s="1" t="s">
         <v>83</v>
@@ -17190,19 +17187,19 @@
     </row>
     <row r="504" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A504" s="1" t="s">
+        <v>1381</v>
+      </c>
+      <c r="B504" s="1" t="s">
+        <v>1358</v>
+      </c>
+      <c r="C504" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D504" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E504" s="1" t="s">
         <v>1382</v>
-      </c>
-      <c r="B504" s="1" t="s">
-        <v>1359</v>
-      </c>
-      <c r="C504" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D504" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E504" s="1" t="s">
-        <v>1383</v>
       </c>
       <c r="F504" s="1" t="s">
         <v>83</v>
@@ -17210,19 +17207,19 @@
     </row>
     <row r="505" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A505" s="1" t="s">
+        <v>1383</v>
+      </c>
+      <c r="B505" s="1" t="s">
+        <v>1361</v>
+      </c>
+      <c r="C505" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D505" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E505" s="1" t="s">
         <v>1384</v>
-      </c>
-      <c r="B505" s="1" t="s">
-        <v>1362</v>
-      </c>
-      <c r="C505" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D505" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E505" s="1" t="s">
-        <v>1385</v>
       </c>
       <c r="F505" s="1" t="s">
         <v>83</v>
@@ -17230,19 +17227,19 @@
     </row>
     <row r="506" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A506" s="1" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B506" s="1" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C506" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D506" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E506" s="1" t="s">
         <v>1386</v>
-      </c>
-      <c r="B506" s="1" t="s">
-        <v>1365</v>
-      </c>
-      <c r="C506" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D506" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E506" s="1" t="s">
-        <v>1387</v>
       </c>
       <c r="F506" s="1" t="s">
         <v>83</v>
@@ -17250,19 +17247,19 @@
     </row>
     <row r="507" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A507" s="1" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B507" s="1" t="s">
+        <v>1367</v>
+      </c>
+      <c r="C507" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D507" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E507" s="1" t="s">
         <v>1388</v>
-      </c>
-      <c r="B507" s="1" t="s">
-        <v>1368</v>
-      </c>
-      <c r="C507" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D507" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E507" s="1" t="s">
-        <v>1389</v>
       </c>
       <c r="F507" s="1" t="s">
         <v>83</v>
@@ -17270,19 +17267,19 @@
     </row>
     <row r="508" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A508" s="1" t="s">
+        <v>1389</v>
+      </c>
+      <c r="B508" s="1" t="s">
         <v>1390</v>
       </c>
-      <c r="B508" s="1" t="s">
+      <c r="C508" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D508" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E508" s="1" t="s">
         <v>1391</v>
-      </c>
-      <c r="C508" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D508" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E508" s="1" t="s">
-        <v>1392</v>
       </c>
       <c r="F508" s="1" t="s">
         <v>83</v>
@@ -17290,19 +17287,19 @@
     </row>
     <row r="509" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A509" s="1" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B509" s="1" t="s">
         <v>1393</v>
       </c>
-      <c r="B509" s="1" t="s">
+      <c r="C509" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D509" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E509" s="1" t="s">
         <v>1394</v>
-      </c>
-      <c r="C509" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D509" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E509" s="1" t="s">
-        <v>1395</v>
       </c>
       <c r="F509" s="1" t="s">
         <v>5</v>
@@ -17310,19 +17307,19 @@
     </row>
     <row r="510" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A510" s="1" t="s">
+        <v>1395</v>
+      </c>
+      <c r="B510" s="1" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C510" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D510" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E510" s="1" t="s">
         <v>1396</v>
-      </c>
-      <c r="B510" s="1" t="s">
-        <v>1394</v>
-      </c>
-      <c r="C510" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D510" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E510" s="1" t="s">
-        <v>1397</v>
       </c>
       <c r="F510" s="1" t="s">
         <v>5</v>
@@ -17330,19 +17327,19 @@
     </row>
     <row r="511" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A511" s="1" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B511" s="1" t="s">
         <v>1398</v>
       </c>
-      <c r="B511" s="1" t="s">
+      <c r="C511" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D511" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E511" s="1" t="s">
         <v>1399</v>
-      </c>
-      <c r="C511" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D511" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E511" s="1" t="s">
-        <v>1400</v>
       </c>
       <c r="F511" s="1" t="s">
         <v>5</v>
@@ -17350,19 +17347,19 @@
     </row>
     <row r="512" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A512" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="B512" s="1" t="s">
         <v>1401</v>
       </c>
-      <c r="B512" s="1" t="s">
+      <c r="C512" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D512" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E512" s="1" t="s">
         <v>1402</v>
-      </c>
-      <c r="C512" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D512" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E512" s="1" t="s">
-        <v>1403</v>
       </c>
       <c r="F512" s="1" t="s">
         <v>5</v>
@@ -17370,19 +17367,19 @@
     </row>
     <row r="513" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A513" s="1" t="s">
+        <v>1403</v>
+      </c>
+      <c r="B513" s="1" t="s">
+        <v>1401</v>
+      </c>
+      <c r="C513" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D513" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E513" s="1" t="s">
         <v>1404</v>
-      </c>
-      <c r="B513" s="1" t="s">
-        <v>1402</v>
-      </c>
-      <c r="C513" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D513" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E513" s="1" t="s">
-        <v>1405</v>
       </c>
       <c r="F513" s="1" t="s">
         <v>5</v>
@@ -17390,19 +17387,19 @@
     </row>
     <row r="514" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A514" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="B514" s="1" t="s">
         <v>1406</v>
       </c>
-      <c r="B514" s="1" t="s">
+      <c r="C514" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D514" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E514" s="1" t="s">
         <v>1407</v>
-      </c>
-      <c r="C514" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D514" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E514" s="1" t="s">
-        <v>1408</v>
       </c>
       <c r="F514" s="1" t="s">
         <v>5</v>
@@ -17410,19 +17407,19 @@
     </row>
     <row r="515" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A515" s="1" t="s">
+        <v>1408</v>
+      </c>
+      <c r="B515" s="1" t="s">
         <v>1409</v>
       </c>
-      <c r="B515" s="1" t="s">
+      <c r="C515" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D515" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E515" s="1" t="s">
         <v>1410</v>
-      </c>
-      <c r="C515" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D515" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E515" s="1" t="s">
-        <v>1411</v>
       </c>
       <c r="F515" s="1" t="s">
         <v>5</v>
@@ -17430,19 +17427,19 @@
     </row>
     <row r="516" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A516" s="1" t="s">
+        <v>1411</v>
+      </c>
+      <c r="B516" s="1" t="s">
         <v>1412</v>
       </c>
-      <c r="B516" s="1" t="s">
+      <c r="C516" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D516" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E516" s="1" t="s">
         <v>1413</v>
-      </c>
-      <c r="C516" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D516" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E516" s="1" t="s">
-        <v>1414</v>
       </c>
       <c r="F516" s="1" t="s">
         <v>5</v>
@@ -17450,19 +17447,19 @@
     </row>
     <row r="517" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A517" s="1" t="s">
+        <v>1414</v>
+      </c>
+      <c r="B517" s="1" t="s">
         <v>1415</v>
       </c>
-      <c r="B517" s="1" t="s">
+      <c r="C517" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D517" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E517" s="1" t="s">
         <v>1416</v>
-      </c>
-      <c r="C517" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D517" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E517" s="1" t="s">
-        <v>1417</v>
       </c>
       <c r="F517" s="1" t="s">
         <v>5</v>
@@ -17470,19 +17467,19 @@
     </row>
     <row r="518" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A518" s="1" t="s">
+        <v>1417</v>
+      </c>
+      <c r="B518" s="1" t="s">
         <v>1418</v>
       </c>
-      <c r="B518" s="1" t="s">
+      <c r="C518" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D518" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E518" s="1" t="s">
         <v>1419</v>
-      </c>
-      <c r="C518" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D518" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E518" s="1" t="s">
-        <v>1420</v>
       </c>
       <c r="F518" s="1" t="s">
         <v>5</v>
@@ -17490,19 +17487,19 @@
     </row>
     <row r="519" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A519" s="1" t="s">
+        <v>1420</v>
+      </c>
+      <c r="B519" s="1" t="s">
         <v>1421</v>
       </c>
-      <c r="B519" s="1" t="s">
+      <c r="C519" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D519" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E519" s="1" t="s">
         <v>1422</v>
-      </c>
-      <c r="C519" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D519" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E519" s="1" t="s">
-        <v>1423</v>
       </c>
       <c r="F519" s="1" t="s">
         <v>5</v>
@@ -17510,19 +17507,19 @@
     </row>
     <row r="520" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A520" s="1" t="s">
+        <v>1423</v>
+      </c>
+      <c r="B520" s="1" t="s">
         <v>1424</v>
       </c>
-      <c r="B520" s="1" t="s">
+      <c r="C520" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D520" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E520" s="1" t="s">
         <v>1425</v>
-      </c>
-      <c r="C520" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D520" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E520" s="1" t="s">
-        <v>1426</v>
       </c>
       <c r="F520" s="1" t="s">
         <v>5</v>
@@ -17530,19 +17527,19 @@
     </row>
     <row r="521" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A521" s="1" t="s">
+        <v>1426</v>
+      </c>
+      <c r="B521" s="1" t="s">
         <v>1427</v>
       </c>
-      <c r="B521" s="1" t="s">
+      <c r="C521" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D521" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E521" s="1" t="s">
         <v>1428</v>
-      </c>
-      <c r="C521" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D521" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E521" s="1" t="s">
-        <v>1429</v>
       </c>
       <c r="F521" s="1" t="s">
         <v>5</v>
@@ -17550,19 +17547,19 @@
     </row>
     <row r="522" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A522" s="1" t="s">
+        <v>1429</v>
+      </c>
+      <c r="B522" s="1" t="s">
         <v>1430</v>
       </c>
-      <c r="B522" s="1" t="s">
+      <c r="C522" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D522" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E522" s="1" t="s">
         <v>1431</v>
-      </c>
-      <c r="C522" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D522" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E522" s="1" t="s">
-        <v>1432</v>
       </c>
       <c r="F522" s="1" t="s">
         <v>5</v>
@@ -17570,19 +17567,19 @@
     </row>
     <row r="523" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A523" s="1" t="s">
+        <v>1432</v>
+      </c>
+      <c r="B523" s="1" t="s">
         <v>1433</v>
       </c>
-      <c r="B523" s="1" t="s">
+      <c r="C523" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D523" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E523" s="1" t="s">
         <v>1434</v>
-      </c>
-      <c r="C523" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D523" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E523" s="1" t="s">
-        <v>1435</v>
       </c>
       <c r="F523" s="1" t="s">
         <v>5</v>
@@ -17590,19 +17587,19 @@
     </row>
     <row r="524" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A524" s="1" t="s">
+        <v>1435</v>
+      </c>
+      <c r="B524" s="1" t="s">
         <v>1436</v>
       </c>
-      <c r="B524" s="1" t="s">
+      <c r="C524" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D524" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E524" s="1" t="s">
         <v>1437</v>
-      </c>
-      <c r="C524" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D524" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E524" s="1" t="s">
-        <v>1438</v>
       </c>
       <c r="F524" s="1" t="s">
         <v>5</v>
@@ -17610,19 +17607,19 @@
     </row>
     <row r="525" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A525" s="1" t="s">
+        <v>1438</v>
+      </c>
+      <c r="B525" s="1" t="s">
         <v>1439</v>
       </c>
-      <c r="B525" s="1" t="s">
+      <c r="C525" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D525" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E525" s="1" t="s">
         <v>1440</v>
-      </c>
-      <c r="C525" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D525" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E525" s="1" t="s">
-        <v>1441</v>
       </c>
       <c r="F525" s="1" t="s">
         <v>5</v>
@@ -17630,19 +17627,19 @@
     </row>
     <row r="526" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A526" s="1" t="s">
+        <v>1441</v>
+      </c>
+      <c r="B526" s="1" t="s">
         <v>1442</v>
       </c>
-      <c r="B526" s="1" t="s">
+      <c r="C526" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D526" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E526" s="1" t="s">
         <v>1443</v>
-      </c>
-      <c r="C526" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D526" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E526" s="1" t="s">
-        <v>1444</v>
       </c>
       <c r="F526" s="1" t="s">
         <v>5</v>
@@ -17650,19 +17647,19 @@
     </row>
     <row r="527" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A527" s="1" t="s">
+        <v>1444</v>
+      </c>
+      <c r="B527" s="1" t="s">
         <v>1445</v>
       </c>
-      <c r="B527" s="1" t="s">
+      <c r="C527" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D527" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E527" s="1" t="s">
         <v>1446</v>
-      </c>
-      <c r="C527" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D527" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E527" s="1" t="s">
-        <v>1447</v>
       </c>
       <c r="F527" s="1" t="s">
         <v>5</v>
@@ -17670,19 +17667,19 @@
     </row>
     <row r="528" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A528" s="1" t="s">
+        <v>1447</v>
+      </c>
+      <c r="B528" s="1" t="s">
+        <v>1439</v>
+      </c>
+      <c r="C528" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D528" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E528" s="1" t="s">
         <v>1448</v>
-      </c>
-      <c r="B528" s="1" t="s">
-        <v>1440</v>
-      </c>
-      <c r="C528" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D528" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E528" s="1" t="s">
-        <v>1449</v>
       </c>
       <c r="F528" s="1" t="s">
         <v>5</v>
@@ -17690,19 +17687,19 @@
     </row>
     <row r="529" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A529" s="1" t="s">
+        <v>1449</v>
+      </c>
+      <c r="B529" s="1" t="s">
         <v>1450</v>
       </c>
-      <c r="B529" s="1" t="s">
+      <c r="C529" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D529" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E529" s="1" t="s">
         <v>1451</v>
-      </c>
-      <c r="C529" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D529" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E529" s="1" t="s">
-        <v>1452</v>
       </c>
       <c r="F529" s="1" t="s">
         <v>5</v>
@@ -17710,19 +17707,19 @@
     </row>
     <row r="530" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A530" s="1" t="s">
+        <v>1452</v>
+      </c>
+      <c r="B530" s="1" t="s">
         <v>1453</v>
       </c>
-      <c r="B530" s="1" t="s">
+      <c r="C530" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D530" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E530" s="1" t="s">
         <v>1454</v>
-      </c>
-      <c r="C530" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D530" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E530" s="1" t="s">
-        <v>1455</v>
       </c>
       <c r="F530" s="1" t="s">
         <v>5</v>
@@ -17730,19 +17727,19 @@
     </row>
     <row r="531" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A531" s="1" t="s">
+        <v>1455</v>
+      </c>
+      <c r="B531" s="1" t="s">
         <v>1456</v>
       </c>
-      <c r="B531" s="1" t="s">
+      <c r="C531" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D531" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E531" s="1" t="s">
         <v>1457</v>
-      </c>
-      <c r="C531" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D531" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E531" s="1" t="s">
-        <v>1458</v>
       </c>
       <c r="F531" s="1" t="s">
         <v>5</v>
@@ -17750,19 +17747,19 @@
     </row>
     <row r="532" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A532" s="1" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B532" s="1" t="s">
+        <v>1456</v>
+      </c>
+      <c r="C532" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D532" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E532" s="1" t="s">
         <v>1459</v>
-      </c>
-      <c r="B532" s="1" t="s">
-        <v>1457</v>
-      </c>
-      <c r="C532" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D532" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E532" s="1" t="s">
-        <v>1460</v>
       </c>
       <c r="F532" s="1" t="s">
         <v>83</v>
@@ -17770,19 +17767,19 @@
     </row>
     <row r="533" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A533" s="1" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B533" s="1" t="s">
         <v>1461</v>
       </c>
-      <c r="B533" s="1" t="s">
+      <c r="C533" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D533" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E533" s="1" t="s">
         <v>1462</v>
-      </c>
-      <c r="C533" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D533" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E533" s="1" t="s">
-        <v>1463</v>
       </c>
       <c r="F533" s="1" t="s">
         <v>5</v>
@@ -17790,19 +17787,19 @@
     </row>
     <row r="534" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A534" s="1" t="s">
+        <v>1463</v>
+      </c>
+      <c r="B534" s="1" t="s">
         <v>1464</v>
       </c>
-      <c r="B534" s="1" t="s">
+      <c r="C534" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D534" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E534" s="1" t="s">
         <v>1465</v>
-      </c>
-      <c r="C534" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D534" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E534" s="1" t="s">
-        <v>1466</v>
       </c>
       <c r="F534" s="1" t="s">
         <v>5</v>
@@ -17810,19 +17807,19 @@
     </row>
     <row r="535" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A535" s="1" t="s">
+        <v>1466</v>
+      </c>
+      <c r="B535" s="1" t="s">
         <v>1467</v>
       </c>
-      <c r="B535" s="1" t="s">
+      <c r="C535" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D535" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E535" s="1" t="s">
         <v>1468</v>
-      </c>
-      <c r="C535" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D535" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E535" s="1" t="s">
-        <v>1469</v>
       </c>
       <c r="F535" s="1" t="s">
         <v>5</v>
@@ -17830,155 +17827,155 @@
     </row>
     <row r="536" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A536" s="1" t="s">
+        <v>1469</v>
+      </c>
+      <c r="B536" s="1" t="s">
         <v>1470</v>
       </c>
-      <c r="B536" s="1" t="s">
+      <c r="C536" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D536" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E536" s="1" t="s">
         <v>1471</v>
-      </c>
-      <c r="C536" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D536" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E536" s="1" t="s">
-        <v>1472</v>
       </c>
     </row>
     <row r="537" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A537" s="1" t="s">
+        <v>1472</v>
+      </c>
+      <c r="B537" s="1" t="s">
         <v>1473</v>
       </c>
-      <c r="B537" s="1" t="s">
+      <c r="C537" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D537" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E537" s="1" t="s">
         <v>1474</v>
-      </c>
-      <c r="C537" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D537" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E537" s="1" t="s">
-        <v>1475</v>
       </c>
     </row>
     <row r="538" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A538" s="1" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B538" s="1" t="s">
         <v>1476</v>
       </c>
-      <c r="B538" s="1" t="s">
+      <c r="C538" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D538" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E538" s="1" t="s">
         <v>1477</v>
-      </c>
-      <c r="C538" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D538" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E538" s="1" t="s">
-        <v>1478</v>
       </c>
     </row>
     <row r="539" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A539" s="1" t="s">
+        <v>1478</v>
+      </c>
+      <c r="B539" s="1" t="s">
         <v>1479</v>
       </c>
-      <c r="B539" s="1" t="s">
+      <c r="C539" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D539" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E539" s="1" t="s">
         <v>1480</v>
-      </c>
-      <c r="C539" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D539" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E539" s="1" t="s">
-        <v>1481</v>
       </c>
     </row>
     <row r="540" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A540" s="1" t="s">
+        <v>1481</v>
+      </c>
+      <c r="B540" s="1" t="s">
+        <v>1470</v>
+      </c>
+      <c r="C540" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D540" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E540" s="1" t="s">
         <v>1482</v>
-      </c>
-      <c r="B540" s="1" t="s">
-        <v>1471</v>
-      </c>
-      <c r="C540" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D540" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E540" s="1" t="s">
-        <v>1483</v>
       </c>
     </row>
     <row r="541" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A541" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="B541" s="1" t="s">
+        <v>1473</v>
+      </c>
+      <c r="C541" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D541" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E541" s="1" t="s">
         <v>1484</v>
-      </c>
-      <c r="B541" s="1" t="s">
-        <v>1474</v>
-      </c>
-      <c r="C541" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D541" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E541" s="1" t="s">
-        <v>1485</v>
       </c>
     </row>
     <row r="542" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A542" s="1" t="s">
+        <v>1485</v>
+      </c>
+      <c r="B542" s="1" t="s">
+        <v>1476</v>
+      </c>
+      <c r="C542" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D542" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E542" s="1" t="s">
         <v>1486</v>
-      </c>
-      <c r="B542" s="1" t="s">
-        <v>1477</v>
-      </c>
-      <c r="C542" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D542" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E542" s="1" t="s">
-        <v>1487</v>
       </c>
     </row>
     <row r="543" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A543" s="1" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B543" s="1" t="s">
+        <v>1479</v>
+      </c>
+      <c r="C543" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D543" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E543" s="1" t="s">
         <v>1488</v>
-      </c>
-      <c r="B543" s="1" t="s">
-        <v>1480</v>
-      </c>
-      <c r="C543" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D543" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E543" s="1" t="s">
-        <v>1489</v>
       </c>
     </row>
     <row r="544" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A544" s="1" t="s">
+        <v>1489</v>
+      </c>
+      <c r="B544" s="1" t="s">
         <v>1490</v>
       </c>
-      <c r="B544" s="1" t="s">
+      <c r="C544" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D544" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E544" s="1" t="s">
         <v>1491</v>
-      </c>
-      <c r="C544" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D544" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E544" s="1" t="s">
-        <v>1492</v>
       </c>
       <c r="F544" s="1" t="s">
         <v>5</v>
@@ -17986,70 +17983,70 @@
     </row>
     <row r="545" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A545" s="1" t="s">
+        <v>1492</v>
+      </c>
+      <c r="B545" s="1" t="s">
         <v>1493</v>
       </c>
-      <c r="B545" s="1" t="s">
+      <c r="C545" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D545" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E545" s="1" t="s">
         <v>1494</v>
-      </c>
-      <c r="C545" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D545" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E545" s="1" t="s">
-        <v>1495</v>
       </c>
     </row>
     <row r="546" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A546" s="1" t="s">
+        <v>1495</v>
+      </c>
+      <c r="B546" s="1" t="s">
         <v>1496</v>
       </c>
-      <c r="B546" s="1" t="s">
+      <c r="C546" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D546" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E546" s="1" t="s">
         <v>1497</v>
-      </c>
-      <c r="C546" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D546" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E546" s="1" t="s">
-        <v>1498</v>
       </c>
     </row>
     <row r="547" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A547" s="1" t="s">
+        <v>1498</v>
+      </c>
+      <c r="B547" s="1" t="s">
+        <v>1496</v>
+      </c>
+      <c r="C547" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D547" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E547" s="1" t="s">
         <v>1499</v>
-      </c>
-      <c r="B547" s="1" t="s">
-        <v>1497</v>
-      </c>
-      <c r="C547" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D547" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E547" s="1" t="s">
-        <v>1500</v>
       </c>
     </row>
     <row r="548" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A548" s="1" t="s">
+        <v>1500</v>
+      </c>
+      <c r="B548" s="1" t="s">
         <v>1501</v>
       </c>
-      <c r="B548" s="1" t="s">
+      <c r="C548" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D548" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E548" s="1" t="s">
         <v>1502</v>
-      </c>
-      <c r="C548" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D548" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E548" s="1" t="s">
-        <v>1503</v>
       </c>
       <c r="F548" s="1" t="s">
         <v>5</v>
@@ -18057,19 +18054,19 @@
     </row>
     <row r="549" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A549" s="1" t="s">
+        <v>1503</v>
+      </c>
+      <c r="B549" s="1" t="s">
         <v>1504</v>
       </c>
-      <c r="B549" s="1" t="s">
+      <c r="C549" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D549" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E549" s="1" t="s">
         <v>1505</v>
-      </c>
-      <c r="C549" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D549" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E549" s="1" t="s">
-        <v>1506</v>
       </c>
       <c r="F549" s="1" t="s">
         <v>5</v>
@@ -18077,19 +18074,19 @@
     </row>
     <row r="550" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A550" s="1" t="s">
+        <v>1506</v>
+      </c>
+      <c r="B550" s="1" t="s">
         <v>1507</v>
       </c>
-      <c r="B550" s="1" t="s">
+      <c r="C550" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D550" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E550" s="1" t="s">
         <v>1508</v>
-      </c>
-      <c r="C550" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D550" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E550" s="1" t="s">
-        <v>1509</v>
       </c>
       <c r="F550" s="1" t="s">
         <v>5</v>
@@ -18097,19 +18094,19 @@
     </row>
     <row r="551" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A551" s="1" t="s">
+        <v>1509</v>
+      </c>
+      <c r="B551" s="1" t="s">
         <v>1510</v>
       </c>
-      <c r="B551" s="1" t="s">
+      <c r="C551" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D551" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E551" s="1" t="s">
         <v>1511</v>
-      </c>
-      <c r="C551" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D551" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E551" s="1" t="s">
-        <v>1512</v>
       </c>
       <c r="F551" s="1" t="s">
         <v>5</v>
@@ -18117,19 +18114,19 @@
     </row>
     <row r="552" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A552" s="1" t="s">
+        <v>1512</v>
+      </c>
+      <c r="B552" s="1" t="s">
         <v>1513</v>
       </c>
-      <c r="B552" s="1" t="s">
+      <c r="C552" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D552" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E552" s="1" t="s">
         <v>1514</v>
-      </c>
-      <c r="C552" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D552" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E552" s="1" t="s">
-        <v>1515</v>
       </c>
       <c r="F552" s="1" t="s">
         <v>5</v>
@@ -18137,19 +18134,19 @@
     </row>
     <row r="553" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A553" s="1" t="s">
+        <v>1515</v>
+      </c>
+      <c r="B553" s="1" t="s">
         <v>1516</v>
       </c>
-      <c r="B553" s="1" t="s">
+      <c r="C553" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D553" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E553" s="1" t="s">
         <v>1517</v>
-      </c>
-      <c r="C553" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D553" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E553" s="1" t="s">
-        <v>1518</v>
       </c>
       <c r="F553" s="1" t="s">
         <v>5</v>
@@ -18157,10 +18154,10 @@
     </row>
     <row r="554" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A554" s="1" t="s">
+        <v>1518</v>
+      </c>
+      <c r="B554" s="1" t="s">
         <v>1519</v>
-      </c>
-      <c r="B554" s="1" t="s">
-        <v>1502</v>
       </c>
       <c r="C554" s="1" t="s">
         <v>3</v>
@@ -18240,7 +18237,7 @@
         <v>1530</v>
       </c>
       <c r="B558" s="1" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="C558" s="1" t="s">
         <v>3</v>
@@ -18260,7 +18257,7 @@
         <v>1532</v>
       </c>
       <c r="B559" s="1" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="C559" s="1" t="s">
         <v>3</v>
@@ -22000,16 +21997,16 @@
         <v>2019</v>
       </c>
       <c r="B746" s="1" t="s">
+        <v>1982</v>
+      </c>
+      <c r="C746" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D746" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E746" s="1" t="s">
         <v>2020</v>
-      </c>
-      <c r="C746" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D746" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E746" s="1" t="s">
-        <v>2021</v>
       </c>
       <c r="F746" s="1" t="s">
         <v>5</v>
@@ -22017,19 +22014,19 @@
     </row>
     <row r="747" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A747" s="1" t="s">
+        <v>2021</v>
+      </c>
+      <c r="B747" s="1" t="s">
         <v>2022</v>
       </c>
-      <c r="B747" s="1" t="s">
+      <c r="C747" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D747" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E747" s="1" t="s">
         <v>2023</v>
-      </c>
-      <c r="C747" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D747" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E747" s="1" t="s">
-        <v>2024</v>
       </c>
       <c r="F747" s="1" t="s">
         <v>5</v>
@@ -22037,19 +22034,19 @@
     </row>
     <row r="748" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A748" s="1" t="s">
+        <v>2024</v>
+      </c>
+      <c r="B748" s="1" t="s">
         <v>2025</v>
       </c>
-      <c r="B748" s="1" t="s">
+      <c r="C748" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D748" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E748" s="1" t="s">
         <v>2026</v>
-      </c>
-      <c r="C748" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D748" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E748" s="1" t="s">
-        <v>2027</v>
       </c>
       <c r="F748" s="1" t="s">
         <v>5</v>
@@ -22057,19 +22054,19 @@
     </row>
     <row r="749" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A749" s="1" t="s">
+        <v>2027</v>
+      </c>
+      <c r="B749" s="1" t="s">
         <v>2028</v>
       </c>
-      <c r="B749" s="1" t="s">
+      <c r="C749" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D749" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E749" s="1" t="s">
         <v>2029</v>
-      </c>
-      <c r="C749" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D749" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E749" s="1" t="s">
-        <v>2030</v>
       </c>
       <c r="F749" s="1" t="s">
         <v>5</v>
@@ -22077,19 +22074,19 @@
     </row>
     <row r="750" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A750" s="1" t="s">
+        <v>2030</v>
+      </c>
+      <c r="B750" s="1" t="s">
         <v>2031</v>
       </c>
-      <c r="B750" s="1" t="s">
+      <c r="C750" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D750" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E750" s="1" t="s">
         <v>2032</v>
-      </c>
-      <c r="C750" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D750" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E750" s="1" t="s">
-        <v>2033</v>
       </c>
       <c r="F750" s="1" t="s">
         <v>5</v>
@@ -22097,19 +22094,19 @@
     </row>
     <row r="751" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A751" s="1" t="s">
+        <v>2033</v>
+      </c>
+      <c r="B751" s="1" t="s">
         <v>2034</v>
       </c>
-      <c r="B751" s="1" t="s">
+      <c r="C751" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D751" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E751" s="1" t="s">
         <v>2035</v>
-      </c>
-      <c r="C751" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D751" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E751" s="1" t="s">
-        <v>2036</v>
       </c>
       <c r="F751" s="1" t="s">
         <v>5</v>
@@ -22117,19 +22114,19 @@
     </row>
     <row r="752" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A752" s="1" t="s">
+        <v>2036</v>
+      </c>
+      <c r="B752" s="1" t="s">
         <v>2037</v>
       </c>
-      <c r="B752" s="1" t="s">
+      <c r="C752" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D752" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E752" s="1" t="s">
         <v>2038</v>
-      </c>
-      <c r="C752" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D752" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E752" s="1" t="s">
-        <v>2039</v>
       </c>
       <c r="F752" s="1" t="s">
         <v>5</v>
@@ -22137,19 +22134,19 @@
     </row>
     <row r="753" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A753" s="1" t="s">
+        <v>2039</v>
+      </c>
+      <c r="B753" s="1" t="s">
         <v>2040</v>
       </c>
-      <c r="B753" s="1" t="s">
+      <c r="C753" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D753" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E753" s="1" t="s">
         <v>2041</v>
-      </c>
-      <c r="C753" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D753" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E753" s="1" t="s">
-        <v>2042</v>
       </c>
       <c r="F753" s="1" t="s">
         <v>5</v>
@@ -22157,19 +22154,19 @@
     </row>
     <row r="754" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A754" s="1" t="s">
+        <v>2042</v>
+      </c>
+      <c r="B754" s="1" t="s">
         <v>2043</v>
       </c>
-      <c r="B754" s="1" t="s">
+      <c r="C754" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D754" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E754" s="1" t="s">
         <v>2044</v>
-      </c>
-      <c r="C754" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D754" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E754" s="1" t="s">
-        <v>2045</v>
       </c>
       <c r="F754" s="1" t="s">
         <v>5</v>
@@ -22177,19 +22174,19 @@
     </row>
     <row r="755" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A755" s="1" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B755" s="1" t="s">
         <v>2046</v>
       </c>
-      <c r="B755" s="1" t="s">
+      <c r="C755" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D755" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E755" s="1" t="s">
         <v>2047</v>
-      </c>
-      <c r="C755" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D755" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E755" s="1" t="s">
-        <v>2048</v>
       </c>
       <c r="F755" s="1" t="s">
         <v>5</v>
@@ -22197,19 +22194,19 @@
     </row>
     <row r="756" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A756" s="1" t="s">
+        <v>2048</v>
+      </c>
+      <c r="B756" s="1" t="s">
         <v>2049</v>
       </c>
-      <c r="B756" s="1" t="s">
+      <c r="C756" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D756" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E756" s="1" t="s">
         <v>2050</v>
-      </c>
-      <c r="C756" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D756" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E756" s="1" t="s">
-        <v>2051</v>
       </c>
       <c r="F756" s="1" t="s">
         <v>5</v>
@@ -22217,19 +22214,19 @@
     </row>
     <row r="757" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A757" s="1" t="s">
+        <v>2051</v>
+      </c>
+      <c r="B757" s="1" t="s">
         <v>2052</v>
       </c>
-      <c r="B757" s="1" t="s">
+      <c r="C757" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D757" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E757" s="1" t="s">
         <v>2053</v>
-      </c>
-      <c r="C757" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D757" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E757" s="1" t="s">
-        <v>2054</v>
       </c>
       <c r="F757" s="1" t="s">
         <v>5</v>
@@ -22237,19 +22234,19 @@
     </row>
     <row r="758" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A758" s="1" t="s">
+        <v>2054</v>
+      </c>
+      <c r="B758" s="1" t="s">
         <v>2055</v>
       </c>
-      <c r="B758" s="1" t="s">
+      <c r="C758" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D758" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E758" s="1" t="s">
         <v>2056</v>
-      </c>
-      <c r="C758" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D758" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E758" s="1" t="s">
-        <v>2057</v>
       </c>
       <c r="F758" s="1" t="s">
         <v>5</v>
@@ -22257,19 +22254,19 @@
     </row>
     <row r="759" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A759" s="1" t="s">
+        <v>2057</v>
+      </c>
+      <c r="B759" s="1" t="s">
         <v>2058</v>
       </c>
-      <c r="B759" s="1" t="s">
+      <c r="C759" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D759" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E759" s="1" t="s">
         <v>2059</v>
-      </c>
-      <c r="C759" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D759" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E759" s="1" t="s">
-        <v>2060</v>
       </c>
       <c r="F759" s="1" t="s">
         <v>5</v>
@@ -22277,19 +22274,19 @@
     </row>
     <row r="760" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A760" s="1" t="s">
+        <v>2060</v>
+      </c>
+      <c r="B760" s="1" t="s">
         <v>2061</v>
       </c>
-      <c r="B760" s="1" t="s">
+      <c r="C760" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D760" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E760" s="1" t="s">
         <v>2062</v>
-      </c>
-      <c r="C760" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D760" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E760" s="1" t="s">
-        <v>2063</v>
       </c>
       <c r="F760" s="1" t="s">
         <v>5</v>
@@ -22297,19 +22294,19 @@
     </row>
     <row r="761" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A761" s="1" t="s">
+        <v>2063</v>
+      </c>
+      <c r="B761" s="1" t="s">
         <v>2064</v>
       </c>
-      <c r="B761" s="1" t="s">
+      <c r="C761" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D761" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E761" s="1" t="s">
         <v>2065</v>
-      </c>
-      <c r="C761" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D761" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E761" s="1" t="s">
-        <v>2066</v>
       </c>
       <c r="F761" s="1" t="s">
         <v>5</v>
@@ -22317,19 +22314,19 @@
     </row>
     <row r="762" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A762" s="1" t="s">
+        <v>2066</v>
+      </c>
+      <c r="B762" s="1" t="s">
         <v>2067</v>
       </c>
-      <c r="B762" s="1" t="s">
+      <c r="C762" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D762" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E762" s="1" t="s">
         <v>2068</v>
-      </c>
-      <c r="C762" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D762" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E762" s="1" t="s">
-        <v>2069</v>
       </c>
       <c r="F762" s="1" t="s">
         <v>5</v>
@@ -22337,19 +22334,19 @@
     </row>
     <row r="763" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A763" s="1" t="s">
+        <v>2069</v>
+      </c>
+      <c r="B763" s="1" t="s">
         <v>2070</v>
       </c>
-      <c r="B763" s="1" t="s">
+      <c r="C763" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D763" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E763" s="1" t="s">
         <v>2071</v>
-      </c>
-      <c r="C763" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D763" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E763" s="1" t="s">
-        <v>2072</v>
       </c>
       <c r="F763" s="1" t="s">
         <v>5</v>
@@ -22357,19 +22354,19 @@
     </row>
     <row r="764" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A764" s="1" t="s">
+        <v>2072</v>
+      </c>
+      <c r="B764" s="1" t="s">
+        <v>2055</v>
+      </c>
+      <c r="C764" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D764" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E764" s="1" t="s">
         <v>2073</v>
-      </c>
-      <c r="B764" s="1" t="s">
-        <v>2056</v>
-      </c>
-      <c r="C764" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D764" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E764" s="1" t="s">
-        <v>2074</v>
       </c>
       <c r="F764" s="1" t="s">
         <v>5</v>
@@ -22377,19 +22374,19 @@
     </row>
     <row r="765" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A765" s="1" t="s">
+        <v>2074</v>
+      </c>
+      <c r="B765" s="1" t="s">
         <v>2075</v>
       </c>
-      <c r="B765" s="1" t="s">
+      <c r="C765" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D765" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E765" s="1" t="s">
         <v>2076</v>
-      </c>
-      <c r="C765" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D765" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E765" s="1" t="s">
-        <v>2077</v>
       </c>
       <c r="F765" s="1" t="s">
         <v>5</v>
@@ -22397,19 +22394,19 @@
     </row>
     <row r="766" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A766" s="1" t="s">
+        <v>2077</v>
+      </c>
+      <c r="B766" s="1" t="s">
         <v>2078</v>
       </c>
-      <c r="B766" s="1" t="s">
+      <c r="C766" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D766" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E766" s="1" t="s">
         <v>2079</v>
-      </c>
-      <c r="C766" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D766" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E766" s="1" t="s">
-        <v>2080</v>
       </c>
       <c r="F766" s="1" t="s">
         <v>5</v>
@@ -22417,19 +22414,19 @@
     </row>
     <row r="767" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A767" s="1" t="s">
+        <v>2080</v>
+      </c>
+      <c r="B767" s="1" t="s">
         <v>2081</v>
       </c>
-      <c r="B767" s="1" t="s">
+      <c r="C767" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D767" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E767" s="1" t="s">
         <v>2082</v>
-      </c>
-      <c r="C767" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D767" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E767" s="1" t="s">
-        <v>2083</v>
       </c>
       <c r="F767" s="1" t="s">
         <v>5</v>
@@ -22437,7 +22434,7 @@
     </row>
     <row r="768" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A768" s="1" t="s">
-        <v>2084</v>
+        <v>2083</v>
       </c>
       <c r="B768" s="1" t="s">
         <v>1600</v>
@@ -22449,7 +22446,7 @@
         <v>4</v>
       </c>
       <c r="E768" s="1" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="F768" s="1" t="s">
         <v>5</v>
@@ -22457,19 +22454,19 @@
     </row>
     <row r="769" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A769" s="1" t="s">
+        <v>2085</v>
+      </c>
+      <c r="B769" s="1" t="s">
         <v>2086</v>
       </c>
-      <c r="B769" s="1" t="s">
+      <c r="C769" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D769" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E769" s="1" t="s">
         <v>2087</v>
-      </c>
-      <c r="C769" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D769" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E769" s="1" t="s">
-        <v>2088</v>
       </c>
       <c r="F769" s="1" t="s">
         <v>5</v>
@@ -22477,19 +22474,19 @@
     </row>
     <row r="770" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A770" s="1" t="s">
+        <v>2088</v>
+      </c>
+      <c r="B770" s="1" t="s">
         <v>2089</v>
       </c>
-      <c r="B770" s="1" t="s">
+      <c r="C770" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D770" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E770" s="1" t="s">
         <v>2090</v>
-      </c>
-      <c r="C770" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D770" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E770" s="1" t="s">
-        <v>2091</v>
       </c>
       <c r="F770" s="1" t="s">
         <v>5</v>
@@ -22497,19 +22494,19 @@
     </row>
     <row r="771" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A771" s="1" t="s">
+        <v>2091</v>
+      </c>
+      <c r="B771" s="1" t="s">
+        <v>2078</v>
+      </c>
+      <c r="C771" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D771" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E771" s="1" t="s">
         <v>2092</v>
-      </c>
-      <c r="B771" s="1" t="s">
-        <v>2079</v>
-      </c>
-      <c r="C771" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D771" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E771" s="1" t="s">
-        <v>2093</v>
       </c>
       <c r="F771" s="1" t="s">
         <v>5</v>
@@ -22517,19 +22514,19 @@
     </row>
     <row r="772" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A772" s="1" t="s">
+        <v>2093</v>
+      </c>
+      <c r="B772" s="1" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C772" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D772" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E772" s="1" t="s">
         <v>2094</v>
-      </c>
-      <c r="B772" s="1" t="s">
-        <v>2082</v>
-      </c>
-      <c r="C772" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D772" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E772" s="1" t="s">
-        <v>2095</v>
       </c>
       <c r="F772" s="1" t="s">
         <v>5</v>
@@ -22537,7 +22534,7 @@
     </row>
     <row r="773" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A773" s="1" t="s">
-        <v>2096</v>
+        <v>2095</v>
       </c>
       <c r="B773" s="1" t="s">
         <v>1600</v>
@@ -22549,7 +22546,7 @@
         <v>4</v>
       </c>
       <c r="E773" s="1" t="s">
-        <v>2097</v>
+        <v>2096</v>
       </c>
       <c r="F773" s="1" t="s">
         <v>5</v>
@@ -22557,19 +22554,19 @@
     </row>
     <row r="774" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A774" s="1" t="s">
+        <v>2097</v>
+      </c>
+      <c r="B774" s="1" t="s">
+        <v>2089</v>
+      </c>
+      <c r="C774" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D774" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E774" s="1" t="s">
         <v>2098</v>
-      </c>
-      <c r="B774" s="1" t="s">
-        <v>2090</v>
-      </c>
-      <c r="C774" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D774" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E774" s="1" t="s">
-        <v>2099</v>
       </c>
       <c r="F774" s="1" t="s">
         <v>5</v>
@@ -22577,19 +22574,19 @@
     </row>
     <row r="775" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A775" s="1" t="s">
+        <v>2099</v>
+      </c>
+      <c r="B775" s="1" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C775" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D775" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E775" s="1" t="s">
         <v>2100</v>
-      </c>
-      <c r="B775" s="1" t="s">
-        <v>2087</v>
-      </c>
-      <c r="C775" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D775" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E775" s="1" t="s">
-        <v>2101</v>
       </c>
       <c r="F775" s="1" t="s">
         <v>5</v>
@@ -22597,19 +22594,19 @@
     </row>
     <row r="776" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A776" s="1" t="s">
+        <v>2101</v>
+      </c>
+      <c r="B776" s="1" t="s">
+        <v>1490</v>
+      </c>
+      <c r="C776" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D776" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E776" s="1" t="s">
         <v>2102</v>
-      </c>
-      <c r="B776" s="1" t="s">
-        <v>1491</v>
-      </c>
-      <c r="C776" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D776" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E776" s="1" t="s">
-        <v>2103</v>
       </c>
       <c r="F776" s="1" t="s">
         <v>5</v>
@@ -22617,19 +22614,19 @@
     </row>
     <row r="777" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A777" s="1" t="s">
+        <v>2103</v>
+      </c>
+      <c r="B777" s="1" t="s">
         <v>2104</v>
       </c>
-      <c r="B777" s="1" t="s">
+      <c r="C777" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D777" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E777" s="1" t="s">
         <v>2105</v>
-      </c>
-      <c r="C777" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D777" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E777" s="1" t="s">
-        <v>2106</v>
       </c>
       <c r="F777" s="1" t="s">
         <v>5</v>
@@ -22637,7 +22634,7 @@
     </row>
     <row r="778" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A778" s="1" t="s">
-        <v>2107</v>
+        <v>2106</v>
       </c>
       <c r="B778" s="1" t="s">
         <v>139</v>
@@ -22649,7 +22646,7 @@
         <v>4</v>
       </c>
       <c r="E778" s="1" t="s">
-        <v>2108</v>
+        <v>2107</v>
       </c>
       <c r="F778" s="1" t="s">
         <v>5</v>
@@ -22657,19 +22654,19 @@
     </row>
     <row r="779" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A779" s="1" t="s">
+        <v>2108</v>
+      </c>
+      <c r="B779" s="1" t="s">
+        <v>2104</v>
+      </c>
+      <c r="C779" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D779" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E779" s="1" t="s">
         <v>2109</v>
-      </c>
-      <c r="B779" s="1" t="s">
-        <v>2105</v>
-      </c>
-      <c r="C779" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D779" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E779" s="1" t="s">
-        <v>2110</v>
       </c>
       <c r="F779" s="1" t="s">
         <v>5</v>
@@ -22677,7 +22674,7 @@
     </row>
     <row r="780" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A780" s="1" t="s">
-        <v>2111</v>
+        <v>2110</v>
       </c>
       <c r="B780" s="1" t="s">
         <v>139</v>
@@ -22689,7 +22686,7 @@
         <v>4</v>
       </c>
       <c r="E780" s="1" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="F780" s="1" t="s">
         <v>5</v>
@@ -22697,19 +22694,19 @@
     </row>
     <row r="781" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A781" s="1" t="s">
+        <v>2112</v>
+      </c>
+      <c r="B781" s="1" t="s">
         <v>2113</v>
       </c>
-      <c r="B781" s="1" t="s">
+      <c r="C781" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D781" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E781" s="1" t="s">
         <v>2114</v>
-      </c>
-      <c r="C781" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D781" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E781" s="1" t="s">
-        <v>2115</v>
       </c>
       <c r="F781" s="1" t="s">
         <v>5</v>
@@ -22717,19 +22714,19 @@
     </row>
     <row r="782" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A782" s="1" t="s">
+        <v>2115</v>
+      </c>
+      <c r="B782" s="1" t="s">
+        <v>2113</v>
+      </c>
+      <c r="C782" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D782" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E782" s="1" t="s">
         <v>2116</v>
-      </c>
-      <c r="B782" s="1" t="s">
-        <v>2114</v>
-      </c>
-      <c r="C782" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D782" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E782" s="1" t="s">
-        <v>2117</v>
       </c>
       <c r="F782" s="1" t="s">
         <v>5</v>
@@ -22737,19 +22734,19 @@
     </row>
     <row r="783" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A783" s="1" t="s">
+        <v>2117</v>
+      </c>
+      <c r="B783" s="1" t="s">
         <v>2118</v>
       </c>
-      <c r="B783" s="1" t="s">
+      <c r="C783" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D783" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E783" s="1" t="s">
         <v>2119</v>
-      </c>
-      <c r="C783" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D783" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E783" s="1" t="s">
-        <v>2120</v>
       </c>
       <c r="F783" s="1" t="s">
         <v>5</v>
@@ -22757,36 +22754,36 @@
     </row>
     <row r="784" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A784" s="1" t="s">
+        <v>2120</v>
+      </c>
+      <c r="B784" s="1" t="s">
         <v>2121</v>
       </c>
-      <c r="B784" s="1" t="s">
+      <c r="C784" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D784" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E784" s="1" t="s">
         <v>2122</v>
-      </c>
-      <c r="C784" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D784" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E784" s="1" t="s">
-        <v>2123</v>
       </c>
     </row>
     <row r="785" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A785" s="1" t="s">
+        <v>2123</v>
+      </c>
+      <c r="B785" s="1" t="s">
         <v>2124</v>
       </c>
-      <c r="B785" s="1" t="s">
+      <c r="C785" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D785" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E785" s="1" t="s">
         <v>2125</v>
-      </c>
-      <c r="C785" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D785" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E785" s="1" t="s">
-        <v>2126</v>
       </c>
       <c r="F785" s="1" t="s">
         <v>5</v>
@@ -22794,36 +22791,36 @@
     </row>
     <row r="786" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A786" s="1" t="s">
+        <v>2126</v>
+      </c>
+      <c r="B786" s="1" t="s">
         <v>2127</v>
       </c>
-      <c r="B786" s="1" t="s">
+      <c r="C786" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D786" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E786" s="1" t="s">
         <v>2128</v>
-      </c>
-      <c r="C786" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D786" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E786" s="1" t="s">
-        <v>2129</v>
       </c>
     </row>
     <row r="787" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A787" s="1" t="s">
+        <v>2129</v>
+      </c>
+      <c r="B787" s="1" t="s">
         <v>2130</v>
       </c>
-      <c r="B787" s="1" t="s">
+      <c r="C787" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D787" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E787" s="1" t="s">
         <v>2131</v>
-      </c>
-      <c r="C787" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D787" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E787" s="1" t="s">
-        <v>2132</v>
       </c>
       <c r="F787" s="1" t="s">
         <v>5</v>
@@ -22831,19 +22828,19 @@
     </row>
     <row r="788" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A788" s="1" t="s">
+        <v>2132</v>
+      </c>
+      <c r="B788" s="1" t="s">
         <v>2133</v>
       </c>
-      <c r="B788" s="1" t="s">
+      <c r="C788" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D788" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E788" s="1" t="s">
         <v>2134</v>
-      </c>
-      <c r="C788" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D788" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E788" s="1" t="s">
-        <v>2135</v>
       </c>
       <c r="F788" s="1" t="s">
         <v>5</v>
@@ -22851,19 +22848,19 @@
     </row>
     <row r="789" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A789" s="1" t="s">
+        <v>2135</v>
+      </c>
+      <c r="B789" s="1" t="s">
         <v>2136</v>
       </c>
-      <c r="B789" s="1" t="s">
+      <c r="C789" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D789" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E789" s="1" t="s">
         <v>2137</v>
-      </c>
-      <c r="C789" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D789" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E789" s="1" t="s">
-        <v>2138</v>
       </c>
       <c r="F789" s="1" t="s">
         <v>5</v>
@@ -22871,19 +22868,19 @@
     </row>
     <row r="790" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A790" s="1" t="s">
+        <v>2138</v>
+      </c>
+      <c r="B790" s="1" t="s">
+        <v>2130</v>
+      </c>
+      <c r="C790" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D790" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E790" s="1" t="s">
         <v>2139</v>
-      </c>
-      <c r="B790" s="1" t="s">
-        <v>2131</v>
-      </c>
-      <c r="C790" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D790" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E790" s="1" t="s">
-        <v>2140</v>
       </c>
       <c r="F790" s="1" t="s">
         <v>5</v>
@@ -22891,19 +22888,19 @@
     </row>
     <row r="791" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A791" s="1" t="s">
+        <v>2140</v>
+      </c>
+      <c r="B791" s="1" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C791" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D791" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E791" s="1" t="s">
         <v>2141</v>
-      </c>
-      <c r="B791" s="1" t="s">
-        <v>2134</v>
-      </c>
-      <c r="C791" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D791" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E791" s="1" t="s">
-        <v>2142</v>
       </c>
       <c r="F791" s="1" t="s">
         <v>5</v>
@@ -22911,19 +22908,19 @@
     </row>
     <row r="792" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A792" s="1" t="s">
+        <v>2142</v>
+      </c>
+      <c r="B792" s="1" t="s">
+        <v>2136</v>
+      </c>
+      <c r="C792" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D792" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E792" s="1" t="s">
         <v>2143</v>
-      </c>
-      <c r="B792" s="1" t="s">
-        <v>2137</v>
-      </c>
-      <c r="C792" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D792" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E792" s="1" t="s">
-        <v>2144</v>
       </c>
       <c r="F792" s="1" t="s">
         <v>5</v>
@@ -22931,19 +22928,19 @@
     </row>
     <row r="793" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A793" s="1" t="s">
+        <v>2144</v>
+      </c>
+      <c r="B793" s="1" t="s">
         <v>2145</v>
       </c>
-      <c r="B793" s="1" t="s">
+      <c r="C793" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D793" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E793" s="1" t="s">
         <v>2146</v>
-      </c>
-      <c r="C793" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D793" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E793" s="1" t="s">
-        <v>2147</v>
       </c>
       <c r="F793" s="1" t="s">
         <v>83</v>
@@ -22951,19 +22948,19 @@
     </row>
     <row r="794" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A794" s="1" t="s">
+        <v>2147</v>
+      </c>
+      <c r="B794" s="1" t="s">
         <v>2148</v>
       </c>
-      <c r="B794" s="1" t="s">
+      <c r="C794" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D794" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E794" s="1" t="s">
         <v>2149</v>
-      </c>
-      <c r="C794" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D794" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E794" s="1" t="s">
-        <v>2150</v>
       </c>
       <c r="F794" s="1" t="s">
         <v>83</v>
@@ -22971,19 +22968,19 @@
     </row>
     <row r="795" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A795" s="1" t="s">
+        <v>2150</v>
+      </c>
+      <c r="B795" s="1" t="s">
         <v>2151</v>
       </c>
-      <c r="B795" s="1" t="s">
+      <c r="C795" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D795" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E795" s="1" t="s">
         <v>2152</v>
-      </c>
-      <c r="C795" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D795" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E795" s="1" t="s">
-        <v>2153</v>
       </c>
       <c r="F795" s="1" t="s">
         <v>83</v>
@@ -22991,19 +22988,19 @@
     </row>
     <row r="796" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A796" s="1" t="s">
+        <v>2153</v>
+      </c>
+      <c r="B796" s="1" t="s">
         <v>2154</v>
       </c>
-      <c r="B796" s="1" t="s">
+      <c r="C796" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D796" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E796" s="1" t="s">
         <v>2155</v>
-      </c>
-      <c r="C796" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D796" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E796" s="1" t="s">
-        <v>2156</v>
       </c>
       <c r="F796" s="1" t="s">
         <v>83</v>
@@ -23011,19 +23008,19 @@
     </row>
     <row r="797" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A797" s="1" t="s">
+        <v>2156</v>
+      </c>
+      <c r="B797" s="1" t="s">
         <v>2157</v>
       </c>
-      <c r="B797" s="1" t="s">
+      <c r="C797" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D797" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E797" s="1" t="s">
         <v>2158</v>
-      </c>
-      <c r="C797" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D797" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E797" s="1" t="s">
-        <v>2159</v>
       </c>
       <c r="F797" s="1" t="s">
         <v>83</v>
@@ -23031,19 +23028,19 @@
     </row>
     <row r="798" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A798" s="1" t="s">
+        <v>2159</v>
+      </c>
+      <c r="B798" s="1" t="s">
         <v>2160</v>
       </c>
-      <c r="B798" s="1" t="s">
+      <c r="C798" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D798" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E798" s="1" t="s">
         <v>2161</v>
-      </c>
-      <c r="C798" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D798" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E798" s="1" t="s">
-        <v>2162</v>
       </c>
       <c r="F798" s="1" t="s">
         <v>83</v>
@@ -23051,19 +23048,19 @@
     </row>
     <row r="799" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A799" s="1" t="s">
+        <v>2162</v>
+      </c>
+      <c r="B799" s="1" t="s">
         <v>2163</v>
       </c>
-      <c r="B799" s="1" t="s">
+      <c r="C799" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D799" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E799" s="1" t="s">
         <v>2164</v>
-      </c>
-      <c r="C799" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D799" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E799" s="1" t="s">
-        <v>2165</v>
       </c>
       <c r="F799" s="1" t="s">
         <v>83</v>
@@ -23071,19 +23068,19 @@
     </row>
     <row r="800" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A800" s="1" t="s">
+        <v>2165</v>
+      </c>
+      <c r="B800" s="1" t="s">
         <v>2166</v>
       </c>
-      <c r="B800" s="1" t="s">
+      <c r="C800" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D800" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E800" s="1" t="s">
         <v>2167</v>
-      </c>
-      <c r="C800" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D800" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E800" s="1" t="s">
-        <v>2168</v>
       </c>
       <c r="F800" s="1" t="s">
         <v>5</v>
@@ -23091,19 +23088,19 @@
     </row>
     <row r="801" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A801" s="1" t="s">
+        <v>2168</v>
+      </c>
+      <c r="B801" s="1" t="s">
         <v>2169</v>
       </c>
-      <c r="B801" s="1" t="s">
+      <c r="C801" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D801" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E801" s="1" t="s">
         <v>2170</v>
-      </c>
-      <c r="C801" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D801" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E801" s="1" t="s">
-        <v>2171</v>
       </c>
       <c r="F801" s="1" t="s">
         <v>5</v>
@@ -23111,19 +23108,19 @@
     </row>
     <row r="802" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A802" s="1" t="s">
+        <v>2171</v>
+      </c>
+      <c r="B802" s="1" t="s">
         <v>2172</v>
       </c>
-      <c r="B802" s="1" t="s">
+      <c r="C802" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D802" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E802" s="1" t="s">
         <v>2173</v>
-      </c>
-      <c r="C802" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D802" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E802" s="1" t="s">
-        <v>2174</v>
       </c>
       <c r="F802" s="1" t="s">
         <v>5</v>
@@ -23131,19 +23128,19 @@
     </row>
     <row r="803" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A803" s="1" t="s">
+        <v>2174</v>
+      </c>
+      <c r="B803" s="1" t="s">
         <v>2175</v>
       </c>
-      <c r="B803" s="1" t="s">
+      <c r="C803" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D803" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E803" s="1" t="s">
         <v>2176</v>
-      </c>
-      <c r="C803" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D803" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E803" s="1" t="s">
-        <v>2177</v>
       </c>
       <c r="F803" s="1" t="s">
         <v>5</v>
@@ -23151,19 +23148,19 @@
     </row>
     <row r="804" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A804" s="1" t="s">
+        <v>2177</v>
+      </c>
+      <c r="B804" s="1" t="s">
         <v>2178</v>
       </c>
-      <c r="B804" s="1" t="s">
+      <c r="C804" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D804" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E804" s="1" t="s">
         <v>2179</v>
-      </c>
-      <c r="C804" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D804" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E804" s="1" t="s">
-        <v>2180</v>
       </c>
       <c r="F804" s="1" t="s">
         <v>5</v>
@@ -23171,19 +23168,19 @@
     </row>
     <row r="805" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A805" s="1" t="s">
+        <v>2180</v>
+      </c>
+      <c r="B805" s="1" t="s">
+        <v>2160</v>
+      </c>
+      <c r="C805" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D805" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E805" s="1" t="s">
         <v>2181</v>
-      </c>
-      <c r="B805" s="1" t="s">
-        <v>2161</v>
-      </c>
-      <c r="C805" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D805" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E805" s="1" t="s">
-        <v>2182</v>
       </c>
       <c r="F805" s="1" t="s">
         <v>5</v>
@@ -23191,19 +23188,19 @@
     </row>
     <row r="806" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A806" s="1" t="s">
+        <v>2182</v>
+      </c>
+      <c r="B806" s="1" t="s">
+        <v>2163</v>
+      </c>
+      <c r="C806" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D806" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E806" s="1" t="s">
         <v>2183</v>
-      </c>
-      <c r="B806" s="1" t="s">
-        <v>2164</v>
-      </c>
-      <c r="C806" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D806" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E806" s="1" t="s">
-        <v>2184</v>
       </c>
       <c r="F806" s="1" t="s">
         <v>5</v>
@@ -23211,39 +23208,39 @@
     </row>
     <row r="807" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A807" s="1" t="s">
+        <v>2184</v>
+      </c>
+      <c r="B807" s="1" t="s">
         <v>2185</v>
       </c>
-      <c r="B807" s="1" t="s">
+      <c r="C807" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D807" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E807" s="1" t="s">
         <v>2186</v>
       </c>
-      <c r="C807" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D807" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E807" s="1" t="s">
+      <c r="F807" s="1" t="s">
         <v>2187</v>
-      </c>
-      <c r="F807" s="1" t="s">
-        <v>2188</v>
       </c>
     </row>
     <row r="808" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A808" s="1" t="s">
+        <v>2188</v>
+      </c>
+      <c r="B808" s="1" t="s">
         <v>2189</v>
       </c>
-      <c r="B808" s="1" t="s">
+      <c r="C808" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D808" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E808" s="1" t="s">
         <v>2190</v>
-      </c>
-      <c r="C808" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D808" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E808" s="1" t="s">
-        <v>2191</v>
       </c>
       <c r="F808" s="1" t="s">
         <v>5</v>
@@ -23251,7 +23248,7 @@
     </row>
     <row r="809" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A809" s="1" t="s">
-        <v>2192</v>
+        <v>2191</v>
       </c>
       <c r="B809" s="1" t="s">
         <v>1985</v>
@@ -23263,7 +23260,7 @@
         <v>4</v>
       </c>
       <c r="E809" s="1" t="s">
-        <v>2193</v>
+        <v>2192</v>
       </c>
       <c r="F809" s="1" t="s">
         <v>5</v>
@@ -23271,19 +23268,19 @@
     </row>
     <row r="810" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A810" s="1" t="s">
+        <v>2193</v>
+      </c>
+      <c r="B810" s="1" t="s">
+        <v>2040</v>
+      </c>
+      <c r="C810" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D810" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E810" s="1" t="s">
         <v>2194</v>
-      </c>
-      <c r="B810" s="1" t="s">
-        <v>2041</v>
-      </c>
-      <c r="C810" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D810" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E810" s="1" t="s">
-        <v>2195</v>
       </c>
       <c r="F810" s="1" t="s">
         <v>5</v>
@@ -23291,19 +23288,19 @@
     </row>
     <row r="811" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A811" s="1" t="s">
+        <v>2195</v>
+      </c>
+      <c r="B811" s="1" t="s">
         <v>2196</v>
       </c>
-      <c r="B811" s="1" t="s">
+      <c r="C811" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D811" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E811" s="1" t="s">
         <v>2197</v>
-      </c>
-      <c r="C811" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D811" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E811" s="1" t="s">
-        <v>2198</v>
       </c>
       <c r="F811" s="1" t="s">
         <v>5</v>
@@ -23311,19 +23308,19 @@
     </row>
     <row r="812" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A812" s="1" t="s">
+        <v>2198</v>
+      </c>
+      <c r="B812" s="1" t="s">
         <v>2199</v>
       </c>
-      <c r="B812" s="1" t="s">
+      <c r="C812" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D812" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E812" s="1" t="s">
         <v>2200</v>
-      </c>
-      <c r="C812" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D812" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E812" s="1" t="s">
-        <v>2201</v>
       </c>
       <c r="F812" s="1" t="s">
         <v>5</v>
@@ -23331,19 +23328,19 @@
     </row>
     <row r="813" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A813" s="1" t="s">
+        <v>2201</v>
+      </c>
+      <c r="B813" s="1" t="s">
         <v>2202</v>
       </c>
-      <c r="B813" s="1" t="s">
+      <c r="C813" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D813" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E813" s="1" t="s">
         <v>2203</v>
-      </c>
-      <c r="C813" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D813" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E813" s="1" t="s">
-        <v>2204</v>
       </c>
       <c r="F813" s="1" t="s">
         <v>5</v>
@@ -23351,19 +23348,19 @@
     </row>
     <row r="814" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A814" s="1" t="s">
+        <v>2204</v>
+      </c>
+      <c r="B814" s="1" t="s">
         <v>2205</v>
       </c>
-      <c r="B814" s="1" t="s">
+      <c r="C814" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D814" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E814" s="1" t="s">
         <v>2206</v>
-      </c>
-      <c r="C814" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D814" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E814" s="1" t="s">
-        <v>2207</v>
       </c>
       <c r="F814" s="1" t="s">
         <v>5</v>
@@ -23371,19 +23368,19 @@
     </row>
     <row r="815" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A815" s="1" t="s">
+        <v>2207</v>
+      </c>
+      <c r="B815" s="1" t="s">
         <v>2208</v>
       </c>
-      <c r="B815" s="1" t="s">
+      <c r="C815" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D815" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E815" s="1" t="s">
         <v>2209</v>
-      </c>
-      <c r="C815" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D815" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E815" s="1" t="s">
-        <v>2210</v>
       </c>
       <c r="F815" s="1" t="s">
         <v>5</v>
@@ -23391,189 +23388,189 @@
     </row>
     <row r="816" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A816" s="1" t="s">
+        <v>2210</v>
+      </c>
+      <c r="B816" s="1" t="s">
         <v>2211</v>
       </c>
-      <c r="B816" s="1" t="s">
+      <c r="C816" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D816" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E816" s="1" t="s">
         <v>2212</v>
-      </c>
-      <c r="C816" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D816" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E816" s="1" t="s">
-        <v>2213</v>
       </c>
     </row>
     <row r="817" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A817" s="1" t="s">
+        <v>2213</v>
+      </c>
+      <c r="B817" s="1" t="s">
         <v>2214</v>
       </c>
-      <c r="B817" s="1" t="s">
+      <c r="C817" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D817" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E817" s="1" t="s">
         <v>2215</v>
-      </c>
-      <c r="C817" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D817" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E817" s="1" t="s">
-        <v>2216</v>
       </c>
     </row>
     <row r="818" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A818" s="1" t="s">
+        <v>2216</v>
+      </c>
+      <c r="B818" s="1" t="s">
         <v>2217</v>
       </c>
-      <c r="B818" s="1" t="s">
+      <c r="C818" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D818" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E818" s="1" t="s">
         <v>2218</v>
-      </c>
-      <c r="C818" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D818" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E818" s="1" t="s">
-        <v>2219</v>
       </c>
     </row>
     <row r="819" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A819" s="1" t="s">
+        <v>2219</v>
+      </c>
+      <c r="B819" s="1" t="s">
         <v>2220</v>
       </c>
-      <c r="B819" s="1" t="s">
+      <c r="C819" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D819" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E819" s="1" t="s">
         <v>2221</v>
-      </c>
-      <c r="C819" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D819" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E819" s="1" t="s">
-        <v>2222</v>
       </c>
     </row>
     <row r="820" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A820" s="1" t="s">
+        <v>2222</v>
+      </c>
+      <c r="B820" s="1" t="s">
+        <v>2211</v>
+      </c>
+      <c r="C820" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D820" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E820" s="1" t="s">
         <v>2223</v>
-      </c>
-      <c r="B820" s="1" t="s">
-        <v>2212</v>
-      </c>
-      <c r="C820" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D820" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E820" s="1" t="s">
-        <v>2224</v>
       </c>
     </row>
     <row r="821" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A821" s="1" t="s">
+        <v>2224</v>
+      </c>
+      <c r="B821" s="1" t="s">
+        <v>2214</v>
+      </c>
+      <c r="C821" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D821" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E821" s="1" t="s">
         <v>2225</v>
-      </c>
-      <c r="B821" s="1" t="s">
-        <v>2215</v>
-      </c>
-      <c r="C821" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D821" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E821" s="1" t="s">
-        <v>2226</v>
       </c>
     </row>
     <row r="822" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A822" s="1" t="s">
+        <v>2226</v>
+      </c>
+      <c r="B822" s="1" t="s">
+        <v>2217</v>
+      </c>
+      <c r="C822" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D822" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E822" s="1" t="s">
         <v>2227</v>
-      </c>
-      <c r="B822" s="1" t="s">
-        <v>2218</v>
-      </c>
-      <c r="C822" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D822" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E822" s="1" t="s">
-        <v>2228</v>
       </c>
     </row>
     <row r="823" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A823" s="1" t="s">
+        <v>2228</v>
+      </c>
+      <c r="B823" s="1" t="s">
+        <v>2220</v>
+      </c>
+      <c r="C823" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D823" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E823" s="1" t="s">
         <v>2229</v>
-      </c>
-      <c r="B823" s="1" t="s">
-        <v>2221</v>
-      </c>
-      <c r="C823" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D823" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E823" s="1" t="s">
-        <v>2230</v>
       </c>
     </row>
     <row r="824" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A824" s="1" t="s">
+        <v>2230</v>
+      </c>
+      <c r="B824" s="1" t="s">
         <v>2231</v>
       </c>
-      <c r="B824" s="1" t="s">
+      <c r="C824" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D824" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E824" s="1" t="s">
         <v>2232</v>
-      </c>
-      <c r="C824" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D824" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E824" s="1" t="s">
-        <v>2233</v>
       </c>
     </row>
     <row r="825" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A825" s="1" t="s">
+        <v>2233</v>
+      </c>
+      <c r="B825" s="1" t="s">
         <v>2234</v>
       </c>
-      <c r="B825" s="1" t="s">
+      <c r="C825" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D825" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E825" s="1" t="s">
         <v>2235</v>
-      </c>
-      <c r="C825" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D825" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E825" s="1" t="s">
-        <v>2236</v>
       </c>
     </row>
     <row r="826" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A826" s="1" t="s">
+        <v>2236</v>
+      </c>
+      <c r="B826" s="1" t="s">
         <v>2237</v>
       </c>
-      <c r="B826" s="1" t="s">
+      <c r="C826" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D826" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E826" s="1" t="s">
         <v>2238</v>
-      </c>
-      <c r="C826" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D826" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E826" s="1" t="s">
-        <v>2239</v>
       </c>
       <c r="F826" s="1" t="s">
         <v>5</v>
@@ -23581,70 +23578,70 @@
     </row>
     <row r="827" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A827" s="1" t="s">
+        <v>2239</v>
+      </c>
+      <c r="B827" s="1" t="s">
+        <v>2231</v>
+      </c>
+      <c r="C827" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D827" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E827" s="1" t="s">
         <v>2240</v>
-      </c>
-      <c r="B827" s="1" t="s">
-        <v>2232</v>
-      </c>
-      <c r="C827" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D827" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E827" s="1" t="s">
-        <v>2241</v>
       </c>
     </row>
     <row r="828" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A828" s="1" t="s">
+        <v>2241</v>
+      </c>
+      <c r="B828" s="1" t="s">
+        <v>2234</v>
+      </c>
+      <c r="C828" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D828" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E828" s="1" t="s">
         <v>2242</v>
-      </c>
-      <c r="B828" s="1" t="s">
-        <v>2235</v>
-      </c>
-      <c r="C828" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D828" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E828" s="1" t="s">
-        <v>2243</v>
       </c>
     </row>
     <row r="829" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A829" s="1" t="s">
+        <v>2243</v>
+      </c>
+      <c r="B829" s="1" t="s">
+        <v>2237</v>
+      </c>
+      <c r="C829" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D829" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E829" s="1" t="s">
         <v>2244</v>
-      </c>
-      <c r="B829" s="1" t="s">
-        <v>2238</v>
-      </c>
-      <c r="C829" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D829" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E829" s="1" t="s">
-        <v>2245</v>
       </c>
     </row>
     <row r="830" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A830" s="1" t="s">
+        <v>2245</v>
+      </c>
+      <c r="B830" s="1" t="s">
         <v>2246</v>
       </c>
-      <c r="B830" s="1" t="s">
+      <c r="C830" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D830" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E830" s="1" t="s">
         <v>2247</v>
-      </c>
-      <c r="C830" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D830" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E830" s="1" t="s">
-        <v>2248</v>
       </c>
       <c r="F830" s="1" t="s">
         <v>5</v>
@@ -23652,19 +23649,19 @@
     </row>
     <row r="831" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A831" s="1" t="s">
+        <v>2248</v>
+      </c>
+      <c r="B831" s="1" t="s">
         <v>2249</v>
       </c>
-      <c r="B831" s="1" t="s">
+      <c r="C831" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D831" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E831" s="1" t="s">
         <v>2250</v>
-      </c>
-      <c r="C831" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D831" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E831" s="1" t="s">
-        <v>2251</v>
       </c>
       <c r="F831" s="1" t="s">
         <v>5</v>
@@ -23672,19 +23669,19 @@
     </row>
     <row r="832" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A832" s="1" t="s">
+        <v>2251</v>
+      </c>
+      <c r="B832" s="1" t="s">
         <v>2252</v>
       </c>
-      <c r="B832" s="1" t="s">
+      <c r="C832" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D832" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E832" s="1" t="s">
         <v>2253</v>
-      </c>
-      <c r="C832" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D832" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E832" s="1" t="s">
-        <v>2254</v>
       </c>
       <c r="F832" s="1" t="s">
         <v>5</v>
@@ -23692,19 +23689,19 @@
     </row>
     <row r="833" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A833" s="1" t="s">
+        <v>2254</v>
+      </c>
+      <c r="B833" s="1" t="s">
         <v>2255</v>
       </c>
-      <c r="B833" s="1" t="s">
+      <c r="C833" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D833" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E833" s="1" t="s">
         <v>2256</v>
-      </c>
-      <c r="C833" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D833" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E833" s="1" t="s">
-        <v>2257</v>
       </c>
       <c r="F833" s="1" t="s">
         <v>5</v>
@@ -23712,19 +23709,19 @@
     </row>
     <row r="834" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A834" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="B834" s="1" t="s">
         <v>2258</v>
       </c>
-      <c r="B834" s="1" t="s">
+      <c r="C834" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D834" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E834" s="1" t="s">
         <v>2259</v>
-      </c>
-      <c r="C834" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D834" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E834" s="1" t="s">
-        <v>2260</v>
       </c>
       <c r="F834" s="1" t="s">
         <v>5</v>
@@ -23732,19 +23729,19 @@
     </row>
     <row r="835" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A835" s="1" t="s">
+        <v>2260</v>
+      </c>
+      <c r="B835" s="1" t="s">
         <v>2261</v>
       </c>
-      <c r="B835" s="1" t="s">
+      <c r="C835" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D835" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E835" s="1" t="s">
         <v>2262</v>
-      </c>
-      <c r="C835" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D835" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E835" s="1" t="s">
-        <v>2263</v>
       </c>
       <c r="F835" s="1" t="s">
         <v>5</v>
@@ -23752,19 +23749,19 @@
     </row>
     <row r="836" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A836" s="1" t="s">
+        <v>2263</v>
+      </c>
+      <c r="B836" s="1" t="s">
         <v>2264</v>
       </c>
-      <c r="B836" s="1" t="s">
+      <c r="C836" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D836" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E836" s="1" t="s">
         <v>2265</v>
-      </c>
-      <c r="C836" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D836" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E836" s="1" t="s">
-        <v>2266</v>
       </c>
       <c r="F836" s="1" t="s">
         <v>5</v>
@@ -23772,19 +23769,19 @@
     </row>
     <row r="837" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A837" s="1" t="s">
+        <v>2266</v>
+      </c>
+      <c r="B837" s="1" t="s">
         <v>2267</v>
       </c>
-      <c r="B837" s="1" t="s">
+      <c r="C837" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D837" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E837" s="1" t="s">
         <v>2268</v>
-      </c>
-      <c r="C837" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D837" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E837" s="1" t="s">
-        <v>2269</v>
       </c>
       <c r="F837" s="1" t="s">
         <v>5</v>
@@ -23792,19 +23789,19 @@
     </row>
     <row r="838" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A838" s="1" t="s">
+        <v>2269</v>
+      </c>
+      <c r="B838" s="1" t="s">
         <v>2270</v>
       </c>
-      <c r="B838" s="1" t="s">
+      <c r="C838" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D838" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E838" s="1" t="s">
         <v>2271</v>
-      </c>
-      <c r="C838" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D838" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E838" s="1" t="s">
-        <v>2272</v>
       </c>
       <c r="F838" s="1" t="s">
         <v>5</v>
@@ -23812,19 +23809,19 @@
     </row>
     <row r="839" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A839" s="1" t="s">
+        <v>2272</v>
+      </c>
+      <c r="B839" s="1" t="s">
         <v>2273</v>
       </c>
-      <c r="B839" s="1" t="s">
+      <c r="C839" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D839" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E839" s="1" t="s">
         <v>2274</v>
-      </c>
-      <c r="C839" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D839" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E839" s="1" t="s">
-        <v>2275</v>
       </c>
       <c r="F839" s="1" t="s">
         <v>5</v>
@@ -23832,19 +23829,19 @@
     </row>
     <row r="840" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A840" s="1" t="s">
+        <v>2275</v>
+      </c>
+      <c r="B840" s="1" t="s">
+        <v>2261</v>
+      </c>
+      <c r="C840" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D840" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E840" s="1" t="s">
         <v>2276</v>
-      </c>
-      <c r="B840" s="1" t="s">
-        <v>2262</v>
-      </c>
-      <c r="C840" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D840" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E840" s="1" t="s">
-        <v>2277</v>
       </c>
       <c r="F840" s="1" t="s">
         <v>5</v>
@@ -23852,19 +23849,19 @@
     </row>
     <row r="841" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A841" s="1" t="s">
+        <v>2277</v>
+      </c>
+      <c r="B841" s="1" t="s">
+        <v>2264</v>
+      </c>
+      <c r="C841" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D841" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E841" s="1" t="s">
         <v>2278</v>
-      </c>
-      <c r="B841" s="1" t="s">
-        <v>2265</v>
-      </c>
-      <c r="C841" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D841" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E841" s="1" t="s">
-        <v>2279</v>
       </c>
       <c r="F841" s="1" t="s">
         <v>5</v>
@@ -23872,19 +23869,19 @@
     </row>
     <row r="842" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A842" s="1" t="s">
+        <v>2279</v>
+      </c>
+      <c r="B842" s="1" t="s">
         <v>2280</v>
       </c>
-      <c r="B842" s="1" t="s">
+      <c r="C842" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D842" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E842" s="1" t="s">
         <v>2281</v>
-      </c>
-      <c r="C842" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D842" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E842" s="1" t="s">
-        <v>2282</v>
       </c>
       <c r="F842" s="1" t="s">
         <v>5</v>
@@ -23892,19 +23889,19 @@
     </row>
     <row r="843" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A843" s="1" t="s">
+        <v>2282</v>
+      </c>
+      <c r="B843" s="1" t="s">
         <v>2283</v>
       </c>
-      <c r="B843" s="1" t="s">
+      <c r="C843" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D843" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E843" s="1" t="s">
         <v>2284</v>
-      </c>
-      <c r="C843" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D843" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E843" s="1" t="s">
-        <v>2285</v>
       </c>
       <c r="F843" s="1" t="s">
         <v>5</v>
@@ -23912,19 +23909,19 @@
     </row>
     <row r="844" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A844" s="1" t="s">
+        <v>2285</v>
+      </c>
+      <c r="B844" s="1" t="s">
+        <v>2273</v>
+      </c>
+      <c r="C844" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D844" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E844" s="1" t="s">
         <v>2286</v>
-      </c>
-      <c r="B844" s="1" t="s">
-        <v>2274</v>
-      </c>
-      <c r="C844" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D844" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E844" s="1" t="s">
-        <v>2287</v>
       </c>
       <c r="F844" s="1" t="s">
         <v>5</v>
@@ -23932,19 +23929,19 @@
     </row>
     <row r="845" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A845" s="1" t="s">
+        <v>2287</v>
+      </c>
+      <c r="B845" s="1" t="s">
         <v>2288</v>
       </c>
-      <c r="B845" s="1" t="s">
+      <c r="C845" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D845" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E845" s="1" t="s">
         <v>2289</v>
-      </c>
-      <c r="C845" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D845" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E845" s="1" t="s">
-        <v>2290</v>
       </c>
       <c r="F845" s="1" t="s">
         <v>5</v>
@@ -23952,19 +23949,19 @@
     </row>
     <row r="846" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A846" s="1" t="s">
+        <v>2290</v>
+      </c>
+      <c r="B846" s="1" t="s">
         <v>2291</v>
       </c>
-      <c r="B846" s="1" t="s">
+      <c r="C846" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D846" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E846" s="1" t="s">
         <v>2292</v>
-      </c>
-      <c r="C846" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D846" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E846" s="1" t="s">
-        <v>2293</v>
       </c>
       <c r="F846" s="1" t="s">
         <v>5</v>
@@ -23972,19 +23969,19 @@
     </row>
     <row r="847" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A847" s="1" t="s">
+        <v>2293</v>
+      </c>
+      <c r="B847" s="1" t="s">
         <v>2294</v>
       </c>
-      <c r="B847" s="1" t="s">
+      <c r="C847" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D847" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E847" s="1" t="s">
         <v>2295</v>
-      </c>
-      <c r="C847" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D847" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E847" s="1" t="s">
-        <v>2296</v>
       </c>
       <c r="F847" s="1" t="s">
         <v>5</v>
@@ -23992,70 +23989,70 @@
     </row>
     <row r="848" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A848" s="1" t="s">
+        <v>2296</v>
+      </c>
+      <c r="B848" s="1" t="s">
         <v>2297</v>
       </c>
-      <c r="B848" s="1" t="s">
+      <c r="C848" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D848" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E848" s="1" t="s">
         <v>2298</v>
-      </c>
-      <c r="C848" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D848" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E848" s="1" t="s">
-        <v>2299</v>
       </c>
     </row>
     <row r="849" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A849" s="1" t="s">
+        <v>2299</v>
+      </c>
+      <c r="B849" s="1" t="s">
         <v>2300</v>
       </c>
-      <c r="B849" s="1" t="s">
+      <c r="C849" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D849" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E849" s="1" t="s">
         <v>2301</v>
-      </c>
-      <c r="C849" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D849" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E849" s="1" t="s">
-        <v>2302</v>
       </c>
     </row>
     <row r="850" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A850" s="1" t="s">
+        <v>2302</v>
+      </c>
+      <c r="B850" s="1" t="s">
         <v>2303</v>
       </c>
-      <c r="B850" s="1" t="s">
+      <c r="C850" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D850" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E850" s="1" t="s">
         <v>2304</v>
-      </c>
-      <c r="C850" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D850" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E850" s="1" t="s">
-        <v>2305</v>
       </c>
     </row>
     <row r="851" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A851" s="1" t="s">
+        <v>2305</v>
+      </c>
+      <c r="B851" s="1" t="s">
         <v>2306</v>
       </c>
-      <c r="B851" s="1" t="s">
+      <c r="C851" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D851" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E851" s="1" t="s">
         <v>2307</v>
-      </c>
-      <c r="C851" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D851" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E851" s="1" t="s">
-        <v>2308</v>
       </c>
       <c r="F851" s="1" t="s">
         <v>5</v>
@@ -24063,19 +24060,19 @@
     </row>
     <row r="852" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A852" s="1" t="s">
+        <v>2308</v>
+      </c>
+      <c r="B852" s="1" t="s">
         <v>2309</v>
       </c>
-      <c r="B852" s="1" t="s">
+      <c r="C852" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D852" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E852" s="1" t="s">
         <v>2310</v>
-      </c>
-      <c r="C852" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D852" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E852" s="1" t="s">
-        <v>2311</v>
       </c>
       <c r="F852" s="1" t="s">
         <v>5</v>
@@ -24083,19 +24080,19 @@
     </row>
     <row r="853" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A853" s="1" t="s">
+        <v>2311</v>
+      </c>
+      <c r="B853" s="1" t="s">
         <v>2312</v>
       </c>
-      <c r="B853" s="1" t="s">
+      <c r="C853" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D853" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E853" s="1" t="s">
         <v>2313</v>
-      </c>
-      <c r="C853" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D853" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E853" s="1" t="s">
-        <v>2314</v>
       </c>
       <c r="F853" s="1" t="s">
         <v>5</v>
@@ -24103,19 +24100,19 @@
     </row>
     <row r="854" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A854" s="1" t="s">
+        <v>2314</v>
+      </c>
+      <c r="B854" s="1" t="s">
         <v>2315</v>
       </c>
-      <c r="B854" s="1" t="s">
+      <c r="C854" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D854" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E854" s="1" t="s">
         <v>2316</v>
-      </c>
-      <c r="C854" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D854" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E854" s="1" t="s">
-        <v>2317</v>
       </c>
       <c r="F854" s="1" t="s">
         <v>5</v>
@@ -24123,19 +24120,19 @@
     </row>
     <row r="855" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A855" s="1" t="s">
+        <v>2317</v>
+      </c>
+      <c r="B855" s="1" t="s">
         <v>2318</v>
       </c>
-      <c r="B855" s="1" t="s">
+      <c r="C855" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D855" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E855" s="1" t="s">
         <v>2319</v>
-      </c>
-      <c r="C855" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D855" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E855" s="1" t="s">
-        <v>2320</v>
       </c>
       <c r="F855" s="1" t="s">
         <v>5</v>
@@ -24143,19 +24140,19 @@
     </row>
     <row r="856" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A856" s="1" t="s">
+        <v>2320</v>
+      </c>
+      <c r="B856" s="1" t="s">
         <v>2321</v>
       </c>
-      <c r="B856" s="1" t="s">
+      <c r="C856" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D856" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E856" s="1" t="s">
         <v>2322</v>
-      </c>
-      <c r="C856" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D856" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E856" s="1" t="s">
-        <v>2323</v>
       </c>
       <c r="F856" s="1" t="s">
         <v>5</v>
@@ -24163,19 +24160,19 @@
     </row>
     <row r="857" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A857" s="1" t="s">
+        <v>2323</v>
+      </c>
+      <c r="B857" s="1" t="s">
         <v>2324</v>
       </c>
-      <c r="B857" s="1" t="s">
+      <c r="C857" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D857" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E857" s="1" t="s">
         <v>2325</v>
-      </c>
-      <c r="C857" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D857" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E857" s="1" t="s">
-        <v>2326</v>
       </c>
       <c r="F857" s="1" t="s">
         <v>5</v>
@@ -24183,19 +24180,19 @@
     </row>
     <row r="858" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A858" s="1" t="s">
+        <v>2326</v>
+      </c>
+      <c r="B858" s="1" t="s">
         <v>2327</v>
       </c>
-      <c r="B858" s="1" t="s">
+      <c r="C858" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D858" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E858" s="1" t="s">
         <v>2328</v>
-      </c>
-      <c r="C858" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D858" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E858" s="1" t="s">
-        <v>2329</v>
       </c>
       <c r="F858" s="1" t="s">
         <v>5</v>
@@ -24203,19 +24200,19 @@
     </row>
     <row r="859" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A859" s="1" t="s">
+        <v>2329</v>
+      </c>
+      <c r="B859" s="1" t="s">
+        <v>2306</v>
+      </c>
+      <c r="C859" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D859" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E859" s="1" t="s">
         <v>2330</v>
-      </c>
-      <c r="B859" s="1" t="s">
-        <v>2307</v>
-      </c>
-      <c r="C859" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D859" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E859" s="1" t="s">
-        <v>2331</v>
       </c>
       <c r="F859" s="1" t="s">
         <v>5</v>
@@ -24223,19 +24220,19 @@
     </row>
     <row r="860" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A860" s="1" t="s">
+        <v>2331</v>
+      </c>
+      <c r="B860" s="1" t="s">
+        <v>2309</v>
+      </c>
+      <c r="C860" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D860" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E860" s="1" t="s">
         <v>2332</v>
-      </c>
-      <c r="B860" s="1" t="s">
-        <v>2310</v>
-      </c>
-      <c r="C860" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D860" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E860" s="1" t="s">
-        <v>2333</v>
       </c>
       <c r="F860" s="1" t="s">
         <v>5</v>
@@ -24243,19 +24240,19 @@
     </row>
     <row r="861" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A861" s="1" t="s">
+        <v>2333</v>
+      </c>
+      <c r="B861" s="1" t="s">
+        <v>2312</v>
+      </c>
+      <c r="C861" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D861" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E861" s="1" t="s">
         <v>2334</v>
-      </c>
-      <c r="B861" s="1" t="s">
-        <v>2313</v>
-      </c>
-      <c r="C861" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D861" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E861" s="1" t="s">
-        <v>2335</v>
       </c>
       <c r="F861" s="1" t="s">
         <v>5</v>
@@ -24263,19 +24260,19 @@
     </row>
     <row r="862" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A862" s="1" t="s">
+        <v>2335</v>
+      </c>
+      <c r="B862" s="1" t="s">
+        <v>2315</v>
+      </c>
+      <c r="C862" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D862" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E862" s="1" t="s">
         <v>2336</v>
-      </c>
-      <c r="B862" s="1" t="s">
-        <v>2316</v>
-      </c>
-      <c r="C862" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D862" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E862" s="1" t="s">
-        <v>2337</v>
       </c>
       <c r="F862" s="1" t="s">
         <v>5</v>
@@ -24283,19 +24280,19 @@
     </row>
     <row r="863" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A863" s="1" t="s">
+        <v>2337</v>
+      </c>
+      <c r="B863" s="1" t="s">
+        <v>2318</v>
+      </c>
+      <c r="C863" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D863" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E863" s="1" t="s">
         <v>2338</v>
-      </c>
-      <c r="B863" s="1" t="s">
-        <v>2319</v>
-      </c>
-      <c r="C863" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D863" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E863" s="1" t="s">
-        <v>2339</v>
       </c>
       <c r="F863" s="1" t="s">
         <v>5</v>
@@ -24303,19 +24300,19 @@
     </row>
     <row r="864" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A864" s="1" t="s">
+        <v>2339</v>
+      </c>
+      <c r="B864" s="1" t="s">
+        <v>2321</v>
+      </c>
+      <c r="C864" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D864" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E864" s="1" t="s">
         <v>2340</v>
-      </c>
-      <c r="B864" s="1" t="s">
-        <v>2322</v>
-      </c>
-      <c r="C864" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D864" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E864" s="1" t="s">
-        <v>2341</v>
       </c>
       <c r="F864" s="1" t="s">
         <v>5</v>
@@ -24323,19 +24320,19 @@
     </row>
     <row r="865" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A865" s="1" t="s">
+        <v>2341</v>
+      </c>
+      <c r="B865" s="1" t="s">
         <v>2342</v>
       </c>
-      <c r="B865" s="1" t="s">
+      <c r="C865" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D865" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E865" s="1" t="s">
         <v>2343</v>
-      </c>
-      <c r="C865" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D865" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E865" s="1" t="s">
-        <v>2344</v>
       </c>
       <c r="F865" s="1" t="s">
         <v>5</v>
@@ -24343,19 +24340,19 @@
     </row>
     <row r="866" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A866" s="1" t="s">
+        <v>2344</v>
+      </c>
+      <c r="B866" s="1" t="s">
+        <v>2327</v>
+      </c>
+      <c r="C866" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D866" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E866" s="1" t="s">
         <v>2345</v>
-      </c>
-      <c r="B866" s="1" t="s">
-        <v>2328</v>
-      </c>
-      <c r="C866" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D866" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E866" s="1" t="s">
-        <v>2346</v>
       </c>
       <c r="F866" s="1" t="s">
         <v>5</v>
@@ -24363,70 +24360,70 @@
     </row>
     <row r="867" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A867" s="1" t="s">
+        <v>2346</v>
+      </c>
+      <c r="B867" s="1" t="s">
         <v>2347</v>
       </c>
-      <c r="B867" s="1" t="s">
+      <c r="C867" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D867" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E867" s="1" t="s">
         <v>2348</v>
-      </c>
-      <c r="C867" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D867" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E867" s="1" t="s">
-        <v>2349</v>
       </c>
     </row>
     <row r="868" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A868" s="1" t="s">
+        <v>2349</v>
+      </c>
+      <c r="B868" s="1" t="s">
         <v>2350</v>
       </c>
-      <c r="B868" s="1" t="s">
+      <c r="C868" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D868" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E868" s="1" t="s">
         <v>2351</v>
-      </c>
-      <c r="C868" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D868" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E868" s="1" t="s">
-        <v>2352</v>
       </c>
     </row>
     <row r="869" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A869" s="1" t="s">
+        <v>2352</v>
+      </c>
+      <c r="B869" s="1" t="s">
         <v>2353</v>
       </c>
-      <c r="B869" s="1" t="s">
+      <c r="C869" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D869" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E869" s="1" t="s">
         <v>2354</v>
-      </c>
-      <c r="C869" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D869" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E869" s="1" t="s">
-        <v>2355</v>
       </c>
     </row>
     <row r="870" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A870" s="1" t="s">
+        <v>2355</v>
+      </c>
+      <c r="B870" s="1" t="s">
         <v>2356</v>
       </c>
-      <c r="B870" s="1" t="s">
+      <c r="C870" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D870" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E870" s="1" t="s">
         <v>2357</v>
-      </c>
-      <c r="C870" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D870" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E870" s="1" t="s">
-        <v>2358</v>
       </c>
     </row>
     <row r="871" spans="1:6" x14ac:dyDescent="0.25">
@@ -24443,7 +24440,7 @@
         <v>4</v>
       </c>
       <c r="E871" s="1" t="s">
-        <v>2359</v>
+        <v>2358</v>
       </c>
       <c r="F871" s="1" t="s">
         <v>5</v>
@@ -24451,19 +24448,19 @@
     </row>
     <row r="872" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A872" s="1" t="s">
+        <v>2359</v>
+      </c>
+      <c r="B872" s="1" t="s">
         <v>2360</v>
       </c>
-      <c r="B872" s="1" t="s">
+      <c r="C872" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D872" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E872" s="1" t="s">
         <v>2361</v>
-      </c>
-      <c r="C872" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D872" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E872" s="1" t="s">
-        <v>2362</v>
       </c>
       <c r="F872" s="1" t="s">
         <v>5</v>
@@ -24471,19 +24468,19 @@
     </row>
     <row r="873" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A873" s="1" t="s">
+        <v>2362</v>
+      </c>
+      <c r="B873" s="1" t="s">
         <v>2363</v>
       </c>
-      <c r="B873" s="1" t="s">
+      <c r="C873" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D873" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E873" s="1" t="s">
         <v>2364</v>
-      </c>
-      <c r="C873" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D873" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E873" s="1" t="s">
-        <v>2365</v>
       </c>
       <c r="F873" s="1" t="s">
         <v>5</v>
@@ -24491,19 +24488,19 @@
     </row>
     <row r="874" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A874" s="1" t="s">
+        <v>2365</v>
+      </c>
+      <c r="B874" s="1" t="s">
         <v>2366</v>
       </c>
-      <c r="B874" s="1" t="s">
+      <c r="C874" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D874" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E874" s="1" t="s">
         <v>2367</v>
-      </c>
-      <c r="C874" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D874" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E874" s="1" t="s">
-        <v>2368</v>
       </c>
       <c r="F874" s="1" t="s">
         <v>5</v>
@@ -24511,19 +24508,19 @@
     </row>
     <row r="875" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A875" s="1" t="s">
+        <v>2368</v>
+      </c>
+      <c r="B875" s="1" t="s">
         <v>2369</v>
       </c>
-      <c r="B875" s="1" t="s">
+      <c r="C875" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D875" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E875" s="1" t="s">
         <v>2370</v>
-      </c>
-      <c r="C875" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D875" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E875" s="1" t="s">
-        <v>2371</v>
       </c>
       <c r="F875" s="1" t="s">
         <v>5</v>
@@ -24531,19 +24528,19 @@
     </row>
     <row r="876" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A876" s="1" t="s">
+        <v>2371</v>
+      </c>
+      <c r="B876" s="1" t="s">
         <v>2372</v>
       </c>
-      <c r="B876" s="1" t="s">
+      <c r="C876" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D876" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E876" s="1" t="s">
         <v>2373</v>
-      </c>
-      <c r="C876" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D876" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E876" s="1" t="s">
-        <v>2374</v>
       </c>
       <c r="F876" s="1" t="s">
         <v>5</v>
@@ -24551,19 +24548,19 @@
     </row>
     <row r="877" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A877" s="1" t="s">
+        <v>2374</v>
+      </c>
+      <c r="B877" s="1" t="s">
         <v>2375</v>
       </c>
-      <c r="B877" s="1" t="s">
+      <c r="C877" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D877" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E877" s="1" t="s">
         <v>2376</v>
-      </c>
-      <c r="C877" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D877" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E877" s="1" t="s">
-        <v>2377</v>
       </c>
       <c r="F877" s="1" t="s">
         <v>5</v>

--- a/E/MKTN.xlsx
+++ b/E/MKTN.xlsx
@@ -577,7 +577,7 @@
     <t>20107602</t>
   </si>
   <si>
-    <t>TLKMS GGMAX FIT 6GB</t>
+    <t>TLKMS SRU.NTN5G1G14H</t>
   </si>
   <si>
     <t>40</t>
@@ -6958,7 +6958,7 @@
     <t>20140486</t>
   </si>
   <si>
-    <t>TLKMSL GGAMX 55K 3GB</t>
+    <t>TLKMS SR.NTN11G4G30H</t>
   </si>
   <si>
     <t>935</t>

--- a/E/MKTN.xlsx
+++ b/E/MKTN.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5125" uniqueCount="2380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5161" uniqueCount="2393">
   <si>
     <t/>
   </si>
@@ -4624,18 +4624,12 @@
     <t>20131141</t>
   </si>
   <si>
-    <t>INDST FRDM 16GB 30HR</t>
-  </si>
-  <si>
     <t>628</t>
   </si>
   <si>
     <t>20131142</t>
   </si>
   <si>
-    <t>INDST FRDM 22GB 30HR</t>
-  </si>
-  <si>
     <t>629</t>
   </si>
   <si>
@@ -4834,9 +4828,6 @@
     <t>20131453</t>
   </si>
   <si>
-    <t>INDST FDM 35GB 85K</t>
-  </si>
-  <si>
     <t>659</t>
   </si>
   <si>
@@ -7151,6 +7142,54 @@
   </si>
   <si>
     <t>961</t>
+  </si>
+  <si>
+    <t>20142767</t>
+  </si>
+  <si>
+    <t>FOLAPLAY BLA GMBRA 7</t>
+  </si>
+  <si>
+    <t>1003</t>
+  </si>
+  <si>
+    <t>20142768</t>
+  </si>
+  <si>
+    <t>FOLAPLAY BLA GMBRA30</t>
+  </si>
+  <si>
+    <t>1004</t>
+  </si>
+  <si>
+    <t>20142769</t>
+  </si>
+  <si>
+    <t>1005</t>
+  </si>
+  <si>
+    <t>20142770</t>
+  </si>
+  <si>
+    <t>1006</t>
+  </si>
+  <si>
+    <t>20142825</t>
+  </si>
+  <si>
+    <t>BOLA GMBR MAXSTRM 7H</t>
+  </si>
+  <si>
+    <t>1007</t>
+  </si>
+  <si>
+    <t>20142826</t>
+  </si>
+  <si>
+    <t>BOLA GMBR MXSTRM 7HR</t>
+  </si>
+  <si>
+    <t>1008</t>
   </si>
 </sst>
 </file>
@@ -7543,14 +7582,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F883"/>
+  <dimension ref="A1:F889"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="3" customWidth="1"/>
-    <col min="5" max="5" width="5" customWidth="1"/>
+    <col min="5" max="5" width="6" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
@@ -18326,16 +18365,16 @@
         <v>1536</v>
       </c>
       <c r="B562" s="1" t="s">
+        <v>1519</v>
+      </c>
+      <c r="C562" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D562" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E562" s="1" t="s">
         <v>1537</v>
-      </c>
-      <c r="C562" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D562" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E562" s="1" t="s">
-        <v>1538</v>
       </c>
       <c r="F562" s="1" t="s">
         <v>5</v>
@@ -18343,19 +18382,19 @@
     </row>
     <row r="563" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A563" s="1" t="s">
+        <v>1538</v>
+      </c>
+      <c r="B563" s="1" t="s">
+        <v>1522</v>
+      </c>
+      <c r="C563" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D563" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E563" s="1" t="s">
         <v>1539</v>
-      </c>
-      <c r="B563" s="1" t="s">
-        <v>1540</v>
-      </c>
-      <c r="C563" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D563" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E563" s="1" t="s">
-        <v>1541</v>
       </c>
       <c r="F563" s="1" t="s">
         <v>5</v>
@@ -18363,7 +18402,7 @@
     </row>
     <row r="564" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A564" s="1" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="B564" s="1" t="s">
         <v>1525</v>
@@ -18375,7 +18414,7 @@
         <v>4</v>
       </c>
       <c r="E564" s="1" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="F564" s="1" t="s">
         <v>5</v>
@@ -18383,7 +18422,7 @@
     </row>
     <row r="565" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A565" s="1" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="B565" s="1" t="s">
         <v>1528</v>
@@ -18395,7 +18434,7 @@
         <v>4</v>
       </c>
       <c r="E565" s="1" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="F565" s="1" t="s">
         <v>5</v>
@@ -18403,19 +18442,19 @@
     </row>
     <row r="566" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A566" s="1" t="s">
+        <v>1544</v>
+      </c>
+      <c r="B566" s="1" t="s">
+        <v>1545</v>
+      </c>
+      <c r="C566" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D566" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E566" s="1" t="s">
         <v>1546</v>
-      </c>
-      <c r="B566" s="1" t="s">
-        <v>1547</v>
-      </c>
-      <c r="C566" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D566" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E566" s="1" t="s">
-        <v>1548</v>
       </c>
       <c r="F566" s="1" t="s">
         <v>5</v>
@@ -18423,19 +18462,19 @@
     </row>
     <row r="567" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A567" s="1" t="s">
+        <v>1547</v>
+      </c>
+      <c r="B567" s="1" t="s">
+        <v>1548</v>
+      </c>
+      <c r="C567" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D567" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E567" s="1" t="s">
         <v>1549</v>
-      </c>
-      <c r="B567" s="1" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C567" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D567" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E567" s="1" t="s">
-        <v>1551</v>
       </c>
       <c r="F567" s="1" t="s">
         <v>5</v>
@@ -18443,10 +18482,10 @@
     </row>
     <row r="568" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A568" s="1" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="B568" s="1" t="s">
-        <v>1550</v>
+        <v>1548</v>
       </c>
       <c r="C568" s="1" t="s">
         <v>3</v>
@@ -18455,7 +18494,7 @@
         <v>4</v>
       </c>
       <c r="E568" s="1" t="s">
-        <v>1553</v>
+        <v>1551</v>
       </c>
       <c r="F568" s="1" t="s">
         <v>5</v>
@@ -18463,19 +18502,19 @@
     </row>
     <row r="569" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A569" s="1" t="s">
+        <v>1552</v>
+      </c>
+      <c r="B569" s="1" t="s">
+        <v>1553</v>
+      </c>
+      <c r="C569" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D569" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E569" s="1" t="s">
         <v>1554</v>
-      </c>
-      <c r="B569" s="1" t="s">
-        <v>1555</v>
-      </c>
-      <c r="C569" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D569" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E569" s="1" t="s">
-        <v>1556</v>
       </c>
       <c r="F569" s="1" t="s">
         <v>5</v>
@@ -18483,19 +18522,19 @@
     </row>
     <row r="570" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A570" s="1" t="s">
+        <v>1555</v>
+      </c>
+      <c r="B570" s="1" t="s">
+        <v>1556</v>
+      </c>
+      <c r="C570" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D570" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E570" s="1" t="s">
         <v>1557</v>
-      </c>
-      <c r="B570" s="1" t="s">
-        <v>1558</v>
-      </c>
-      <c r="C570" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D570" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E570" s="1" t="s">
-        <v>1559</v>
       </c>
       <c r="F570" s="1" t="s">
         <v>96</v>
@@ -18503,19 +18542,19 @@
     </row>
     <row r="571" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A571" s="1" t="s">
+        <v>1558</v>
+      </c>
+      <c r="B571" s="1" t="s">
+        <v>1559</v>
+      </c>
+      <c r="C571" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D571" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E571" s="1" t="s">
         <v>1560</v>
-      </c>
-      <c r="B571" s="1" t="s">
-        <v>1561</v>
-      </c>
-      <c r="C571" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D571" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E571" s="1" t="s">
-        <v>1562</v>
       </c>
       <c r="F571" s="1" t="s">
         <v>96</v>
@@ -18523,19 +18562,19 @@
     </row>
     <row r="572" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A572" s="1" t="s">
+        <v>1561</v>
+      </c>
+      <c r="B572" s="1" t="s">
+        <v>1562</v>
+      </c>
+      <c r="C572" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D572" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E572" s="1" t="s">
         <v>1563</v>
-      </c>
-      <c r="B572" s="1" t="s">
-        <v>1564</v>
-      </c>
-      <c r="C572" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D572" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E572" s="1" t="s">
-        <v>1565</v>
       </c>
       <c r="F572" s="1" t="s">
         <v>5</v>
@@ -18543,19 +18582,19 @@
     </row>
     <row r="573" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A573" s="1" t="s">
+        <v>1564</v>
+      </c>
+      <c r="B573" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="C573" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D573" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E573" s="1" t="s">
         <v>1566</v>
-      </c>
-      <c r="B573" s="1" t="s">
-        <v>1567</v>
-      </c>
-      <c r="C573" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D573" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E573" s="1" t="s">
-        <v>1568</v>
       </c>
       <c r="F573" s="1" t="s">
         <v>5</v>
@@ -18563,19 +18602,19 @@
     </row>
     <row r="574" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A574" s="1" t="s">
+        <v>1567</v>
+      </c>
+      <c r="B574" s="1" t="s">
+        <v>1568</v>
+      </c>
+      <c r="C574" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D574" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E574" s="1" t="s">
         <v>1569</v>
-      </c>
-      <c r="B574" s="1" t="s">
-        <v>1570</v>
-      </c>
-      <c r="C574" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D574" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E574" s="1" t="s">
-        <v>1571</v>
       </c>
       <c r="F574" s="1" t="s">
         <v>5</v>
@@ -18583,19 +18622,19 @@
     </row>
     <row r="575" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A575" s="1" t="s">
+        <v>1570</v>
+      </c>
+      <c r="B575" s="1" t="s">
+        <v>1571</v>
+      </c>
+      <c r="C575" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D575" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E575" s="1" t="s">
         <v>1572</v>
-      </c>
-      <c r="B575" s="1" t="s">
-        <v>1573</v>
-      </c>
-      <c r="C575" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D575" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E575" s="1" t="s">
-        <v>1574</v>
       </c>
       <c r="F575" s="1" t="s">
         <v>5</v>
@@ -18603,19 +18642,19 @@
     </row>
     <row r="576" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A576" s="1" t="s">
+        <v>1573</v>
+      </c>
+      <c r="B576" s="1" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C576" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D576" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E576" s="1" t="s">
         <v>1575</v>
-      </c>
-      <c r="B576" s="1" t="s">
-        <v>1576</v>
-      </c>
-      <c r="C576" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D576" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E576" s="1" t="s">
-        <v>1577</v>
       </c>
       <c r="F576" s="1" t="s">
         <v>5</v>
@@ -18623,10 +18662,10 @@
     </row>
     <row r="577" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A577" s="1" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="B577" s="1" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="C577" s="1" t="s">
         <v>3</v>
@@ -18635,7 +18674,7 @@
         <v>4</v>
       </c>
       <c r="E577" s="1" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="F577" s="1" t="s">
         <v>5</v>
@@ -18643,10 +18682,10 @@
     </row>
     <row r="578" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A578" s="1" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="B578" s="1" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="C578" s="1" t="s">
         <v>3</v>
@@ -18655,7 +18694,7 @@
         <v>4</v>
       </c>
       <c r="E578" s="1" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="F578" s="1" t="s">
         <v>5</v>
@@ -18663,10 +18702,10 @@
     </row>
     <row r="579" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A579" s="1" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="B579" s="1" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="C579" s="1" t="s">
         <v>3</v>
@@ -18675,7 +18714,7 @@
         <v>4</v>
       </c>
       <c r="E579" s="1" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
       <c r="F579" s="1" t="s">
         <v>5</v>
@@ -18695,7 +18734,7 @@
         <v>4</v>
       </c>
       <c r="E580" s="1" t="s">
-        <v>1584</v>
+        <v>1582</v>
       </c>
       <c r="F580" s="1" t="s">
         <v>5</v>
@@ -18715,7 +18754,7 @@
         <v>4</v>
       </c>
       <c r="E581" s="1" t="s">
-        <v>1585</v>
+        <v>1583</v>
       </c>
       <c r="F581" s="1" t="s">
         <v>5</v>
@@ -18735,7 +18774,7 @@
         <v>4</v>
       </c>
       <c r="E582" s="1" t="s">
-        <v>1586</v>
+        <v>1584</v>
       </c>
       <c r="F582" s="1" t="s">
         <v>5</v>
@@ -18755,7 +18794,7 @@
         <v>4</v>
       </c>
       <c r="E583" s="1" t="s">
-        <v>1587</v>
+        <v>1585</v>
       </c>
       <c r="F583" s="1" t="s">
         <v>5</v>
@@ -18763,19 +18802,19 @@
     </row>
     <row r="584" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A584" s="1" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B584" s="1" t="s">
+        <v>1587</v>
+      </c>
+      <c r="C584" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D584" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E584" s="1" t="s">
         <v>1588</v>
-      </c>
-      <c r="B584" s="1" t="s">
-        <v>1589</v>
-      </c>
-      <c r="C584" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D584" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E584" s="1" t="s">
-        <v>1590</v>
       </c>
       <c r="F584" s="1" t="s">
         <v>96</v>
@@ -18783,19 +18822,19 @@
     </row>
     <row r="585" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A585" s="1" t="s">
+        <v>1589</v>
+      </c>
+      <c r="B585" s="1" t="s">
+        <v>1590</v>
+      </c>
+      <c r="C585" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D585" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E585" s="1" t="s">
         <v>1591</v>
-      </c>
-      <c r="B585" s="1" t="s">
-        <v>1592</v>
-      </c>
-      <c r="C585" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D585" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E585" s="1" t="s">
-        <v>1593</v>
       </c>
       <c r="F585" s="1" t="s">
         <v>96</v>
@@ -18803,19 +18842,19 @@
     </row>
     <row r="586" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A586" s="1" t="s">
+        <v>1592</v>
+      </c>
+      <c r="B586" s="1" t="s">
+        <v>1593</v>
+      </c>
+      <c r="C586" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D586" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E586" s="1" t="s">
         <v>1594</v>
-      </c>
-      <c r="B586" s="1" t="s">
-        <v>1595</v>
-      </c>
-      <c r="C586" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D586" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E586" s="1" t="s">
-        <v>1596</v>
       </c>
       <c r="F586" s="1" t="s">
         <v>96</v>
@@ -18823,19 +18862,19 @@
     </row>
     <row r="587" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A587" s="1" t="s">
+        <v>1595</v>
+      </c>
+      <c r="B587" s="1" t="s">
+        <v>1596</v>
+      </c>
+      <c r="C587" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D587" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E587" s="1" t="s">
         <v>1597</v>
-      </c>
-      <c r="B587" s="1" t="s">
-        <v>1598</v>
-      </c>
-      <c r="C587" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D587" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E587" s="1" t="s">
-        <v>1599</v>
       </c>
       <c r="F587" s="1" t="s">
         <v>96</v>
@@ -18843,19 +18882,19 @@
     </row>
     <row r="588" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A588" s="1" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B588" s="1" t="s">
+        <v>1599</v>
+      </c>
+      <c r="C588" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D588" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E588" s="1" t="s">
         <v>1600</v>
-      </c>
-      <c r="B588" s="1" t="s">
-        <v>1601</v>
-      </c>
-      <c r="C588" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D588" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E588" s="1" t="s">
-        <v>1602</v>
       </c>
       <c r="F588" s="1" t="s">
         <v>5</v>
@@ -18863,19 +18902,19 @@
     </row>
     <row r="589" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A589" s="1" t="s">
+        <v>1601</v>
+      </c>
+      <c r="B589" s="1" t="s">
+        <v>1602</v>
+      </c>
+      <c r="C589" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D589" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E589" s="1" t="s">
         <v>1603</v>
-      </c>
-      <c r="B589" s="1" t="s">
-        <v>1604</v>
-      </c>
-      <c r="C589" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D589" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E589" s="1" t="s">
-        <v>1605</v>
       </c>
       <c r="F589" s="1" t="s">
         <v>5</v>
@@ -18883,10 +18922,10 @@
     </row>
     <row r="590" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A590" s="1" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="B590" s="1" t="s">
-        <v>1607</v>
+        <v>1599</v>
       </c>
       <c r="C590" s="1" t="s">
         <v>3</v>
@@ -18895,7 +18934,7 @@
         <v>4</v>
       </c>
       <c r="E590" s="1" t="s">
-        <v>1608</v>
+        <v>1605</v>
       </c>
       <c r="F590" s="1" t="s">
         <v>5</v>
@@ -18903,10 +18942,10 @@
     </row>
     <row r="591" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A591" s="1" t="s">
-        <v>1609</v>
+        <v>1606</v>
       </c>
       <c r="B591" s="1" t="s">
-        <v>1604</v>
+        <v>1602</v>
       </c>
       <c r="C591" s="1" t="s">
         <v>3</v>
@@ -18915,7 +18954,7 @@
         <v>4</v>
       </c>
       <c r="E591" s="1" t="s">
-        <v>1610</v>
+        <v>1607</v>
       </c>
       <c r="F591" s="1" t="s">
         <v>5</v>
@@ -18923,10 +18962,10 @@
     </row>
     <row r="592" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A592" s="1" t="s">
-        <v>1611</v>
+        <v>1608</v>
       </c>
       <c r="B592" s="1" t="s">
-        <v>1612</v>
+        <v>1609</v>
       </c>
       <c r="C592" s="1" t="s">
         <v>3</v>
@@ -18935,7 +18974,7 @@
         <v>4</v>
       </c>
       <c r="E592" s="1" t="s">
-        <v>1613</v>
+        <v>1610</v>
       </c>
       <c r="F592" s="1" t="s">
         <v>5</v>
@@ -18943,19 +18982,19 @@
     </row>
     <row r="593" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A593" s="1" t="s">
-        <v>1614</v>
+        <v>1611</v>
       </c>
       <c r="B593" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="C593" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D593" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E593" s="1" t="s">
         <v>1612</v>
-      </c>
-      <c r="C593" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D593" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E593" s="1" t="s">
-        <v>1615</v>
       </c>
       <c r="F593" s="1" t="s">
         <v>5</v>
@@ -18963,10 +19002,10 @@
     </row>
     <row r="594" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A594" s="1" t="s">
-        <v>1616</v>
+        <v>1613</v>
       </c>
       <c r="B594" s="1" t="s">
-        <v>1617</v>
+        <v>1614</v>
       </c>
       <c r="C594" s="1" t="s">
         <v>3</v>
@@ -18975,7 +19014,7 @@
         <v>4</v>
       </c>
       <c r="E594" s="1" t="s">
-        <v>1618</v>
+        <v>1615</v>
       </c>
       <c r="F594" s="1" t="s">
         <v>5</v>
@@ -18983,19 +19022,19 @@
     </row>
     <row r="595" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A595" s="1" t="s">
-        <v>1619</v>
+        <v>1616</v>
       </c>
       <c r="B595" s="1" t="s">
+        <v>1614</v>
+      </c>
+      <c r="C595" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D595" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E595" s="1" t="s">
         <v>1617</v>
-      </c>
-      <c r="C595" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D595" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E595" s="1" t="s">
-        <v>1620</v>
       </c>
       <c r="F595" s="1" t="s">
         <v>5</v>
@@ -19003,10 +19042,10 @@
     </row>
     <row r="596" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A596" s="1" t="s">
-        <v>1621</v>
+        <v>1618</v>
       </c>
       <c r="B596" s="1" t="s">
-        <v>1622</v>
+        <v>1619</v>
       </c>
       <c r="C596" s="1" t="s">
         <v>3</v>
@@ -19015,7 +19054,7 @@
         <v>4</v>
       </c>
       <c r="E596" s="1" t="s">
-        <v>1623</v>
+        <v>1620</v>
       </c>
       <c r="F596" s="1" t="s">
         <v>5</v>
@@ -19023,19 +19062,19 @@
     </row>
     <row r="597" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A597" s="1" t="s">
-        <v>1624</v>
+        <v>1621</v>
       </c>
       <c r="B597" s="1" t="s">
+        <v>1619</v>
+      </c>
+      <c r="C597" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D597" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E597" s="1" t="s">
         <v>1622</v>
-      </c>
-      <c r="C597" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D597" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E597" s="1" t="s">
-        <v>1625</v>
       </c>
       <c r="F597" s="1" t="s">
         <v>5</v>
@@ -19043,10 +19082,10 @@
     </row>
     <row r="598" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A598" s="1" t="s">
-        <v>1626</v>
+        <v>1623</v>
       </c>
       <c r="B598" s="1" t="s">
-        <v>1627</v>
+        <v>1624</v>
       </c>
       <c r="C598" s="1" t="s">
         <v>3</v>
@@ -19055,7 +19094,7 @@
         <v>4</v>
       </c>
       <c r="E598" s="1" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
       <c r="F598" s="1" t="s">
         <v>5</v>
@@ -19063,10 +19102,10 @@
     </row>
     <row r="599" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A599" s="1" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
       <c r="B599" s="1" t="s">
-        <v>1630</v>
+        <v>1627</v>
       </c>
       <c r="C599" s="1" t="s">
         <v>3</v>
@@ -19075,7 +19114,7 @@
         <v>4</v>
       </c>
       <c r="E599" s="1" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
       <c r="F599" s="1" t="s">
         <v>5</v>
@@ -19083,10 +19122,10 @@
     </row>
     <row r="600" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A600" s="1" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
       <c r="B600" s="1" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
       <c r="C600" s="1" t="s">
         <v>3</v>
@@ -19095,7 +19134,7 @@
         <v>4</v>
       </c>
       <c r="E600" s="1" t="s">
-        <v>1634</v>
+        <v>1631</v>
       </c>
       <c r="F600" s="1" t="s">
         <v>5</v>
@@ -19103,10 +19142,10 @@
     </row>
     <row r="601" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A601" s="1" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
       <c r="B601" s="1" t="s">
-        <v>1630</v>
+        <v>1627</v>
       </c>
       <c r="C601" s="1" t="s">
         <v>3</v>
@@ -19115,7 +19154,7 @@
         <v>4</v>
       </c>
       <c r="E601" s="1" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
       <c r="F601" s="1" t="s">
         <v>5</v>
@@ -19123,10 +19162,10 @@
     </row>
     <row r="602" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A602" s="1" t="s">
-        <v>1637</v>
+        <v>1634</v>
       </c>
       <c r="B602" s="1" t="s">
-        <v>1638</v>
+        <v>1635</v>
       </c>
       <c r="C602" s="1" t="s">
         <v>3</v>
@@ -19135,7 +19174,7 @@
         <v>4</v>
       </c>
       <c r="E602" s="1" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
       <c r="F602" s="1" t="s">
         <v>5</v>
@@ -19143,10 +19182,10 @@
     </row>
     <row r="603" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A603" s="1" t="s">
-        <v>1640</v>
+        <v>1637</v>
       </c>
       <c r="B603" s="1" t="s">
-        <v>1641</v>
+        <v>1638</v>
       </c>
       <c r="C603" s="1" t="s">
         <v>3</v>
@@ -19155,7 +19194,7 @@
         <v>4</v>
       </c>
       <c r="E603" s="1" t="s">
-        <v>1642</v>
+        <v>1639</v>
       </c>
       <c r="F603" s="1" t="s">
         <v>5</v>
@@ -19163,10 +19202,10 @@
     </row>
     <row r="604" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A604" s="1" t="s">
-        <v>1643</v>
+        <v>1640</v>
       </c>
       <c r="B604" s="1" t="s">
-        <v>1644</v>
+        <v>1641</v>
       </c>
       <c r="C604" s="1" t="s">
         <v>3</v>
@@ -19175,7 +19214,7 @@
         <v>4</v>
       </c>
       <c r="E604" s="1" t="s">
-        <v>1645</v>
+        <v>1642</v>
       </c>
       <c r="F604" s="1" t="s">
         <v>5</v>
@@ -19183,10 +19222,10 @@
     </row>
     <row r="605" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A605" s="1" t="s">
-        <v>1646</v>
+        <v>1643</v>
       </c>
       <c r="B605" s="1" t="s">
-        <v>1647</v>
+        <v>1644</v>
       </c>
       <c r="C605" s="1" t="s">
         <v>3</v>
@@ -19195,7 +19234,7 @@
         <v>4</v>
       </c>
       <c r="E605" s="1" t="s">
-        <v>1648</v>
+        <v>1645</v>
       </c>
       <c r="F605" s="1" t="s">
         <v>5</v>
@@ -19203,10 +19242,10 @@
     </row>
     <row r="606" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A606" s="1" t="s">
-        <v>1649</v>
+        <v>1646</v>
       </c>
       <c r="B606" s="1" t="s">
-        <v>1650</v>
+        <v>1647</v>
       </c>
       <c r="C606" s="1" t="s">
         <v>3</v>
@@ -19215,7 +19254,7 @@
         <v>4</v>
       </c>
       <c r="E606" s="1" t="s">
-        <v>1651</v>
+        <v>1648</v>
       </c>
       <c r="F606" s="1" t="s">
         <v>5</v>
@@ -19223,10 +19262,10 @@
     </row>
     <row r="607" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A607" s="1" t="s">
-        <v>1652</v>
+        <v>1649</v>
       </c>
       <c r="B607" s="1" t="s">
-        <v>1653</v>
+        <v>1650</v>
       </c>
       <c r="C607" s="1" t="s">
         <v>3</v>
@@ -19235,7 +19274,7 @@
         <v>4</v>
       </c>
       <c r="E607" s="1" t="s">
-        <v>1654</v>
+        <v>1651</v>
       </c>
       <c r="F607" s="1" t="s">
         <v>5</v>
@@ -19243,19 +19282,19 @@
     </row>
     <row r="608" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A608" s="1" t="s">
-        <v>1655</v>
+        <v>1652</v>
       </c>
       <c r="B608" s="1" t="s">
+        <v>1650</v>
+      </c>
+      <c r="C608" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D608" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E608" s="1" t="s">
         <v>1653</v>
-      </c>
-      <c r="C608" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D608" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E608" s="1" t="s">
-        <v>1656</v>
       </c>
       <c r="F608" s="1" t="s">
         <v>5</v>
@@ -19263,10 +19302,10 @@
     </row>
     <row r="609" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A609" s="1" t="s">
-        <v>1657</v>
+        <v>1654</v>
       </c>
       <c r="B609" s="1" t="s">
-        <v>1658</v>
+        <v>1655</v>
       </c>
       <c r="C609" s="1" t="s">
         <v>3</v>
@@ -19275,7 +19314,7 @@
         <v>4</v>
       </c>
       <c r="E609" s="1" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
       <c r="F609" s="1" t="s">
         <v>5</v>
@@ -19283,10 +19322,10 @@
     </row>
     <row r="610" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A610" s="1" t="s">
-        <v>1660</v>
+        <v>1657</v>
       </c>
       <c r="B610" s="1" t="s">
-        <v>1661</v>
+        <v>1658</v>
       </c>
       <c r="C610" s="1" t="s">
         <v>3</v>
@@ -19295,7 +19334,7 @@
         <v>4</v>
       </c>
       <c r="E610" s="1" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
       <c r="F610" s="1" t="s">
         <v>5</v>
@@ -19303,10 +19342,10 @@
     </row>
     <row r="611" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A611" s="1" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="B611" s="1" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
       <c r="C611" s="1" t="s">
         <v>3</v>
@@ -19315,7 +19354,7 @@
         <v>4</v>
       </c>
       <c r="E611" s="1" t="s">
-        <v>1665</v>
+        <v>1662</v>
       </c>
       <c r="F611" s="1" t="s">
         <v>5</v>
@@ -19323,10 +19362,10 @@
     </row>
     <row r="612" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A612" s="1" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
       <c r="B612" s="1" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
       <c r="C612" s="1" t="s">
         <v>3</v>
@@ -19335,7 +19374,7 @@
         <v>4</v>
       </c>
       <c r="E612" s="1" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="F612" s="1" t="s">
         <v>5</v>
@@ -19343,10 +19382,10 @@
     </row>
     <row r="613" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A613" s="1" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="B613" s="1" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
       <c r="C613" s="1" t="s">
         <v>3</v>
@@ -19355,7 +19394,7 @@
         <v>4</v>
       </c>
       <c r="E613" s="1" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="F613" s="1" t="s">
         <v>5</v>
@@ -19363,19 +19402,19 @@
     </row>
     <row r="614" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A614" s="1" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="B614" s="1" t="s">
+        <v>1667</v>
+      </c>
+      <c r="C614" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D614" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E614" s="1" t="s">
         <v>1670</v>
-      </c>
-      <c r="C614" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D614" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E614" s="1" t="s">
-        <v>1673</v>
       </c>
       <c r="F614" s="1" t="s">
         <v>5</v>
@@ -19383,10 +19422,10 @@
     </row>
     <row r="615" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A615" s="1" t="s">
-        <v>1674</v>
+        <v>1671</v>
       </c>
       <c r="B615" s="1" t="s">
-        <v>1675</v>
+        <v>1672</v>
       </c>
       <c r="C615" s="1" t="s">
         <v>3</v>
@@ -19395,7 +19434,7 @@
         <v>4</v>
       </c>
       <c r="E615" s="1" t="s">
-        <v>1676</v>
+        <v>1673</v>
       </c>
       <c r="F615" s="1" t="s">
         <v>5</v>
@@ -19403,19 +19442,19 @@
     </row>
     <row r="616" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A616" s="1" t="s">
-        <v>1677</v>
+        <v>1674</v>
       </c>
       <c r="B616" s="1" t="s">
+        <v>1672</v>
+      </c>
+      <c r="C616" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D616" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E616" s="1" t="s">
         <v>1675</v>
-      </c>
-      <c r="C616" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D616" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E616" s="1" t="s">
-        <v>1678</v>
       </c>
       <c r="F616" s="1" t="s">
         <v>5</v>
@@ -19423,10 +19462,10 @@
     </row>
     <row r="617" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A617" s="1" t="s">
-        <v>1679</v>
+        <v>1676</v>
       </c>
       <c r="B617" s="1" t="s">
-        <v>1680</v>
+        <v>1677</v>
       </c>
       <c r="C617" s="1" t="s">
         <v>3</v>
@@ -19435,7 +19474,7 @@
         <v>4</v>
       </c>
       <c r="E617" s="1" t="s">
-        <v>1681</v>
+        <v>1678</v>
       </c>
       <c r="F617" s="1" t="s">
         <v>5</v>
@@ -19443,19 +19482,19 @@
     </row>
     <row r="618" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A618" s="1" t="s">
-        <v>1682</v>
+        <v>1679</v>
       </c>
       <c r="B618" s="1" t="s">
+        <v>1677</v>
+      </c>
+      <c r="C618" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D618" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E618" s="1" t="s">
         <v>1680</v>
-      </c>
-      <c r="C618" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D618" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E618" s="1" t="s">
-        <v>1683</v>
       </c>
       <c r="F618" s="1" t="s">
         <v>5</v>
@@ -19463,10 +19502,10 @@
     </row>
     <row r="619" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A619" s="1" t="s">
-        <v>1684</v>
+        <v>1681</v>
       </c>
       <c r="B619" s="1" t="s">
-        <v>1685</v>
+        <v>1682</v>
       </c>
       <c r="C619" s="1" t="s">
         <v>3</v>
@@ -19475,7 +19514,7 @@
         <v>4</v>
       </c>
       <c r="E619" s="1" t="s">
-        <v>1686</v>
+        <v>1683</v>
       </c>
       <c r="F619" s="1" t="s">
         <v>5</v>
@@ -19483,10 +19522,10 @@
     </row>
     <row r="620" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A620" s="1" t="s">
-        <v>1687</v>
+        <v>1684</v>
       </c>
       <c r="B620" s="1" t="s">
-        <v>1688</v>
+        <v>1685</v>
       </c>
       <c r="C620" s="1" t="s">
         <v>3</v>
@@ -19495,7 +19534,7 @@
         <v>4</v>
       </c>
       <c r="E620" s="1" t="s">
-        <v>1689</v>
+        <v>1686</v>
       </c>
       <c r="F620" s="1" t="s">
         <v>5</v>
@@ -19503,10 +19542,10 @@
     </row>
     <row r="621" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A621" s="1" t="s">
-        <v>1690</v>
+        <v>1687</v>
       </c>
       <c r="B621" s="1" t="s">
-        <v>1691</v>
+        <v>1688</v>
       </c>
       <c r="C621" s="1" t="s">
         <v>3</v>
@@ -19515,7 +19554,7 @@
         <v>4</v>
       </c>
       <c r="E621" s="1" t="s">
-        <v>1692</v>
+        <v>1689</v>
       </c>
       <c r="F621" s="1" t="s">
         <v>5</v>
@@ -19523,19 +19562,19 @@
     </row>
     <row r="622" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A622" s="1" t="s">
-        <v>1693</v>
+        <v>1690</v>
       </c>
       <c r="B622" s="1" t="s">
+        <v>1688</v>
+      </c>
+      <c r="C622" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D622" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E622" s="1" t="s">
         <v>1691</v>
-      </c>
-      <c r="C622" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D622" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E622" s="1" t="s">
-        <v>1694</v>
       </c>
       <c r="F622" s="1" t="s">
         <v>5</v>
@@ -19543,10 +19582,10 @@
     </row>
     <row r="623" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A623" s="1" t="s">
-        <v>1695</v>
+        <v>1692</v>
       </c>
       <c r="B623" s="1" t="s">
-        <v>1696</v>
+        <v>1693</v>
       </c>
       <c r="C623" s="1" t="s">
         <v>3</v>
@@ -19555,7 +19594,7 @@
         <v>4</v>
       </c>
       <c r="E623" s="1" t="s">
-        <v>1697</v>
+        <v>1694</v>
       </c>
       <c r="F623" s="1" t="s">
         <v>5</v>
@@ -19563,10 +19602,10 @@
     </row>
     <row r="624" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A624" s="1" t="s">
-        <v>1698</v>
+        <v>1695</v>
       </c>
       <c r="B624" s="1" t="s">
-        <v>1699</v>
+        <v>1696</v>
       </c>
       <c r="C624" s="1" t="s">
         <v>3</v>
@@ -19575,7 +19614,7 @@
         <v>4</v>
       </c>
       <c r="E624" s="1" t="s">
-        <v>1700</v>
+        <v>1697</v>
       </c>
       <c r="F624" s="1" t="s">
         <v>5</v>
@@ -19583,10 +19622,10 @@
     </row>
     <row r="625" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A625" s="1" t="s">
-        <v>1701</v>
+        <v>1698</v>
       </c>
       <c r="B625" s="1" t="s">
-        <v>1702</v>
+        <v>1699</v>
       </c>
       <c r="C625" s="1" t="s">
         <v>3</v>
@@ -19595,7 +19634,7 @@
         <v>4</v>
       </c>
       <c r="E625" s="1" t="s">
-        <v>1703</v>
+        <v>1700</v>
       </c>
       <c r="F625" s="1" t="s">
         <v>5</v>
@@ -19603,19 +19642,19 @@
     </row>
     <row r="626" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A626" s="1" t="s">
-        <v>1704</v>
+        <v>1701</v>
       </c>
       <c r="B626" s="1" t="s">
+        <v>1699</v>
+      </c>
+      <c r="C626" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D626" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E626" s="1" t="s">
         <v>1702</v>
-      </c>
-      <c r="C626" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D626" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E626" s="1" t="s">
-        <v>1705</v>
       </c>
       <c r="F626" s="1" t="s">
         <v>5</v>
@@ -19623,10 +19662,10 @@
     </row>
     <row r="627" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A627" s="1" t="s">
-        <v>1706</v>
+        <v>1703</v>
       </c>
       <c r="B627" s="1" t="s">
-        <v>1707</v>
+        <v>1704</v>
       </c>
       <c r="C627" s="1" t="s">
         <v>3</v>
@@ -19635,7 +19674,7 @@
         <v>4</v>
       </c>
       <c r="E627" s="1" t="s">
-        <v>1708</v>
+        <v>1705</v>
       </c>
       <c r="F627" s="1" t="s">
         <v>5</v>
@@ -19643,19 +19682,19 @@
     </row>
     <row r="628" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A628" s="1" t="s">
-        <v>1709</v>
+        <v>1706</v>
       </c>
       <c r="B628" s="1" t="s">
+        <v>1704</v>
+      </c>
+      <c r="C628" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D628" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E628" s="1" t="s">
         <v>1707</v>
-      </c>
-      <c r="C628" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D628" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E628" s="1" t="s">
-        <v>1710</v>
       </c>
       <c r="F628" s="1" t="s">
         <v>5</v>
@@ -19663,10 +19702,10 @@
     </row>
     <row r="629" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A629" s="1" t="s">
-        <v>1711</v>
+        <v>1708</v>
       </c>
       <c r="B629" s="1" t="s">
-        <v>1712</v>
+        <v>1709</v>
       </c>
       <c r="C629" s="1" t="s">
         <v>3</v>
@@ -19675,7 +19714,7 @@
         <v>4</v>
       </c>
       <c r="E629" s="1" t="s">
-        <v>1713</v>
+        <v>1710</v>
       </c>
       <c r="F629" s="1" t="s">
         <v>5</v>
@@ -19683,19 +19722,19 @@
     </row>
     <row r="630" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A630" s="1" t="s">
-        <v>1714</v>
+        <v>1711</v>
       </c>
       <c r="B630" s="1" t="s">
+        <v>1709</v>
+      </c>
+      <c r="C630" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D630" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E630" s="1" t="s">
         <v>1712</v>
-      </c>
-      <c r="C630" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D630" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E630" s="1" t="s">
-        <v>1715</v>
       </c>
       <c r="F630" s="1" t="s">
         <v>5</v>
@@ -19703,10 +19742,10 @@
     </row>
     <row r="631" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A631" s="1" t="s">
-        <v>1716</v>
+        <v>1713</v>
       </c>
       <c r="B631" s="1" t="s">
-        <v>1717</v>
+        <v>1714</v>
       </c>
       <c r="C631" s="1" t="s">
         <v>3</v>
@@ -19715,7 +19754,7 @@
         <v>4</v>
       </c>
       <c r="E631" s="1" t="s">
-        <v>1718</v>
+        <v>1715</v>
       </c>
       <c r="F631" s="1" t="s">
         <v>5</v>
@@ -19723,19 +19762,19 @@
     </row>
     <row r="632" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A632" s="1" t="s">
-        <v>1719</v>
+        <v>1716</v>
       </c>
       <c r="B632" s="1" t="s">
+        <v>1714</v>
+      </c>
+      <c r="C632" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D632" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E632" s="1" t="s">
         <v>1717</v>
-      </c>
-      <c r="C632" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D632" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E632" s="1" t="s">
-        <v>1720</v>
       </c>
       <c r="F632" s="1" t="s">
         <v>5</v>
@@ -19743,10 +19782,10 @@
     </row>
     <row r="633" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A633" s="1" t="s">
-        <v>1721</v>
+        <v>1718</v>
       </c>
       <c r="B633" s="1" t="s">
-        <v>1722</v>
+        <v>1719</v>
       </c>
       <c r="C633" s="1" t="s">
         <v>3</v>
@@ -19755,7 +19794,7 @@
         <v>4</v>
       </c>
       <c r="E633" s="1" t="s">
-        <v>1723</v>
+        <v>1720</v>
       </c>
       <c r="F633" s="1" t="s">
         <v>5</v>
@@ -19763,10 +19802,10 @@
     </row>
     <row r="634" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A634" s="1" t="s">
-        <v>1724</v>
+        <v>1721</v>
       </c>
       <c r="B634" s="1" t="s">
-        <v>1725</v>
+        <v>1722</v>
       </c>
       <c r="C634" s="1" t="s">
         <v>3</v>
@@ -19775,7 +19814,7 @@
         <v>4</v>
       </c>
       <c r="E634" s="1" t="s">
-        <v>1726</v>
+        <v>1723</v>
       </c>
       <c r="F634" s="1" t="s">
         <v>5</v>
@@ -19783,10 +19822,10 @@
     </row>
     <row r="635" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A635" s="1" t="s">
-        <v>1727</v>
+        <v>1724</v>
       </c>
       <c r="B635" s="1" t="s">
-        <v>1728</v>
+        <v>1725</v>
       </c>
       <c r="C635" s="1" t="s">
         <v>3</v>
@@ -19795,7 +19834,7 @@
         <v>4</v>
       </c>
       <c r="E635" s="1" t="s">
-        <v>1729</v>
+        <v>1726</v>
       </c>
       <c r="F635" s="1" t="s">
         <v>5</v>
@@ -19803,10 +19842,10 @@
     </row>
     <row r="636" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A636" s="1" t="s">
-        <v>1730</v>
+        <v>1727</v>
       </c>
       <c r="B636" s="1" t="s">
-        <v>1731</v>
+        <v>1728</v>
       </c>
       <c r="C636" s="1" t="s">
         <v>3</v>
@@ -19815,7 +19854,7 @@
         <v>4</v>
       </c>
       <c r="E636" s="1" t="s">
-        <v>1732</v>
+        <v>1729</v>
       </c>
       <c r="F636" s="1" t="s">
         <v>5</v>
@@ -19823,10 +19862,10 @@
     </row>
     <row r="637" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A637" s="1" t="s">
-        <v>1733</v>
+        <v>1730</v>
       </c>
       <c r="B637" s="1" t="s">
-        <v>1734</v>
+        <v>1731</v>
       </c>
       <c r="C637" s="1" t="s">
         <v>3</v>
@@ -19835,7 +19874,7 @@
         <v>4</v>
       </c>
       <c r="E637" s="1" t="s">
-        <v>1735</v>
+        <v>1732</v>
       </c>
       <c r="F637" s="1" t="s">
         <v>5</v>
@@ -19843,10 +19882,10 @@
     </row>
     <row r="638" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A638" s="1" t="s">
-        <v>1736</v>
+        <v>1733</v>
       </c>
       <c r="B638" s="1" t="s">
-        <v>1737</v>
+        <v>1734</v>
       </c>
       <c r="C638" s="1" t="s">
         <v>3</v>
@@ -19855,7 +19894,7 @@
         <v>4</v>
       </c>
       <c r="E638" s="1" t="s">
-        <v>1738</v>
+        <v>1735</v>
       </c>
       <c r="F638" s="1" t="s">
         <v>5</v>
@@ -19863,10 +19902,10 @@
     </row>
     <row r="639" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A639" s="1" t="s">
-        <v>1739</v>
+        <v>1736</v>
       </c>
       <c r="B639" s="1" t="s">
-        <v>1740</v>
+        <v>1737</v>
       </c>
       <c r="C639" s="1" t="s">
         <v>3</v>
@@ -19875,7 +19914,7 @@
         <v>4</v>
       </c>
       <c r="E639" s="1" t="s">
-        <v>1741</v>
+        <v>1738</v>
       </c>
       <c r="F639" s="1" t="s">
         <v>5</v>
@@ -19883,10 +19922,10 @@
     </row>
     <row r="640" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A640" s="1" t="s">
-        <v>1742</v>
+        <v>1739</v>
       </c>
       <c r="B640" s="1" t="s">
-        <v>1743</v>
+        <v>1740</v>
       </c>
       <c r="C640" s="1" t="s">
         <v>3</v>
@@ -19895,7 +19934,7 @@
         <v>4</v>
       </c>
       <c r="E640" s="1" t="s">
-        <v>1744</v>
+        <v>1741</v>
       </c>
       <c r="F640" s="1" t="s">
         <v>5</v>
@@ -19903,10 +19942,10 @@
     </row>
     <row r="641" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A641" s="1" t="s">
-        <v>1745</v>
+        <v>1742</v>
       </c>
       <c r="B641" s="1" t="s">
-        <v>1746</v>
+        <v>1743</v>
       </c>
       <c r="C641" s="1" t="s">
         <v>3</v>
@@ -19915,7 +19954,7 @@
         <v>4</v>
       </c>
       <c r="E641" s="1" t="s">
-        <v>1747</v>
+        <v>1744</v>
       </c>
       <c r="F641" s="1" t="s">
         <v>5</v>
@@ -19923,10 +19962,10 @@
     </row>
     <row r="642" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A642" s="1" t="s">
-        <v>1748</v>
+        <v>1745</v>
       </c>
       <c r="B642" s="1" t="s">
-        <v>1749</v>
+        <v>1746</v>
       </c>
       <c r="C642" s="1" t="s">
         <v>3</v>
@@ -19935,7 +19974,7 @@
         <v>4</v>
       </c>
       <c r="E642" s="1" t="s">
-        <v>1750</v>
+        <v>1747</v>
       </c>
       <c r="F642" s="1" t="s">
         <v>5</v>
@@ -19943,10 +19982,10 @@
     </row>
     <row r="643" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A643" s="1" t="s">
-        <v>1751</v>
+        <v>1748</v>
       </c>
       <c r="B643" s="1" t="s">
-        <v>1752</v>
+        <v>1749</v>
       </c>
       <c r="C643" s="1" t="s">
         <v>3</v>
@@ -19955,7 +19994,7 @@
         <v>4</v>
       </c>
       <c r="E643" s="1" t="s">
-        <v>1753</v>
+        <v>1750</v>
       </c>
       <c r="F643" s="1" t="s">
         <v>5</v>
@@ -19963,19 +20002,19 @@
     </row>
     <row r="644" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A644" s="1" t="s">
-        <v>1754</v>
+        <v>1751</v>
       </c>
       <c r="B644" s="1" t="s">
+        <v>1749</v>
+      </c>
+      <c r="C644" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D644" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E644" s="1" t="s">
         <v>1752</v>
-      </c>
-      <c r="C644" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D644" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E644" s="1" t="s">
-        <v>1755</v>
       </c>
       <c r="F644" s="1" t="s">
         <v>5</v>
@@ -19983,10 +20022,10 @@
     </row>
     <row r="645" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A645" s="1" t="s">
-        <v>1756</v>
+        <v>1753</v>
       </c>
       <c r="B645" s="1" t="s">
-        <v>1757</v>
+        <v>1754</v>
       </c>
       <c r="C645" s="1" t="s">
         <v>3</v>
@@ -19995,7 +20034,7 @@
         <v>4</v>
       </c>
       <c r="E645" s="1" t="s">
-        <v>1758</v>
+        <v>1755</v>
       </c>
       <c r="F645" s="1" t="s">
         <v>5</v>
@@ -20003,10 +20042,10 @@
     </row>
     <row r="646" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A646" s="1" t="s">
-        <v>1759</v>
+        <v>1756</v>
       </c>
       <c r="B646" s="1" t="s">
-        <v>1760</v>
+        <v>1757</v>
       </c>
       <c r="C646" s="1" t="s">
         <v>3</v>
@@ -20015,7 +20054,7 @@
         <v>4</v>
       </c>
       <c r="E646" s="1" t="s">
-        <v>1761</v>
+        <v>1758</v>
       </c>
       <c r="F646" s="1" t="s">
         <v>5</v>
@@ -20023,10 +20062,10 @@
     </row>
     <row r="647" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A647" s="1" t="s">
-        <v>1762</v>
+        <v>1759</v>
       </c>
       <c r="B647" s="1" t="s">
-        <v>1763</v>
+        <v>1760</v>
       </c>
       <c r="C647" s="1" t="s">
         <v>3</v>
@@ -20035,7 +20074,7 @@
         <v>4</v>
       </c>
       <c r="E647" s="1" t="s">
-        <v>1764</v>
+        <v>1761</v>
       </c>
       <c r="F647" s="1" t="s">
         <v>5</v>
@@ -20043,10 +20082,10 @@
     </row>
     <row r="648" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A648" s="1" t="s">
-        <v>1765</v>
+        <v>1762</v>
       </c>
       <c r="B648" s="1" t="s">
-        <v>1766</v>
+        <v>1763</v>
       </c>
       <c r="C648" s="1" t="s">
         <v>3</v>
@@ -20055,7 +20094,7 @@
         <v>4</v>
       </c>
       <c r="E648" s="1" t="s">
-        <v>1767</v>
+        <v>1764</v>
       </c>
       <c r="F648" s="1" t="s">
         <v>5</v>
@@ -20063,10 +20102,10 @@
     </row>
     <row r="649" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A649" s="1" t="s">
-        <v>1768</v>
+        <v>1765</v>
       </c>
       <c r="B649" s="1" t="s">
-        <v>1769</v>
+        <v>1766</v>
       </c>
       <c r="C649" s="1" t="s">
         <v>3</v>
@@ -20075,7 +20114,7 @@
         <v>4</v>
       </c>
       <c r="E649" s="1" t="s">
-        <v>1770</v>
+        <v>1767</v>
       </c>
       <c r="F649" s="1" t="s">
         <v>5</v>
@@ -20083,10 +20122,10 @@
     </row>
     <row r="650" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A650" s="1" t="s">
-        <v>1771</v>
+        <v>1768</v>
       </c>
       <c r="B650" s="1" t="s">
-        <v>1728</v>
+        <v>1725</v>
       </c>
       <c r="C650" s="1" t="s">
         <v>3</v>
@@ -20095,7 +20134,7 @@
         <v>4</v>
       </c>
       <c r="E650" s="1" t="s">
-        <v>1772</v>
+        <v>1769</v>
       </c>
       <c r="F650" s="1" t="s">
         <v>5</v>
@@ -20103,10 +20142,10 @@
     </row>
     <row r="651" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A651" s="1" t="s">
-        <v>1773</v>
+        <v>1770</v>
       </c>
       <c r="B651" s="1" t="s">
-        <v>1731</v>
+        <v>1728</v>
       </c>
       <c r="C651" s="1" t="s">
         <v>3</v>
@@ -20115,7 +20154,7 @@
         <v>4</v>
       </c>
       <c r="E651" s="1" t="s">
-        <v>1774</v>
+        <v>1771</v>
       </c>
       <c r="F651" s="1" t="s">
         <v>5</v>
@@ -20123,10 +20162,10 @@
     </row>
     <row r="652" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A652" s="1" t="s">
-        <v>1775</v>
+        <v>1772</v>
       </c>
       <c r="B652" s="1" t="s">
-        <v>1734</v>
+        <v>1731</v>
       </c>
       <c r="C652" s="1" t="s">
         <v>3</v>
@@ -20135,7 +20174,7 @@
         <v>4</v>
       </c>
       <c r="E652" s="1" t="s">
-        <v>1776</v>
+        <v>1773</v>
       </c>
       <c r="F652" s="1" t="s">
         <v>5</v>
@@ -20143,10 +20182,10 @@
     </row>
     <row r="653" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A653" s="1" t="s">
-        <v>1777</v>
+        <v>1774</v>
       </c>
       <c r="B653" s="1" t="s">
-        <v>1737</v>
+        <v>1734</v>
       </c>
       <c r="C653" s="1" t="s">
         <v>3</v>
@@ -20155,7 +20194,7 @@
         <v>4</v>
       </c>
       <c r="E653" s="1" t="s">
-        <v>1778</v>
+        <v>1775</v>
       </c>
       <c r="F653" s="1" t="s">
         <v>5</v>
@@ -20163,10 +20202,10 @@
     </row>
     <row r="654" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A654" s="1" t="s">
-        <v>1779</v>
+        <v>1776</v>
       </c>
       <c r="B654" s="1" t="s">
-        <v>1740</v>
+        <v>1737</v>
       </c>
       <c r="C654" s="1" t="s">
         <v>3</v>
@@ -20175,7 +20214,7 @@
         <v>4</v>
       </c>
       <c r="E654" s="1" t="s">
-        <v>1780</v>
+        <v>1777</v>
       </c>
       <c r="F654" s="1" t="s">
         <v>5</v>
@@ -20183,10 +20222,10 @@
     </row>
     <row r="655" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A655" s="1" t="s">
-        <v>1781</v>
+        <v>1778</v>
       </c>
       <c r="B655" s="1" t="s">
-        <v>1743</v>
+        <v>1740</v>
       </c>
       <c r="C655" s="1" t="s">
         <v>3</v>
@@ -20195,7 +20234,7 @@
         <v>4</v>
       </c>
       <c r="E655" s="1" t="s">
-        <v>1782</v>
+        <v>1779</v>
       </c>
       <c r="F655" s="1" t="s">
         <v>5</v>
@@ -20203,10 +20242,10 @@
     </row>
     <row r="656" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A656" s="1" t="s">
-        <v>1783</v>
+        <v>1780</v>
       </c>
       <c r="B656" s="1" t="s">
-        <v>1784</v>
+        <v>1781</v>
       </c>
       <c r="C656" s="1" t="s">
         <v>3</v>
@@ -20215,7 +20254,7 @@
         <v>4</v>
       </c>
       <c r="E656" s="1" t="s">
-        <v>1785</v>
+        <v>1782</v>
       </c>
       <c r="F656" s="1" t="s">
         <v>5</v>
@@ -20223,10 +20262,10 @@
     </row>
     <row r="657" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A657" s="1" t="s">
-        <v>1786</v>
+        <v>1783</v>
       </c>
       <c r="B657" s="1" t="s">
-        <v>1749</v>
+        <v>1746</v>
       </c>
       <c r="C657" s="1" t="s">
         <v>3</v>
@@ -20235,7 +20274,7 @@
         <v>4</v>
       </c>
       <c r="E657" s="1" t="s">
-        <v>1787</v>
+        <v>1784</v>
       </c>
       <c r="F657" s="1" t="s">
         <v>5</v>
@@ -20243,10 +20282,10 @@
     </row>
     <row r="658" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A658" s="1" t="s">
-        <v>1788</v>
+        <v>1785</v>
       </c>
       <c r="B658" s="1" t="s">
-        <v>1789</v>
+        <v>1786</v>
       </c>
       <c r="C658" s="1" t="s">
         <v>3</v>
@@ -20255,7 +20294,7 @@
         <v>4</v>
       </c>
       <c r="E658" s="1" t="s">
-        <v>1790</v>
+        <v>1787</v>
       </c>
       <c r="F658" s="1" t="s">
         <v>5</v>
@@ -20263,19 +20302,19 @@
     </row>
     <row r="659" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A659" s="1" t="s">
-        <v>1791</v>
+        <v>1788</v>
       </c>
       <c r="B659" s="1" t="s">
+        <v>1786</v>
+      </c>
+      <c r="C659" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D659" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E659" s="1" t="s">
         <v>1789</v>
-      </c>
-      <c r="C659" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D659" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E659" s="1" t="s">
-        <v>1792</v>
       </c>
       <c r="F659" s="1" t="s">
         <v>5</v>
@@ -20283,10 +20322,10 @@
     </row>
     <row r="660" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A660" s="1" t="s">
-        <v>1793</v>
+        <v>1790</v>
       </c>
       <c r="B660" s="1" t="s">
-        <v>1722</v>
+        <v>1719</v>
       </c>
       <c r="C660" s="1" t="s">
         <v>3</v>
@@ -20295,7 +20334,7 @@
         <v>4</v>
       </c>
       <c r="E660" s="1" t="s">
-        <v>1794</v>
+        <v>1791</v>
       </c>
       <c r="F660" s="1" t="s">
         <v>5</v>
@@ -20303,10 +20342,10 @@
     </row>
     <row r="661" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A661" s="1" t="s">
-        <v>1795</v>
+        <v>1792</v>
       </c>
       <c r="B661" s="1" t="s">
-        <v>1796</v>
+        <v>1793</v>
       </c>
       <c r="C661" s="1" t="s">
         <v>3</v>
@@ -20315,7 +20354,7 @@
         <v>4</v>
       </c>
       <c r="E661" s="1" t="s">
-        <v>1797</v>
+        <v>1794</v>
       </c>
       <c r="F661" s="1" t="s">
         <v>5</v>
@@ -20323,10 +20362,10 @@
     </row>
     <row r="662" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A662" s="1" t="s">
-        <v>1798</v>
+        <v>1795</v>
       </c>
       <c r="B662" s="1" t="s">
-        <v>1799</v>
+        <v>1796</v>
       </c>
       <c r="C662" s="1" t="s">
         <v>3</v>
@@ -20335,7 +20374,7 @@
         <v>4</v>
       </c>
       <c r="E662" s="1" t="s">
-        <v>1800</v>
+        <v>1797</v>
       </c>
       <c r="F662" s="1" t="s">
         <v>5</v>
@@ -20343,10 +20382,10 @@
     </row>
     <row r="663" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A663" s="1" t="s">
-        <v>1801</v>
+        <v>1798</v>
       </c>
       <c r="B663" s="1" t="s">
-        <v>1802</v>
+        <v>1799</v>
       </c>
       <c r="C663" s="1" t="s">
         <v>3</v>
@@ -20355,7 +20394,7 @@
         <v>4</v>
       </c>
       <c r="E663" s="1" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="F663" s="1" t="s">
         <v>5</v>
@@ -20363,10 +20402,10 @@
     </row>
     <row r="664" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A664" s="1" t="s">
-        <v>1804</v>
+        <v>1801</v>
       </c>
       <c r="B664" s="1" t="s">
-        <v>1796</v>
+        <v>1793</v>
       </c>
       <c r="C664" s="1" t="s">
         <v>3</v>
@@ -20375,7 +20414,7 @@
         <v>4</v>
       </c>
       <c r="E664" s="1" t="s">
-        <v>1805</v>
+        <v>1802</v>
       </c>
       <c r="F664" s="1" t="s">
         <v>5</v>
@@ -20383,10 +20422,10 @@
     </row>
     <row r="665" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A665" s="1" t="s">
-        <v>1806</v>
+        <v>1803</v>
       </c>
       <c r="B665" s="1" t="s">
-        <v>1799</v>
+        <v>1796</v>
       </c>
       <c r="C665" s="1" t="s">
         <v>3</v>
@@ -20395,7 +20434,7 @@
         <v>4</v>
       </c>
       <c r="E665" s="1" t="s">
-        <v>1807</v>
+        <v>1804</v>
       </c>
       <c r="F665" s="1" t="s">
         <v>5</v>
@@ -20403,10 +20442,10 @@
     </row>
     <row r="666" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A666" s="1" t="s">
-        <v>1808</v>
+        <v>1805</v>
       </c>
       <c r="B666" s="1" t="s">
-        <v>1802</v>
+        <v>1799</v>
       </c>
       <c r="C666" s="1" t="s">
         <v>3</v>
@@ -20415,7 +20454,7 @@
         <v>4</v>
       </c>
       <c r="E666" s="1" t="s">
-        <v>1809</v>
+        <v>1806</v>
       </c>
       <c r="F666" s="1" t="s">
         <v>5</v>
@@ -20423,10 +20462,10 @@
     </row>
     <row r="667" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A667" s="1" t="s">
-        <v>1810</v>
+        <v>1807</v>
       </c>
       <c r="B667" s="1" t="s">
-        <v>1811</v>
+        <v>1808</v>
       </c>
       <c r="C667" s="1" t="s">
         <v>3</v>
@@ -20435,7 +20474,7 @@
         <v>4</v>
       </c>
       <c r="E667" s="1" t="s">
-        <v>1812</v>
+        <v>1809</v>
       </c>
       <c r="F667" s="1" t="s">
         <v>5</v>
@@ -20443,19 +20482,19 @@
     </row>
     <row r="668" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A668" s="1" t="s">
-        <v>1813</v>
+        <v>1810</v>
       </c>
       <c r="B668" s="1" t="s">
+        <v>1808</v>
+      </c>
+      <c r="C668" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D668" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E668" s="1" t="s">
         <v>1811</v>
-      </c>
-      <c r="C668" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D668" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E668" s="1" t="s">
-        <v>1814</v>
       </c>
       <c r="F668" s="1" t="s">
         <v>5</v>
@@ -20463,10 +20502,10 @@
     </row>
     <row r="669" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A669" s="1" t="s">
-        <v>1815</v>
+        <v>1812</v>
       </c>
       <c r="B669" s="1" t="s">
-        <v>1816</v>
+        <v>1813</v>
       </c>
       <c r="C669" s="1" t="s">
         <v>3</v>
@@ -20475,7 +20514,7 @@
         <v>4</v>
       </c>
       <c r="E669" s="1" t="s">
-        <v>1817</v>
+        <v>1814</v>
       </c>
       <c r="F669" s="1" t="s">
         <v>5</v>
@@ -20483,19 +20522,19 @@
     </row>
     <row r="670" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A670" s="1" t="s">
-        <v>1818</v>
+        <v>1815</v>
       </c>
       <c r="B670" s="1" t="s">
+        <v>1813</v>
+      </c>
+      <c r="C670" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D670" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E670" s="1" t="s">
         <v>1816</v>
-      </c>
-      <c r="C670" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D670" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E670" s="1" t="s">
-        <v>1819</v>
       </c>
       <c r="F670" s="1" t="s">
         <v>5</v>
@@ -20503,10 +20542,10 @@
     </row>
     <row r="671" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A671" s="1" t="s">
-        <v>1820</v>
+        <v>1817</v>
       </c>
       <c r="B671" s="1" t="s">
-        <v>1821</v>
+        <v>1818</v>
       </c>
       <c r="C671" s="1" t="s">
         <v>3</v>
@@ -20515,7 +20554,7 @@
         <v>4</v>
       </c>
       <c r="E671" s="1" t="s">
-        <v>1822</v>
+        <v>1819</v>
       </c>
       <c r="F671" s="1" t="s">
         <v>5</v>
@@ -20523,19 +20562,19 @@
     </row>
     <row r="672" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A672" s="1" t="s">
-        <v>1823</v>
+        <v>1820</v>
       </c>
       <c r="B672" s="1" t="s">
+        <v>1818</v>
+      </c>
+      <c r="C672" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D672" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E672" s="1" t="s">
         <v>1821</v>
-      </c>
-      <c r="C672" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D672" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E672" s="1" t="s">
-        <v>1824</v>
       </c>
       <c r="F672" s="1" t="s">
         <v>5</v>
@@ -20543,10 +20582,10 @@
     </row>
     <row r="673" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A673" s="1" t="s">
-        <v>1825</v>
+        <v>1822</v>
       </c>
       <c r="B673" s="1" t="s">
-        <v>1826</v>
+        <v>1823</v>
       </c>
       <c r="C673" s="1" t="s">
         <v>3</v>
@@ -20555,7 +20594,7 @@
         <v>4</v>
       </c>
       <c r="E673" s="1" t="s">
-        <v>1827</v>
+        <v>1824</v>
       </c>
       <c r="F673" s="1" t="s">
         <v>5</v>
@@ -20563,19 +20602,19 @@
     </row>
     <row r="674" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A674" s="1" t="s">
-        <v>1828</v>
+        <v>1825</v>
       </c>
       <c r="B674" s="1" t="s">
+        <v>1823</v>
+      </c>
+      <c r="C674" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D674" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E674" s="1" t="s">
         <v>1826</v>
-      </c>
-      <c r="C674" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D674" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E674" s="1" t="s">
-        <v>1829</v>
       </c>
       <c r="F674" s="1" t="s">
         <v>5</v>
@@ -20583,10 +20622,10 @@
     </row>
     <row r="675" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A675" s="1" t="s">
-        <v>1830</v>
+        <v>1827</v>
       </c>
       <c r="B675" s="1" t="s">
-        <v>1831</v>
+        <v>1828</v>
       </c>
       <c r="C675" s="1" t="s">
         <v>3</v>
@@ -20595,7 +20634,7 @@
         <v>4</v>
       </c>
       <c r="E675" s="1" t="s">
-        <v>1832</v>
+        <v>1829</v>
       </c>
       <c r="F675" s="1" t="s">
         <v>80</v>
@@ -20603,7 +20642,7 @@
     </row>
     <row r="676" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A676" s="1" t="s">
-        <v>1833</v>
+        <v>1830</v>
       </c>
       <c r="B676" s="1" t="s">
         <v>1099</v>
@@ -20615,7 +20654,7 @@
         <v>4</v>
       </c>
       <c r="E676" s="1" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="F676" s="1" t="s">
         <v>5</v>
@@ -20623,7 +20662,7 @@
     </row>
     <row r="677" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A677" s="1" t="s">
-        <v>1835</v>
+        <v>1832</v>
       </c>
       <c r="B677" s="1" t="s">
         <v>1092</v>
@@ -20635,7 +20674,7 @@
         <v>4</v>
       </c>
       <c r="E677" s="1" t="s">
-        <v>1836</v>
+        <v>1833</v>
       </c>
       <c r="F677" s="1" t="s">
         <v>5</v>
@@ -20643,7 +20682,7 @@
     </row>
     <row r="678" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A678" s="1" t="s">
-        <v>1837</v>
+        <v>1834</v>
       </c>
       <c r="B678" s="1" t="s">
         <v>1085</v>
@@ -20655,7 +20694,7 @@
         <v>4</v>
       </c>
       <c r="E678" s="1" t="s">
-        <v>1838</v>
+        <v>1835</v>
       </c>
       <c r="F678" s="1" t="s">
         <v>5</v>
@@ -20663,7 +20702,7 @@
     </row>
     <row r="679" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A679" s="1" t="s">
-        <v>1839</v>
+        <v>1836</v>
       </c>
       <c r="B679" s="1" t="s">
         <v>1079</v>
@@ -20675,7 +20714,7 @@
         <v>4</v>
       </c>
       <c r="E679" s="1" t="s">
-        <v>1840</v>
+        <v>1837</v>
       </c>
       <c r="F679" s="1" t="s">
         <v>5</v>
@@ -20683,7 +20722,7 @@
     </row>
     <row r="680" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A680" s="1" t="s">
-        <v>1841</v>
+        <v>1838</v>
       </c>
       <c r="B680" s="1" t="s">
         <v>1082</v>
@@ -20695,7 +20734,7 @@
         <v>4</v>
       </c>
       <c r="E680" s="1" t="s">
-        <v>1842</v>
+        <v>1839</v>
       </c>
       <c r="F680" s="1" t="s">
         <v>5</v>
@@ -20715,7 +20754,7 @@
         <v>4</v>
       </c>
       <c r="E681" s="1" t="s">
-        <v>1843</v>
+        <v>1840</v>
       </c>
       <c r="F681" s="1" t="s">
         <v>5</v>
@@ -20735,7 +20774,7 @@
         <v>4</v>
       </c>
       <c r="E682" s="1" t="s">
-        <v>1844</v>
+        <v>1841</v>
       </c>
       <c r="F682" s="1" t="s">
         <v>5</v>
@@ -20743,10 +20782,10 @@
     </row>
     <row r="683" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A683" s="1" t="s">
-        <v>1845</v>
+        <v>1842</v>
       </c>
       <c r="B683" s="1" t="s">
-        <v>1846</v>
+        <v>1843</v>
       </c>
       <c r="C683" s="1" t="s">
         <v>3</v>
@@ -20755,7 +20794,7 @@
         <v>4</v>
       </c>
       <c r="E683" s="1" t="s">
-        <v>1847</v>
+        <v>1844</v>
       </c>
       <c r="F683" s="1" t="s">
         <v>5</v>
@@ -20763,10 +20802,10 @@
     </row>
     <row r="684" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A684" s="1" t="s">
-        <v>1848</v>
+        <v>1845</v>
       </c>
       <c r="B684" s="1" t="s">
-        <v>1849</v>
+        <v>1846</v>
       </c>
       <c r="C684" s="1" t="s">
         <v>3</v>
@@ -20775,7 +20814,7 @@
         <v>4</v>
       </c>
       <c r="E684" s="1" t="s">
-        <v>1850</v>
+        <v>1847</v>
       </c>
       <c r="F684" s="1" t="s">
         <v>5</v>
@@ -20783,10 +20822,10 @@
     </row>
     <row r="685" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A685" s="1" t="s">
-        <v>1851</v>
+        <v>1848</v>
       </c>
       <c r="B685" s="1" t="s">
-        <v>1852</v>
+        <v>1849</v>
       </c>
       <c r="C685" s="1" t="s">
         <v>3</v>
@@ -20795,7 +20834,7 @@
         <v>4</v>
       </c>
       <c r="E685" s="1" t="s">
-        <v>1853</v>
+        <v>1850</v>
       </c>
       <c r="F685" s="1" t="s">
         <v>5</v>
@@ -20803,10 +20842,10 @@
     </row>
     <row r="686" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A686" s="1" t="s">
-        <v>1854</v>
+        <v>1851</v>
       </c>
       <c r="B686" s="1" t="s">
-        <v>1855</v>
+        <v>1852</v>
       </c>
       <c r="C686" s="1" t="s">
         <v>3</v>
@@ -20815,7 +20854,7 @@
         <v>4</v>
       </c>
       <c r="E686" s="1" t="s">
-        <v>1856</v>
+        <v>1853</v>
       </c>
       <c r="F686" s="1" t="s">
         <v>5</v>
@@ -20823,10 +20862,10 @@
     </row>
     <row r="687" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A687" s="1" t="s">
-        <v>1857</v>
+        <v>1854</v>
       </c>
       <c r="B687" s="1" t="s">
-        <v>1858</v>
+        <v>1855</v>
       </c>
       <c r="C687" s="1" t="s">
         <v>3</v>
@@ -20835,7 +20874,7 @@
         <v>4</v>
       </c>
       <c r="E687" s="1" t="s">
-        <v>1859</v>
+        <v>1856</v>
       </c>
       <c r="F687" s="1" t="s">
         <v>5</v>
@@ -20843,10 +20882,10 @@
     </row>
     <row r="688" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A688" s="1" t="s">
-        <v>1860</v>
+        <v>1857</v>
       </c>
       <c r="B688" s="1" t="s">
-        <v>1861</v>
+        <v>1858</v>
       </c>
       <c r="C688" s="1" t="s">
         <v>3</v>
@@ -20855,7 +20894,7 @@
         <v>4</v>
       </c>
       <c r="E688" s="1" t="s">
-        <v>1862</v>
+        <v>1859</v>
       </c>
       <c r="F688" s="1" t="s">
         <v>5</v>
@@ -20863,10 +20902,10 @@
     </row>
     <row r="689" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A689" s="1" t="s">
-        <v>1863</v>
+        <v>1860</v>
       </c>
       <c r="B689" s="1" t="s">
-        <v>1864</v>
+        <v>1861</v>
       </c>
       <c r="C689" s="1" t="s">
         <v>3</v>
@@ -20875,7 +20914,7 @@
         <v>4</v>
       </c>
       <c r="E689" s="1" t="s">
-        <v>1865</v>
+        <v>1862</v>
       </c>
       <c r="F689" s="1" t="s">
         <v>5</v>
@@ -20883,10 +20922,10 @@
     </row>
     <row r="690" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A690" s="1" t="s">
-        <v>1866</v>
+        <v>1863</v>
       </c>
       <c r="B690" s="1" t="s">
-        <v>1867</v>
+        <v>1864</v>
       </c>
       <c r="C690" s="1" t="s">
         <v>3</v>
@@ -20895,7 +20934,7 @@
         <v>4</v>
       </c>
       <c r="E690" s="1" t="s">
-        <v>1868</v>
+        <v>1865</v>
       </c>
       <c r="F690" s="1" t="s">
         <v>5</v>
@@ -20903,10 +20942,10 @@
     </row>
     <row r="691" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A691" s="1" t="s">
-        <v>1869</v>
+        <v>1866</v>
       </c>
       <c r="B691" s="1" t="s">
-        <v>1870</v>
+        <v>1867</v>
       </c>
       <c r="C691" s="1" t="s">
         <v>3</v>
@@ -20915,7 +20954,7 @@
         <v>4</v>
       </c>
       <c r="E691" s="1" t="s">
-        <v>1871</v>
+        <v>1868</v>
       </c>
       <c r="F691" s="1" t="s">
         <v>5</v>
@@ -20923,10 +20962,10 @@
     </row>
     <row r="692" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A692" s="1" t="s">
-        <v>1872</v>
+        <v>1869</v>
       </c>
       <c r="B692" s="1" t="s">
-        <v>1873</v>
+        <v>1870</v>
       </c>
       <c r="C692" s="1" t="s">
         <v>3</v>
@@ -20935,7 +20974,7 @@
         <v>4</v>
       </c>
       <c r="E692" s="1" t="s">
-        <v>1874</v>
+        <v>1871</v>
       </c>
       <c r="F692" s="1" t="s">
         <v>5</v>
@@ -20943,10 +20982,10 @@
     </row>
     <row r="693" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A693" s="1" t="s">
-        <v>1875</v>
+        <v>1872</v>
       </c>
       <c r="B693" s="1" t="s">
-        <v>1876</v>
+        <v>1873</v>
       </c>
       <c r="C693" s="1" t="s">
         <v>3</v>
@@ -20955,7 +20994,7 @@
         <v>4</v>
       </c>
       <c r="E693" s="1" t="s">
-        <v>1877</v>
+        <v>1874</v>
       </c>
       <c r="F693" s="1" t="s">
         <v>5</v>
@@ -20963,10 +21002,10 @@
     </row>
     <row r="694" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A694" s="1" t="s">
-        <v>1878</v>
+        <v>1875</v>
       </c>
       <c r="B694" s="1" t="s">
-        <v>1879</v>
+        <v>1876</v>
       </c>
       <c r="C694" s="1" t="s">
         <v>3</v>
@@ -20975,7 +21014,7 @@
         <v>4</v>
       </c>
       <c r="E694" s="1" t="s">
-        <v>1880</v>
+        <v>1877</v>
       </c>
       <c r="F694" s="1" t="s">
         <v>5</v>
@@ -20983,10 +21022,10 @@
     </row>
     <row r="695" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A695" s="1" t="s">
-        <v>1881</v>
+        <v>1878</v>
       </c>
       <c r="B695" s="1" t="s">
-        <v>1882</v>
+        <v>1879</v>
       </c>
       <c r="C695" s="1" t="s">
         <v>3</v>
@@ -20995,7 +21034,7 @@
         <v>4</v>
       </c>
       <c r="E695" s="1" t="s">
-        <v>1883</v>
+        <v>1880</v>
       </c>
       <c r="F695" s="1" t="s">
         <v>5</v>
@@ -21003,10 +21042,10 @@
     </row>
     <row r="696" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A696" s="1" t="s">
-        <v>1884</v>
+        <v>1881</v>
       </c>
       <c r="B696" s="1" t="s">
-        <v>1885</v>
+        <v>1882</v>
       </c>
       <c r="C696" s="1" t="s">
         <v>3</v>
@@ -21015,7 +21054,7 @@
         <v>4</v>
       </c>
       <c r="E696" s="1" t="s">
-        <v>1886</v>
+        <v>1883</v>
       </c>
       <c r="F696" s="1" t="s">
         <v>5</v>
@@ -21023,10 +21062,10 @@
     </row>
     <row r="697" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A697" s="1" t="s">
-        <v>1887</v>
+        <v>1884</v>
       </c>
       <c r="B697" s="1" t="s">
-        <v>1888</v>
+        <v>1885</v>
       </c>
       <c r="C697" s="1" t="s">
         <v>3</v>
@@ -21035,7 +21074,7 @@
         <v>4</v>
       </c>
       <c r="E697" s="1" t="s">
-        <v>1889</v>
+        <v>1886</v>
       </c>
       <c r="F697" s="1" t="s">
         <v>5</v>
@@ -21043,10 +21082,10 @@
     </row>
     <row r="698" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A698" s="1" t="s">
-        <v>1890</v>
+        <v>1887</v>
       </c>
       <c r="B698" s="1" t="s">
-        <v>1891</v>
+        <v>1888</v>
       </c>
       <c r="C698" s="1" t="s">
         <v>3</v>
@@ -21055,7 +21094,7 @@
         <v>4</v>
       </c>
       <c r="E698" s="1" t="s">
-        <v>1892</v>
+        <v>1889</v>
       </c>
       <c r="F698" s="1" t="s">
         <v>5</v>
@@ -21063,10 +21102,10 @@
     </row>
     <row r="699" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A699" s="1" t="s">
-        <v>1893</v>
+        <v>1890</v>
       </c>
       <c r="B699" s="1" t="s">
-        <v>1894</v>
+        <v>1891</v>
       </c>
       <c r="C699" s="1" t="s">
         <v>3</v>
@@ -21075,7 +21114,7 @@
         <v>4</v>
       </c>
       <c r="E699" s="1" t="s">
-        <v>1895</v>
+        <v>1892</v>
       </c>
       <c r="F699" s="1" t="s">
         <v>5</v>
@@ -21083,10 +21122,10 @@
     </row>
     <row r="700" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A700" s="1" t="s">
-        <v>1896</v>
+        <v>1893</v>
       </c>
       <c r="B700" s="1" t="s">
-        <v>1897</v>
+        <v>1894</v>
       </c>
       <c r="C700" s="1" t="s">
         <v>3</v>
@@ -21095,7 +21134,7 @@
         <v>4</v>
       </c>
       <c r="E700" s="1" t="s">
-        <v>1898</v>
+        <v>1895</v>
       </c>
       <c r="F700" s="1" t="s">
         <v>5</v>
@@ -21103,10 +21142,10 @@
     </row>
     <row r="701" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A701" s="1" t="s">
-        <v>1899</v>
+        <v>1896</v>
       </c>
       <c r="B701" s="1" t="s">
-        <v>1900</v>
+        <v>1897</v>
       </c>
       <c r="C701" s="1" t="s">
         <v>3</v>
@@ -21115,7 +21154,7 @@
         <v>4</v>
       </c>
       <c r="E701" s="1" t="s">
-        <v>1901</v>
+        <v>1898</v>
       </c>
       <c r="F701" s="1" t="s">
         <v>5</v>
@@ -21123,10 +21162,10 @@
     </row>
     <row r="702" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A702" s="1" t="s">
-        <v>1902</v>
+        <v>1899</v>
       </c>
       <c r="B702" s="1" t="s">
-        <v>1876</v>
+        <v>1873</v>
       </c>
       <c r="C702" s="1" t="s">
         <v>3</v>
@@ -21135,7 +21174,7 @@
         <v>4</v>
       </c>
       <c r="E702" s="1" t="s">
-        <v>1903</v>
+        <v>1900</v>
       </c>
       <c r="F702" s="1" t="s">
         <v>5</v>
@@ -21143,10 +21182,10 @@
     </row>
     <row r="703" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A703" s="1" t="s">
-        <v>1904</v>
+        <v>1901</v>
       </c>
       <c r="B703" s="1" t="s">
-        <v>1879</v>
+        <v>1876</v>
       </c>
       <c r="C703" s="1" t="s">
         <v>3</v>
@@ -21155,7 +21194,7 @@
         <v>4</v>
       </c>
       <c r="E703" s="1" t="s">
-        <v>1905</v>
+        <v>1902</v>
       </c>
       <c r="F703" s="1" t="s">
         <v>5</v>
@@ -21163,10 +21202,10 @@
     </row>
     <row r="704" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A704" s="1" t="s">
-        <v>1906</v>
+        <v>1903</v>
       </c>
       <c r="B704" s="1" t="s">
-        <v>1882</v>
+        <v>1879</v>
       </c>
       <c r="C704" s="1" t="s">
         <v>3</v>
@@ -21175,7 +21214,7 @@
         <v>4</v>
       </c>
       <c r="E704" s="1" t="s">
-        <v>1907</v>
+        <v>1904</v>
       </c>
       <c r="F704" s="1" t="s">
         <v>5</v>
@@ -21183,10 +21222,10 @@
     </row>
     <row r="705" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A705" s="1" t="s">
-        <v>1908</v>
+        <v>1905</v>
       </c>
       <c r="B705" s="1" t="s">
-        <v>1885</v>
+        <v>1882</v>
       </c>
       <c r="C705" s="1" t="s">
         <v>3</v>
@@ -21195,7 +21234,7 @@
         <v>4</v>
       </c>
       <c r="E705" s="1" t="s">
-        <v>1909</v>
+        <v>1906</v>
       </c>
       <c r="F705" s="1" t="s">
         <v>5</v>
@@ -21203,10 +21242,10 @@
     </row>
     <row r="706" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A706" s="1" t="s">
-        <v>1910</v>
+        <v>1907</v>
       </c>
       <c r="B706" s="1" t="s">
-        <v>1888</v>
+        <v>1885</v>
       </c>
       <c r="C706" s="1" t="s">
         <v>3</v>
@@ -21215,7 +21254,7 @@
         <v>4</v>
       </c>
       <c r="E706" s="1" t="s">
-        <v>1911</v>
+        <v>1908</v>
       </c>
       <c r="F706" s="1" t="s">
         <v>5</v>
@@ -21223,10 +21262,10 @@
     </row>
     <row r="707" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A707" s="1" t="s">
-        <v>1912</v>
+        <v>1909</v>
       </c>
       <c r="B707" s="1" t="s">
-        <v>1891</v>
+        <v>1888</v>
       </c>
       <c r="C707" s="1" t="s">
         <v>3</v>
@@ -21235,7 +21274,7 @@
         <v>4</v>
       </c>
       <c r="E707" s="1" t="s">
-        <v>1913</v>
+        <v>1910</v>
       </c>
       <c r="F707" s="1" t="s">
         <v>5</v>
@@ -21243,10 +21282,10 @@
     </row>
     <row r="708" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A708" s="1" t="s">
-        <v>1914</v>
+        <v>1911</v>
       </c>
       <c r="B708" s="1" t="s">
-        <v>1894</v>
+        <v>1891</v>
       </c>
       <c r="C708" s="1" t="s">
         <v>3</v>
@@ -21255,7 +21294,7 @@
         <v>4</v>
       </c>
       <c r="E708" s="1" t="s">
-        <v>1915</v>
+        <v>1912</v>
       </c>
       <c r="F708" s="1" t="s">
         <v>5</v>
@@ -21263,10 +21302,10 @@
     </row>
     <row r="709" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A709" s="1" t="s">
-        <v>1916</v>
+        <v>1913</v>
       </c>
       <c r="B709" s="1" t="s">
-        <v>1897</v>
+        <v>1894</v>
       </c>
       <c r="C709" s="1" t="s">
         <v>3</v>
@@ -21275,7 +21314,7 @@
         <v>4</v>
       </c>
       <c r="E709" s="1" t="s">
-        <v>1917</v>
+        <v>1914</v>
       </c>
       <c r="F709" s="1" t="s">
         <v>5</v>
@@ -21283,10 +21322,10 @@
     </row>
     <row r="710" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A710" s="1" t="s">
-        <v>1918</v>
+        <v>1915</v>
       </c>
       <c r="B710" s="1" t="s">
-        <v>1900</v>
+        <v>1897</v>
       </c>
       <c r="C710" s="1" t="s">
         <v>3</v>
@@ -21295,7 +21334,7 @@
         <v>4</v>
       </c>
       <c r="E710" s="1" t="s">
-        <v>1919</v>
+        <v>1916</v>
       </c>
       <c r="F710" s="1" t="s">
         <v>5</v>
@@ -21303,10 +21342,10 @@
     </row>
     <row r="711" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A711" s="1" t="s">
-        <v>1920</v>
+        <v>1917</v>
       </c>
       <c r="B711" s="1" t="s">
-        <v>1921</v>
+        <v>1918</v>
       </c>
       <c r="C711" s="1" t="s">
         <v>3</v>
@@ -21315,7 +21354,7 @@
         <v>4</v>
       </c>
       <c r="E711" s="1" t="s">
-        <v>1922</v>
+        <v>1919</v>
       </c>
       <c r="F711" s="1" t="s">
         <v>5</v>
@@ -21323,10 +21362,10 @@
     </row>
     <row r="712" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A712" s="1" t="s">
-        <v>1923</v>
+        <v>1920</v>
       </c>
       <c r="B712" s="1" t="s">
-        <v>1924</v>
+        <v>1921</v>
       </c>
       <c r="C712" s="1" t="s">
         <v>3</v>
@@ -21335,7 +21374,7 @@
         <v>4</v>
       </c>
       <c r="E712" s="1" t="s">
-        <v>1925</v>
+        <v>1922</v>
       </c>
       <c r="F712" s="1" t="s">
         <v>5</v>
@@ -21343,10 +21382,10 @@
     </row>
     <row r="713" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A713" s="1" t="s">
-        <v>1926</v>
+        <v>1923</v>
       </c>
       <c r="B713" s="1" t="s">
-        <v>1927</v>
+        <v>1924</v>
       </c>
       <c r="C713" s="1" t="s">
         <v>3</v>
@@ -21355,7 +21394,7 @@
         <v>4</v>
       </c>
       <c r="E713" s="1" t="s">
-        <v>1928</v>
+        <v>1925</v>
       </c>
       <c r="F713" s="1" t="s">
         <v>5</v>
@@ -21363,19 +21402,19 @@
     </row>
     <row r="714" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A714" s="1" t="s">
-        <v>1929</v>
+        <v>1926</v>
       </c>
       <c r="B714" s="1" t="s">
+        <v>1924</v>
+      </c>
+      <c r="C714" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D714" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E714" s="1" t="s">
         <v>1927</v>
-      </c>
-      <c r="C714" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D714" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E714" s="1" t="s">
-        <v>1930</v>
       </c>
       <c r="F714" s="1" t="s">
         <v>5</v>
@@ -21383,10 +21422,10 @@
     </row>
     <row r="715" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A715" s="1" t="s">
-        <v>1931</v>
+        <v>1928</v>
       </c>
       <c r="B715" s="1" t="s">
-        <v>1932</v>
+        <v>1929</v>
       </c>
       <c r="C715" s="1" t="s">
         <v>3</v>
@@ -21395,7 +21434,7 @@
         <v>4</v>
       </c>
       <c r="E715" s="1" t="s">
-        <v>1933</v>
+        <v>1930</v>
       </c>
       <c r="F715" s="1" t="s">
         <v>5</v>
@@ -21403,10 +21442,10 @@
     </row>
     <row r="716" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A716" s="1" t="s">
-        <v>1934</v>
+        <v>1931</v>
       </c>
       <c r="B716" s="1" t="s">
-        <v>1935</v>
+        <v>1932</v>
       </c>
       <c r="C716" s="1" t="s">
         <v>3</v>
@@ -21415,7 +21454,7 @@
         <v>4</v>
       </c>
       <c r="E716" s="1" t="s">
-        <v>1936</v>
+        <v>1933</v>
       </c>
       <c r="F716" s="1" t="s">
         <v>5</v>
@@ -21423,10 +21462,10 @@
     </row>
     <row r="717" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A717" s="1" t="s">
-        <v>1937</v>
+        <v>1934</v>
       </c>
       <c r="B717" s="1" t="s">
-        <v>1938</v>
+        <v>1935</v>
       </c>
       <c r="C717" s="1" t="s">
         <v>3</v>
@@ -21435,7 +21474,7 @@
         <v>4</v>
       </c>
       <c r="E717" s="1" t="s">
-        <v>1939</v>
+        <v>1936</v>
       </c>
       <c r="F717" s="1" t="s">
         <v>5</v>
@@ -21443,10 +21482,10 @@
     </row>
     <row r="718" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A718" s="1" t="s">
-        <v>1940</v>
+        <v>1937</v>
       </c>
       <c r="B718" s="1" t="s">
-        <v>1921</v>
+        <v>1918</v>
       </c>
       <c r="C718" s="1" t="s">
         <v>3</v>
@@ -21455,7 +21494,7 @@
         <v>4</v>
       </c>
       <c r="E718" s="1" t="s">
-        <v>1941</v>
+        <v>1938</v>
       </c>
       <c r="F718" s="1" t="s">
         <v>5</v>
@@ -21463,10 +21502,10 @@
     </row>
     <row r="719" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A719" s="1" t="s">
-        <v>1942</v>
+        <v>1939</v>
       </c>
       <c r="B719" s="1" t="s">
-        <v>1924</v>
+        <v>1921</v>
       </c>
       <c r="C719" s="1" t="s">
         <v>3</v>
@@ -21475,7 +21514,7 @@
         <v>4</v>
       </c>
       <c r="E719" s="1" t="s">
-        <v>1943</v>
+        <v>1940</v>
       </c>
       <c r="F719" s="1" t="s">
         <v>5</v>
@@ -21483,10 +21522,10 @@
     </row>
     <row r="720" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A720" s="1" t="s">
-        <v>1944</v>
+        <v>1941</v>
       </c>
       <c r="B720" s="1" t="s">
-        <v>1945</v>
+        <v>1942</v>
       </c>
       <c r="C720" s="1" t="s">
         <v>3</v>
@@ -21495,7 +21534,7 @@
         <v>4</v>
       </c>
       <c r="E720" s="1" t="s">
-        <v>1946</v>
+        <v>1943</v>
       </c>
       <c r="F720" s="1" t="s">
         <v>5</v>
@@ -21503,10 +21542,10 @@
     </row>
     <row r="721" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A721" s="1" t="s">
-        <v>1947</v>
+        <v>1944</v>
       </c>
       <c r="B721" s="1" t="s">
-        <v>1927</v>
+        <v>1924</v>
       </c>
       <c r="C721" s="1" t="s">
         <v>3</v>
@@ -21515,7 +21554,7 @@
         <v>4</v>
       </c>
       <c r="E721" s="1" t="s">
-        <v>1948</v>
+        <v>1945</v>
       </c>
       <c r="F721" s="1" t="s">
         <v>5</v>
@@ -21523,10 +21562,10 @@
     </row>
     <row r="722" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A722" s="1" t="s">
-        <v>1949</v>
+        <v>1946</v>
       </c>
       <c r="B722" s="1" t="s">
-        <v>1950</v>
+        <v>1947</v>
       </c>
       <c r="C722" s="1" t="s">
         <v>3</v>
@@ -21535,7 +21574,7 @@
         <v>4</v>
       </c>
       <c r="E722" s="1" t="s">
-        <v>1951</v>
+        <v>1948</v>
       </c>
       <c r="F722" s="1" t="s">
         <v>5</v>
@@ -21543,10 +21582,10 @@
     </row>
     <row r="723" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A723" s="1" t="s">
-        <v>1952</v>
+        <v>1949</v>
       </c>
       <c r="B723" s="1" t="s">
-        <v>1938</v>
+        <v>1935</v>
       </c>
       <c r="C723" s="1" t="s">
         <v>3</v>
@@ -21555,7 +21594,7 @@
         <v>4</v>
       </c>
       <c r="E723" s="1" t="s">
-        <v>1953</v>
+        <v>1950</v>
       </c>
       <c r="F723" s="1" t="s">
         <v>5</v>
@@ -21563,10 +21602,10 @@
     </row>
     <row r="724" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A724" s="1" t="s">
-        <v>1954</v>
+        <v>1951</v>
       </c>
       <c r="B724" s="1" t="s">
-        <v>1955</v>
+        <v>1952</v>
       </c>
       <c r="C724" s="1" t="s">
         <v>3</v>
@@ -21575,7 +21614,7 @@
         <v>4</v>
       </c>
       <c r="E724" s="1" t="s">
-        <v>1956</v>
+        <v>1953</v>
       </c>
       <c r="F724" s="1" t="s">
         <v>5</v>
@@ -21583,10 +21622,10 @@
     </row>
     <row r="725" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A725" s="1" t="s">
-        <v>1957</v>
+        <v>1954</v>
       </c>
       <c r="B725" s="1" t="s">
-        <v>1958</v>
+        <v>1955</v>
       </c>
       <c r="C725" s="1" t="s">
         <v>3</v>
@@ -21595,7 +21634,7 @@
         <v>4</v>
       </c>
       <c r="E725" s="1" t="s">
-        <v>1959</v>
+        <v>1956</v>
       </c>
       <c r="F725" s="1" t="s">
         <v>5</v>
@@ -21603,10 +21642,10 @@
     </row>
     <row r="726" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A726" s="1" t="s">
-        <v>1960</v>
+        <v>1957</v>
       </c>
       <c r="B726" s="1" t="s">
-        <v>1961</v>
+        <v>1958</v>
       </c>
       <c r="C726" s="1" t="s">
         <v>3</v>
@@ -21615,7 +21654,7 @@
         <v>4</v>
       </c>
       <c r="E726" s="1" t="s">
-        <v>1962</v>
+        <v>1959</v>
       </c>
       <c r="F726" s="1" t="s">
         <v>5</v>
@@ -21623,10 +21662,10 @@
     </row>
     <row r="727" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A727" s="1" t="s">
-        <v>1963</v>
+        <v>1960</v>
       </c>
       <c r="B727" s="1" t="s">
-        <v>1964</v>
+        <v>1961</v>
       </c>
       <c r="C727" s="1" t="s">
         <v>3</v>
@@ -21635,7 +21674,7 @@
         <v>4</v>
       </c>
       <c r="E727" s="1" t="s">
-        <v>1965</v>
+        <v>1962</v>
       </c>
       <c r="F727" s="1" t="s">
         <v>5</v>
@@ -21643,10 +21682,10 @@
     </row>
     <row r="728" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A728" s="1" t="s">
-        <v>1966</v>
+        <v>1963</v>
       </c>
       <c r="B728" s="1" t="s">
-        <v>1967</v>
+        <v>1964</v>
       </c>
       <c r="C728" s="1" t="s">
         <v>3</v>
@@ -21655,7 +21694,7 @@
         <v>4</v>
       </c>
       <c r="E728" s="1" t="s">
-        <v>1968</v>
+        <v>1965</v>
       </c>
       <c r="F728" s="1" t="s">
         <v>5</v>
@@ -21663,10 +21702,10 @@
     </row>
     <row r="729" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A729" s="1" t="s">
-        <v>1969</v>
+        <v>1966</v>
       </c>
       <c r="B729" s="1" t="s">
-        <v>1970</v>
+        <v>1967</v>
       </c>
       <c r="C729" s="1" t="s">
         <v>3</v>
@@ -21675,7 +21714,7 @@
         <v>4</v>
       </c>
       <c r="E729" s="1" t="s">
-        <v>1971</v>
+        <v>1968</v>
       </c>
       <c r="F729" s="1" t="s">
         <v>5</v>
@@ -21683,10 +21722,10 @@
     </row>
     <row r="730" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A730" s="1" t="s">
-        <v>1972</v>
+        <v>1969</v>
       </c>
       <c r="B730" s="1" t="s">
-        <v>1973</v>
+        <v>1970</v>
       </c>
       <c r="C730" s="1" t="s">
         <v>3</v>
@@ -21695,7 +21734,7 @@
         <v>4</v>
       </c>
       <c r="E730" s="1" t="s">
-        <v>1974</v>
+        <v>1971</v>
       </c>
       <c r="F730" s="1" t="s">
         <v>5</v>
@@ -21703,10 +21742,10 @@
     </row>
     <row r="731" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A731" s="1" t="s">
-        <v>1975</v>
+        <v>1972</v>
       </c>
       <c r="B731" s="1" t="s">
-        <v>1976</v>
+        <v>1973</v>
       </c>
       <c r="C731" s="1" t="s">
         <v>3</v>
@@ -21715,7 +21754,7 @@
         <v>4</v>
       </c>
       <c r="E731" s="1" t="s">
-        <v>1977</v>
+        <v>1974</v>
       </c>
       <c r="F731" s="1" t="s">
         <v>5</v>
@@ -21723,10 +21762,10 @@
     </row>
     <row r="732" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A732" s="1" t="s">
-        <v>1978</v>
+        <v>1975</v>
       </c>
       <c r="B732" s="1" t="s">
-        <v>1979</v>
+        <v>1976</v>
       </c>
       <c r="C732" s="1" t="s">
         <v>3</v>
@@ -21735,7 +21774,7 @@
         <v>4</v>
       </c>
       <c r="E732" s="1" t="s">
-        <v>1980</v>
+        <v>1977</v>
       </c>
       <c r="F732" s="1" t="s">
         <v>5</v>
@@ -21743,10 +21782,10 @@
     </row>
     <row r="733" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A733" s="1" t="s">
-        <v>1981</v>
+        <v>1978</v>
       </c>
       <c r="B733" s="1" t="s">
-        <v>1982</v>
+        <v>1979</v>
       </c>
       <c r="C733" s="1" t="s">
         <v>3</v>
@@ -21755,7 +21794,7 @@
         <v>4</v>
       </c>
       <c r="E733" s="1" t="s">
-        <v>1983</v>
+        <v>1980</v>
       </c>
       <c r="F733" s="1" t="s">
         <v>5</v>
@@ -21763,10 +21802,10 @@
     </row>
     <row r="734" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A734" s="1" t="s">
-        <v>1984</v>
+        <v>1981</v>
       </c>
       <c r="B734" s="1" t="s">
-        <v>1985</v>
+        <v>1982</v>
       </c>
       <c r="C734" s="1" t="s">
         <v>3</v>
@@ -21775,7 +21814,7 @@
         <v>4</v>
       </c>
       <c r="E734" s="1" t="s">
-        <v>1986</v>
+        <v>1983</v>
       </c>
       <c r="F734" s="1" t="s">
         <v>5</v>
@@ -21783,10 +21822,10 @@
     </row>
     <row r="735" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A735" s="1" t="s">
-        <v>1987</v>
+        <v>1984</v>
       </c>
       <c r="B735" s="1" t="s">
-        <v>1988</v>
+        <v>1985</v>
       </c>
       <c r="C735" s="1" t="s">
         <v>3</v>
@@ -21795,7 +21834,7 @@
         <v>4</v>
       </c>
       <c r="E735" s="1" t="s">
-        <v>1989</v>
+        <v>1986</v>
       </c>
       <c r="F735" s="1" t="s">
         <v>5</v>
@@ -21803,10 +21842,10 @@
     </row>
     <row r="736" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A736" s="1" t="s">
-        <v>1990</v>
+        <v>1987</v>
       </c>
       <c r="B736" s="1" t="s">
-        <v>1991</v>
+        <v>1988</v>
       </c>
       <c r="C736" s="1" t="s">
         <v>3</v>
@@ -21815,7 +21854,7 @@
         <v>4</v>
       </c>
       <c r="E736" s="1" t="s">
-        <v>1992</v>
+        <v>1989</v>
       </c>
       <c r="F736" s="1" t="s">
         <v>5</v>
@@ -21823,10 +21862,10 @@
     </row>
     <row r="737" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A737" s="1" t="s">
-        <v>1993</v>
+        <v>1990</v>
       </c>
       <c r="B737" s="1" t="s">
-        <v>1994</v>
+        <v>1991</v>
       </c>
       <c r="C737" s="1" t="s">
         <v>3</v>
@@ -21835,7 +21874,7 @@
         <v>4</v>
       </c>
       <c r="E737" s="1" t="s">
-        <v>1995</v>
+        <v>1992</v>
       </c>
       <c r="F737" s="1" t="s">
         <v>5</v>
@@ -21843,10 +21882,10 @@
     </row>
     <row r="738" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A738" s="1" t="s">
-        <v>1996</v>
+        <v>1993</v>
       </c>
       <c r="B738" s="1" t="s">
-        <v>1997</v>
+        <v>1994</v>
       </c>
       <c r="C738" s="1" t="s">
         <v>3</v>
@@ -21855,7 +21894,7 @@
         <v>4</v>
       </c>
       <c r="E738" s="1" t="s">
-        <v>1998</v>
+        <v>1995</v>
       </c>
       <c r="F738" s="1" t="s">
         <v>5</v>
@@ -21863,10 +21902,10 @@
     </row>
     <row r="739" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A739" s="1" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="B739" s="1" t="s">
-        <v>2000</v>
+        <v>1997</v>
       </c>
       <c r="C739" s="1" t="s">
         <v>3</v>
@@ -21875,7 +21914,7 @@
         <v>4</v>
       </c>
       <c r="E739" s="1" t="s">
-        <v>2001</v>
+        <v>1998</v>
       </c>
       <c r="F739" s="1" t="s">
         <v>5</v>
@@ -21883,10 +21922,10 @@
     </row>
     <row r="740" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A740" s="1" t="s">
-        <v>2002</v>
+        <v>1999</v>
       </c>
       <c r="B740" s="1" t="s">
-        <v>2003</v>
+        <v>2000</v>
       </c>
       <c r="C740" s="1" t="s">
         <v>3</v>
@@ -21895,7 +21934,7 @@
         <v>4</v>
       </c>
       <c r="E740" s="1" t="s">
-        <v>2004</v>
+        <v>2001</v>
       </c>
       <c r="F740" s="1" t="s">
         <v>5</v>
@@ -21903,10 +21942,10 @@
     </row>
     <row r="741" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A741" s="1" t="s">
-        <v>2005</v>
+        <v>2002</v>
       </c>
       <c r="B741" s="1" t="s">
-        <v>1958</v>
+        <v>1955</v>
       </c>
       <c r="C741" s="1" t="s">
         <v>3</v>
@@ -21915,7 +21954,7 @@
         <v>4</v>
       </c>
       <c r="E741" s="1" t="s">
-        <v>2006</v>
+        <v>2003</v>
       </c>
       <c r="F741" s="1" t="s">
         <v>5</v>
@@ -21923,10 +21962,10 @@
     </row>
     <row r="742" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A742" s="1" t="s">
-        <v>2007</v>
+        <v>2004</v>
       </c>
       <c r="B742" s="1" t="s">
-        <v>1961</v>
+        <v>1958</v>
       </c>
       <c r="C742" s="1" t="s">
         <v>3</v>
@@ -21935,7 +21974,7 @@
         <v>4</v>
       </c>
       <c r="E742" s="1" t="s">
-        <v>2008</v>
+        <v>2005</v>
       </c>
       <c r="F742" s="1" t="s">
         <v>5</v>
@@ -21943,10 +21982,10 @@
     </row>
     <row r="743" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A743" s="1" t="s">
-        <v>2009</v>
+        <v>2006</v>
       </c>
       <c r="B743" s="1" t="s">
-        <v>1967</v>
+        <v>1964</v>
       </c>
       <c r="C743" s="1" t="s">
         <v>3</v>
@@ -21955,7 +21994,7 @@
         <v>4</v>
       </c>
       <c r="E743" s="1" t="s">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="F743" s="1" t="s">
         <v>5</v>
@@ -21963,10 +22002,10 @@
     </row>
     <row r="744" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A744" s="1" t="s">
-        <v>2011</v>
+        <v>2008</v>
       </c>
       <c r="B744" s="1" t="s">
-        <v>1970</v>
+        <v>1967</v>
       </c>
       <c r="C744" s="1" t="s">
         <v>3</v>
@@ -21975,7 +22014,7 @@
         <v>4</v>
       </c>
       <c r="E744" s="1" t="s">
-        <v>2012</v>
+        <v>2009</v>
       </c>
       <c r="F744" s="1" t="s">
         <v>5</v>
@@ -21983,10 +22022,10 @@
     </row>
     <row r="745" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A745" s="1" t="s">
-        <v>2013</v>
+        <v>2010</v>
       </c>
       <c r="B745" s="1" t="s">
-        <v>1973</v>
+        <v>1970</v>
       </c>
       <c r="C745" s="1" t="s">
         <v>3</v>
@@ -21995,7 +22034,7 @@
         <v>4</v>
       </c>
       <c r="E745" s="1" t="s">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="F745" s="1" t="s">
         <v>5</v>
@@ -22003,10 +22042,10 @@
     </row>
     <row r="746" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A746" s="1" t="s">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="B746" s="1" t="s">
-        <v>1976</v>
+        <v>1973</v>
       </c>
       <c r="C746" s="1" t="s">
         <v>3</v>
@@ -22015,7 +22054,7 @@
         <v>4</v>
       </c>
       <c r="E746" s="1" t="s">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="F746" s="1" t="s">
         <v>5</v>
@@ -22023,10 +22062,10 @@
     </row>
     <row r="747" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A747" s="1" t="s">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="B747" s="1" t="s">
-        <v>1979</v>
+        <v>1976</v>
       </c>
       <c r="C747" s="1" t="s">
         <v>3</v>
@@ -22035,7 +22074,7 @@
         <v>4</v>
       </c>
       <c r="E747" s="1" t="s">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="F747" s="1" t="s">
         <v>5</v>
@@ -22043,10 +22082,10 @@
     </row>
     <row r="748" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A748" s="1" t="s">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="B748" s="1" t="s">
-        <v>1982</v>
+        <v>1979</v>
       </c>
       <c r="C748" s="1" t="s">
         <v>3</v>
@@ -22055,7 +22094,7 @@
         <v>4</v>
       </c>
       <c r="E748" s="1" t="s">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="F748" s="1" t="s">
         <v>5</v>
@@ -22063,10 +22102,10 @@
     </row>
     <row r="749" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A749" s="1" t="s">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="B749" s="1" t="s">
-        <v>1985</v>
+        <v>1982</v>
       </c>
       <c r="C749" s="1" t="s">
         <v>3</v>
@@ -22075,7 +22114,7 @@
         <v>4</v>
       </c>
       <c r="E749" s="1" t="s">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="F749" s="1" t="s">
         <v>5</v>
@@ -22083,10 +22122,10 @@
     </row>
     <row r="750" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A750" s="1" t="s">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="B750" s="1" t="s">
-        <v>1988</v>
+        <v>1985</v>
       </c>
       <c r="C750" s="1" t="s">
         <v>3</v>
@@ -22095,7 +22134,7 @@
         <v>4</v>
       </c>
       <c r="E750" s="1" t="s">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="F750" s="1" t="s">
         <v>5</v>
@@ -22103,10 +22142,10 @@
     </row>
     <row r="751" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A751" s="1" t="s">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B751" s="1" t="s">
-        <v>1991</v>
+        <v>1988</v>
       </c>
       <c r="C751" s="1" t="s">
         <v>3</v>
@@ -22115,7 +22154,7 @@
         <v>4</v>
       </c>
       <c r="E751" s="1" t="s">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="F751" s="1" t="s">
         <v>5</v>
@@ -22123,10 +22162,10 @@
     </row>
     <row r="752" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A752" s="1" t="s">
-        <v>2027</v>
+        <v>2024</v>
       </c>
       <c r="B752" s="1" t="s">
-        <v>1994</v>
+        <v>1991</v>
       </c>
       <c r="C752" s="1" t="s">
         <v>3</v>
@@ -22135,7 +22174,7 @@
         <v>4</v>
       </c>
       <c r="E752" s="1" t="s">
-        <v>2028</v>
+        <v>2025</v>
       </c>
       <c r="F752" s="1" t="s">
         <v>5</v>
@@ -22143,10 +22182,10 @@
     </row>
     <row r="753" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A753" s="1" t="s">
-        <v>2029</v>
+        <v>2026</v>
       </c>
       <c r="B753" s="1" t="s">
-        <v>2030</v>
+        <v>2027</v>
       </c>
       <c r="C753" s="1" t="s">
         <v>3</v>
@@ -22155,7 +22194,7 @@
         <v>4</v>
       </c>
       <c r="E753" s="1" t="s">
-        <v>2031</v>
+        <v>2028</v>
       </c>
       <c r="F753" s="1" t="s">
         <v>5</v>
@@ -22163,10 +22202,10 @@
     </row>
     <row r="754" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A754" s="1" t="s">
-        <v>2032</v>
+        <v>2029</v>
       </c>
       <c r="B754" s="1" t="s">
-        <v>2033</v>
+        <v>2030</v>
       </c>
       <c r="C754" s="1" t="s">
         <v>3</v>
@@ -22175,7 +22214,7 @@
         <v>4</v>
       </c>
       <c r="E754" s="1" t="s">
-        <v>2034</v>
+        <v>2031</v>
       </c>
       <c r="F754" s="1" t="s">
         <v>5</v>
@@ -22183,10 +22222,10 @@
     </row>
     <row r="755" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A755" s="1" t="s">
-        <v>2035</v>
+        <v>2032</v>
       </c>
       <c r="B755" s="1" t="s">
-        <v>2036</v>
+        <v>2033</v>
       </c>
       <c r="C755" s="1" t="s">
         <v>3</v>
@@ -22195,7 +22234,7 @@
         <v>4</v>
       </c>
       <c r="E755" s="1" t="s">
-        <v>2037</v>
+        <v>2034</v>
       </c>
       <c r="F755" s="1" t="s">
         <v>5</v>
@@ -22203,10 +22242,10 @@
     </row>
     <row r="756" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A756" s="1" t="s">
-        <v>2038</v>
+        <v>2035</v>
       </c>
       <c r="B756" s="1" t="s">
-        <v>2039</v>
+        <v>2036</v>
       </c>
       <c r="C756" s="1" t="s">
         <v>3</v>
@@ -22215,7 +22254,7 @@
         <v>4</v>
       </c>
       <c r="E756" s="1" t="s">
-        <v>2040</v>
+        <v>2037</v>
       </c>
       <c r="F756" s="1" t="s">
         <v>5</v>
@@ -22223,10 +22262,10 @@
     </row>
     <row r="757" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A757" s="1" t="s">
-        <v>2041</v>
+        <v>2038</v>
       </c>
       <c r="B757" s="1" t="s">
-        <v>2042</v>
+        <v>2039</v>
       </c>
       <c r="C757" s="1" t="s">
         <v>3</v>
@@ -22235,7 +22274,7 @@
         <v>4</v>
       </c>
       <c r="E757" s="1" t="s">
-        <v>2043</v>
+        <v>2040</v>
       </c>
       <c r="F757" s="1" t="s">
         <v>5</v>
@@ -22243,10 +22282,10 @@
     </row>
     <row r="758" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A758" s="1" t="s">
-        <v>2044</v>
+        <v>2041</v>
       </c>
       <c r="B758" s="1" t="s">
-        <v>2045</v>
+        <v>2042</v>
       </c>
       <c r="C758" s="1" t="s">
         <v>3</v>
@@ -22255,7 +22294,7 @@
         <v>4</v>
       </c>
       <c r="E758" s="1" t="s">
-        <v>2046</v>
+        <v>2043</v>
       </c>
       <c r="F758" s="1" t="s">
         <v>5</v>
@@ -22263,10 +22302,10 @@
     </row>
     <row r="759" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A759" s="1" t="s">
-        <v>2047</v>
+        <v>2044</v>
       </c>
       <c r="B759" s="1" t="s">
-        <v>2048</v>
+        <v>2045</v>
       </c>
       <c r="C759" s="1" t="s">
         <v>3</v>
@@ -22275,7 +22314,7 @@
         <v>4</v>
       </c>
       <c r="E759" s="1" t="s">
-        <v>2049</v>
+        <v>2046</v>
       </c>
       <c r="F759" s="1" t="s">
         <v>5</v>
@@ -22283,10 +22322,10 @@
     </row>
     <row r="760" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A760" s="1" t="s">
-        <v>2050</v>
+        <v>2047</v>
       </c>
       <c r="B760" s="1" t="s">
-        <v>2051</v>
+        <v>2048</v>
       </c>
       <c r="C760" s="1" t="s">
         <v>3</v>
@@ -22295,7 +22334,7 @@
         <v>4</v>
       </c>
       <c r="E760" s="1" t="s">
-        <v>2052</v>
+        <v>2049</v>
       </c>
       <c r="F760" s="1" t="s">
         <v>5</v>
@@ -22303,10 +22342,10 @@
     </row>
     <row r="761" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A761" s="1" t="s">
-        <v>2053</v>
+        <v>2050</v>
       </c>
       <c r="B761" s="1" t="s">
-        <v>2054</v>
+        <v>2051</v>
       </c>
       <c r="C761" s="1" t="s">
         <v>3</v>
@@ -22315,7 +22354,7 @@
         <v>4</v>
       </c>
       <c r="E761" s="1" t="s">
-        <v>2055</v>
+        <v>2052</v>
       </c>
       <c r="F761" s="1" t="s">
         <v>5</v>
@@ -22323,10 +22362,10 @@
     </row>
     <row r="762" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A762" s="1" t="s">
-        <v>2056</v>
+        <v>2053</v>
       </c>
       <c r="B762" s="1" t="s">
-        <v>2057</v>
+        <v>2054</v>
       </c>
       <c r="C762" s="1" t="s">
         <v>3</v>
@@ -22335,7 +22374,7 @@
         <v>4</v>
       </c>
       <c r="E762" s="1" t="s">
-        <v>2058</v>
+        <v>2055</v>
       </c>
       <c r="F762" s="1" t="s">
         <v>5</v>
@@ -22343,10 +22382,10 @@
     </row>
     <row r="763" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A763" s="1" t="s">
-        <v>2059</v>
+        <v>2056</v>
       </c>
       <c r="B763" s="1" t="s">
-        <v>2060</v>
+        <v>2057</v>
       </c>
       <c r="C763" s="1" t="s">
         <v>3</v>
@@ -22355,7 +22394,7 @@
         <v>4</v>
       </c>
       <c r="E763" s="1" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
       <c r="F763" s="1" t="s">
         <v>5</v>
@@ -22363,10 +22402,10 @@
     </row>
     <row r="764" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A764" s="1" t="s">
-        <v>2062</v>
+        <v>2059</v>
       </c>
       <c r="B764" s="1" t="s">
-        <v>2063</v>
+        <v>2060</v>
       </c>
       <c r="C764" s="1" t="s">
         <v>3</v>
@@ -22375,7 +22414,7 @@
         <v>4</v>
       </c>
       <c r="E764" s="1" t="s">
-        <v>2064</v>
+        <v>2061</v>
       </c>
       <c r="F764" s="1" t="s">
         <v>5</v>
@@ -22383,10 +22422,10 @@
     </row>
     <row r="765" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A765" s="1" t="s">
-        <v>2065</v>
+        <v>2062</v>
       </c>
       <c r="B765" s="1" t="s">
-        <v>2066</v>
+        <v>2063</v>
       </c>
       <c r="C765" s="1" t="s">
         <v>3</v>
@@ -22395,7 +22434,7 @@
         <v>4</v>
       </c>
       <c r="E765" s="1" t="s">
-        <v>2067</v>
+        <v>2064</v>
       </c>
       <c r="F765" s="1" t="s">
         <v>5</v>
@@ -22403,10 +22442,10 @@
     </row>
     <row r="766" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A766" s="1" t="s">
-        <v>2068</v>
+        <v>2065</v>
       </c>
       <c r="B766" s="1" t="s">
-        <v>2069</v>
+        <v>2066</v>
       </c>
       <c r="C766" s="1" t="s">
         <v>3</v>
@@ -22415,7 +22454,7 @@
         <v>4</v>
       </c>
       <c r="E766" s="1" t="s">
-        <v>2070</v>
+        <v>2067</v>
       </c>
       <c r="F766" s="1" t="s">
         <v>5</v>
@@ -22423,10 +22462,10 @@
     </row>
     <row r="767" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A767" s="1" t="s">
-        <v>2071</v>
+        <v>2068</v>
       </c>
       <c r="B767" s="1" t="s">
-        <v>2072</v>
+        <v>2069</v>
       </c>
       <c r="C767" s="1" t="s">
         <v>3</v>
@@ -22435,7 +22474,7 @@
         <v>4</v>
       </c>
       <c r="E767" s="1" t="s">
-        <v>2073</v>
+        <v>2070</v>
       </c>
       <c r="F767" s="1" t="s">
         <v>5</v>
@@ -22443,10 +22482,10 @@
     </row>
     <row r="768" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A768" s="1" t="s">
-        <v>2074</v>
+        <v>2071</v>
       </c>
       <c r="B768" s="1" t="s">
-        <v>2075</v>
+        <v>2072</v>
       </c>
       <c r="C768" s="1" t="s">
         <v>3</v>
@@ -22455,7 +22494,7 @@
         <v>4</v>
       </c>
       <c r="E768" s="1" t="s">
-        <v>2076</v>
+        <v>2073</v>
       </c>
       <c r="F768" s="1" t="s">
         <v>5</v>
@@ -22463,10 +22502,10 @@
     </row>
     <row r="769" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A769" s="1" t="s">
-        <v>2077</v>
+        <v>2074</v>
       </c>
       <c r="B769" s="1" t="s">
-        <v>2078</v>
+        <v>2075</v>
       </c>
       <c r="C769" s="1" t="s">
         <v>3</v>
@@ -22475,7 +22514,7 @@
         <v>4</v>
       </c>
       <c r="E769" s="1" t="s">
-        <v>2079</v>
+        <v>2076</v>
       </c>
       <c r="F769" s="1" t="s">
         <v>5</v>
@@ -22483,10 +22522,10 @@
     </row>
     <row r="770" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A770" s="1" t="s">
-        <v>2080</v>
+        <v>2077</v>
       </c>
       <c r="B770" s="1" t="s">
-        <v>2063</v>
+        <v>2060</v>
       </c>
       <c r="C770" s="1" t="s">
         <v>3</v>
@@ -22495,7 +22534,7 @@
         <v>4</v>
       </c>
       <c r="E770" s="1" t="s">
-        <v>2081</v>
+        <v>2078</v>
       </c>
       <c r="F770" s="1" t="s">
         <v>5</v>
@@ -22503,10 +22542,10 @@
     </row>
     <row r="771" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A771" s="1" t="s">
-        <v>2082</v>
+        <v>2079</v>
       </c>
       <c r="B771" s="1" t="s">
-        <v>2083</v>
+        <v>2080</v>
       </c>
       <c r="C771" s="1" t="s">
         <v>3</v>
@@ -22515,7 +22554,7 @@
         <v>4</v>
       </c>
       <c r="E771" s="1" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="F771" s="1" t="s">
         <v>5</v>
@@ -22523,10 +22562,10 @@
     </row>
     <row r="772" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A772" s="1" t="s">
-        <v>2085</v>
+        <v>2082</v>
       </c>
       <c r="B772" s="1" t="s">
-        <v>2086</v>
+        <v>2083</v>
       </c>
       <c r="C772" s="1" t="s">
         <v>3</v>
@@ -22535,7 +22574,7 @@
         <v>4</v>
       </c>
       <c r="E772" s="1" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="F772" s="1" t="s">
         <v>5</v>
@@ -22543,10 +22582,10 @@
     </row>
     <row r="773" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A773" s="1" t="s">
-        <v>2088</v>
+        <v>2085</v>
       </c>
       <c r="B773" s="1" t="s">
-        <v>2089</v>
+        <v>2086</v>
       </c>
       <c r="C773" s="1" t="s">
         <v>3</v>
@@ -22555,7 +22594,7 @@
         <v>4</v>
       </c>
       <c r="E773" s="1" t="s">
-        <v>2090</v>
+        <v>2087</v>
       </c>
       <c r="F773" s="1" t="s">
         <v>5</v>
@@ -22563,10 +22602,10 @@
     </row>
     <row r="774" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A774" s="1" t="s">
-        <v>2091</v>
+        <v>2088</v>
       </c>
       <c r="B774" s="1" t="s">
-        <v>2092</v>
+        <v>2089</v>
       </c>
       <c r="C774" s="1" t="s">
         <v>3</v>
@@ -22575,7 +22614,7 @@
         <v>4</v>
       </c>
       <c r="E774" s="1" t="s">
-        <v>2093</v>
+        <v>2090</v>
       </c>
       <c r="F774" s="1" t="s">
         <v>5</v>
@@ -22583,10 +22622,10 @@
     </row>
     <row r="775" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A775" s="1" t="s">
-        <v>2094</v>
+        <v>2091</v>
       </c>
       <c r="B775" s="1" t="s">
-        <v>2095</v>
+        <v>2092</v>
       </c>
       <c r="C775" s="1" t="s">
         <v>3</v>
@@ -22595,7 +22634,7 @@
         <v>4</v>
       </c>
       <c r="E775" s="1" t="s">
-        <v>2096</v>
+        <v>2093</v>
       </c>
       <c r="F775" s="1" t="s">
         <v>5</v>
@@ -22603,10 +22642,10 @@
     </row>
     <row r="776" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A776" s="1" t="s">
-        <v>2097</v>
+        <v>2094</v>
       </c>
       <c r="B776" s="1" t="s">
-        <v>2098</v>
+        <v>2095</v>
       </c>
       <c r="C776" s="1" t="s">
         <v>3</v>
@@ -22615,7 +22654,7 @@
         <v>4</v>
       </c>
       <c r="E776" s="1" t="s">
-        <v>2099</v>
+        <v>2096</v>
       </c>
       <c r="F776" s="1" t="s">
         <v>5</v>
@@ -22623,10 +22662,10 @@
     </row>
     <row r="777" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A777" s="1" t="s">
-        <v>2100</v>
+        <v>2097</v>
       </c>
       <c r="B777" s="1" t="s">
-        <v>2086</v>
+        <v>2083</v>
       </c>
       <c r="C777" s="1" t="s">
         <v>3</v>
@@ -22635,7 +22674,7 @@
         <v>4</v>
       </c>
       <c r="E777" s="1" t="s">
-        <v>2101</v>
+        <v>2098</v>
       </c>
       <c r="F777" s="1" t="s">
         <v>5</v>
@@ -22643,10 +22682,10 @@
     </row>
     <row r="778" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A778" s="1" t="s">
-        <v>2102</v>
+        <v>2099</v>
       </c>
       <c r="B778" s="1" t="s">
-        <v>2089</v>
+        <v>2086</v>
       </c>
       <c r="C778" s="1" t="s">
         <v>3</v>
@@ -22655,7 +22694,7 @@
         <v>4</v>
       </c>
       <c r="E778" s="1" t="s">
-        <v>2103</v>
+        <v>2100</v>
       </c>
       <c r="F778" s="1" t="s">
         <v>5</v>
@@ -22663,10 +22702,10 @@
     </row>
     <row r="779" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A779" s="1" t="s">
-        <v>2104</v>
+        <v>2101</v>
       </c>
       <c r="B779" s="1" t="s">
-        <v>2092</v>
+        <v>2089</v>
       </c>
       <c r="C779" s="1" t="s">
         <v>3</v>
@@ -22675,7 +22714,7 @@
         <v>4</v>
       </c>
       <c r="E779" s="1" t="s">
-        <v>2105</v>
+        <v>2102</v>
       </c>
       <c r="F779" s="1" t="s">
         <v>5</v>
@@ -22683,10 +22722,10 @@
     </row>
     <row r="780" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A780" s="1" t="s">
-        <v>2106</v>
+        <v>2103</v>
       </c>
       <c r="B780" s="1" t="s">
-        <v>2098</v>
+        <v>2095</v>
       </c>
       <c r="C780" s="1" t="s">
         <v>3</v>
@@ -22695,7 +22734,7 @@
         <v>4</v>
       </c>
       <c r="E780" s="1" t="s">
-        <v>2107</v>
+        <v>2104</v>
       </c>
       <c r="F780" s="1" t="s">
         <v>5</v>
@@ -22703,10 +22742,10 @@
     </row>
     <row r="781" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A781" s="1" t="s">
-        <v>2108</v>
+        <v>2105</v>
       </c>
       <c r="B781" s="1" t="s">
-        <v>2095</v>
+        <v>2092</v>
       </c>
       <c r="C781" s="1" t="s">
         <v>3</v>
@@ -22715,7 +22754,7 @@
         <v>4</v>
       </c>
       <c r="E781" s="1" t="s">
-        <v>2109</v>
+        <v>2106</v>
       </c>
       <c r="F781" s="1" t="s">
         <v>5</v>
@@ -22723,7 +22762,7 @@
     </row>
     <row r="782" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A782" s="1" t="s">
-        <v>2110</v>
+        <v>2107</v>
       </c>
       <c r="B782" s="1" t="s">
         <v>1502</v>
@@ -22735,7 +22774,7 @@
         <v>4</v>
       </c>
       <c r="E782" s="1" t="s">
-        <v>2111</v>
+        <v>2108</v>
       </c>
       <c r="F782" s="1" t="s">
         <v>5</v>
@@ -22743,10 +22782,10 @@
     </row>
     <row r="783" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A783" s="1" t="s">
-        <v>2112</v>
+        <v>2109</v>
       </c>
       <c r="B783" s="1" t="s">
-        <v>2113</v>
+        <v>2110</v>
       </c>
       <c r="C783" s="1" t="s">
         <v>3</v>
@@ -22755,7 +22794,7 @@
         <v>4</v>
       </c>
       <c r="E783" s="1" t="s">
-        <v>2114</v>
+        <v>2111</v>
       </c>
       <c r="F783" s="1" t="s">
         <v>5</v>
@@ -22763,7 +22802,7 @@
     </row>
     <row r="784" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A784" s="1" t="s">
-        <v>2115</v>
+        <v>2112</v>
       </c>
       <c r="B784" s="1" t="s">
         <v>152</v>
@@ -22775,7 +22814,7 @@
         <v>4</v>
       </c>
       <c r="E784" s="1" t="s">
-        <v>2116</v>
+        <v>2113</v>
       </c>
       <c r="F784" s="1" t="s">
         <v>5</v>
@@ -22783,10 +22822,10 @@
     </row>
     <row r="785" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A785" s="1" t="s">
-        <v>2117</v>
+        <v>2114</v>
       </c>
       <c r="B785" s="1" t="s">
-        <v>2113</v>
+        <v>2110</v>
       </c>
       <c r="C785" s="1" t="s">
         <v>3</v>
@@ -22795,7 +22834,7 @@
         <v>4</v>
       </c>
       <c r="E785" s="1" t="s">
-        <v>2118</v>
+        <v>2115</v>
       </c>
       <c r="F785" s="1" t="s">
         <v>5</v>
@@ -22803,7 +22842,7 @@
     </row>
     <row r="786" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A786" s="1" t="s">
-        <v>2119</v>
+        <v>2116</v>
       </c>
       <c r="B786" s="1" t="s">
         <v>152</v>
@@ -22815,7 +22854,7 @@
         <v>4</v>
       </c>
       <c r="E786" s="1" t="s">
-        <v>2120</v>
+        <v>2117</v>
       </c>
       <c r="F786" s="1" t="s">
         <v>5</v>
@@ -22823,10 +22862,10 @@
     </row>
     <row r="787" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A787" s="1" t="s">
-        <v>2121</v>
+        <v>2118</v>
       </c>
       <c r="B787" s="1" t="s">
-        <v>2122</v>
+        <v>2119</v>
       </c>
       <c r="C787" s="1" t="s">
         <v>3</v>
@@ -22835,7 +22874,7 @@
         <v>4</v>
       </c>
       <c r="E787" s="1" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
       <c r="F787" s="1" t="s">
         <v>5</v>
@@ -22843,19 +22882,19 @@
     </row>
     <row r="788" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A788" s="1" t="s">
-        <v>2124</v>
+        <v>2121</v>
       </c>
       <c r="B788" s="1" t="s">
+        <v>2119</v>
+      </c>
+      <c r="C788" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D788" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E788" s="1" t="s">
         <v>2122</v>
-      </c>
-      <c r="C788" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D788" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E788" s="1" t="s">
-        <v>2125</v>
       </c>
       <c r="F788" s="1" t="s">
         <v>5</v>
@@ -22863,10 +22902,10 @@
     </row>
     <row r="789" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A789" s="1" t="s">
-        <v>2126</v>
+        <v>2123</v>
       </c>
       <c r="B789" s="1" t="s">
-        <v>2127</v>
+        <v>2124</v>
       </c>
       <c r="C789" s="1" t="s">
         <v>3</v>
@@ -22875,7 +22914,7 @@
         <v>4</v>
       </c>
       <c r="E789" s="1" t="s">
-        <v>2128</v>
+        <v>2125</v>
       </c>
       <c r="F789" s="1" t="s">
         <v>5</v>
@@ -22883,10 +22922,10 @@
     </row>
     <row r="790" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A790" s="1" t="s">
-        <v>2129</v>
+        <v>2126</v>
       </c>
       <c r="B790" s="1" t="s">
-        <v>2130</v>
+        <v>2127</v>
       </c>
       <c r="C790" s="1" t="s">
         <v>3</v>
@@ -22895,15 +22934,15 @@
         <v>4</v>
       </c>
       <c r="E790" s="1" t="s">
-        <v>2131</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="791" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A791" s="1" t="s">
-        <v>2132</v>
+        <v>2129</v>
       </c>
       <c r="B791" s="1" t="s">
-        <v>2133</v>
+        <v>2130</v>
       </c>
       <c r="C791" s="1" t="s">
         <v>3</v>
@@ -22912,7 +22951,7 @@
         <v>4</v>
       </c>
       <c r="E791" s="1" t="s">
-        <v>2134</v>
+        <v>2131</v>
       </c>
       <c r="F791" s="1" t="s">
         <v>5</v>
@@ -22920,10 +22959,10 @@
     </row>
     <row r="792" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A792" s="1" t="s">
-        <v>2135</v>
+        <v>2132</v>
       </c>
       <c r="B792" s="1" t="s">
-        <v>2136</v>
+        <v>2133</v>
       </c>
       <c r="C792" s="1" t="s">
         <v>3</v>
@@ -22932,15 +22971,15 @@
         <v>4</v>
       </c>
       <c r="E792" s="1" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="793" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A793" s="1" t="s">
-        <v>2138</v>
+        <v>2135</v>
       </c>
       <c r="B793" s="1" t="s">
-        <v>2139</v>
+        <v>2136</v>
       </c>
       <c r="C793" s="1" t="s">
         <v>3</v>
@@ -22949,7 +22988,7 @@
         <v>4</v>
       </c>
       <c r="E793" s="1" t="s">
-        <v>2140</v>
+        <v>2137</v>
       </c>
       <c r="F793" s="1" t="s">
         <v>5</v>
@@ -22957,10 +22996,10 @@
     </row>
     <row r="794" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A794" s="1" t="s">
-        <v>2141</v>
+        <v>2138</v>
       </c>
       <c r="B794" s="1" t="s">
-        <v>2142</v>
+        <v>2139</v>
       </c>
       <c r="C794" s="1" t="s">
         <v>3</v>
@@ -22969,7 +23008,7 @@
         <v>4</v>
       </c>
       <c r="E794" s="1" t="s">
-        <v>2143</v>
+        <v>2140</v>
       </c>
       <c r="F794" s="1" t="s">
         <v>5</v>
@@ -22977,10 +23016,10 @@
     </row>
     <row r="795" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A795" s="1" t="s">
-        <v>2144</v>
+        <v>2141</v>
       </c>
       <c r="B795" s="1" t="s">
-        <v>2145</v>
+        <v>2142</v>
       </c>
       <c r="C795" s="1" t="s">
         <v>3</v>
@@ -22989,7 +23028,7 @@
         <v>4</v>
       </c>
       <c r="E795" s="1" t="s">
-        <v>2146</v>
+        <v>2143</v>
       </c>
       <c r="F795" s="1" t="s">
         <v>5</v>
@@ -22997,10 +23036,10 @@
     </row>
     <row r="796" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A796" s="1" t="s">
-        <v>2147</v>
+        <v>2144</v>
       </c>
       <c r="B796" s="1" t="s">
-        <v>2139</v>
+        <v>2136</v>
       </c>
       <c r="C796" s="1" t="s">
         <v>3</v>
@@ -23009,7 +23048,7 @@
         <v>4</v>
       </c>
       <c r="E796" s="1" t="s">
-        <v>2148</v>
+        <v>2145</v>
       </c>
       <c r="F796" s="1" t="s">
         <v>5</v>
@@ -23017,10 +23056,10 @@
     </row>
     <row r="797" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A797" s="1" t="s">
-        <v>2149</v>
+        <v>2146</v>
       </c>
       <c r="B797" s="1" t="s">
-        <v>2142</v>
+        <v>2139</v>
       </c>
       <c r="C797" s="1" t="s">
         <v>3</v>
@@ -23029,7 +23068,7 @@
         <v>4</v>
       </c>
       <c r="E797" s="1" t="s">
-        <v>2150</v>
+        <v>2147</v>
       </c>
       <c r="F797" s="1" t="s">
         <v>5</v>
@@ -23037,10 +23076,10 @@
     </row>
     <row r="798" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A798" s="1" t="s">
-        <v>2151</v>
+        <v>2148</v>
       </c>
       <c r="B798" s="1" t="s">
-        <v>2145</v>
+        <v>2142</v>
       </c>
       <c r="C798" s="1" t="s">
         <v>3</v>
@@ -23049,7 +23088,7 @@
         <v>4</v>
       </c>
       <c r="E798" s="1" t="s">
-        <v>2152</v>
+        <v>2149</v>
       </c>
       <c r="F798" s="1" t="s">
         <v>5</v>
@@ -23057,10 +23096,10 @@
     </row>
     <row r="799" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A799" s="1" t="s">
-        <v>2153</v>
+        <v>2150</v>
       </c>
       <c r="B799" s="1" t="s">
-        <v>2154</v>
+        <v>2151</v>
       </c>
       <c r="C799" s="1" t="s">
         <v>3</v>
@@ -23069,7 +23108,7 @@
         <v>4</v>
       </c>
       <c r="E799" s="1" t="s">
-        <v>2155</v>
+        <v>2152</v>
       </c>
       <c r="F799" s="1" t="s">
         <v>96</v>
@@ -23077,10 +23116,10 @@
     </row>
     <row r="800" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A800" s="1" t="s">
-        <v>2156</v>
+        <v>2153</v>
       </c>
       <c r="B800" s="1" t="s">
-        <v>2157</v>
+        <v>2154</v>
       </c>
       <c r="C800" s="1" t="s">
         <v>3</v>
@@ -23089,7 +23128,7 @@
         <v>4</v>
       </c>
       <c r="E800" s="1" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="F800" s="1" t="s">
         <v>96</v>
@@ -23097,10 +23136,10 @@
     </row>
     <row r="801" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A801" s="1" t="s">
-        <v>2159</v>
+        <v>2156</v>
       </c>
       <c r="B801" s="1" t="s">
-        <v>2160</v>
+        <v>2157</v>
       </c>
       <c r="C801" s="1" t="s">
         <v>3</v>
@@ -23109,7 +23148,7 @@
         <v>4</v>
       </c>
       <c r="E801" s="1" t="s">
-        <v>2161</v>
+        <v>2158</v>
       </c>
       <c r="F801" s="1" t="s">
         <v>96</v>
@@ -23117,10 +23156,10 @@
     </row>
     <row r="802" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A802" s="1" t="s">
-        <v>2162</v>
+        <v>2159</v>
       </c>
       <c r="B802" s="1" t="s">
-        <v>2163</v>
+        <v>2160</v>
       </c>
       <c r="C802" s="1" t="s">
         <v>3</v>
@@ -23129,7 +23168,7 @@
         <v>4</v>
       </c>
       <c r="E802" s="1" t="s">
-        <v>2164</v>
+        <v>2161</v>
       </c>
       <c r="F802" s="1" t="s">
         <v>96</v>
@@ -23137,10 +23176,10 @@
     </row>
     <row r="803" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A803" s="1" t="s">
-        <v>2165</v>
+        <v>2162</v>
       </c>
       <c r="B803" s="1" t="s">
-        <v>2166</v>
+        <v>2163</v>
       </c>
       <c r="C803" s="1" t="s">
         <v>3</v>
@@ -23149,7 +23188,7 @@
         <v>4</v>
       </c>
       <c r="E803" s="1" t="s">
-        <v>2167</v>
+        <v>2164</v>
       </c>
       <c r="F803" s="1" t="s">
         <v>96</v>
@@ -23157,10 +23196,10 @@
     </row>
     <row r="804" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A804" s="1" t="s">
-        <v>2168</v>
+        <v>2165</v>
       </c>
       <c r="B804" s="1" t="s">
-        <v>2169</v>
+        <v>2166</v>
       </c>
       <c r="C804" s="1" t="s">
         <v>3</v>
@@ -23169,7 +23208,7 @@
         <v>4</v>
       </c>
       <c r="E804" s="1" t="s">
-        <v>2170</v>
+        <v>2167</v>
       </c>
       <c r="F804" s="1" t="s">
         <v>96</v>
@@ -23177,10 +23216,10 @@
     </row>
     <row r="805" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A805" s="1" t="s">
-        <v>2171</v>
+        <v>2168</v>
       </c>
       <c r="B805" s="1" t="s">
-        <v>2172</v>
+        <v>2169</v>
       </c>
       <c r="C805" s="1" t="s">
         <v>3</v>
@@ -23189,7 +23228,7 @@
         <v>4</v>
       </c>
       <c r="E805" s="1" t="s">
-        <v>2173</v>
+        <v>2170</v>
       </c>
       <c r="F805" s="1" t="s">
         <v>96</v>
@@ -23197,10 +23236,10 @@
     </row>
     <row r="806" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A806" s="1" t="s">
-        <v>2174</v>
+        <v>2171</v>
       </c>
       <c r="B806" s="1" t="s">
-        <v>2175</v>
+        <v>2172</v>
       </c>
       <c r="C806" s="1" t="s">
         <v>3</v>
@@ -23209,7 +23248,7 @@
         <v>4</v>
       </c>
       <c r="E806" s="1" t="s">
-        <v>2176</v>
+        <v>2173</v>
       </c>
       <c r="F806" s="1" t="s">
         <v>5</v>
@@ -23217,10 +23256,10 @@
     </row>
     <row r="807" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A807" s="1" t="s">
-        <v>2177</v>
+        <v>2174</v>
       </c>
       <c r="B807" s="1" t="s">
-        <v>2178</v>
+        <v>2175</v>
       </c>
       <c r="C807" s="1" t="s">
         <v>3</v>
@@ -23229,7 +23268,7 @@
         <v>4</v>
       </c>
       <c r="E807" s="1" t="s">
-        <v>2179</v>
+        <v>2176</v>
       </c>
       <c r="F807" s="1" t="s">
         <v>5</v>
@@ -23237,10 +23276,10 @@
     </row>
     <row r="808" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A808" s="1" t="s">
-        <v>2180</v>
+        <v>2177</v>
       </c>
       <c r="B808" s="1" t="s">
-        <v>2181</v>
+        <v>2178</v>
       </c>
       <c r="C808" s="1" t="s">
         <v>3</v>
@@ -23249,7 +23288,7 @@
         <v>4</v>
       </c>
       <c r="E808" s="1" t="s">
-        <v>2182</v>
+        <v>2179</v>
       </c>
       <c r="F808" s="1" t="s">
         <v>5</v>
@@ -23257,10 +23296,10 @@
     </row>
     <row r="809" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A809" s="1" t="s">
-        <v>2183</v>
+        <v>2180</v>
       </c>
       <c r="B809" s="1" t="s">
-        <v>2184</v>
+        <v>2181</v>
       </c>
       <c r="C809" s="1" t="s">
         <v>3</v>
@@ -23269,7 +23308,7 @@
         <v>4</v>
       </c>
       <c r="E809" s="1" t="s">
-        <v>2185</v>
+        <v>2182</v>
       </c>
       <c r="F809" s="1" t="s">
         <v>5</v>
@@ -23277,10 +23316,10 @@
     </row>
     <row r="810" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A810" s="1" t="s">
-        <v>2186</v>
+        <v>2183</v>
       </c>
       <c r="B810" s="1" t="s">
-        <v>2187</v>
+        <v>2184</v>
       </c>
       <c r="C810" s="1" t="s">
         <v>3</v>
@@ -23289,7 +23328,7 @@
         <v>4</v>
       </c>
       <c r="E810" s="1" t="s">
-        <v>2188</v>
+        <v>2185</v>
       </c>
       <c r="F810" s="1" t="s">
         <v>5</v>
@@ -23297,10 +23336,10 @@
     </row>
     <row r="811" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A811" s="1" t="s">
-        <v>2189</v>
+        <v>2186</v>
       </c>
       <c r="B811" s="1" t="s">
-        <v>2169</v>
+        <v>2166</v>
       </c>
       <c r="C811" s="1" t="s">
         <v>3</v>
@@ -23309,7 +23348,7 @@
         <v>4</v>
       </c>
       <c r="E811" s="1" t="s">
-        <v>2190</v>
+        <v>2187</v>
       </c>
       <c r="F811" s="1" t="s">
         <v>5</v>
@@ -23317,10 +23356,10 @@
     </row>
     <row r="812" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A812" s="1" t="s">
-        <v>2191</v>
+        <v>2188</v>
       </c>
       <c r="B812" s="1" t="s">
-        <v>2172</v>
+        <v>2169</v>
       </c>
       <c r="C812" s="1" t="s">
         <v>3</v>
@@ -23329,7 +23368,7 @@
         <v>4</v>
       </c>
       <c r="E812" s="1" t="s">
-        <v>2192</v>
+        <v>2189</v>
       </c>
       <c r="F812" s="1" t="s">
         <v>5</v>
@@ -23337,10 +23376,10 @@
     </row>
     <row r="813" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A813" s="1" t="s">
-        <v>2193</v>
+        <v>2190</v>
       </c>
       <c r="B813" s="1" t="s">
-        <v>1964</v>
+        <v>1961</v>
       </c>
       <c r="C813" s="1" t="s">
         <v>3</v>
@@ -23349,7 +23388,7 @@
         <v>4</v>
       </c>
       <c r="E813" s="1" t="s">
-        <v>2194</v>
+        <v>2191</v>
       </c>
       <c r="F813" s="1" t="s">
         <v>63</v>
@@ -23357,10 +23396,10 @@
     </row>
     <row r="814" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A814" s="1" t="s">
-        <v>2195</v>
+        <v>2192</v>
       </c>
       <c r="B814" s="1" t="s">
-        <v>2196</v>
+        <v>2193</v>
       </c>
       <c r="C814" s="1" t="s">
         <v>3</v>
@@ -23369,7 +23408,7 @@
         <v>4</v>
       </c>
       <c r="E814" s="1" t="s">
-        <v>2197</v>
+        <v>2194</v>
       </c>
       <c r="F814" s="1" t="s">
         <v>5</v>
@@ -23377,10 +23416,10 @@
     </row>
     <row r="815" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A815" s="1" t="s">
-        <v>2198</v>
+        <v>2195</v>
       </c>
       <c r="B815" s="1" t="s">
-        <v>1997</v>
+        <v>1994</v>
       </c>
       <c r="C815" s="1" t="s">
         <v>3</v>
@@ -23389,7 +23428,7 @@
         <v>4</v>
       </c>
       <c r="E815" s="1" t="s">
-        <v>2199</v>
+        <v>2196</v>
       </c>
       <c r="F815" s="1" t="s">
         <v>5</v>
@@ -23397,10 +23436,10 @@
     </row>
     <row r="816" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A816" s="1" t="s">
-        <v>2200</v>
+        <v>2197</v>
       </c>
       <c r="B816" s="1" t="s">
-        <v>2048</v>
+        <v>2045</v>
       </c>
       <c r="C816" s="1" t="s">
         <v>3</v>
@@ -23409,7 +23448,7 @@
         <v>4</v>
       </c>
       <c r="E816" s="1" t="s">
-        <v>2201</v>
+        <v>2198</v>
       </c>
       <c r="F816" s="1" t="s">
         <v>5</v>
@@ -23417,10 +23456,10 @@
     </row>
     <row r="817" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A817" s="1" t="s">
-        <v>2202</v>
+        <v>2199</v>
       </c>
       <c r="B817" s="1" t="s">
-        <v>2033</v>
+        <v>2030</v>
       </c>
       <c r="C817" s="1" t="s">
         <v>3</v>
@@ -23429,7 +23468,7 @@
         <v>4</v>
       </c>
       <c r="E817" s="1" t="s">
-        <v>2203</v>
+        <v>2200</v>
       </c>
       <c r="F817" s="1" t="s">
         <v>5</v>
@@ -23437,10 +23476,10 @@
     </row>
     <row r="818" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A818" s="1" t="s">
-        <v>2204</v>
+        <v>2201</v>
       </c>
       <c r="B818" s="1" t="s">
-        <v>2036</v>
+        <v>2033</v>
       </c>
       <c r="C818" s="1" t="s">
         <v>3</v>
@@ -23449,7 +23488,7 @@
         <v>4</v>
       </c>
       <c r="E818" s="1" t="s">
-        <v>2205</v>
+        <v>2202</v>
       </c>
       <c r="F818" s="1" t="s">
         <v>5</v>
@@ -23457,10 +23496,10 @@
     </row>
     <row r="819" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A819" s="1" t="s">
-        <v>2206</v>
+        <v>2203</v>
       </c>
       <c r="B819" s="1" t="s">
-        <v>2039</v>
+        <v>2036</v>
       </c>
       <c r="C819" s="1" t="s">
         <v>3</v>
@@ -23469,7 +23508,7 @@
         <v>4</v>
       </c>
       <c r="E819" s="1" t="s">
-        <v>2207</v>
+        <v>2204</v>
       </c>
       <c r="F819" s="1" t="s">
         <v>5</v>
@@ -23477,10 +23516,10 @@
     </row>
     <row r="820" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A820" s="1" t="s">
-        <v>2208</v>
+        <v>2205</v>
       </c>
       <c r="B820" s="1" t="s">
-        <v>2042</v>
+        <v>2039</v>
       </c>
       <c r="C820" s="1" t="s">
         <v>3</v>
@@ -23489,7 +23528,7 @@
         <v>4</v>
       </c>
       <c r="E820" s="1" t="s">
-        <v>2209</v>
+        <v>2206</v>
       </c>
       <c r="F820" s="1" t="s">
         <v>5</v>
@@ -23497,10 +23536,10 @@
     </row>
     <row r="821" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A821" s="1" t="s">
-        <v>2210</v>
+        <v>2207</v>
       </c>
       <c r="B821" s="1" t="s">
-        <v>2211</v>
+        <v>2208</v>
       </c>
       <c r="C821" s="1" t="s">
         <v>3</v>
@@ -23509,7 +23548,7 @@
         <v>4</v>
       </c>
       <c r="E821" s="1" t="s">
-        <v>2212</v>
+        <v>2209</v>
       </c>
       <c r="F821" s="1" t="s">
         <v>5</v>
@@ -23517,10 +23556,10 @@
     </row>
     <row r="822" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A822" s="1" t="s">
-        <v>2213</v>
+        <v>2210</v>
       </c>
       <c r="B822" s="1" t="s">
-        <v>2214</v>
+        <v>2211</v>
       </c>
       <c r="C822" s="1" t="s">
         <v>3</v>
@@ -23529,15 +23568,15 @@
         <v>4</v>
       </c>
       <c r="E822" s="1" t="s">
-        <v>2215</v>
+        <v>2212</v>
       </c>
     </row>
     <row r="823" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A823" s="1" t="s">
-        <v>2216</v>
+        <v>2213</v>
       </c>
       <c r="B823" s="1" t="s">
-        <v>2217</v>
+        <v>2214</v>
       </c>
       <c r="C823" s="1" t="s">
         <v>3</v>
@@ -23546,15 +23585,15 @@
         <v>4</v>
       </c>
       <c r="E823" s="1" t="s">
-        <v>2218</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="824" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A824" s="1" t="s">
-        <v>2219</v>
+        <v>2216</v>
       </c>
       <c r="B824" s="1" t="s">
-        <v>2220</v>
+        <v>2217</v>
       </c>
       <c r="C824" s="1" t="s">
         <v>3</v>
@@ -23563,15 +23602,15 @@
         <v>4</v>
       </c>
       <c r="E824" s="1" t="s">
-        <v>2221</v>
+        <v>2218</v>
       </c>
     </row>
     <row r="825" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A825" s="1" t="s">
-        <v>2222</v>
+        <v>2219</v>
       </c>
       <c r="B825" s="1" t="s">
-        <v>2223</v>
+        <v>2220</v>
       </c>
       <c r="C825" s="1" t="s">
         <v>3</v>
@@ -23580,15 +23619,15 @@
         <v>4</v>
       </c>
       <c r="E825" s="1" t="s">
-        <v>2224</v>
+        <v>2221</v>
       </c>
     </row>
     <row r="826" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A826" s="1" t="s">
-        <v>2225</v>
+        <v>2222</v>
       </c>
       <c r="B826" s="1" t="s">
-        <v>2214</v>
+        <v>2211</v>
       </c>
       <c r="C826" s="1" t="s">
         <v>3</v>
@@ -23597,15 +23636,15 @@
         <v>4</v>
       </c>
       <c r="E826" s="1" t="s">
-        <v>2226</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="827" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A827" s="1" t="s">
-        <v>2227</v>
+        <v>2224</v>
       </c>
       <c r="B827" s="1" t="s">
-        <v>2217</v>
+        <v>2214</v>
       </c>
       <c r="C827" s="1" t="s">
         <v>3</v>
@@ -23614,15 +23653,15 @@
         <v>4</v>
       </c>
       <c r="E827" s="1" t="s">
-        <v>2228</v>
+        <v>2225</v>
       </c>
     </row>
     <row r="828" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A828" s="1" t="s">
-        <v>2229</v>
+        <v>2226</v>
       </c>
       <c r="B828" s="1" t="s">
-        <v>2220</v>
+        <v>2217</v>
       </c>
       <c r="C828" s="1" t="s">
         <v>3</v>
@@ -23631,15 +23670,15 @@
         <v>4</v>
       </c>
       <c r="E828" s="1" t="s">
-        <v>2230</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="829" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A829" s="1" t="s">
-        <v>2231</v>
+        <v>2228</v>
       </c>
       <c r="B829" s="1" t="s">
-        <v>2223</v>
+        <v>2220</v>
       </c>
       <c r="C829" s="1" t="s">
         <v>3</v>
@@ -23648,15 +23687,15 @@
         <v>4</v>
       </c>
       <c r="E829" s="1" t="s">
-        <v>2232</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="830" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A830" s="1" t="s">
-        <v>2233</v>
+        <v>2230</v>
       </c>
       <c r="B830" s="1" t="s">
-        <v>2234</v>
+        <v>2231</v>
       </c>
       <c r="C830" s="1" t="s">
         <v>3</v>
@@ -23665,15 +23704,15 @@
         <v>4</v>
       </c>
       <c r="E830" s="1" t="s">
-        <v>2235</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="831" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A831" s="1" t="s">
-        <v>2236</v>
+        <v>2233</v>
       </c>
       <c r="B831" s="1" t="s">
-        <v>2237</v>
+        <v>2234</v>
       </c>
       <c r="C831" s="1" t="s">
         <v>3</v>
@@ -23682,15 +23721,15 @@
         <v>4</v>
       </c>
       <c r="E831" s="1" t="s">
-        <v>2238</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="832" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A832" s="1" t="s">
-        <v>2239</v>
+        <v>2236</v>
       </c>
       <c r="B832" s="1" t="s">
-        <v>2240</v>
+        <v>2237</v>
       </c>
       <c r="C832" s="1" t="s">
         <v>3</v>
@@ -23699,7 +23738,7 @@
         <v>4</v>
       </c>
       <c r="E832" s="1" t="s">
-        <v>2241</v>
+        <v>2238</v>
       </c>
       <c r="F832" s="1" t="s">
         <v>5</v>
@@ -23707,10 +23746,10 @@
     </row>
     <row r="833" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A833" s="1" t="s">
-        <v>2242</v>
+        <v>2239</v>
       </c>
       <c r="B833" s="1" t="s">
-        <v>2234</v>
+        <v>2231</v>
       </c>
       <c r="C833" s="1" t="s">
         <v>3</v>
@@ -23719,15 +23758,15 @@
         <v>4</v>
       </c>
       <c r="E833" s="1" t="s">
-        <v>2243</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="834" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A834" s="1" t="s">
-        <v>2244</v>
+        <v>2241</v>
       </c>
       <c r="B834" s="1" t="s">
-        <v>2237</v>
+        <v>2234</v>
       </c>
       <c r="C834" s="1" t="s">
         <v>3</v>
@@ -23736,15 +23775,15 @@
         <v>4</v>
       </c>
       <c r="E834" s="1" t="s">
-        <v>2245</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="835" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A835" s="1" t="s">
-        <v>2246</v>
+        <v>2243</v>
       </c>
       <c r="B835" s="1" t="s">
-        <v>2240</v>
+        <v>2237</v>
       </c>
       <c r="C835" s="1" t="s">
         <v>3</v>
@@ -23753,15 +23792,15 @@
         <v>4</v>
       </c>
       <c r="E835" s="1" t="s">
-        <v>2247</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="836" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A836" s="1" t="s">
-        <v>2248</v>
+        <v>2245</v>
       </c>
       <c r="B836" s="1" t="s">
-        <v>2249</v>
+        <v>2246</v>
       </c>
       <c r="C836" s="1" t="s">
         <v>3</v>
@@ -23770,7 +23809,7 @@
         <v>4</v>
       </c>
       <c r="E836" s="1" t="s">
-        <v>2250</v>
+        <v>2247</v>
       </c>
       <c r="F836" s="1" t="s">
         <v>5</v>
@@ -23778,10 +23817,10 @@
     </row>
     <row r="837" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A837" s="1" t="s">
-        <v>2251</v>
+        <v>2248</v>
       </c>
       <c r="B837" s="1" t="s">
-        <v>2252</v>
+        <v>2249</v>
       </c>
       <c r="C837" s="1" t="s">
         <v>3</v>
@@ -23790,7 +23829,7 @@
         <v>4</v>
       </c>
       <c r="E837" s="1" t="s">
-        <v>2253</v>
+        <v>2250</v>
       </c>
       <c r="F837" s="1" t="s">
         <v>5</v>
@@ -23798,10 +23837,10 @@
     </row>
     <row r="838" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A838" s="1" t="s">
-        <v>2254</v>
+        <v>2251</v>
       </c>
       <c r="B838" s="1" t="s">
-        <v>2255</v>
+        <v>2252</v>
       </c>
       <c r="C838" s="1" t="s">
         <v>3</v>
@@ -23810,7 +23849,7 @@
         <v>4</v>
       </c>
       <c r="E838" s="1" t="s">
-        <v>2256</v>
+        <v>2253</v>
       </c>
       <c r="F838" s="1" t="s">
         <v>5</v>
@@ -23818,10 +23857,10 @@
     </row>
     <row r="839" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A839" s="1" t="s">
-        <v>2257</v>
+        <v>2254</v>
       </c>
       <c r="B839" s="1" t="s">
-        <v>2258</v>
+        <v>2255</v>
       </c>
       <c r="C839" s="1" t="s">
         <v>3</v>
@@ -23830,7 +23869,7 @@
         <v>4</v>
       </c>
       <c r="E839" s="1" t="s">
-        <v>2259</v>
+        <v>2256</v>
       </c>
       <c r="F839" s="1" t="s">
         <v>5</v>
@@ -23838,10 +23877,10 @@
     </row>
     <row r="840" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A840" s="1" t="s">
-        <v>2260</v>
+        <v>2257</v>
       </c>
       <c r="B840" s="1" t="s">
-        <v>2261</v>
+        <v>2258</v>
       </c>
       <c r="C840" s="1" t="s">
         <v>3</v>
@@ -23850,7 +23889,7 @@
         <v>4</v>
       </c>
       <c r="E840" s="1" t="s">
-        <v>2262</v>
+        <v>2259</v>
       </c>
       <c r="F840" s="1" t="s">
         <v>5</v>
@@ -23858,10 +23897,10 @@
     </row>
     <row r="841" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A841" s="1" t="s">
-        <v>2263</v>
+        <v>2260</v>
       </c>
       <c r="B841" s="1" t="s">
-        <v>2264</v>
+        <v>2261</v>
       </c>
       <c r="C841" s="1" t="s">
         <v>3</v>
@@ -23870,7 +23909,7 @@
         <v>4</v>
       </c>
       <c r="E841" s="1" t="s">
-        <v>2265</v>
+        <v>2262</v>
       </c>
       <c r="F841" s="1" t="s">
         <v>5</v>
@@ -23878,10 +23917,10 @@
     </row>
     <row r="842" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A842" s="1" t="s">
-        <v>2266</v>
+        <v>2263</v>
       </c>
       <c r="B842" s="1" t="s">
-        <v>2267</v>
+        <v>2264</v>
       </c>
       <c r="C842" s="1" t="s">
         <v>3</v>
@@ -23890,7 +23929,7 @@
         <v>4</v>
       </c>
       <c r="E842" s="1" t="s">
-        <v>2268</v>
+        <v>2265</v>
       </c>
       <c r="F842" s="1" t="s">
         <v>5</v>
@@ -23898,10 +23937,10 @@
     </row>
     <row r="843" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A843" s="1" t="s">
-        <v>2269</v>
+        <v>2266</v>
       </c>
       <c r="B843" s="1" t="s">
-        <v>2270</v>
+        <v>2267</v>
       </c>
       <c r="C843" s="1" t="s">
         <v>3</v>
@@ -23910,7 +23949,7 @@
         <v>4</v>
       </c>
       <c r="E843" s="1" t="s">
-        <v>2271</v>
+        <v>2268</v>
       </c>
       <c r="F843" s="1" t="s">
         <v>5</v>
@@ -23918,10 +23957,10 @@
     </row>
     <row r="844" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A844" s="1" t="s">
-        <v>2272</v>
+        <v>2269</v>
       </c>
       <c r="B844" s="1" t="s">
-        <v>2273</v>
+        <v>2270</v>
       </c>
       <c r="C844" s="1" t="s">
         <v>3</v>
@@ -23930,7 +23969,7 @@
         <v>4</v>
       </c>
       <c r="E844" s="1" t="s">
-        <v>2274</v>
+        <v>2271</v>
       </c>
       <c r="F844" s="1" t="s">
         <v>5</v>
@@ -23938,10 +23977,10 @@
     </row>
     <row r="845" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A845" s="1" t="s">
-        <v>2275</v>
+        <v>2272</v>
       </c>
       <c r="B845" s="1" t="s">
-        <v>2276</v>
+        <v>2273</v>
       </c>
       <c r="C845" s="1" t="s">
         <v>3</v>
@@ -23950,7 +23989,7 @@
         <v>4</v>
       </c>
       <c r="E845" s="1" t="s">
-        <v>2277</v>
+        <v>2274</v>
       </c>
       <c r="F845" s="1" t="s">
         <v>5</v>
@@ -23958,10 +23997,10 @@
     </row>
     <row r="846" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A846" s="1" t="s">
-        <v>2278</v>
+        <v>2275</v>
       </c>
       <c r="B846" s="1" t="s">
-        <v>2264</v>
+        <v>2261</v>
       </c>
       <c r="C846" s="1" t="s">
         <v>3</v>
@@ -23970,7 +24009,7 @@
         <v>4</v>
       </c>
       <c r="E846" s="1" t="s">
-        <v>2279</v>
+        <v>2276</v>
       </c>
       <c r="F846" s="1" t="s">
         <v>5</v>
@@ -23978,10 +24017,10 @@
     </row>
     <row r="847" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A847" s="1" t="s">
-        <v>2280</v>
+        <v>2277</v>
       </c>
       <c r="B847" s="1" t="s">
-        <v>2267</v>
+        <v>2264</v>
       </c>
       <c r="C847" s="1" t="s">
         <v>3</v>
@@ -23990,7 +24029,7 @@
         <v>4</v>
       </c>
       <c r="E847" s="1" t="s">
-        <v>2281</v>
+        <v>2278</v>
       </c>
       <c r="F847" s="1" t="s">
         <v>5</v>
@@ -23998,10 +24037,10 @@
     </row>
     <row r="848" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A848" s="1" t="s">
-        <v>2282</v>
+        <v>2279</v>
       </c>
       <c r="B848" s="1" t="s">
-        <v>2283</v>
+        <v>2280</v>
       </c>
       <c r="C848" s="1" t="s">
         <v>3</v>
@@ -24010,7 +24049,7 @@
         <v>4</v>
       </c>
       <c r="E848" s="1" t="s">
-        <v>2284</v>
+        <v>2281</v>
       </c>
       <c r="F848" s="1" t="s">
         <v>5</v>
@@ -24018,10 +24057,10 @@
     </row>
     <row r="849" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A849" s="1" t="s">
-        <v>2285</v>
+        <v>2282</v>
       </c>
       <c r="B849" s="1" t="s">
-        <v>2286</v>
+        <v>2283</v>
       </c>
       <c r="C849" s="1" t="s">
         <v>3</v>
@@ -24030,7 +24069,7 @@
         <v>4</v>
       </c>
       <c r="E849" s="1" t="s">
-        <v>2287</v>
+        <v>2284</v>
       </c>
       <c r="F849" s="1" t="s">
         <v>5</v>
@@ -24038,10 +24077,10 @@
     </row>
     <row r="850" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A850" s="1" t="s">
-        <v>2288</v>
+        <v>2285</v>
       </c>
       <c r="B850" s="1" t="s">
-        <v>2276</v>
+        <v>2273</v>
       </c>
       <c r="C850" s="1" t="s">
         <v>3</v>
@@ -24050,7 +24089,7 @@
         <v>4</v>
       </c>
       <c r="E850" s="1" t="s">
-        <v>2289</v>
+        <v>2286</v>
       </c>
       <c r="F850" s="1" t="s">
         <v>5</v>
@@ -24058,10 +24097,10 @@
     </row>
     <row r="851" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A851" s="1" t="s">
-        <v>2290</v>
+        <v>2287</v>
       </c>
       <c r="B851" s="1" t="s">
-        <v>2291</v>
+        <v>2288</v>
       </c>
       <c r="C851" s="1" t="s">
         <v>3</v>
@@ -24070,7 +24109,7 @@
         <v>4</v>
       </c>
       <c r="E851" s="1" t="s">
-        <v>2292</v>
+        <v>2289</v>
       </c>
       <c r="F851" s="1" t="s">
         <v>5</v>
@@ -24078,10 +24117,10 @@
     </row>
     <row r="852" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A852" s="1" t="s">
-        <v>2293</v>
+        <v>2290</v>
       </c>
       <c r="B852" s="1" t="s">
-        <v>2294</v>
+        <v>2291</v>
       </c>
       <c r="C852" s="1" t="s">
         <v>3</v>
@@ -24090,7 +24129,7 @@
         <v>4</v>
       </c>
       <c r="E852" s="1" t="s">
-        <v>2295</v>
+        <v>2292</v>
       </c>
       <c r="F852" s="1" t="s">
         <v>5</v>
@@ -24098,10 +24137,10 @@
     </row>
     <row r="853" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A853" s="1" t="s">
-        <v>2296</v>
+        <v>2293</v>
       </c>
       <c r="B853" s="1" t="s">
-        <v>2297</v>
+        <v>2294</v>
       </c>
       <c r="C853" s="1" t="s">
         <v>3</v>
@@ -24110,7 +24149,7 @@
         <v>4</v>
       </c>
       <c r="E853" s="1" t="s">
-        <v>2298</v>
+        <v>2295</v>
       </c>
       <c r="F853" s="1" t="s">
         <v>5</v>
@@ -24118,10 +24157,10 @@
     </row>
     <row r="854" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A854" s="1" t="s">
-        <v>2299</v>
+        <v>2296</v>
       </c>
       <c r="B854" s="1" t="s">
-        <v>2300</v>
+        <v>2297</v>
       </c>
       <c r="C854" s="1" t="s">
         <v>3</v>
@@ -24130,15 +24169,15 @@
         <v>4</v>
       </c>
       <c r="E854" s="1" t="s">
-        <v>2301</v>
+        <v>2298</v>
       </c>
     </row>
     <row r="855" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A855" s="1" t="s">
-        <v>2302</v>
+        <v>2299</v>
       </c>
       <c r="B855" s="1" t="s">
-        <v>2303</v>
+        <v>2300</v>
       </c>
       <c r="C855" s="1" t="s">
         <v>3</v>
@@ -24147,15 +24186,15 @@
         <v>4</v>
       </c>
       <c r="E855" s="1" t="s">
-        <v>2304</v>
+        <v>2301</v>
       </c>
     </row>
     <row r="856" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A856" s="1" t="s">
-        <v>2305</v>
+        <v>2302</v>
       </c>
       <c r="B856" s="1" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="C856" s="1" t="s">
         <v>3</v>
@@ -24164,15 +24203,15 @@
         <v>4</v>
       </c>
       <c r="E856" s="1" t="s">
-        <v>2307</v>
+        <v>2304</v>
       </c>
     </row>
     <row r="857" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A857" s="1" t="s">
-        <v>2308</v>
+        <v>2305</v>
       </c>
       <c r="B857" s="1" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="C857" s="1" t="s">
         <v>3</v>
@@ -24181,7 +24220,7 @@
         <v>4</v>
       </c>
       <c r="E857" s="1" t="s">
-        <v>2310</v>
+        <v>2307</v>
       </c>
       <c r="F857" s="1" t="s">
         <v>5</v>
@@ -24189,10 +24228,10 @@
     </row>
     <row r="858" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A858" s="1" t="s">
-        <v>2311</v>
+        <v>2308</v>
       </c>
       <c r="B858" s="1" t="s">
-        <v>2312</v>
+        <v>2309</v>
       </c>
       <c r="C858" s="1" t="s">
         <v>3</v>
@@ -24201,7 +24240,7 @@
         <v>4</v>
       </c>
       <c r="E858" s="1" t="s">
-        <v>2313</v>
+        <v>2310</v>
       </c>
       <c r="F858" s="1" t="s">
         <v>5</v>
@@ -24209,10 +24248,10 @@
     </row>
     <row r="859" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A859" s="1" t="s">
-        <v>2314</v>
+        <v>2311</v>
       </c>
       <c r="B859" s="1" t="s">
-        <v>2315</v>
+        <v>2312</v>
       </c>
       <c r="C859" s="1" t="s">
         <v>3</v>
@@ -24221,7 +24260,7 @@
         <v>4</v>
       </c>
       <c r="E859" s="1" t="s">
-        <v>2316</v>
+        <v>2313</v>
       </c>
       <c r="F859" s="1" t="s">
         <v>5</v>
@@ -24229,10 +24268,10 @@
     </row>
     <row r="860" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A860" s="1" t="s">
-        <v>2317</v>
+        <v>2314</v>
       </c>
       <c r="B860" s="1" t="s">
-        <v>2318</v>
+        <v>2315</v>
       </c>
       <c r="C860" s="1" t="s">
         <v>3</v>
@@ -24241,7 +24280,7 @@
         <v>4</v>
       </c>
       <c r="E860" s="1" t="s">
-        <v>2319</v>
+        <v>2316</v>
       </c>
       <c r="F860" s="1" t="s">
         <v>5</v>
@@ -24249,10 +24288,10 @@
     </row>
     <row r="861" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A861" s="1" t="s">
-        <v>2320</v>
+        <v>2317</v>
       </c>
       <c r="B861" s="1" t="s">
-        <v>2321</v>
+        <v>2318</v>
       </c>
       <c r="C861" s="1" t="s">
         <v>3</v>
@@ -24261,7 +24300,7 @@
         <v>4</v>
       </c>
       <c r="E861" s="1" t="s">
-        <v>2322</v>
+        <v>2319</v>
       </c>
       <c r="F861" s="1" t="s">
         <v>5</v>
@@ -24269,10 +24308,10 @@
     </row>
     <row r="862" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A862" s="1" t="s">
-        <v>2323</v>
+        <v>2320</v>
       </c>
       <c r="B862" s="1" t="s">
-        <v>2324</v>
+        <v>2321</v>
       </c>
       <c r="C862" s="1" t="s">
         <v>3</v>
@@ -24281,7 +24320,7 @@
         <v>4</v>
       </c>
       <c r="E862" s="1" t="s">
-        <v>2325</v>
+        <v>2322</v>
       </c>
       <c r="F862" s="1" t="s">
         <v>5</v>
@@ -24289,10 +24328,10 @@
     </row>
     <row r="863" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A863" s="1" t="s">
-        <v>2326</v>
+        <v>2323</v>
       </c>
       <c r="B863" s="1" t="s">
-        <v>2327</v>
+        <v>2324</v>
       </c>
       <c r="C863" s="1" t="s">
         <v>3</v>
@@ -24301,7 +24340,7 @@
         <v>4</v>
       </c>
       <c r="E863" s="1" t="s">
-        <v>2328</v>
+        <v>2325</v>
       </c>
       <c r="F863" s="1" t="s">
         <v>5</v>
@@ -24309,10 +24348,10 @@
     </row>
     <row r="864" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A864" s="1" t="s">
-        <v>2329</v>
+        <v>2326</v>
       </c>
       <c r="B864" s="1" t="s">
-        <v>2330</v>
+        <v>2327</v>
       </c>
       <c r="C864" s="1" t="s">
         <v>3</v>
@@ -24321,7 +24360,7 @@
         <v>4</v>
       </c>
       <c r="E864" s="1" t="s">
-        <v>2331</v>
+        <v>2328</v>
       </c>
       <c r="F864" s="1" t="s">
         <v>5</v>
@@ -24329,10 +24368,10 @@
     </row>
     <row r="865" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A865" s="1" t="s">
-        <v>2332</v>
+        <v>2329</v>
       </c>
       <c r="B865" s="1" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="C865" s="1" t="s">
         <v>3</v>
@@ -24341,7 +24380,7 @@
         <v>4</v>
       </c>
       <c r="E865" s="1" t="s">
-        <v>2333</v>
+        <v>2330</v>
       </c>
       <c r="F865" s="1" t="s">
         <v>5</v>
@@ -24349,10 +24388,10 @@
     </row>
     <row r="866" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A866" s="1" t="s">
-        <v>2334</v>
+        <v>2331</v>
       </c>
       <c r="B866" s="1" t="s">
-        <v>2312</v>
+        <v>2309</v>
       </c>
       <c r="C866" s="1" t="s">
         <v>3</v>
@@ -24361,7 +24400,7 @@
         <v>4</v>
       </c>
       <c r="E866" s="1" t="s">
-        <v>2335</v>
+        <v>2332</v>
       </c>
       <c r="F866" s="1" t="s">
         <v>5</v>
@@ -24369,10 +24408,10 @@
     </row>
     <row r="867" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A867" s="1" t="s">
-        <v>2336</v>
+        <v>2333</v>
       </c>
       <c r="B867" s="1" t="s">
-        <v>2315</v>
+        <v>2312</v>
       </c>
       <c r="C867" s="1" t="s">
         <v>3</v>
@@ -24381,7 +24420,7 @@
         <v>4</v>
       </c>
       <c r="E867" s="1" t="s">
-        <v>2337</v>
+        <v>2334</v>
       </c>
       <c r="F867" s="1" t="s">
         <v>5</v>
@@ -24389,10 +24428,10 @@
     </row>
     <row r="868" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A868" s="1" t="s">
-        <v>2338</v>
+        <v>2335</v>
       </c>
       <c r="B868" s="1" t="s">
-        <v>2318</v>
+        <v>2315</v>
       </c>
       <c r="C868" s="1" t="s">
         <v>3</v>
@@ -24401,7 +24440,7 @@
         <v>4</v>
       </c>
       <c r="E868" s="1" t="s">
-        <v>2339</v>
+        <v>2336</v>
       </c>
       <c r="F868" s="1" t="s">
         <v>5</v>
@@ -24409,10 +24448,10 @@
     </row>
     <row r="869" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A869" s="1" t="s">
-        <v>2340</v>
+        <v>2337</v>
       </c>
       <c r="B869" s="1" t="s">
-        <v>2321</v>
+        <v>2318</v>
       </c>
       <c r="C869" s="1" t="s">
         <v>3</v>
@@ -24421,7 +24460,7 @@
         <v>4</v>
       </c>
       <c r="E869" s="1" t="s">
-        <v>2341</v>
+        <v>2338</v>
       </c>
       <c r="F869" s="1" t="s">
         <v>5</v>
@@ -24429,10 +24468,10 @@
     </row>
     <row r="870" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A870" s="1" t="s">
-        <v>2342</v>
+        <v>2339</v>
       </c>
       <c r="B870" s="1" t="s">
-        <v>2324</v>
+        <v>2321</v>
       </c>
       <c r="C870" s="1" t="s">
         <v>3</v>
@@ -24441,7 +24480,7 @@
         <v>4</v>
       </c>
       <c r="E870" s="1" t="s">
-        <v>2343</v>
+        <v>2340</v>
       </c>
       <c r="F870" s="1" t="s">
         <v>5</v>
@@ -24449,10 +24488,10 @@
     </row>
     <row r="871" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A871" s="1" t="s">
-        <v>2344</v>
+        <v>2341</v>
       </c>
       <c r="B871" s="1" t="s">
-        <v>2345</v>
+        <v>2342</v>
       </c>
       <c r="C871" s="1" t="s">
         <v>3</v>
@@ -24461,7 +24500,7 @@
         <v>4</v>
       </c>
       <c r="E871" s="1" t="s">
-        <v>2346</v>
+        <v>2343</v>
       </c>
       <c r="F871" s="1" t="s">
         <v>5</v>
@@ -24469,10 +24508,10 @@
     </row>
     <row r="872" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A872" s="1" t="s">
-        <v>2347</v>
+        <v>2344</v>
       </c>
       <c r="B872" s="1" t="s">
-        <v>2330</v>
+        <v>2327</v>
       </c>
       <c r="C872" s="1" t="s">
         <v>3</v>
@@ -24481,7 +24520,7 @@
         <v>4</v>
       </c>
       <c r="E872" s="1" t="s">
-        <v>2348</v>
+        <v>2345</v>
       </c>
       <c r="F872" s="1" t="s">
         <v>5</v>
@@ -24489,10 +24528,10 @@
     </row>
     <row r="873" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A873" s="1" t="s">
-        <v>2349</v>
+        <v>2346</v>
       </c>
       <c r="B873" s="1" t="s">
-        <v>2350</v>
+        <v>2347</v>
       </c>
       <c r="C873" s="1" t="s">
         <v>3</v>
@@ -24501,15 +24540,15 @@
         <v>4</v>
       </c>
       <c r="E873" s="1" t="s">
-        <v>2351</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="874" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A874" s="1" t="s">
-        <v>2352</v>
+        <v>2349</v>
       </c>
       <c r="B874" s="1" t="s">
-        <v>2353</v>
+        <v>2350</v>
       </c>
       <c r="C874" s="1" t="s">
         <v>3</v>
@@ -24518,15 +24557,15 @@
         <v>4</v>
       </c>
       <c r="E874" s="1" t="s">
-        <v>2354</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="875" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A875" s="1" t="s">
-        <v>2355</v>
+        <v>2352</v>
       </c>
       <c r="B875" s="1" t="s">
-        <v>2356</v>
+        <v>2353</v>
       </c>
       <c r="C875" s="1" t="s">
         <v>3</v>
@@ -24535,15 +24574,15 @@
         <v>4</v>
       </c>
       <c r="E875" s="1" t="s">
-        <v>2357</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="876" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A876" s="1" t="s">
-        <v>2358</v>
+        <v>2355</v>
       </c>
       <c r="B876" s="1" t="s">
-        <v>2359</v>
+        <v>2356</v>
       </c>
       <c r="C876" s="1" t="s">
         <v>3</v>
@@ -24552,7 +24591,7 @@
         <v>4</v>
       </c>
       <c r="E876" s="1" t="s">
-        <v>2360</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="877" spans="1:6" x14ac:dyDescent="0.25">
@@ -24569,7 +24608,7 @@
         <v>4</v>
       </c>
       <c r="E877" s="1" t="s">
-        <v>2361</v>
+        <v>2358</v>
       </c>
       <c r="F877" s="1" t="s">
         <v>5</v>
@@ -24577,10 +24616,10 @@
     </row>
     <row r="878" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A878" s="1" t="s">
-        <v>2362</v>
+        <v>2359</v>
       </c>
       <c r="B878" s="1" t="s">
-        <v>2363</v>
+        <v>2360</v>
       </c>
       <c r="C878" s="1" t="s">
         <v>3</v>
@@ -24589,7 +24628,7 @@
         <v>4</v>
       </c>
       <c r="E878" s="1" t="s">
-        <v>2364</v>
+        <v>2361</v>
       </c>
       <c r="F878" s="1" t="s">
         <v>5</v>
@@ -24597,10 +24636,10 @@
     </row>
     <row r="879" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A879" s="1" t="s">
-        <v>2365</v>
+        <v>2362</v>
       </c>
       <c r="B879" s="1" t="s">
-        <v>2366</v>
+        <v>2363</v>
       </c>
       <c r="C879" s="1" t="s">
         <v>3</v>
@@ -24609,7 +24648,7 @@
         <v>4</v>
       </c>
       <c r="E879" s="1" t="s">
-        <v>2367</v>
+        <v>2364</v>
       </c>
       <c r="F879" s="1" t="s">
         <v>5</v>
@@ -24617,10 +24656,10 @@
     </row>
     <row r="880" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A880" s="1" t="s">
-        <v>2368</v>
+        <v>2365</v>
       </c>
       <c r="B880" s="1" t="s">
-        <v>2369</v>
+        <v>2366</v>
       </c>
       <c r="C880" s="1" t="s">
         <v>3</v>
@@ -24629,7 +24668,7 @@
         <v>4</v>
       </c>
       <c r="E880" s="1" t="s">
-        <v>2370</v>
+        <v>2367</v>
       </c>
       <c r="F880" s="1" t="s">
         <v>5</v>
@@ -24637,10 +24676,10 @@
     </row>
     <row r="881" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A881" s="1" t="s">
-        <v>2371</v>
+        <v>2368</v>
       </c>
       <c r="B881" s="1" t="s">
-        <v>2372</v>
+        <v>2369</v>
       </c>
       <c r="C881" s="1" t="s">
         <v>3</v>
@@ -24649,7 +24688,7 @@
         <v>4</v>
       </c>
       <c r="E881" s="1" t="s">
-        <v>2373</v>
+        <v>2370</v>
       </c>
       <c r="F881" s="1" t="s">
         <v>5</v>
@@ -24657,10 +24696,10 @@
     </row>
     <row r="882" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A882" s="1" t="s">
-        <v>2374</v>
+        <v>2371</v>
       </c>
       <c r="B882" s="1" t="s">
-        <v>2375</v>
+        <v>2372</v>
       </c>
       <c r="C882" s="1" t="s">
         <v>3</v>
@@ -24669,7 +24708,7 @@
         <v>4</v>
       </c>
       <c r="E882" s="1" t="s">
-        <v>2376</v>
+        <v>2373</v>
       </c>
       <c r="F882" s="1" t="s">
         <v>5</v>
@@ -24677,21 +24716,141 @@
     </row>
     <row r="883" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A883" s="1" t="s">
+        <v>2374</v>
+      </c>
+      <c r="B883" s="1" t="s">
+        <v>2375</v>
+      </c>
+      <c r="C883" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D883" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E883" s="1" t="s">
+        <v>2376</v>
+      </c>
+      <c r="F883" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="884" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A884" s="1" t="s">
         <v>2377</v>
       </c>
-      <c r="B883" s="1" t="s">
+      <c r="B884" s="1" t="s">
         <v>2378</v>
       </c>
-      <c r="C883" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D883" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E883" s="1" t="s">
+      <c r="C884" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D884" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E884" s="1" t="s">
         <v>2379</v>
       </c>
-      <c r="F883" s="1" t="s">
+      <c r="F884" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="885" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A885" s="1" t="s">
+        <v>2380</v>
+      </c>
+      <c r="B885" s="1" t="s">
+        <v>2381</v>
+      </c>
+      <c r="C885" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D885" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E885" s="1" t="s">
+        <v>2382</v>
+      </c>
+      <c r="F885" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="886" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A886" s="1" t="s">
+        <v>2383</v>
+      </c>
+      <c r="B886" s="1" t="s">
+        <v>2378</v>
+      </c>
+      <c r="C886" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D886" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E886" s="1" t="s">
+        <v>2384</v>
+      </c>
+      <c r="F886" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="887" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A887" s="1" t="s">
+        <v>2385</v>
+      </c>
+      <c r="B887" s="1" t="s">
+        <v>2381</v>
+      </c>
+      <c r="C887" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D887" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E887" s="1" t="s">
+        <v>2386</v>
+      </c>
+      <c r="F887" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="888" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A888" s="1" t="s">
+        <v>2387</v>
+      </c>
+      <c r="B888" s="1" t="s">
+        <v>2388</v>
+      </c>
+      <c r="C888" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D888" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E888" s="1" t="s">
+        <v>2389</v>
+      </c>
+      <c r="F888" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="889" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A889" s="1" t="s">
+        <v>2390</v>
+      </c>
+      <c r="B889" s="1" t="s">
+        <v>2391</v>
+      </c>
+      <c r="C889" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D889" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E889" s="1" t="s">
+        <v>2392</v>
+      </c>
+      <c r="F889" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/E/MKTN.xlsx
+++ b/E/MKTN.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5161" uniqueCount="2393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5149" uniqueCount="2389">
   <si>
     <t/>
   </si>
@@ -7144,31 +7144,19 @@
     <t>961</t>
   </si>
   <si>
-    <t>20142767</t>
+    <t>20142769</t>
   </si>
   <si>
     <t>FOLAPLAY BLA GMBRA 7</t>
   </si>
   <si>
-    <t>1003</t>
-  </si>
-  <si>
-    <t>20142768</t>
+    <t>1005</t>
+  </si>
+  <si>
+    <t>20142770</t>
   </si>
   <si>
     <t>FOLAPLAY BLA GMBRA30</t>
-  </si>
-  <si>
-    <t>1004</t>
-  </si>
-  <si>
-    <t>20142769</t>
-  </si>
-  <si>
-    <t>1005</t>
-  </si>
-  <si>
-    <t>20142770</t>
   </si>
   <si>
     <t>1006</t>
@@ -7582,7 +7570,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F889"/>
+  <dimension ref="A1:F887"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -24779,7 +24767,7 @@
         <v>2383</v>
       </c>
       <c r="B886" s="1" t="s">
-        <v>2378</v>
+        <v>2384</v>
       </c>
       <c r="C886" s="1" t="s">
         <v>3</v>
@@ -24788,7 +24776,7 @@
         <v>4</v>
       </c>
       <c r="E886" s="1" t="s">
-        <v>2384</v>
+        <v>2385</v>
       </c>
       <c r="F886" s="1" t="s">
         <v>5</v>
@@ -24796,10 +24784,10 @@
     </row>
     <row r="887" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A887" s="1" t="s">
-        <v>2385</v>
+        <v>2386</v>
       </c>
       <c r="B887" s="1" t="s">
-        <v>2381</v>
+        <v>2387</v>
       </c>
       <c r="C887" s="1" t="s">
         <v>3</v>
@@ -24808,49 +24796,9 @@
         <v>4</v>
       </c>
       <c r="E887" s="1" t="s">
-        <v>2386</v>
+        <v>2388</v>
       </c>
       <c r="F887" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="888" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A888" s="1" t="s">
-        <v>2387</v>
-      </c>
-      <c r="B888" s="1" t="s">
-        <v>2388</v>
-      </c>
-      <c r="C888" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D888" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E888" s="1" t="s">
-        <v>2389</v>
-      </c>
-      <c r="F888" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="889" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A889" s="1" t="s">
-        <v>2390</v>
-      </c>
-      <c r="B889" s="1" t="s">
-        <v>2391</v>
-      </c>
-      <c r="C889" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D889" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E889" s="1" t="s">
-        <v>2392</v>
-      </c>
-      <c r="F889" s="1" t="s">
         <v>5</v>
       </c>
     </row>
